--- a/PUNTOS_DE_VENTA_completado.xlsx
+++ b/PUNTOS_DE_VENTA_completado.xlsx
@@ -551,6 +551,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4" ht="15.75" customHeight="1" s="19">
       <c r="A4" s="8" t="n">
@@ -576,6 +578,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5" ht="15.75" customHeight="1" s="19">
       <c r="A5" s="8" t="n">
@@ -601,6 +605,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6" ht="15.75" customHeight="1" s="19">
       <c r="A6" s="8" t="n">
@@ -626,6 +632,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7" ht="15.75" customHeight="1" s="19">
       <c r="A7" s="8" t="n">
@@ -651,6 +659,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8" ht="15.75" customHeight="1" s="19">
       <c r="A8" s="8" t="n">
@@ -676,6 +686,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>+54 11 4216-5280</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9" ht="15.75" customHeight="1" s="19">
       <c r="A9" s="8" t="n">
@@ -701,6 +717,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>+54 9 11 3916-6951</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>http://www.vetesantalucia.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" s="19">
       <c r="A10" s="8" t="n">
@@ -726,6 +752,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>+54 11 6724-1172</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>http://www.diagnosticolanus.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" s="19">
       <c r="A11" s="8" t="n">
@@ -751,6 +787,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12" ht="15.75" customHeight="1" s="19">
       <c r="A12" s="8" t="n">
@@ -776,6 +814,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>+54 2320 43-3270</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13" ht="15.75" customHeight="1" s="19">
       <c r="A13" s="8" t="n">
@@ -801,6 +845,12 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>+54 3327 48-0381</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="19">
       <c r="A14" s="8" t="n">
@@ -826,6 +876,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="19">
       <c r="A15" s="8" t="n">
@@ -851,6 +903,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>+54 11 7114-7781</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>http://www.comercialnorte.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" s="19">
       <c r="A16" s="8" t="n">
@@ -876,6 +938,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>+54 2320 49-5433</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17" ht="15.75" customHeight="1" s="19">
       <c r="A17" s="8" t="n">
@@ -901,6 +969,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>+54 11 4769-4640</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18" ht="15.75" customHeight="1" s="19">
       <c r="A18" s="8" t="n">
@@ -926,6 +1000,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19" ht="15.75" customHeight="1" s="19">
       <c r="A19" s="8" t="n">
@@ -951,6 +1027,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20" ht="15.75" customHeight="1" s="19">
       <c r="A20" s="8" t="n">
@@ -976,6 +1054,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>+54 11 5048-1441</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="19">
       <c r="A21" s="8" t="n">
@@ -1001,6 +1085,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="19">
       <c r="A22" s="8" t="n">
@@ -1026,6 +1112,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>+54 11 6297-2238</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="19">
       <c r="A23" s="8" t="n">
@@ -1051,6 +1143,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>+54 11 2171-9894</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="19">
       <c r="A24" s="8" t="n">
@@ -1076,6 +1174,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="19">
       <c r="A25" s="8" t="n">
@@ -1101,6 +1201,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="19">
       <c r="A26" s="8" t="n">
@@ -1126,6 +1228,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="19">
       <c r="A27" s="8" t="n">
@@ -1151,6 +1255,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="19">
       <c r="A28" s="8" t="n">
@@ -1176,6 +1282,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="19">
       <c r="A29" s="8" t="n">
@@ -1201,6 +1309,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>+54 11 4753-4245</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://clinicaveterinariasanmartinmascotas.com/</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="19">
       <c r="A30" s="8" t="n">
@@ -1226,6 +1344,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="19">
       <c r="A31" s="8" t="n">
@@ -1251,6 +1371,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>+54 11 4919-0143</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vete.puente</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="19">
       <c r="A32" s="8" t="n">
@@ -1276,6 +1406,16 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>+54 11 4509-6060</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>http://www.peirano.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="19">
       <c r="A33" s="8" t="n">
@@ -1301,6 +1441,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>+54 11 4641-1575</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="19">
       <c r="A34" s="8" t="n">
@@ -1326,6 +1472,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>+54 11 4662-0329</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="19">
       <c r="A35" s="8" t="n">
@@ -1351,6 +1503,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="19">
       <c r="A36" s="8" t="n">
@@ -1376,6 +1530,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="19">
       <c r="A37" s="8" t="n">
@@ -1401,6 +1557,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="19">
       <c r="A38" s="8" t="n">
@@ -1426,6 +1584,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="19">
       <c r="A39" s="8" t="n">
@@ -1451,6 +1611,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>+54 11 4611-6887</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="19">
       <c r="A40" s="8" t="n">
@@ -1476,6 +1642,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="19">
       <c r="A41" s="8" t="n">
@@ -1501,6 +1669,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="19">
       <c r="A42" s="8" t="n">
@@ -1526,6 +1696,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="19">
       <c r="A43" s="8" t="n">
@@ -1551,6 +1723,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="19">
       <c r="A44" s="8" t="n">
@@ -1576,6 +1750,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>+54 11 4631-7331</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>http://www.ecoanimal.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="19">
       <c r="A45" s="8" t="n">
@@ -1601,6 +1785,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>+54 11 2285-5532</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="19">
       <c r="A46" s="8" t="n">
@@ -1626,6 +1816,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="19">
       <c r="A47" s="8" t="n">
@@ -1651,6 +1843,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="19">
       <c r="A48" s="8" t="n">
@@ -1676,6 +1870,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="19">
       <c r="A49" s="8" t="n">
@@ -1701,6 +1897,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="19">
       <c r="A50" s="8" t="n">
@@ -1726,6 +1924,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>+54 11 4758-0890</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://m.facebook.com/upa16tresdefebrero/</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="19">
       <c r="A51" s="8" t="n">
@@ -1751,6 +1959,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52" ht="15.75" customHeight="1" s="19">
       <c r="A52" s="8" t="n">
@@ -1776,6 +1986,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53" ht="15.75" customHeight="1" s="19">
       <c r="A53" s="8" t="n">
@@ -12997,12 +13209,6 @@
           <t>Veterinaria</t>
         </is>
       </c>
-      <c r="F501" t="inlineStr">
-        <is>
-          <t>011-4544-4059</t>
-        </is>
-      </c>
-      <c r="G501" t="inlineStr"/>
     </row>
     <row r="502" ht="15.75" customHeight="1" s="19">
       <c r="A502" s="8" t="n">
@@ -16195,12 +16401,6 @@
           <t>Veterinaria</t>
         </is>
       </c>
-      <c r="F629" t="inlineStr">
-        <is>
-          <t>011-4706-0311</t>
-        </is>
-      </c>
-      <c r="G629" t="inlineStr"/>
     </row>
     <row r="630" ht="15.75" customHeight="1" s="19">
       <c r="A630" s="8" t="n">
@@ -17026,12 +17226,6 @@
           <t>Veterinaria</t>
         </is>
       </c>
-      <c r="F662" t="inlineStr">
-        <is>
-          <t>011-4778-3430</t>
-        </is>
-      </c>
-      <c r="G662" t="inlineStr"/>
     </row>
     <row r="663" ht="15.75" customHeight="1" s="19">
       <c r="A663" s="8" t="n">
@@ -17182,12 +17376,6 @@
           <t>Veterinaria</t>
         </is>
       </c>
-      <c r="F668" t="inlineStr">
-        <is>
-          <t>011-4702-2389</t>
-        </is>
-      </c>
-      <c r="G668" t="inlineStr"/>
     </row>
     <row r="669" ht="15.75" customHeight="1" s="19">
       <c r="A669" s="8" t="n">
@@ -17213,16 +17401,6 @@
           <t>Veterinaria</t>
         </is>
       </c>
-      <c r="F669" t="inlineStr">
-        <is>
-          <t>011-4776-3560</t>
-        </is>
-      </c>
-      <c r="G669" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/Veterinaria-Percebes-826945940685596/</t>
-        </is>
-      </c>
     </row>
     <row r="670" ht="15.75" customHeight="1" s="19">
       <c r="A670" s="8" t="n">
@@ -20619,12 +20797,6 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
-      <c r="F805" t="inlineStr">
-        <is>
-          <t>011-4788-8128</t>
-        </is>
-      </c>
-      <c r="G805" t="inlineStr"/>
     </row>
     <row r="806" ht="15.75" customHeight="1" s="19">
       <c r="A806" s="8" t="n">
@@ -21971,12 +22143,6 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
-      <c r="F859" t="inlineStr">
-        <is>
-          <t>011-4553-5821</t>
-        </is>
-      </c>
-      <c r="G859" t="inlineStr"/>
     </row>
     <row r="860" ht="15.75" customHeight="1" s="19">
       <c r="A860" s="8" t="n">
@@ -28884,12 +29050,6 @@
           <t>Veterinaria</t>
         </is>
       </c>
-      <c r="F1136" t="inlineStr">
-        <is>
-          <t>011-4770-9349</t>
-        </is>
-      </c>
-      <c r="G1136" t="inlineStr"/>
     </row>
     <row r="1137" ht="15.75" customHeight="1" s="19">
       <c r="A1137" s="8" t="n">
@@ -41725,12 +41885,6 @@
           <t>Pet Shop</t>
         </is>
       </c>
-      <c r="F1651" t="inlineStr">
-        <is>
-          <t>011-4702-8122</t>
-        </is>
-      </c>
-      <c r="G1651" t="inlineStr"/>
     </row>
     <row r="1652" ht="15.75" customHeight="1" s="19">
       <c r="A1652" s="8" t="n">
@@ -46792,16 +46946,6 @@
           <t>Pet Shop</t>
         </is>
       </c>
-      <c r="F1854" t="inlineStr">
-        <is>
-          <t>011-4567-1682</t>
-        </is>
-      </c>
-      <c r="G1854" t="inlineStr">
-        <is>
-          <t>www.indigopets.com.ar</t>
-        </is>
-      </c>
     </row>
     <row r="1855" ht="15.75" customHeight="1" s="19">
       <c r="A1855" s="8" t="n">
@@ -72518,12 +72662,6 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
-      <c r="F2886" t="inlineStr">
-        <is>
-          <t>011-4786-5518</t>
-        </is>
-      </c>
-      <c r="G2886" t="inlineStr"/>
     </row>
     <row r="2887" ht="15.75" customHeight="1" s="19">
       <c r="A2887" s="10" t="n">

--- a/PUNTOS_DE_VENTA_completado.xlsx
+++ b/PUNTOS_DE_VENTA_completado.xlsx
@@ -464,7 +464,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G2952"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11.22" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.22" defaultRowHeight="15" customHeight="1" outlineLevelCol="0"/>
   <cols>
     <col width="22.11" customWidth="1" style="19" min="1" max="1"/>
     <col width="31.11" customWidth="1" style="19" min="2" max="2"/>
@@ -2013,6 +2013,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>+54 11 4567-8807</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54" ht="15.75" customHeight="1" s="19">
       <c r="A54" s="8" t="n">
@@ -2038,6 +2044,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55" ht="15.75" customHeight="1" s="19">
       <c r="A55" s="8" t="n">
@@ -2063,6 +2071,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56" ht="15.75" customHeight="1" s="19">
       <c r="A56" s="8" t="n">
@@ -2088,6 +2098,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>+54 11 4634-0222</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.linaresveterinaria.com/</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="15.75" customHeight="1" s="19">
       <c r="A57" s="8" t="n">
@@ -2113,6 +2133,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>+54 11 4637-0782</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58" ht="15.75" customHeight="1" s="19">
       <c r="A58" s="8" t="n">
@@ -2138,6 +2164,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59" ht="15.75" customHeight="1" s="19">
       <c r="A59" s="8" t="n">
@@ -2163,6 +2191,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60" ht="15.75" customHeight="1" s="19">
       <c r="A60" s="8" t="n">
@@ -2188,6 +2218,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>+54 11 4632-2174</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://petcenter.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="15.75" customHeight="1" s="19">
       <c r="A61" s="8" t="n">
@@ -2213,6 +2253,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62" ht="15.75" customHeight="1" s="19">
       <c r="A62" s="8" t="n">
@@ -2238,6 +2280,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>+54 230 442-0784</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>http://www.lasanmartin.com/</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="15.75" customHeight="1" s="19">
       <c r="A63" s="8" t="n">
@@ -2263,6 +2315,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64" ht="15.75" customHeight="1" s="19">
       <c r="A64" s="8" t="n">
@@ -2288,6 +2342,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65" ht="15.75" customHeight="1" s="19">
       <c r="A65" s="8" t="n">
@@ -2313,6 +2369,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66" ht="15.75" customHeight="1" s="19">
       <c r="A66" s="8" t="n">
@@ -2338,6 +2396,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>+54 11 4631-7331</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>http://www.ecoanimal.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="15.75" customHeight="1" s="19">
       <c r="A67" s="8" t="n">
@@ -2363,6 +2431,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68" ht="15.75" customHeight="1" s="19">
       <c r="A68" s="8" t="n">
@@ -2388,6 +2458,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69" ht="15.75" customHeight="1" s="19">
       <c r="A69" s="8" t="n">
@@ -2413,6 +2485,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70" ht="15.75" customHeight="1" s="19">
       <c r="A70" s="8" t="n">
@@ -2438,6 +2512,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71" ht="15.75" customHeight="1" s="19">
       <c r="A71" s="8" t="n">
@@ -2463,6 +2539,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>+54 11 6092-7325</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Consultorioscomunitariosderqui</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="15.75" customHeight="1" s="19">
       <c r="A72" s="8" t="n">
@@ -2488,6 +2574,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73" ht="15.75" customHeight="1" s="19">
       <c r="A73" s="8" t="n">
@@ -2513,6 +2601,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74" ht="15.75" customHeight="1" s="19">
       <c r="A74" s="8" t="n">
@@ -2538,6 +2628,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>+54 11 2880-6661</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vetemaggiolo/</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="15.75" customHeight="1" s="19">
       <c r="A75" s="8" t="n">
@@ -2563,6 +2663,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>+54 11 4664-0417</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://clinicaveterinariamitre.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="15.75" customHeight="1" s="19">
       <c r="A76" s="8" t="n">
@@ -2588,6 +2698,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77" ht="15.75" customHeight="1" s="19">
       <c r="A77" s="8" t="n">
@@ -2613,6 +2725,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>+54 11 2501-4777</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>http://www.vetintegral.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="15.75" customHeight="1" s="19">
       <c r="A78" s="8" t="n">
@@ -2638,6 +2760,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79" ht="15.75" customHeight="1" s="19">
       <c r="A79" s="8" t="n">
@@ -2663,6 +2787,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
     </row>
     <row r="80" ht="15.75" customHeight="1" s="19">
       <c r="A80" s="8" t="n">
@@ -2688,6 +2814,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>+54 11 5263-7873</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>http://www.musicosas.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="15.75" customHeight="1" s="19">
       <c r="A81" s="8" t="n">
@@ -2713,6 +2849,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>+54 11 4982-8184</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>http://plazaconsultorios.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="15.75" customHeight="1" s="19">
       <c r="A82" s="8" t="n">
@@ -2738,6 +2884,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>+54 11 5227-7000</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
     </row>
     <row r="83" ht="15.75" customHeight="1" s="19">
       <c r="A83" s="8" t="n">
@@ -2763,6 +2915,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
     </row>
     <row r="84" ht="15.75" customHeight="1" s="19">
       <c r="A84" s="8" t="n">
@@ -2788,6 +2942,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>+54 11 4637-1613</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://m.facebook.com/Zoovidas-334149570073718/</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="15.75" customHeight="1" s="19">
       <c r="A85" s="8" t="n">
@@ -2813,6 +2977,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86" ht="15.75" customHeight="1" s="19">
       <c r="A86" s="8" t="n">
@@ -2838,6 +3004,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>+54 11 4437-3911</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>http://www.farmavet.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="15.75" customHeight="1" s="19">
       <c r="A87" s="8" t="n">
@@ -2863,6 +3039,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>+54 11 5263-8681</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.veterinariahonorio.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="15.75" customHeight="1" s="19">
       <c r="A88" s="8" t="n">
@@ -2888,6 +3074,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>+54 9 11 6101-2107</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>http://www.vet-life.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="15.75" customHeight="1" s="19">
       <c r="A89" s="8" t="n">
@@ -2913,6 +3109,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
     </row>
     <row r="90" ht="15.75" customHeight="1" s="19">
       <c r="A90" s="8" t="n">
@@ -2938,6 +3136,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>+54 11 6366-2680</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91" ht="15.75" customHeight="1" s="19">
       <c r="A91" s="8" t="n">
@@ -2963,6 +3167,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
     </row>
     <row r="92" ht="15.75" customHeight="1" s="19">
       <c r="A92" s="8" t="n">
@@ -2988,6 +3194,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93" ht="15.75" customHeight="1" s="19">
       <c r="A93" s="8" t="n">
@@ -3013,6 +3221,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>+54 11 4585-0117</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.veterinarias.com.ar/kinder-vet-2</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="15.75" customHeight="1" s="19">
       <c r="A94" s="8" t="n">
@@ -3038,6 +3256,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
     </row>
     <row r="95" ht="15.75" customHeight="1" s="19">
       <c r="A95" s="8" t="n">
@@ -3063,6 +3283,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
     </row>
     <row r="96" ht="15.75" customHeight="1" s="19">
       <c r="A96" s="8" t="n">
@@ -3088,6 +3310,16 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>+54 11 3807-7677</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://instagram.com/sugarpopbsas</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="15.75" customHeight="1" s="19">
       <c r="A97" s="8" t="n">
@@ -3113,6 +3345,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
     </row>
     <row r="98" ht="15.75" customHeight="1" s="19">
       <c r="A98" s="8" t="n">
@@ -3138,6 +3372,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>+54 345 508-0870</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
     </row>
     <row r="99" ht="15.75" customHeight="1" s="19">
       <c r="A99" s="8" t="n">
@@ -3163,6 +3403,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>+54 11 4716-2166</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
     </row>
     <row r="100" ht="15.75" customHeight="1" s="19">
       <c r="A100" s="8" t="n">
@@ -3188,6 +3434,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
     </row>
     <row r="101" ht="15.75" customHeight="1" s="19">
       <c r="A101" s="8" t="n">
@@ -3213,6 +3461,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>+54 11 2201-8310</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
     </row>
     <row r="102" ht="15.75" customHeight="1" s="19">
       <c r="A102" s="8" t="n">
@@ -3238,6 +3492,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>+54 46472947</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
     </row>
     <row r="103" ht="15.75" customHeight="1" s="19">
       <c r="A103" s="8" t="n">
@@ -3263,6 +3523,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
     </row>
     <row r="104" ht="15.75" customHeight="1" s="19">
       <c r="A104" s="8" t="n">
@@ -3288,6 +3550,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>+54 11 6014-4553</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
     </row>
     <row r="105" ht="15.75" customHeight="1" s="19">
       <c r="A105" s="8" t="n">
@@ -3313,6 +3581,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106" ht="15.75" customHeight="1" s="19">
       <c r="A106" s="8" t="n">
@@ -3338,6 +3608,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
     </row>
     <row r="107" ht="15.75" customHeight="1" s="19">
       <c r="A107" s="8" t="n">
@@ -3363,6 +3635,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
     </row>
     <row r="108" ht="15.75" customHeight="1" s="19">
       <c r="A108" s="8" t="n">
@@ -3388,6 +3662,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
     </row>
     <row r="109" ht="15.75" customHeight="1" s="19">
       <c r="A109" s="8" t="n">
@@ -3413,6 +3689,12 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://m.facebook.com/tumascotalovale/?ref=content_filter</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="15.75" customHeight="1" s="19">
       <c r="A110" s="8" t="n">
@@ -3438,6 +3720,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
     </row>
     <row r="111" ht="15.75" customHeight="1" s="19">
       <c r="A111" s="8" t="n">
@@ -3463,6 +3747,16 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>+54 11 4228-6329</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>http://www.confiterialasrosas.com.ar/home</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="15.75" customHeight="1" s="19">
       <c r="A112" s="8" t="n">
@@ -3488,6 +3782,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>+54 11 5133-7935</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://mirandabeauty.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="15.75" customHeight="1" s="19">
       <c r="A113" s="8" t="n">
@@ -3513,6 +3817,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>+54 11 4582-3229</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr"/>
     </row>
     <row r="114" ht="15.75" customHeight="1" s="19">
       <c r="A114" s="8" t="n">
@@ -3538,6 +3848,16 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>+54 11 6538-3804</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>http://www.josimar.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="15.75" customHeight="1" s="19">
       <c r="A115" s="8" t="n">
@@ -3563,6 +3883,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
     </row>
     <row r="116" ht="15.75" customHeight="1" s="19">
       <c r="A116" s="8" t="n">
@@ -3588,6 +3910,12 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>+54 11 5963-8925</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
     </row>
     <row r="117" ht="15.75" customHeight="1" s="19">
       <c r="A117" s="8" t="n">
@@ -3613,6 +3941,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>+54 11 6134-3773</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://conman.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="15.75" customHeight="1" s="19">
       <c r="A118" s="8" t="n">
@@ -3638,6 +3976,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119" ht="15.75" customHeight="1" s="19">
       <c r="A119" s="8" t="n">
@@ -3663,6 +4003,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.doctoraliar.com/esteban-esjaita/psiquiatra/capital-federal?utm_source=google&amp;utm_medium=gmb&amp;utm_campaign=19734&amp;utm_content=website</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="15.75" customHeight="1" s="19">
       <c r="A120" s="8" t="n">
@@ -3688,6 +4034,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
     </row>
     <row r="121" ht="15.75" customHeight="1" s="19">
       <c r="A121" s="8" t="n">
@@ -3713,6 +4061,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
     </row>
     <row r="122" ht="15.75" customHeight="1" s="19">
       <c r="A122" s="8" t="n">
@@ -3738,6 +4088,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
     </row>
     <row r="123" ht="15.75" customHeight="1" s="19">
       <c r="A123" s="8" t="n">
@@ -3763,6 +4115,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124" ht="15.75" customHeight="1" s="19">
       <c r="A124" s="8" t="n">
@@ -3788,6 +4142,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>+54 11 4982-0045</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr"/>
     </row>
     <row r="125" ht="15.75" customHeight="1" s="19">
       <c r="A125" s="8" t="n">
@@ -3813,6 +4173,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
     </row>
     <row r="126" ht="15.75" customHeight="1" s="19">
       <c r="A126" s="8" t="n">
@@ -3838,6 +4200,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
     </row>
     <row r="127" ht="15.75" customHeight="1" s="19">
       <c r="A127" s="8" t="n">
@@ -3863,6 +4227,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
     </row>
     <row r="128" ht="15.75" customHeight="1" s="19">
       <c r="A128" s="8" t="n">
@@ -3888,6 +4254,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
     </row>
     <row r="129" ht="15.75" customHeight="1" s="19">
       <c r="A129" s="8" t="n">
@@ -3913,6 +4281,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
     </row>
     <row r="130" ht="15.75" customHeight="1" s="19">
       <c r="A130" s="8" t="n">
@@ -3938,6 +4308,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>+54 9 11 2560-8218</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>http://www.deliverydeflores.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="15.75" customHeight="1" s="19">
       <c r="A131" s="8" t="n">
@@ -3963,6 +4343,12 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>+54 11 4202-5237</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr"/>
     </row>
     <row r="132" ht="15.75" customHeight="1" s="19">
       <c r="A132" s="8" t="n">
@@ -3988,6 +4374,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>+54 9 11 4487-4664</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr"/>
     </row>
     <row r="133" ht="15.75" customHeight="1" s="19">
       <c r="A133" s="8" t="n">
@@ -4013,6 +4405,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>+54 11 4487-5288</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr"/>
     </row>
     <row r="134" ht="15.75" customHeight="1" s="19">
       <c r="A134" s="8" t="n">
@@ -4038,6 +4436,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>+54 9 11 4061-9346</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr"/>
     </row>
     <row r="135" ht="15.75" customHeight="1" s="19">
       <c r="A135" s="8" t="n">
@@ -4063,6 +4467,16 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>+54 11 4240-1858</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/juanmanuellanus/</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="15.75" customHeight="1" s="19">
       <c r="A136" s="8" t="n">
@@ -4088,6 +4502,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>+54 44870151</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>http://www.facebook.com/delparqueveterinariaGR</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="15.75" customHeight="1" s="19">
       <c r="A137" s="8" t="n">
@@ -4113,6 +4537,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
     </row>
     <row r="138" ht="15.75" customHeight="1" s="19">
       <c r="A138" s="8" t="n">
@@ -4138,6 +4564,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
     </row>
     <row r="139" ht="15.75" customHeight="1" s="19">
       <c r="A139" s="8" t="n">
@@ -4163,6 +4591,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
     </row>
     <row r="140" ht="15.75" customHeight="1" s="19">
       <c r="A140" s="8" t="n">
@@ -4188,6 +4618,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>+54 44570100</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hospitallaferrere</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="15.75" customHeight="1" s="19">
       <c r="A141" s="8" t="n">
@@ -4213,6 +4653,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
     </row>
     <row r="142" ht="15.75" customHeight="1" s="19">
       <c r="A142" s="8" t="n">
@@ -4238,6 +4680,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
     </row>
     <row r="143" ht="15.75" customHeight="1" s="19">
       <c r="A143" s="8" t="n">
@@ -4263,6 +4707,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>+54 11 4481-2239</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/VetAlmagro/</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="15.75" customHeight="1" s="19">
       <c r="A144" s="8" t="n">
@@ -4288,6 +4742,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
     </row>
     <row r="145" ht="15.75" customHeight="1" s="19">
       <c r="A145" s="8" t="n">
@@ -4313,6 +4769,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
     </row>
     <row r="146" ht="15.75" customHeight="1" s="19">
       <c r="A146" s="8" t="n">
@@ -4338,6 +4796,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>+54 11 6510-1033</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr"/>
     </row>
     <row r="147" ht="15.75" customHeight="1" s="19">
       <c r="A147" s="8" t="n">
@@ -4363,6 +4827,12 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>+54 11 4248-3306</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr"/>
     </row>
     <row r="148" ht="15.75" customHeight="1" s="19">
       <c r="A148" s="8" t="n">
@@ -4388,6 +4858,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>+54 220 494-8999</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr"/>
     </row>
     <row r="149" ht="15.75" customHeight="1" s="19">
       <c r="A149" s="8" t="n">
@@ -4413,6 +4889,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>+54 11 2400-8278</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr"/>
     </row>
     <row r="150" ht="15.75" customHeight="1" s="19">
       <c r="A150" s="8" t="n">
@@ -4438,6 +4920,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
     </row>
     <row r="151" ht="15.75" customHeight="1" s="19">
       <c r="A151" s="8" t="n">
@@ -4463,6 +4947,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
     </row>
     <row r="152" ht="15.75" customHeight="1" s="19">
       <c r="A152" s="8" t="n">
@@ -4488,6 +4974,12 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>+54 11 4240-8714</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr"/>
     </row>
     <row r="153" ht="15.75" customHeight="1" s="19">
       <c r="A153" s="8" t="n">

--- a/PUNTOS_DE_VENTA_completado.xlsx
+++ b/PUNTOS_DE_VENTA_completado.xlsx
@@ -5005,6 +5005,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
     </row>
     <row r="154" ht="15.75" customHeight="1" s="19">
       <c r="A154" s="8" t="n">
@@ -5030,6 +5032,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
     </row>
     <row r="155" ht="15.75" customHeight="1" s="19">
       <c r="A155" s="8" t="n">
@@ -5055,6 +5059,12 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>+54 11 4242-2289</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr"/>
     </row>
     <row r="156" ht="15.75" customHeight="1" s="19">
       <c r="A156" s="8" t="n">
@@ -5080,6 +5090,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>+54 220 477-1205</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr"/>
     </row>
     <row r="157" ht="15.75" customHeight="1" s="19">
       <c r="A157" s="8" t="n">
@@ -5105,6 +5121,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>+54 9 11 2511-7999</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://bazarycia.com/</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="15.75" customHeight="1" s="19">
       <c r="A158" s="8" t="n">
@@ -5130,6 +5156,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>+54 220 477-7363</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr"/>
     </row>
     <row r="159" ht="15.75" customHeight="1" s="19">
       <c r="A159" s="8" t="n">
@@ -5155,6 +5187,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
     </row>
     <row r="160" ht="15.75" customHeight="1" s="19">
       <c r="A160" s="8" t="n">
@@ -5180,6 +5214,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>+54 11 5488-2373</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr"/>
     </row>
     <row r="161" ht="15.75" customHeight="1" s="19">
       <c r="A161" s="8" t="n">
@@ -5205,6 +5245,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
     </row>
     <row r="162" ht="15.75" customHeight="1" s="19">
       <c r="A162" s="8" t="n">
@@ -5230,6 +5272,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>+54 11 5863-7629</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr"/>
     </row>
     <row r="163" ht="15.75" customHeight="1" s="19">
       <c r="A163" s="8" t="n">
@@ -5255,6 +5303,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>+54 11 3884-4210</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr"/>
     </row>
     <row r="164" ht="15.75" customHeight="1" s="19">
       <c r="A164" s="8" t="n">
@@ -5280,6 +5334,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>+54 11 4936-3637</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://ar.near-place.com/veterinaria-graham-bell-alejandro-graham-bell-2410-paso-del-rey</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="15.75" customHeight="1" s="19">
       <c r="A165" s="8" t="n">
@@ -5305,6 +5369,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
     </row>
     <row r="166" ht="15.75" customHeight="1" s="19">
       <c r="A166" s="8" t="n">
@@ -5330,6 +5396,12 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>+54 11 4202-7158</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr"/>
     </row>
     <row r="167" ht="15.75" customHeight="1" s="19">
       <c r="A167" s="8" t="n">
@@ -5355,6 +5427,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
     </row>
     <row r="168" ht="15.75" customHeight="1" s="19">
       <c r="A168" s="8" t="n">
@@ -5380,6 +5454,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>+54 237 462-6901</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr"/>
     </row>
     <row r="169" ht="15.75" customHeight="1" s="19">
       <c r="A169" s="8" t="n">
@@ -5405,6 +5485,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>+54 11 6524-7005</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/veterinariagaona/</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="15.75" customHeight="1" s="19">
       <c r="A170" s="8" t="n">
@@ -5430,6 +5520,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
     </row>
     <row r="171" ht="15.75" customHeight="1" s="19">
       <c r="A171" s="8" t="n">
@@ -5455,6 +5547,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
     </row>
     <row r="172" ht="15.75" customHeight="1" s="19">
       <c r="A172" s="8" t="n">
@@ -5480,6 +5574,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>+54 237 463-9838</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr"/>
     </row>
     <row r="173" ht="15.75" customHeight="1" s="19">
       <c r="A173" s="8" t="n">
@@ -5505,6 +5605,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
     </row>
     <row r="174" ht="15.75" customHeight="1" s="19">
       <c r="A174" s="8" t="n">
@@ -5530,6 +5632,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
     </row>
     <row r="175" ht="15.75" customHeight="1" s="19">
       <c r="A175" s="8" t="n">
@@ -5555,6 +5659,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>+54 11 6400-6966</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr"/>
     </row>
     <row r="176" ht="15.75" customHeight="1" s="19">
       <c r="A176" s="8" t="n">
@@ -5580,6 +5690,12 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>+54 11 2766-6477</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr"/>
     </row>
     <row r="177" ht="15.75" customHeight="1" s="19">
       <c r="A177" s="8" t="n">
@@ -5605,6 +5721,12 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>+54 11 4224-1101</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
     </row>
     <row r="178" ht="15.75" customHeight="1" s="19">
       <c r="A178" s="8" t="n">
@@ -5630,6 +5752,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>+54 11 4629-8820</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>http://www.veterinariaeltrebol.com/</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="15.75" customHeight="1" s="19">
       <c r="A179" s="8" t="n">
@@ -5655,6 +5787,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
     </row>
     <row r="180" ht="15.75" customHeight="1" s="19">
       <c r="A180" s="8" t="n">
@@ -5680,6 +5814,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>+54 11 4627-0585</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr"/>
     </row>
     <row r="181" ht="15.75" customHeight="1" s="19">
       <c r="A181" s="8" t="n">
@@ -5705,6 +5845,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>+54 11 6241-0930</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://www.thebridgebar.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="15.75" customHeight="1" s="19">
       <c r="A182" s="8" t="n">
@@ -5730,6 +5880,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
     </row>
     <row r="183" ht="15.75" customHeight="1" s="19">
       <c r="A183" s="8" t="n">
@@ -5755,6 +5907,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>+54 9 11 4949-9584</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr"/>
     </row>
     <row r="184" ht="15.75" customHeight="1" s="19">
       <c r="A184" s="8" t="n">
@@ -5780,6 +5938,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
     </row>
     <row r="185" ht="15.75" customHeight="1" s="19">
       <c r="A185" s="8" t="n">
@@ -5805,6 +5965,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
     </row>
     <row r="186" ht="15.75" customHeight="1" s="19">
       <c r="A186" s="8" t="n">
@@ -5830,6 +5992,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
     </row>
     <row r="187" ht="15.75" customHeight="1" s="19">
       <c r="A187" s="8" t="n">
@@ -5855,6 +6019,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>+54 11 4180-0673</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://alejandroblancomv.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="188" ht="15.75" customHeight="1" s="19">
       <c r="A188" s="8" t="n">
@@ -5880,6 +6054,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
     </row>
     <row r="189" ht="15.75" customHeight="1" s="19">
       <c r="A189" s="8" t="n">
@@ -5905,6 +6081,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
     </row>
     <row r="190" ht="15.75" customHeight="1" s="19">
       <c r="A190" s="8" t="n">
@@ -5930,6 +6108,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
     </row>
     <row r="191" ht="15.75" customHeight="1" s="19">
       <c r="A191" s="8" t="n">
@@ -5955,6 +6135,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr"/>
     </row>
     <row r="192" ht="15.75" customHeight="1" s="19">
       <c r="A192" s="8" t="n">
@@ -5980,6 +6162,12 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>+54 11 4248-3306</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
     </row>
     <row r="193" ht="15.75" customHeight="1" s="19">
       <c r="A193" s="8" t="n">
@@ -6005,6 +6193,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr"/>
     </row>
     <row r="194" ht="15.75" customHeight="1" s="19">
       <c r="A194" s="8" t="n">
@@ -6030,6 +6220,12 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/modobeautystudio</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="15.75" customHeight="1" s="19">
       <c r="A195" s="8" t="n">
@@ -6055,6 +6251,12 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>+54 11 4249-7345</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr"/>
     </row>
     <row r="196" ht="15.75" customHeight="1" s="19">
       <c r="A196" s="8" t="n">
@@ -6080,6 +6282,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>+54 11 4484-3964</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
     </row>
     <row r="197" ht="15.75" customHeight="1" s="19">
       <c r="A197" s="8" t="n">
@@ -6105,6 +6313,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr"/>
     </row>
     <row r="198" ht="15.75" customHeight="1" s="19">
       <c r="A198" s="8" t="n">
@@ -6130,6 +6340,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr"/>
     </row>
     <row r="199" ht="15.75" customHeight="1" s="19">
       <c r="A199" s="8" t="n">
@@ -6155,6 +6367,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>+54 11 4482-2630</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr"/>
     </row>
     <row r="200" ht="15.75" customHeight="1" s="19">
       <c r="A200" s="8" t="n">
@@ -6180,6 +6398,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>+54 11 4482-0073</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr"/>
     </row>
     <row r="201" ht="15.75" customHeight="1" s="19">
       <c r="A201" s="8" t="n">
@@ -6205,6 +6429,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr"/>
     </row>
     <row r="202" ht="15.75" customHeight="1" s="19">
       <c r="A202" s="8" t="n">
@@ -6230,6 +6456,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr"/>
     </row>
     <row r="203" ht="15.75" customHeight="1" s="19">
       <c r="A203" s="8" t="n">
@@ -6255,6 +6483,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr"/>
     </row>
     <row r="204" ht="15.75" customHeight="1" s="19">
       <c r="A204" s="8" t="n">
@@ -6280,6 +6510,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr"/>
     </row>
     <row r="205" ht="15.75" customHeight="1" s="19">
       <c r="A205" s="8" t="n">
@@ -6305,6 +6537,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr"/>
     </row>
     <row r="206" ht="15.75" customHeight="1" s="19">
       <c r="A206" s="8" t="n">
@@ -6326,6 +6560,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>http://www.argentina.gob.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="15.75" customHeight="1" s="19">
       <c r="A207" s="8" t="n">
@@ -6351,6 +6591,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr"/>
     </row>
     <row r="208" ht="15.75" customHeight="1" s="19">
       <c r="A208" s="8" t="n">
@@ -6376,6 +6618,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>+54 11 4241-0229</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>https://es-la.facebook.com/Arrocera-del-Sur-401488776583816/</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="15.75" customHeight="1" s="19">
       <c r="A209" s="8" t="n">
@@ -6401,6 +6653,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>+54 11 2308-0063</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr"/>
     </row>
     <row r="210" ht="15.75" customHeight="1" s="19">
       <c r="A210" s="8" t="n">
@@ -6426,6 +6684,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr"/>
     </row>
     <row r="211" ht="15.75" customHeight="1" s="19">
       <c r="A211" s="8" t="n">
@@ -6451,6 +6711,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>+54 11 4624-9154</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr"/>
     </row>
     <row r="212" ht="15.75" customHeight="1" s="19">
       <c r="A212" s="8" t="n">
@@ -6476,6 +6742,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>+54 11 4628-8858</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr"/>
     </row>
     <row r="213" ht="15.75" customHeight="1" s="19">
       <c r="A213" s="8" t="n">
@@ -6501,6 +6773,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr"/>
     </row>
     <row r="214" ht="15.75" customHeight="1" s="19">
       <c r="A214" s="8" t="n">
@@ -6526,6 +6800,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>+54 9 11 3882-4546</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr"/>
     </row>
     <row r="215" ht="15.75" customHeight="1" s="19">
       <c r="A215" s="8" t="n">
@@ -6551,6 +6831,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>+54 11 4078-2691</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>https://geekzonetelefonia.mitiendanube.com/</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="15.75" customHeight="1" s="19">
       <c r="A216" s="8" t="n">
@@ -6576,6 +6866,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="inlineStr"/>
     </row>
     <row r="217" ht="15.75" customHeight="1" s="19">
       <c r="A217" s="8" t="n">
@@ -6601,6 +6893,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr"/>
     </row>
     <row r="218" ht="15.75" customHeight="1" s="19">
       <c r="A218" s="8" t="n">
@@ -6626,6 +6920,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr"/>
     </row>
     <row r="219" ht="15.75" customHeight="1" s="19">
       <c r="A219" s="8" t="n">
@@ -6651,6 +6947,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>+54 11 4656-3778</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr"/>
     </row>
     <row r="220" ht="15.75" customHeight="1" s="19">
       <c r="A220" s="8" t="n">
@@ -6676,6 +6978,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>+54 44601522</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>https://cmvsanjoseobrero.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="221" ht="15.75" customHeight="1" s="19">
       <c r="A221" s="8" t="n">
@@ -6701,6 +7013,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr"/>
     </row>
     <row r="222" ht="15.75" customHeight="1" s="19">
       <c r="A222" s="8" t="n">
@@ -6726,6 +7040,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr"/>
     </row>
     <row r="223" ht="15.75" customHeight="1" s="19">
       <c r="A223" s="8" t="n">
@@ -6751,6 +7067,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr"/>
     </row>
     <row r="224" ht="15.75" customHeight="1" s="19">
       <c r="A224" s="8" t="n">
@@ -6776,6 +7094,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr"/>
     </row>
     <row r="225" ht="15.75" customHeight="1" s="19">
       <c r="A225" s="8" t="n">
@@ -6801,6 +7121,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr"/>
     </row>
     <row r="226" ht="15.75" customHeight="1" s="19">
       <c r="A226" s="8" t="n">
@@ -6826,6 +7148,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr"/>
     </row>
     <row r="227" ht="15.75" customHeight="1" s="19">
       <c r="A227" s="8" t="n">
@@ -6851,6 +7175,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr"/>
     </row>
     <row r="228" ht="15.75" customHeight="1" s="19">
       <c r="A228" s="8" t="n">
@@ -6876,6 +7202,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr"/>
     </row>
     <row r="229" ht="15.75" customHeight="1" s="19">
       <c r="A229" s="8" t="n">
@@ -6901,6 +7229,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr"/>
     </row>
     <row r="230" ht="15.75" customHeight="1" s="19">
       <c r="A230" s="8" t="n">
@@ -6926,6 +7256,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr"/>
     </row>
     <row r="231" ht="15.75" customHeight="1" s="19">
       <c r="A231" s="8" t="n">
@@ -6951,6 +7283,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr"/>
     </row>
     <row r="232" ht="15.75" customHeight="1" s="19">
       <c r="A232" s="8" t="n">
@@ -6976,6 +7310,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr"/>
     </row>
     <row r="233" ht="15.75" customHeight="1" s="19">
       <c r="A233" s="8" t="n">
@@ -7001,6 +7337,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr"/>
     </row>
     <row r="234" ht="15.75" customHeight="1" s="19">
       <c r="A234" s="8" t="n">
@@ -7026,6 +7364,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="inlineStr"/>
     </row>
     <row r="235" ht="15.75" customHeight="1" s="19">
       <c r="A235" s="8" t="n">
@@ -7051,6 +7391,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr"/>
     </row>
     <row r="236" ht="15.75" customHeight="1" s="19">
       <c r="A236" s="8" t="n">
@@ -7076,6 +7418,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr"/>
     </row>
     <row r="237" ht="15.75" customHeight="1" s="19">
       <c r="A237" s="8" t="n">
@@ -7101,6 +7445,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="inlineStr"/>
     </row>
     <row r="238" ht="15.75" customHeight="1" s="19">
       <c r="A238" s="8" t="n">
@@ -7126,6 +7472,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>+54 221 479-9966</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>https://brothersvet.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="239" ht="15.75" customHeight="1" s="19">
       <c r="A239" s="8" t="n">
@@ -7151,6 +7507,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>+54 221 570-4907</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>http://www.suplementacionlaplata.com/</t>
+        </is>
+      </c>
     </row>
     <row r="240" ht="15.75" customHeight="1" s="19">
       <c r="A240" s="8" t="n">
@@ -7176,6 +7542,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>+54 221 455-2080</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr"/>
     </row>
     <row r="241" ht="15.75" customHeight="1" s="19">
       <c r="A241" s="8" t="n">
@@ -7201,6 +7573,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr"/>
     </row>
     <row r="242" ht="15.75" customHeight="1" s="19">
       <c r="A242" s="8" t="n">
@@ -7226,6 +7600,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F242" t="inlineStr"/>
+      <c r="G242" t="inlineStr"/>
     </row>
     <row r="243" ht="15.75" customHeight="1" s="19">
       <c r="A243" s="8" t="n">
@@ -7251,6 +7627,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F243" t="inlineStr"/>
+      <c r="G243" t="inlineStr"/>
     </row>
     <row r="244" ht="15.75" customHeight="1" s="19">
       <c r="A244" s="8" t="n">
@@ -7276,6 +7654,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>+54 221 427-1754</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>https://www.hospitalveterinariomatheusa.com/</t>
+        </is>
+      </c>
     </row>
     <row r="245" ht="15.75" customHeight="1" s="19">
       <c r="A245" s="8" t="n">
@@ -7301,6 +7689,16 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>+54 11 2394-3611</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>https://instagram.com/dieteticalahermelinda?igshid=YmMyMTA2M2Y=</t>
+        </is>
+      </c>
     </row>
     <row r="246" ht="15.75" customHeight="1" s="19">
       <c r="A246" s="8" t="n">
@@ -7326,6 +7724,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr"/>
     </row>
     <row r="247" ht="15.75" customHeight="1" s="19">
       <c r="A247" s="8" t="n">
@@ -7351,6 +7751,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F247" t="inlineStr"/>
+      <c r="G247" t="inlineStr"/>
     </row>
     <row r="248" ht="15.75" customHeight="1" s="19">
       <c r="A248" s="8" t="n">
@@ -7376,6 +7778,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="inlineStr"/>
     </row>
     <row r="249" ht="15.75" customHeight="1" s="19">
       <c r="A249" s="8" t="n">
@@ -7401,6 +7805,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>+54 221 591-8114</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>http://www.facebook.com/veterinariamedicans/</t>
+        </is>
+      </c>
     </row>
     <row r="250" ht="15.75" customHeight="1" s="19">
       <c r="A250" s="8" t="n">
@@ -7426,6 +7840,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F250" t="inlineStr"/>
+      <c r="G250" t="inlineStr"/>
     </row>
     <row r="251" ht="15.75" customHeight="1" s="19">
       <c r="A251" s="8" t="n">
@@ -7451,6 +7867,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>+54 221 455-2080</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr"/>
     </row>
     <row r="252" ht="15.75" customHeight="1" s="19">
       <c r="A252" s="8" t="n">
@@ -7476,6 +7898,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F252" t="inlineStr"/>
+      <c r="G252" t="inlineStr"/>
     </row>
     <row r="253" ht="15.75" customHeight="1" s="19">
       <c r="A253" s="8" t="n">

--- a/PUNTOS_DE_VENTA_completado.xlsx
+++ b/PUNTOS_DE_VENTA_completado.xlsx
@@ -7925,6 +7925,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F253" t="inlineStr"/>
+      <c r="G253" t="inlineStr"/>
     </row>
     <row r="254" ht="15.75" customHeight="1" s="19">
       <c r="A254" s="8" t="n">
@@ -7950,6 +7952,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="inlineStr"/>
     </row>
     <row r="255" ht="15.75" customHeight="1" s="19">
       <c r="A255" s="8" t="n">
@@ -7975,6 +7979,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F255" t="inlineStr"/>
+      <c r="G255" t="inlineStr"/>
     </row>
     <row r="256" ht="15.75" customHeight="1" s="19">
       <c r="A256" s="8" t="n">
@@ -8000,6 +8006,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>+54 11 4003-4100</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>https://www.bersa.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="257" ht="15.75" customHeight="1" s="19">
       <c r="A257" s="8" t="n">
@@ -8025,6 +8041,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>+54 221 355-7581</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>https://cortinasmetalicaslaplata.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="258" ht="15.75" customHeight="1" s="19">
       <c r="A258" s="8" t="n">
@@ -8050,6 +8076,16 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>+54 11 4003-4100</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>https://www.bersa.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="259" ht="15.75" customHeight="1" s="19">
       <c r="A259" s="8" t="n">
@@ -8075,6 +8111,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>+54 221 453-6860</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>http://grupogestar.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="260" ht="15.75" customHeight="1" s="19">
       <c r="A260" s="8" t="n">
@@ -8100,6 +8146,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="inlineStr"/>
     </row>
     <row r="261" ht="15.75" customHeight="1" s="19">
       <c r="A261" s="8" t="n">
@@ -8125,6 +8173,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr"/>
     </row>
     <row r="262" ht="15.75" customHeight="1" s="19">
       <c r="A262" s="8" t="n">
@@ -8150,6 +8200,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>+54 221 421-1331</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/pages/Veterinaria-Fucos-Dr-Marcos-Furlan/217126501707840</t>
+        </is>
+      </c>
     </row>
     <row r="263" ht="15.75" customHeight="1" s="19">
       <c r="A263" s="8" t="n">
@@ -8175,6 +8235,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F263" t="inlineStr"/>
+      <c r="G263" t="inlineStr"/>
     </row>
     <row r="264" ht="15.75" customHeight="1" s="19">
       <c r="A264" s="8" t="n">
@@ -8200,6 +8262,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F264" t="inlineStr"/>
+      <c r="G264" t="inlineStr"/>
     </row>
     <row r="265" ht="15.75" customHeight="1" s="19">
       <c r="A265" s="8" t="n">
@@ -8225,6 +8289,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F265" t="inlineStr"/>
+      <c r="G265" t="inlineStr"/>
     </row>
     <row r="266" ht="15.75" customHeight="1" s="19">
       <c r="A266" s="8" t="n">
@@ -8250,6 +8316,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>+54 11 6453-6162</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr"/>
     </row>
     <row r="267" ht="15.75" customHeight="1" s="19">
       <c r="A267" s="8" t="n">
@@ -8275,6 +8347,16 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>+54 11 2385-3662</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>http://www.animalbrothers.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="268" ht="15.75" customHeight="1" s="19">
       <c r="A268" s="8" t="n">
@@ -8300,6 +8382,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="inlineStr"/>
     </row>
     <row r="269" ht="15.75" customHeight="1" s="19">
       <c r="A269" s="8" t="n">
@@ -8325,6 +8409,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F269" t="inlineStr"/>
+      <c r="G269" t="inlineStr"/>
     </row>
     <row r="270" ht="15.75" customHeight="1" s="19">
       <c r="A270" s="8" t="n">
@@ -8350,6 +8436,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F270" t="inlineStr"/>
+      <c r="G270" t="inlineStr"/>
     </row>
     <row r="271" ht="15.75" customHeight="1" s="19">
       <c r="A271" s="8" t="n">
@@ -8375,6 +8463,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F271" t="inlineStr"/>
+      <c r="G271" t="inlineStr"/>
     </row>
     <row r="272" ht="15.75" customHeight="1" s="19">
       <c r="A272" s="8" t="n">
@@ -8400,6 +8490,16 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>+54 11 2070-0687</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>http://www.hierbasguiral.com/</t>
+        </is>
+      </c>
     </row>
     <row r="273" ht="15.75" customHeight="1" s="19">
       <c r="A273" s="8" t="n">
@@ -8425,6 +8525,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F273" t="inlineStr"/>
+      <c r="G273" t="inlineStr"/>
     </row>
     <row r="274" ht="15.75" customHeight="1" s="19">
       <c r="A274" s="8" t="n">
@@ -8450,6 +8552,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F274" t="inlineStr"/>
+      <c r="G274" t="inlineStr"/>
     </row>
     <row r="275" ht="15.75" customHeight="1" s="19">
       <c r="A275" s="8" t="n">
@@ -8475,6 +8579,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F275" t="inlineStr"/>
+      <c r="G275" t="inlineStr"/>
     </row>
     <row r="276" ht="15.75" customHeight="1" s="19">
       <c r="A276" s="8" t="n">
@@ -8500,6 +8606,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>+54 221 461-2565</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr"/>
     </row>
     <row r="277" ht="15.75" customHeight="1" s="19">
       <c r="A277" s="8" t="n">
@@ -8525,6 +8637,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>+54 221 421-5056</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>http://centromedicodiag.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="278" ht="15.75" customHeight="1" s="19">
       <c r="A278" s="8" t="n">
@@ -8550,6 +8672,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F278" t="inlineStr"/>
+      <c r="G278" t="inlineStr"/>
     </row>
     <row r="279" ht="15.75" customHeight="1" s="19">
       <c r="A279" s="8" t="n">
@@ -8575,6 +8699,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F279" t="inlineStr"/>
+      <c r="G279" t="inlineStr"/>
     </row>
     <row r="280" ht="15.75" customHeight="1" s="19">
       <c r="A280" s="8" t="n">
@@ -8600,6 +8726,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F280" t="inlineStr"/>
+      <c r="G280" t="inlineStr"/>
     </row>
     <row r="281" ht="15.75" customHeight="1" s="19">
       <c r="A281" s="8" t="n">
@@ -8625,6 +8753,12 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>+54 44620151</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr"/>
     </row>
     <row r="282" ht="15.75" customHeight="1" s="19">
       <c r="A282" s="8" t="n">
@@ -8650,6 +8784,12 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>+54 44620151</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr"/>
     </row>
     <row r="283" ht="15.75" customHeight="1" s="19">
       <c r="A283" s="8" t="n">
@@ -8675,6 +8815,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F283" t="inlineStr"/>
+      <c r="G283" t="inlineStr"/>
     </row>
     <row r="284" ht="15.75" customHeight="1" s="19">
       <c r="A284" s="8" t="n">
@@ -8700,6 +8842,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>+54 221 418-8616</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr"/>
     </row>
     <row r="285" ht="15.75" customHeight="1" s="19">
       <c r="A285" s="8" t="n">
@@ -8725,6 +8873,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F285" t="inlineStr"/>
+      <c r="G285" t="inlineStr"/>
     </row>
     <row r="286" ht="15.75" customHeight="1" s="19">
       <c r="A286" s="8" t="n">
@@ -8750,6 +8900,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F286" t="inlineStr"/>
+      <c r="G286" t="inlineStr"/>
     </row>
     <row r="287" ht="15.75" customHeight="1" s="19">
       <c r="A287" s="8" t="n">
@@ -8775,6 +8927,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F287" t="inlineStr"/>
+      <c r="G287" t="inlineStr"/>
     </row>
     <row r="288" ht="15.75" customHeight="1" s="19">
       <c r="A288" s="8" t="n">
@@ -8800,6 +8954,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F288" t="inlineStr"/>
+      <c r="G288" t="inlineStr"/>
     </row>
     <row r="289" ht="15.75" customHeight="1" s="19">
       <c r="A289" s="8" t="n">
@@ -8825,6 +8981,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F289" t="inlineStr"/>
+      <c r="G289" t="inlineStr"/>
     </row>
     <row r="290" ht="15.75" customHeight="1" s="19">
       <c r="A290" s="8" t="n">
@@ -8850,6 +9008,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F290" t="inlineStr"/>
+      <c r="G290" t="inlineStr"/>
     </row>
     <row r="291" ht="15.75" customHeight="1" s="19">
       <c r="A291" s="8" t="n">
@@ -8875,6 +9035,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F291" t="inlineStr"/>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/proyect.escalada/</t>
+        </is>
+      </c>
     </row>
     <row r="292" ht="15.75" customHeight="1" s="19">
       <c r="A292" s="8" t="n">
@@ -8900,6 +9066,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F292" t="inlineStr"/>
+      <c r="G292" t="inlineStr"/>
     </row>
     <row r="293" ht="15.75" customHeight="1" s="19">
       <c r="A293" s="8" t="n">
@@ -8925,6 +9093,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>+54 221 427-0932</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr"/>
     </row>
     <row r="294" ht="15.75" customHeight="1" s="19">
       <c r="A294" s="8" t="n">
@@ -8950,6 +9124,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F294" t="inlineStr"/>
+      <c r="G294" t="inlineStr"/>
     </row>
     <row r="295" ht="15.75" customHeight="1" s="19">
       <c r="A295" s="8" t="n">
@@ -8975,6 +9151,16 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>+54 2202 45-6599</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>http://www.distrib-sosahnos.com/</t>
+        </is>
+      </c>
     </row>
     <row r="296" ht="15.75" customHeight="1" s="19">
       <c r="A296" s="8" t="n">
@@ -9000,6 +9186,12 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>+54 11 6878-4043</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr"/>
     </row>
     <row r="297" ht="15.75" customHeight="1" s="19">
       <c r="A297" s="8" t="n">
@@ -9025,6 +9217,16 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>+54 237 465-4613</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>https://petsclass2.mitiendanube.com/</t>
+        </is>
+      </c>
     </row>
     <row r="298" ht="15.75" customHeight="1" s="19">
       <c r="A298" s="8" t="n">
@@ -9050,6 +9252,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F298" t="inlineStr"/>
+      <c r="G298" t="inlineStr"/>
     </row>
     <row r="299" ht="15.75" customHeight="1" s="19">
       <c r="A299" s="8" t="n">
@@ -9075,6 +9279,12 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>+54 11 6025-4931</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr"/>
     </row>
     <row r="300" ht="15.75" customHeight="1" s="19">
       <c r="A300" s="8" t="n">
@@ -9100,6 +9310,12 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F300" t="inlineStr"/>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>https://mercadocentral.gob.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="301" ht="15.75" customHeight="1" s="19">
       <c r="A301" s="8" t="n">
@@ -9125,6 +9341,12 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>+54 11 2125-8327</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr"/>
     </row>
     <row r="302" ht="15.75" customHeight="1" s="19">
       <c r="A302" s="8" t="n">
@@ -9150,6 +9372,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>+54 9 221 316-1678</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/veterinariasanpablo.lp</t>
+        </is>
+      </c>
     </row>
     <row r="303" ht="15.75" customHeight="1" s="19">
       <c r="A303" s="8" t="n">
@@ -9175,6 +9407,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F303" t="inlineStr"/>
+      <c r="G303" t="inlineStr"/>
     </row>
     <row r="304" ht="15.75" customHeight="1" s="19">
       <c r="A304" s="8" t="n">
@@ -9200,6 +9434,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F304" t="inlineStr"/>
+      <c r="G304" t="inlineStr"/>
     </row>
     <row r="305" ht="15.75" customHeight="1" s="19">
       <c r="A305" s="8" t="n">
@@ -9225,6 +9461,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>+54 221 451-0425</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr"/>
     </row>
     <row r="306" ht="15.75" customHeight="1" s="19">
       <c r="A306" s="8" t="n">
@@ -9250,6 +9492,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>+54 221 563-4334</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/levislp5</t>
+        </is>
+      </c>
     </row>
     <row r="307" ht="15.75" customHeight="1" s="19">
       <c r="A307" s="8" t="n">
@@ -9275,6 +9527,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F307" t="inlineStr"/>
+      <c r="G307" t="inlineStr"/>
     </row>
     <row r="308" ht="15.75" customHeight="1" s="19">
       <c r="A308" s="8" t="n">
@@ -9300,6 +9554,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F308" t="inlineStr"/>
+      <c r="G308" t="inlineStr"/>
     </row>
     <row r="309" ht="15.75" customHeight="1" s="19">
       <c r="A309" s="8" t="n">
@@ -9325,6 +9581,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F309" t="inlineStr"/>
+      <c r="G309" t="inlineStr"/>
     </row>
     <row r="310" ht="15.75" customHeight="1" s="19">
       <c r="A310" s="8" t="n">
@@ -9350,6 +9608,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>+54 9 221 649-1755</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mirafloreslp/</t>
+        </is>
+      </c>
     </row>
     <row r="311" ht="15.75" customHeight="1" s="19">
       <c r="A311" s="8" t="n">
@@ -9375,6 +9643,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F311" t="inlineStr"/>
+      <c r="G311" t="inlineStr"/>
     </row>
     <row r="312" ht="15.75" customHeight="1" s="19">
       <c r="A312" s="8" t="n">
@@ -9400,6 +9670,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>+54 9 221 537-4388</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>http://www.centroolmos.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="313" ht="15.75" customHeight="1" s="19">
       <c r="A313" s="8" t="n">
@@ -9425,6 +9705,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F313" t="inlineStr"/>
+      <c r="G313" t="inlineStr"/>
     </row>
     <row r="314" ht="15.75" customHeight="1" s="19">
       <c r="A314" s="8" t="n">
@@ -9450,6 +9732,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F314" t="inlineStr"/>
+      <c r="G314" t="inlineStr"/>
     </row>
     <row r="315" ht="15.75" customHeight="1" s="19">
       <c r="A315" s="8" t="n">
@@ -9475,6 +9759,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F315" t="inlineStr"/>
+      <c r="G315" t="inlineStr"/>
     </row>
     <row r="316" ht="15.75" customHeight="1" s="19">
       <c r="A316" s="8" t="n">
@@ -9500,6 +9786,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F316" t="inlineStr"/>
+      <c r="G316" t="inlineStr"/>
     </row>
     <row r="317" ht="15.75" customHeight="1" s="19">
       <c r="A317" s="8" t="n">
@@ -9525,6 +9813,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F317" t="inlineStr"/>
+      <c r="G317" t="inlineStr"/>
     </row>
     <row r="318" ht="15.75" customHeight="1" s="19">
       <c r="A318" s="8" t="n">
@@ -9550,6 +9840,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>+54 221 484-2293</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>https://www.correoargentino.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="319" ht="15.75" customHeight="1" s="19">
       <c r="A319" s="8" t="n">
@@ -9575,6 +9875,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>+54 221 484-7700</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr"/>
     </row>
     <row r="320" ht="15.75" customHeight="1" s="19">
       <c r="A320" s="8" t="n">
@@ -9600,6 +9906,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>+54 221 471-3500</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>http://www.mseg.gba.gov.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="321" ht="15.75" customHeight="1" s="19">
       <c r="A321" s="8" t="n">
@@ -9625,6 +9941,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F321" t="inlineStr"/>
+      <c r="G321" t="inlineStr"/>
     </row>
     <row r="322" ht="15.75" customHeight="1" s="19">
       <c r="A322" s="8" t="n">
@@ -9650,6 +9968,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F322" t="inlineStr"/>
+      <c r="G322" t="inlineStr"/>
     </row>
     <row r="323" ht="15.75" customHeight="1" s="19">
       <c r="A323" s="8" t="n">
@@ -9675,6 +9995,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F323" t="inlineStr"/>
+      <c r="G323" t="inlineStr"/>
     </row>
     <row r="324" ht="15.75" customHeight="1" s="19">
       <c r="A324" s="8" t="n">
@@ -9700,6 +10022,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F324" t="inlineStr"/>
+      <c r="G324" t="inlineStr"/>
     </row>
     <row r="325" ht="15.75" customHeight="1" s="19">
       <c r="A325" s="8" t="n">
@@ -9725,6 +10049,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F325" t="inlineStr"/>
+      <c r="G325" t="inlineStr"/>
     </row>
     <row r="326" ht="15.75" customHeight="1" s="19">
       <c r="A326" s="8" t="n">
@@ -9750,6 +10076,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F326" t="inlineStr"/>
+      <c r="G326" t="inlineStr"/>
     </row>
     <row r="327" ht="15.75" customHeight="1" s="19">
       <c r="A327" s="8" t="n">
@@ -9775,6 +10103,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F327" t="inlineStr"/>
+      <c r="G327" t="inlineStr"/>
     </row>
     <row r="328" ht="15.75" customHeight="1" s="19">
       <c r="A328" s="8" t="n">
@@ -9800,6 +10130,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F328" t="inlineStr"/>
+      <c r="G328" t="inlineStr"/>
     </row>
     <row r="329" ht="15.75" customHeight="1" s="19">
       <c r="A329" s="8" t="n">
@@ -9825,6 +10157,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F329" t="inlineStr"/>
+      <c r="G329" t="inlineStr"/>
     </row>
     <row r="330" ht="15.75" customHeight="1" s="19">
       <c r="A330" s="8" t="n">
@@ -9850,6 +10184,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>+54 11 4228-3860</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=100063537914732</t>
+        </is>
+      </c>
     </row>
     <row r="331" ht="15.75" customHeight="1" s="19">
       <c r="A331" s="8" t="n">
@@ -9875,6 +10219,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>+54 11 3846-8936</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr"/>
     </row>
     <row r="332" ht="15.75" customHeight="1" s="19">
       <c r="A332" s="8" t="n">
@@ -9900,6 +10250,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>+54 9 11 6467-7151</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr"/>
     </row>
     <row r="333" ht="15.75" customHeight="1" s="19">
       <c r="A333" s="8" t="n">
@@ -9925,6 +10281,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F333" t="inlineStr"/>
+      <c r="G333" t="inlineStr"/>
     </row>
     <row r="334" ht="15.75" customHeight="1" s="19">
       <c r="A334" s="8" t="n">
@@ -9950,6 +10308,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F334" t="inlineStr"/>
+      <c r="G334" t="inlineStr"/>
     </row>
     <row r="335" ht="15.75" customHeight="1" s="19">
       <c r="A335" s="8" t="n">
@@ -9975,6 +10335,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>+54 11 4434-1216</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr"/>
     </row>
     <row r="336" ht="15.75" customHeight="1" s="19">
       <c r="A336" s="8" t="n">
@@ -10000,6 +10366,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>+54 11 3656-4646</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>http://www.avicolazapiola.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="337" ht="15.75" customHeight="1" s="19">
       <c r="A337" s="8" t="n">
@@ -10025,6 +10401,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>+54 11 4222-4231</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr"/>
     </row>
     <row r="338" ht="15.75" customHeight="1" s="19">
       <c r="A338" s="8" t="n">
@@ -10050,6 +10432,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>+54 11 4251-7885</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Vete.Sanmartin/</t>
+        </is>
+      </c>
     </row>
     <row r="339" ht="15.75" customHeight="1" s="19">
       <c r="A339" s="8" t="n">
@@ -10075,6 +10467,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>+54 9 11 4975-6432</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr"/>
     </row>
     <row r="340" ht="15.75" customHeight="1" s="19">
       <c r="A340" s="8" t="n">
@@ -10100,6 +10498,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>+54 11 4259-2799</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr"/>
     </row>
     <row r="341" ht="15.75" customHeight="1" s="19">
       <c r="A341" s="8" t="n">
@@ -10125,6 +10529,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>+54 11 4251-1082</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>http://www.inar.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="342" ht="15.75" customHeight="1" s="19">
       <c r="A342" s="8" t="n">
@@ -10150,6 +10564,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F342" t="inlineStr"/>
+      <c r="G342" t="inlineStr"/>
     </row>
     <row r="343" ht="15.75" customHeight="1" s="19">
       <c r="A343" s="8" t="n">
@@ -10175,6 +10591,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>+54 11 4228-9143</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr"/>
     </row>
     <row r="344" ht="15.75" customHeight="1" s="19">
       <c r="A344" s="8" t="n">
@@ -10200,6 +10622,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>+54 11 3221-5989</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr"/>
     </row>
     <row r="345" ht="15.75" customHeight="1" s="19">
       <c r="A345" s="8" t="n">
@@ -10225,6 +10653,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>+54 42097525</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr"/>
     </row>
     <row r="346" ht="15.75" customHeight="1" s="19">
       <c r="A346" s="8" t="n">
@@ -10250,6 +10684,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F346" t="inlineStr"/>
+      <c r="G346" t="inlineStr"/>
     </row>
     <row r="347" ht="15.75" customHeight="1" s="19">
       <c r="A347" s="8" t="n">
@@ -10275,6 +10711,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>+54 11 4220-6849</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr"/>
     </row>
     <row r="348" ht="15.75" customHeight="1" s="19">
       <c r="A348" s="8" t="n">
@@ -10300,6 +10742,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F348" t="inlineStr"/>
+      <c r="G348" t="inlineStr"/>
     </row>
     <row r="349" ht="15.75" customHeight="1" s="19">
       <c r="A349" s="8" t="n">
@@ -10325,6 +10769,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>+54 11 7366-5956</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>http://www.malaconducta.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="350" ht="15.75" customHeight="1" s="19">
       <c r="A350" s="8" t="n">
@@ -10350,6 +10804,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F350" t="inlineStr"/>
+      <c r="G350" t="inlineStr"/>
     </row>
     <row r="351" ht="15.75" customHeight="1" s="19">
       <c r="A351" s="8" t="n">
@@ -10375,6 +10831,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F351" t="inlineStr"/>
+      <c r="G351" t="inlineStr"/>
     </row>
     <row r="352" ht="15.75" customHeight="1" s="19">
       <c r="A352" s="8" t="n">
@@ -10398,6 +10856,16 @@
       <c r="E352" s="8" t="inlineStr">
         <is>
           <t>Veterinaria</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>+54 11 4218-0144</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>https://lamarinasa.com.ar/</t>
         </is>
       </c>
     </row>

--- a/PUNTOS_DE_VENTA_completado.xlsx
+++ b/PUNTOS_DE_VENTA_completado.xlsx
@@ -10893,6 +10893,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F353" t="inlineStr"/>
+      <c r="G353" t="inlineStr"/>
     </row>
     <row r="354" ht="15.75" customHeight="1" s="19">
       <c r="A354" s="8" t="n">
@@ -10918,6 +10920,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F354" t="inlineStr"/>
+      <c r="G354" t="inlineStr"/>
     </row>
     <row r="355" ht="15.75" customHeight="1" s="19">
       <c r="A355" s="8" t="n">
@@ -10943,6 +10947,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F355" t="inlineStr"/>
+      <c r="G355" t="inlineStr"/>
     </row>
     <row r="356" ht="15.75" customHeight="1" s="19">
       <c r="A356" s="8" t="n">
@@ -10968,6 +10974,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F356" t="inlineStr"/>
+      <c r="G356" t="inlineStr"/>
     </row>
     <row r="357" ht="15.75" customHeight="1" s="19">
       <c r="A357" s="8" t="n">
@@ -10993,6 +11001,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>+54 9 11 5408-8383</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr"/>
     </row>
     <row r="358" ht="15.75" customHeight="1" s="19">
       <c r="A358" s="8" t="n">
@@ -11018,6 +11032,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>+54 11 4224-6404</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/quilmeshockeyoficial/?hl=es</t>
+        </is>
+      </c>
     </row>
     <row r="359" ht="15.75" customHeight="1" s="19">
       <c r="A359" s="8" t="n">
@@ -11043,6 +11067,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F359" t="inlineStr"/>
+      <c r="G359" t="inlineStr"/>
     </row>
     <row r="360" ht="15.75" customHeight="1" s="19">
       <c r="A360" s="8" t="n">
@@ -11068,6 +11094,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F360" t="inlineStr"/>
+      <c r="G360" t="inlineStr"/>
     </row>
     <row r="361" ht="15.75" customHeight="1" s="19">
       <c r="A361" s="8" t="n">
@@ -11093,6 +11121,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F361" t="inlineStr"/>
+      <c r="G361" t="inlineStr"/>
     </row>
     <row r="362" ht="15.75" customHeight="1" s="19">
       <c r="A362" s="8" t="n">
@@ -11118,6 +11148,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F362" t="inlineStr"/>
+      <c r="G362" t="inlineStr"/>
     </row>
     <row r="363" ht="15.75" customHeight="1" s="19">
       <c r="A363" s="8" t="n">
@@ -11143,6 +11175,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F363" t="inlineStr"/>
+      <c r="G363" t="inlineStr"/>
     </row>
     <row r="364" ht="15.75" customHeight="1" s="19">
       <c r="A364" s="8" t="n">
@@ -11168,6 +11202,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>+54 42502713</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>http://belgranovigil.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="365" ht="15.75" customHeight="1" s="19">
       <c r="A365" s="8" t="n">
@@ -11193,6 +11237,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F365" t="inlineStr"/>
+      <c r="G365" t="inlineStr"/>
     </row>
     <row r="366" ht="15.75" customHeight="1" s="19">
       <c r="A366" s="8" t="n">
@@ -11218,6 +11264,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F366" t="inlineStr"/>
+      <c r="G366" t="inlineStr"/>
     </row>
     <row r="367" ht="15.75" customHeight="1" s="19">
       <c r="A367" s="8" t="n">
@@ -11243,6 +11291,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>+54 11 4254-1932</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr"/>
     </row>
     <row r="368" ht="15.75" customHeight="1" s="19">
       <c r="A368" s="8" t="n">
@@ -11268,6 +11322,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>+54 11 4361-8962</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>http://www.veterinarias.com.ar/azara-veterinaria</t>
+        </is>
+      </c>
     </row>
     <row r="369" ht="15.75" customHeight="1" s="19">
       <c r="A369" s="8" t="n">
@@ -11293,6 +11357,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>+54 11 4302-5724</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>http://www.veterinariaburbuja.com/</t>
+        </is>
+      </c>
     </row>
     <row r="370" ht="15.75" customHeight="1" s="19">
       <c r="A370" s="8" t="n">
@@ -11318,6 +11392,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F370" t="inlineStr"/>
+      <c r="G370" t="inlineStr"/>
     </row>
     <row r="371" ht="15.75" customHeight="1" s="19">
       <c r="A371" s="8" t="n">
@@ -11343,6 +11419,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>+54 11 4922-0118</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>http://veterinariawalterperez.setmore.com/</t>
+        </is>
+      </c>
     </row>
     <row r="372" ht="15.75" customHeight="1" s="19">
       <c r="A372" s="8" t="n">
@@ -11368,6 +11454,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F372" t="inlineStr"/>
+      <c r="G372" t="inlineStr"/>
     </row>
     <row r="373" ht="15.75" customHeight="1" s="19">
       <c r="A373" s="8" t="n">
@@ -11393,6 +11481,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F373" t="inlineStr"/>
+      <c r="G373" t="inlineStr"/>
     </row>
     <row r="374" ht="15.75" customHeight="1" s="19">
       <c r="A374" s="8" t="n">
@@ -11418,6 +11508,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F374" t="inlineStr"/>
+      <c r="G374" t="inlineStr"/>
     </row>
     <row r="375" ht="15.75" customHeight="1" s="19">
       <c r="A375" s="8" t="n">
@@ -11443,6 +11535,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F375" t="inlineStr"/>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>https://koala.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="376" ht="15.75" customHeight="1" s="19">
       <c r="A376" s="8" t="n">
@@ -11468,6 +11566,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F376" t="inlineStr"/>
+      <c r="G376" t="inlineStr"/>
     </row>
     <row r="377" ht="15.75" customHeight="1" s="19">
       <c r="A377" s="8" t="n">
@@ -11493,6 +11593,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F377" t="inlineStr"/>
+      <c r="G377" t="inlineStr"/>
     </row>
     <row r="378" ht="15.75" customHeight="1" s="19">
       <c r="A378" s="8" t="n">
@@ -11518,6 +11620,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>+54 11 4827-9369</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr"/>
     </row>
     <row r="379" ht="15.75" customHeight="1" s="19">
       <c r="A379" s="8" t="n">
@@ -11543,6 +11651,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>+54 11 4454-8080</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr"/>
     </row>
     <row r="380" ht="15.75" customHeight="1" s="19">
       <c r="A380" s="8" t="n">
@@ -11568,6 +11682,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F380" t="inlineStr"/>
+      <c r="G380" t="inlineStr"/>
     </row>
     <row r="381" ht="15.75" customHeight="1" s="19">
       <c r="A381" s="8" t="n">
@@ -11593,6 +11709,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>+54 49523706</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/veterinaria.svensen?igsh=NTRteTRzNWV3emFk</t>
+        </is>
+      </c>
     </row>
     <row r="382" ht="15.75" customHeight="1" s="19">
       <c r="A382" s="8" t="n">
@@ -11618,6 +11744,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F382" t="inlineStr"/>
+      <c r="G382" t="inlineStr"/>
     </row>
     <row r="383" ht="15.75" customHeight="1" s="19">
       <c r="A383" s="8" t="n">
@@ -11643,6 +11771,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>+54 11 4966-0771</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>http://www.clinicavetcordoba.com/</t>
+        </is>
+      </c>
     </row>
     <row r="384" ht="15.75" customHeight="1" s="19">
       <c r="A384" s="8" t="n">
@@ -11668,6 +11806,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F384" t="inlineStr"/>
+      <c r="G384" t="inlineStr"/>
     </row>
     <row r="385" ht="15.75" customHeight="1" s="19">
       <c r="A385" s="8" t="n">
@@ -11693,6 +11833,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>+54 11 4381-2531</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr"/>
     </row>
     <row r="386" ht="15.75" customHeight="1" s="19">
       <c r="A386" s="8" t="n">
@@ -11718,6 +11864,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F386" t="inlineStr"/>
+      <c r="G386" t="inlineStr"/>
     </row>
     <row r="387" ht="15.75" customHeight="1" s="19">
       <c r="A387" s="8" t="n">
@@ -11743,6 +11891,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F387" t="inlineStr"/>
+      <c r="G387" t="inlineStr"/>
     </row>
     <row r="388" ht="15.75" customHeight="1" s="19">
       <c r="A388" s="8" t="n">
@@ -11768,6 +11918,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F388" t="inlineStr"/>
+      <c r="G388" t="inlineStr"/>
     </row>
     <row r="389" ht="15.75" customHeight="1" s="19">
       <c r="A389" s="8" t="n">
@@ -11793,6 +11945,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F389" t="inlineStr"/>
+      <c r="G389" t="inlineStr"/>
     </row>
     <row r="390" ht="15.75" customHeight="1" s="19">
       <c r="A390" s="8" t="n">
@@ -11818,6 +11972,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>+54 11 4826-2655</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>http://www.veterinarias.com.ar/lechien-veterinaria</t>
+        </is>
+      </c>
     </row>
     <row r="391" ht="15.75" customHeight="1" s="19">
       <c r="A391" s="8" t="n">
@@ -11843,6 +12007,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F391" t="inlineStr"/>
+      <c r="G391" t="inlineStr"/>
     </row>
     <row r="392" ht="15.75" customHeight="1" s="19">
       <c r="A392" s="8" t="n">
@@ -11868,6 +12034,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F392" t="inlineStr"/>
+      <c r="G392" t="inlineStr"/>
     </row>
     <row r="393" ht="15.75" customHeight="1" s="19">
       <c r="A393" s="8" t="n">
@@ -11893,6 +12061,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F393" t="inlineStr"/>
+      <c r="G393" t="inlineStr"/>
     </row>
     <row r="394" ht="15.75" customHeight="1" s="19">
       <c r="A394" s="8" t="n">
@@ -11918,6 +12088,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>+54 11 4801-4032</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr"/>
     </row>
     <row r="395" ht="15.75" customHeight="1" s="19">
       <c r="A395" s="8" t="n">
@@ -11943,6 +12119,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F395" t="inlineStr"/>
+      <c r="G395" t="inlineStr"/>
     </row>
     <row r="396" ht="15.75" customHeight="1" s="19">
       <c r="A396" s="8" t="n">
@@ -11968,6 +12146,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F396" t="inlineStr"/>
+      <c r="G396" t="inlineStr"/>
     </row>
     <row r="397" ht="15.75" customHeight="1" s="19">
       <c r="A397" s="8" t="n">
@@ -11993,6 +12173,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F397" t="inlineStr"/>
+      <c r="G397" t="inlineStr"/>
     </row>
     <row r="398" ht="15.75" customHeight="1" s="19">
       <c r="A398" s="8" t="n">
@@ -12018,6 +12200,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>+54 11 4303-3539</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>https://www.montesdeocavetcenter.com/</t>
+        </is>
+      </c>
     </row>
     <row r="399" ht="15.75" customHeight="1" s="19">
       <c r="A399" s="8" t="n">
@@ -12043,6 +12235,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>+54 9 11 6257-3889</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>https://patasclub.com/</t>
+        </is>
+      </c>
     </row>
     <row r="400" ht="15.75" customHeight="1" s="19">
       <c r="A400" s="8" t="n">
@@ -12068,6 +12270,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F400" t="inlineStr"/>
+      <c r="G400" t="inlineStr"/>
     </row>
     <row r="401" ht="15.75" customHeight="1" s="19">
       <c r="A401" s="8" t="n">
@@ -12093,6 +12297,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>+54 11 4300-9239</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr"/>
     </row>
     <row r="402" ht="15.75" customHeight="1" s="19">
       <c r="A402" s="8" t="n">
@@ -12118,6 +12328,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F402" t="inlineStr"/>
+      <c r="G402" t="inlineStr"/>
     </row>
     <row r="403" ht="15.75" customHeight="1" s="19">
       <c r="A403" s="8" t="n">
@@ -12143,6 +12355,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F403" t="inlineStr"/>
+      <c r="G403" t="inlineStr"/>
     </row>
     <row r="404" ht="15.75" customHeight="1" s="19">
       <c r="A404" s="8" t="n">
@@ -12168,6 +12382,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F404" t="inlineStr"/>
+      <c r="G404" t="inlineStr"/>
     </row>
     <row r="405" ht="15.75" customHeight="1" s="19">
       <c r="A405" s="8" t="n">
@@ -12193,6 +12409,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>+54 48265180</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>http://instagram.com/lasmarias.vet</t>
+        </is>
+      </c>
     </row>
     <row r="406" ht="15.75" customHeight="1" s="19">
       <c r="A406" s="8" t="n">
@@ -12218,6 +12444,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F406" t="inlineStr"/>
+      <c r="G406" t="inlineStr"/>
     </row>
     <row r="407" ht="15.75" customHeight="1" s="19">
       <c r="A407" s="8" t="n">
@@ -12243,6 +12471,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F407" t="inlineStr"/>
+      <c r="G407" t="inlineStr"/>
     </row>
     <row r="408" ht="15.75" customHeight="1" s="19">
       <c r="A408" s="8" t="n">
@@ -12268,6 +12498,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>+54 11 4342-1773</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>http://www.veterinariablinka.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="409" ht="15.75" customHeight="1" s="19">
       <c r="A409" s="8" t="n">
@@ -12293,6 +12533,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>+54 11 4931-5568</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>http://www.veterinariafenix.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="410" ht="15.75" customHeight="1" s="19">
       <c r="A410" s="8" t="n">
@@ -12318,6 +12568,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F410" t="inlineStr"/>
+      <c r="G410" t="inlineStr"/>
     </row>
     <row r="411" ht="15.75" customHeight="1" s="19">
       <c r="A411" s="8" t="n">
@@ -12343,6 +12595,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F411" t="inlineStr"/>
+      <c r="G411" t="inlineStr"/>
     </row>
     <row r="412" ht="15.75" customHeight="1" s="19">
       <c r="A412" s="8" t="n">
@@ -12368,6 +12622,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>+54 11 4855-8756</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr"/>
     </row>
     <row r="413" ht="15.75" customHeight="1" s="19">
       <c r="A413" s="8" t="n">
@@ -12393,6 +12653,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>+54 11 5765-7813</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Macarenaeventos-536788826705170/</t>
+        </is>
+      </c>
     </row>
     <row r="414" ht="15.75" customHeight="1" s="19">
       <c r="A414" s="8" t="n">
@@ -12418,6 +12688,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>+54 11 4448-6979</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr"/>
     </row>
     <row r="415" ht="15.75" customHeight="1" s="19">
       <c r="A415" s="8" t="n">
@@ -12443,6 +12719,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F415" t="inlineStr"/>
+      <c r="G415" t="inlineStr"/>
     </row>
     <row r="416" ht="15.75" customHeight="1" s="19">
       <c r="A416" s="8" t="n">
@@ -12468,6 +12746,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F416" t="inlineStr"/>
+      <c r="G416" t="inlineStr"/>
     </row>
     <row r="417" ht="15.75" customHeight="1" s="19">
       <c r="A417" s="8" t="n">
@@ -12493,6 +12773,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F417" t="inlineStr"/>
+      <c r="G417" t="inlineStr"/>
     </row>
     <row r="418" ht="15.75" customHeight="1" s="19">
       <c r="A418" s="8" t="n">
@@ -12518,6 +12800,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>+54 11 4823-6420</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>http://www.thanimalcenter.com/</t>
+        </is>
+      </c>
     </row>
     <row r="419" ht="15.75" customHeight="1" s="19">
       <c r="A419" s="8" t="n">
@@ -12543,6 +12835,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>+54 11 5855-3923</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr"/>
     </row>
     <row r="420" ht="15.75" customHeight="1" s="19">
       <c r="A420" s="8" t="n">
@@ -12568,6 +12866,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>+54 11 7160-1893</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>http://www.casperpetstore.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="421" ht="15.75" customHeight="1" s="19">
       <c r="A421" s="8" t="n">
@@ -12593,6 +12901,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F421" t="inlineStr"/>
+      <c r="G421" t="inlineStr"/>
     </row>
     <row r="422" ht="15.75" customHeight="1" s="19">
       <c r="A422" s="8" t="n">
@@ -12618,6 +12928,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F422" t="inlineStr"/>
+      <c r="G422" t="inlineStr"/>
     </row>
     <row r="423" ht="15.75" customHeight="1" s="19">
       <c r="A423" s="8" t="n">
@@ -12643,6 +12955,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F423" t="inlineStr"/>
+      <c r="G423" t="inlineStr"/>
     </row>
     <row r="424" ht="15.75" customHeight="1" s="19">
       <c r="A424" s="8" t="n">
@@ -12668,6 +12982,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>+54 11 4247-1282</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr"/>
     </row>
     <row r="425" ht="15.75" customHeight="1" s="19">
       <c r="A425" s="8" t="n">
@@ -12693,6 +13013,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>+54 11 4203-7929</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>http://www.veterinariagutierrez.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="426" ht="15.75" customHeight="1" s="19">
       <c r="A426" s="8" t="n">
@@ -12718,6 +13048,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>+54 11 6423-7306</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/veterinarialomasdelsur/?utm_source=ig_web_button_share_sheet&amp;igshid=OGQ5ZDc2ODk2ZA==</t>
+        </is>
+      </c>
     </row>
     <row r="427" ht="15.75" customHeight="1" s="19">
       <c r="A427" s="8" t="n">
@@ -12743,6 +13083,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>+54 11 4353-1811</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr"/>
     </row>
     <row r="428" ht="15.75" customHeight="1" s="19">
       <c r="A428" s="8" t="n">
@@ -12768,6 +13114,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>+54 11 4339-1200</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>http://www.cementosavellaneda.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="429" ht="15.75" customHeight="1" s="19">
       <c r="A429" s="8" t="n">
@@ -12793,6 +13149,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>+54 11 4247-8437</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=100007901895289</t>
+        </is>
+      </c>
     </row>
     <row r="430" ht="15.75" customHeight="1" s="19">
       <c r="A430" s="8" t="n">
@@ -12818,6 +13184,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>+54 11 4096-1876</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/elgobernadorparrilla/</t>
+        </is>
+      </c>
     </row>
     <row r="431" ht="15.75" customHeight="1" s="19">
       <c r="A431" s="8" t="n">
@@ -12843,6 +13219,12 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>+54 11 4246-3762</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr"/>
     </row>
     <row r="432" ht="15.75" customHeight="1" s="19">
       <c r="A432" s="8" t="n">
@@ -12868,6 +13250,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>+54 11 4253-1900</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr"/>
     </row>
     <row r="433" ht="15.75" customHeight="1" s="19">
       <c r="A433" s="8" t="n">
@@ -12893,6 +13281,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>+54 221 423-6476</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>http://www.opticabermudez.com/</t>
+        </is>
+      </c>
     </row>
     <row r="434" ht="15.75" customHeight="1" s="19">
       <c r="A434" s="8" t="n">
@@ -12918,6 +13316,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>+54 221 479-0715</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr"/>
     </row>
     <row r="435" ht="15.75" customHeight="1" s="19">
       <c r="A435" s="8" t="n">
@@ -12943,6 +13347,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>+54 221 470-8239</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr"/>
     </row>
     <row r="436" ht="15.75" customHeight="1" s="19">
       <c r="A436" s="8" t="n">
@@ -12968,6 +13378,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>+54 221 425-6719</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr"/>
     </row>
     <row r="437" ht="15.75" customHeight="1" s="19">
       <c r="A437" s="8" t="n">
@@ -12993,6 +13409,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F437" t="inlineStr"/>
+      <c r="G437" t="inlineStr"/>
     </row>
     <row r="438" ht="15.75" customHeight="1" s="19">
       <c r="A438" s="8" t="n">
@@ -13018,6 +13436,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F438" t="inlineStr"/>
+      <c r="G438" t="inlineStr"/>
     </row>
     <row r="439" ht="15.75" customHeight="1" s="19">
       <c r="A439" s="8" t="n">
@@ -13043,6 +13463,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>+54 221 451-9330</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>http://dnrpa.gov.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="440" ht="15.75" customHeight="1" s="19">
       <c r="A440" s="8" t="n">
@@ -13068,6 +13498,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>+54 221 644-2070</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>http://www.jursoc.unlp.edu.ar</t>
+        </is>
+      </c>
     </row>
     <row r="441" ht="15.75" customHeight="1" s="19">
       <c r="A441" s="8" t="n">
@@ -13093,6 +13533,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F441" t="inlineStr"/>
+      <c r="G441" t="inlineStr"/>
     </row>
     <row r="442" ht="15.75" customHeight="1" s="19">
       <c r="A442" s="8" t="n">
@@ -13118,6 +13560,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F442" t="inlineStr"/>
+      <c r="G442" t="inlineStr"/>
     </row>
     <row r="443" ht="15.75" customHeight="1" s="19">
       <c r="A443" s="8" t="n">
@@ -13143,6 +13587,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>+54 221 201-4775</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr"/>
     </row>
     <row r="444" ht="15.75" customHeight="1" s="19">
       <c r="A444" s="8" t="n">
@@ -13168,6 +13618,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F444" t="inlineStr"/>
+      <c r="G444" t="inlineStr"/>
     </row>
     <row r="445" ht="15.75" customHeight="1" s="19">
       <c r="A445" s="8" t="n">
@@ -13193,6 +13645,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F445" t="inlineStr"/>
+      <c r="G445" t="inlineStr"/>
     </row>
     <row r="446" ht="15.75" customHeight="1" s="19">
       <c r="A446" s="8" t="n">
@@ -13218,6 +13672,12 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>+54 11 3381-2336</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr"/>
     </row>
     <row r="447" ht="15.75" customHeight="1" s="19">
       <c r="A447" s="8" t="n">
@@ -13243,6 +13703,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F447" t="inlineStr"/>
+      <c r="G447" t="inlineStr"/>
     </row>
     <row r="448" ht="15.75" customHeight="1" s="19">
       <c r="A448" s="8" t="n">
@@ -13268,6 +13730,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F448" t="inlineStr"/>
+      <c r="G448" t="inlineStr"/>
     </row>
     <row r="449" ht="15.75" customHeight="1" s="19">
       <c r="A449" s="8" t="n">
@@ -13293,6 +13757,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F449" t="inlineStr"/>
+      <c r="G449" t="inlineStr"/>
     </row>
     <row r="450" ht="15.75" customHeight="1" s="19">
       <c r="A450" s="8" t="n">
@@ -13318,6 +13784,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F450" t="inlineStr"/>
+      <c r="G450" t="inlineStr"/>
     </row>
     <row r="451" ht="15.75" customHeight="1" s="19">
       <c r="A451" s="8" t="n">
@@ -13343,6 +13811,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>+54 11 4295-1850</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr"/>
     </row>
     <row r="452" ht="15.75" customHeight="1" s="19">
       <c r="A452" s="8" t="n">
@@ -13368,6 +13842,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F452" t="inlineStr"/>
+      <c r="G452" t="inlineStr"/>
     </row>
     <row r="453" ht="15.75" customHeight="1" s="19">
       <c r="A453" s="8" t="n">

--- a/PUNTOS_DE_VENTA_completado.xlsx
+++ b/PUNTOS_DE_VENTA_completado.xlsx
@@ -13869,6 +13869,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F453" t="inlineStr"/>
+      <c r="G453" t="inlineStr"/>
     </row>
     <row r="454" ht="15.75" customHeight="1" s="19">
       <c r="A454" s="8" t="n">
@@ -13894,6 +13896,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>+54 11 6698-3024</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr"/>
     </row>
     <row r="455" ht="15.75" customHeight="1" s="19">
       <c r="A455" s="8" t="n">
@@ -13919,6 +13927,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>+54 11 4243-1117</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr"/>
     </row>
     <row r="456" ht="15.75" customHeight="1" s="19">
       <c r="A456" s="8" t="n">
@@ -13944,6 +13958,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F456" t="inlineStr"/>
+      <c r="G456" t="inlineStr"/>
     </row>
     <row r="457" ht="15.75" customHeight="1" s="19">
       <c r="A457" s="8" t="n">
@@ -13969,6 +13985,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F457" t="inlineStr"/>
+      <c r="G457" t="inlineStr"/>
     </row>
     <row r="458" ht="15.75" customHeight="1" s="19">
       <c r="A458" s="8" t="n">
@@ -13994,6 +14012,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F458" t="inlineStr"/>
+      <c r="G458" t="inlineStr"/>
     </row>
     <row r="459" ht="15.75" customHeight="1" s="19">
       <c r="A459" s="8" t="n">
@@ -14019,6 +14039,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>+54 2224 47-0441</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr"/>
     </row>
     <row r="460" ht="15.75" customHeight="1" s="19">
       <c r="A460" s="8" t="n">
@@ -14044,6 +14070,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F460" t="inlineStr"/>
+      <c r="G460" t="inlineStr"/>
     </row>
     <row r="461" ht="15.75" customHeight="1" s="19">
       <c r="A461" s="8" t="n">
@@ -14069,6 +14097,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>+54 11 4232-9911</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr"/>
     </row>
     <row r="462" ht="15.75" customHeight="1" s="19">
       <c r="A462" s="8" t="n">
@@ -14094,6 +14128,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F462" t="inlineStr"/>
+      <c r="G462" t="inlineStr"/>
     </row>
     <row r="463" ht="15.75" customHeight="1" s="19">
       <c r="A463" s="8" t="n">
@@ -14119,6 +14155,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>+54 11 2390-3947</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>https://instagram.com/veterinaria_zazu?igshid=YmMyMTA2M2Y=</t>
+        </is>
+      </c>
     </row>
     <row r="464" ht="15.75" customHeight="1" s="19">
       <c r="A464" s="8" t="n">
@@ -14144,6 +14190,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F464" t="inlineStr"/>
+      <c r="G464" t="inlineStr"/>
     </row>
     <row r="465" ht="15.75" customHeight="1" s="19">
       <c r="A465" s="8" t="n">
@@ -14169,6 +14217,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F465" t="inlineStr"/>
+      <c r="G465" t="inlineStr"/>
     </row>
     <row r="466" ht="15.75" customHeight="1" s="19">
       <c r="A466" s="8" t="n">
@@ -14194,6 +14244,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F466" t="inlineStr"/>
+      <c r="G466" t="inlineStr"/>
     </row>
     <row r="467" ht="15.75" customHeight="1" s="19">
       <c r="A467" s="8" t="n">
@@ -14219,6 +14271,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F467" t="inlineStr"/>
+      <c r="G467" t="inlineStr"/>
     </row>
     <row r="468" ht="15.75" customHeight="1" s="19">
       <c r="A468" s="8" t="n">
@@ -14244,6 +14298,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>+54 11 4245-0131</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr"/>
     </row>
     <row r="469" ht="15.75" customHeight="1" s="19">
       <c r="A469" s="8" t="n">
@@ -14269,6 +14329,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>+54 11 6807-6595</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr"/>
     </row>
     <row r="470" ht="15.75" customHeight="1" s="19">
       <c r="A470" s="8" t="n">
@@ -14294,6 +14360,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>+54 11 4236-3606</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr"/>
     </row>
     <row r="471" ht="15.75" customHeight="1" s="19">
       <c r="A471" s="8" t="n">
@@ -14319,6 +14391,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F471" t="inlineStr"/>
+      <c r="G471" t="inlineStr"/>
     </row>
     <row r="472" ht="15.75" customHeight="1" s="19">
       <c r="A472" s="8" t="n">
@@ -14344,6 +14418,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>+54 11 2701-7285</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr"/>
     </row>
     <row r="473" ht="15.75" customHeight="1" s="19">
       <c r="A473" s="8" t="n">
@@ -14369,6 +14449,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>+54 2224 47-3804</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ElDetalleOk/</t>
+        </is>
+      </c>
     </row>
     <row r="474" ht="15.75" customHeight="1" s="19">
       <c r="A474" s="8" t="n">
@@ -14394,6 +14484,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>+54 11 6377-9708</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr"/>
     </row>
     <row r="475" ht="15.75" customHeight="1" s="19">
       <c r="A475" s="8" t="n">
@@ -14419,6 +14515,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>+54 11 5350-4470</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>https://bit.ly/31xcZ68</t>
+        </is>
+      </c>
     </row>
     <row r="476" ht="15.75" customHeight="1" s="19">
       <c r="A476" s="8" t="n">
@@ -14444,6 +14550,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F476" t="inlineStr"/>
+      <c r="G476" t="inlineStr"/>
     </row>
     <row r="477" ht="15.75" customHeight="1" s="19">
       <c r="A477" s="8" t="n">
@@ -14469,6 +14577,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F477" t="inlineStr"/>
+      <c r="G477" t="inlineStr"/>
     </row>
     <row r="478" ht="15.75" customHeight="1" s="19">
       <c r="A478" s="8" t="n">
@@ -14494,6 +14604,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>+54 9 11 6288-7506</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>https://instagram.com/csabogados</t>
+        </is>
+      </c>
     </row>
     <row r="479" ht="15.75" customHeight="1" s="19">
       <c r="A479" s="8" t="n">
@@ -14519,6 +14639,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F479" t="inlineStr"/>
+      <c r="G479" t="inlineStr"/>
     </row>
     <row r="480" ht="15.75" customHeight="1" s="19">
       <c r="A480" s="8" t="n">
@@ -14544,6 +14666,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>+54 9 11 3761-9825</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/lavetedeluisguillon</t>
+        </is>
+      </c>
     </row>
     <row r="481" ht="15.75" customHeight="1" s="19">
       <c r="A481" s="8" t="n">
@@ -14569,6 +14701,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F481" t="inlineStr"/>
+      <c r="G481" t="inlineStr"/>
     </row>
     <row r="482" ht="15.75" customHeight="1" s="19">
       <c r="A482" s="8" t="n">
@@ -14594,6 +14728,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F482" t="inlineStr"/>
+      <c r="G482" t="inlineStr"/>
     </row>
     <row r="483" ht="15.75" customHeight="1" s="19">
       <c r="A483" s="8" t="n">
@@ -14619,6 +14755,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F483" t="inlineStr"/>
+      <c r="G483" t="inlineStr"/>
     </row>
     <row r="484" ht="15.75" customHeight="1" s="19">
       <c r="A484" s="8" t="n">
@@ -14644,6 +14782,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F484" t="inlineStr"/>
+      <c r="G484" t="inlineStr"/>
     </row>
     <row r="485" ht="15.75" customHeight="1" s="19">
       <c r="A485" s="8" t="n">
@@ -14669,6 +14809,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F485" t="inlineStr"/>
+      <c r="G485" t="inlineStr"/>
     </row>
     <row r="486" ht="15.75" customHeight="1" s="19">
       <c r="A486" s="8" t="n">
@@ -14694,6 +14836,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F486" t="inlineStr"/>
+      <c r="G486" t="inlineStr"/>
     </row>
     <row r="487" ht="15.75" customHeight="1" s="19">
       <c r="A487" s="8" t="n">
@@ -14719,6 +14863,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F487" t="inlineStr"/>
+      <c r="G487" t="inlineStr"/>
     </row>
     <row r="488" ht="15.75" customHeight="1" s="19">
       <c r="A488" s="8" t="n">
@@ -14744,6 +14890,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F488" t="inlineStr"/>
+      <c r="G488" t="inlineStr"/>
     </row>
     <row r="489" ht="15.75" customHeight="1" s="19">
       <c r="A489" s="8" t="n">
@@ -14769,6 +14917,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F489" t="inlineStr"/>
+      <c r="G489" t="inlineStr"/>
     </row>
     <row r="490" ht="15.75" customHeight="1" s="19">
       <c r="A490" s="8" t="n">
@@ -14794,6 +14944,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F490" t="inlineStr"/>
+      <c r="G490" t="inlineStr"/>
     </row>
     <row r="491" ht="15.75" customHeight="1" s="19">
       <c r="A491" s="8" t="n">
@@ -14819,6 +14971,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F491" t="inlineStr"/>
+      <c r="G491" t="inlineStr"/>
     </row>
     <row r="492" ht="15.75" customHeight="1" s="19">
       <c r="A492" s="8" t="n">
@@ -14844,6 +14998,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F492" t="inlineStr"/>
+      <c r="G492" t="inlineStr"/>
     </row>
     <row r="493" ht="15.75" customHeight="1" s="19">
       <c r="A493" s="8" t="n">
@@ -14869,6 +15025,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F493" t="inlineStr"/>
+      <c r="G493" t="inlineStr"/>
     </row>
     <row r="494" ht="15.75" customHeight="1" s="19">
       <c r="A494" s="8" t="n">
@@ -14894,6 +15052,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F494" t="inlineStr"/>
+      <c r="G494" t="inlineStr"/>
     </row>
     <row r="495" ht="15.75" customHeight="1" s="19">
       <c r="A495" s="8" t="n">
@@ -14919,6 +15079,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F495" t="inlineStr"/>
+      <c r="G495" t="inlineStr"/>
     </row>
     <row r="496" ht="15.75" customHeight="1" s="19">
       <c r="A496" s="8" t="n">
@@ -14944,6 +15106,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F496" t="inlineStr"/>
+      <c r="G496" t="inlineStr"/>
     </row>
     <row r="497" ht="15.75" customHeight="1" s="19">
       <c r="A497" s="8" t="n">
@@ -14969,6 +15133,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F497" t="inlineStr"/>
+      <c r="G497" t="inlineStr"/>
     </row>
     <row r="498" ht="15.75" customHeight="1" s="19">
       <c r="A498" s="8" t="n">
@@ -14994,6 +15160,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F498" t="inlineStr"/>
+      <c r="G498" t="inlineStr"/>
     </row>
     <row r="499" ht="15.75" customHeight="1" s="19">
       <c r="A499" s="8" t="n">
@@ -15019,6 +15187,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>+54 11 4925-2203</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>https://www.veterinarias.com.ar/la-cabana-veterinaria.html</t>
+        </is>
+      </c>
     </row>
     <row r="500" ht="15.75" customHeight="1" s="19">
       <c r="A500" s="8" t="n">
@@ -15044,6 +15222,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>+54 11 4896-1270</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr"/>
     </row>
     <row r="501" ht="15.75" customHeight="1" s="19">
       <c r="A501" s="8" t="n">
@@ -15069,6 +15253,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F501" t="inlineStr"/>
+      <c r="G501" t="inlineStr"/>
     </row>
     <row r="502" ht="15.75" customHeight="1" s="19">
       <c r="A502" s="8" t="n">
@@ -15092,6 +15278,16 @@
       <c r="E502" s="8" t="inlineStr">
         <is>
           <t>Veterinaria</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>+54 11 2848-5811</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>https://sites.google.com/view/veterinaria-maure/home</t>
         </is>
       </c>
     </row>

--- a/PUNTOS_DE_VENTA_completado.xlsx
+++ b/PUNTOS_DE_VENTA_completado.xlsx
@@ -15315,6 +15315,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>+54 11 4545-8402</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr"/>
     </row>
     <row r="504" ht="15.75" customHeight="1" s="19">
       <c r="A504" s="8" t="n">
@@ -15340,6 +15346,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F504" t="inlineStr"/>
+      <c r="G504" t="inlineStr"/>
     </row>
     <row r="505" ht="15.75" customHeight="1" s="19">
       <c r="A505" s="8" t="n">
@@ -15365,6 +15373,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F505" t="inlineStr"/>
+      <c r="G505" t="inlineStr"/>
     </row>
     <row r="506" ht="15.75" customHeight="1" s="19">
       <c r="A506" s="8" t="n">
@@ -15390,6 +15400,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>+54 21444243</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>http://www.veterinarias.com.ar/alfa-veterinaria.html</t>
+        </is>
+      </c>
     </row>
     <row r="507" ht="15.75" customHeight="1" s="19">
       <c r="A507" s="8" t="n">
@@ -15415,6 +15435,16 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>+54 11 2558-9916</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>https://fratoj.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="508" ht="15.75" customHeight="1" s="19">
       <c r="A508" s="8" t="n">
@@ -15440,6 +15470,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>+54 11 4568-9927</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>http://www.veterinarias.com.ar/de-simone-clinica-veterinaria</t>
+        </is>
+      </c>
     </row>
     <row r="509" ht="15.75" customHeight="1" s="19">
       <c r="A509" s="8" t="n">
@@ -15465,6 +15505,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>+54 11 4741-2818</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>https://wa.me/message/FSHH5NLHRK5BL1</t>
+        </is>
+      </c>
     </row>
     <row r="510" ht="15.75" customHeight="1" s="19">
       <c r="A510" s="8" t="n">
@@ -15490,6 +15540,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>+54 11 5844-5085</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr"/>
     </row>
     <row r="511" ht="15.75" customHeight="1" s="19">
       <c r="A511" s="8" t="n">
@@ -15515,6 +15571,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>+54 11 4722-0965</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr"/>
     </row>
     <row r="512" ht="15.75" customHeight="1" s="19">
       <c r="A512" s="8" t="n">
@@ -15540,6 +15602,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>+54 11 4747-6452</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr"/>
     </row>
     <row r="513" ht="15.75" customHeight="1" s="19">
       <c r="A513" s="8" t="n">
@@ -15565,6 +15633,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>+54 11 6541-5678</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/reinamadreespacio/</t>
+        </is>
+      </c>
     </row>
     <row r="514" ht="15.75" customHeight="1" s="19">
       <c r="A514" s="8" t="n">
@@ -15590,6 +15668,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>+54 11 5852-1007</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>https://wa.me/5491158521007</t>
+        </is>
+      </c>
     </row>
     <row r="515" ht="15.75" customHeight="1" s="19">
       <c r="A515" s="8" t="n">
@@ -15615,6 +15703,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>+54 11 6380-7666</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>https://cumellen.com/</t>
+        </is>
+      </c>
     </row>
     <row r="516" ht="15.75" customHeight="1" s="19">
       <c r="A516" s="8" t="n">
@@ -15640,6 +15738,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F516" t="inlineStr"/>
+      <c r="G516" t="inlineStr"/>
     </row>
     <row r="517" ht="15.75" customHeight="1" s="19">
       <c r="A517" s="8" t="n">
@@ -15665,6 +15765,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F517" t="inlineStr"/>
+      <c r="G517" t="inlineStr"/>
     </row>
     <row r="518" ht="15.75" customHeight="1" s="19">
       <c r="A518" s="8" t="n">
@@ -15690,6 +15792,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>+54 11 3164-8780</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr"/>
     </row>
     <row r="519" ht="15.75" customHeight="1" s="19">
       <c r="A519" s="8" t="n">
@@ -15715,6 +15823,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>+54 11 5250-9102</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr"/>
     </row>
     <row r="520" ht="15.75" customHeight="1" s="19">
       <c r="A520" s="8" t="n">
@@ -15740,6 +15854,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F520" t="inlineStr"/>
+      <c r="G520" t="inlineStr"/>
     </row>
     <row r="521" ht="15.75" customHeight="1" s="19">
       <c r="A521" s="8" t="n">
@@ -15761,6 +15877,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F521" t="inlineStr"/>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>http://www.argentina.gob.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="522" ht="15.75" customHeight="1" s="19">
       <c r="A522" s="8" t="n">
@@ -15786,6 +15908,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>+54 11 4726-1897</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr"/>
     </row>
     <row r="523" ht="15.75" customHeight="1" s="19">
       <c r="A523" s="8" t="n">
@@ -15811,6 +15939,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F523" t="inlineStr"/>
+      <c r="G523" t="inlineStr"/>
     </row>
     <row r="524" ht="15.75" customHeight="1" s="19">
       <c r="A524" s="8" t="n">
@@ -15836,6 +15966,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F524" t="inlineStr"/>
+      <c r="G524" t="inlineStr"/>
     </row>
     <row r="525" ht="15.75" customHeight="1" s="19">
       <c r="A525" s="8" t="n">
@@ -15861,6 +15993,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F525" t="inlineStr"/>
+      <c r="G525" t="inlineStr"/>
     </row>
     <row r="526" ht="15.75" customHeight="1" s="19">
       <c r="A526" s="8" t="n">
@@ -15886,6 +16020,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F526" t="inlineStr"/>
+      <c r="G526" t="inlineStr"/>
     </row>
     <row r="527" ht="15.75" customHeight="1" s="19">
       <c r="A527" s="8" t="n">
@@ -15911,6 +16047,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F527" t="inlineStr"/>
+      <c r="G527" t="inlineStr"/>
     </row>
     <row r="528" ht="15.75" customHeight="1" s="19">
       <c r="A528" s="8" t="n">
@@ -15936,6 +16074,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>+54 11 2397-2567</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>https://veterinariadelascabañas.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="529" ht="15.75" customHeight="1" s="19">
       <c r="A529" s="8" t="n">
@@ -15961,6 +16109,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>+54 263 435-8848</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/floridacafebistro/</t>
+        </is>
+      </c>
     </row>
     <row r="530" ht="15.75" customHeight="1" s="19">
       <c r="A530" s="8" t="n">
@@ -15986,6 +16144,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F530" t="inlineStr"/>
+      <c r="G530" t="inlineStr"/>
     </row>
     <row r="531" ht="15.75" customHeight="1" s="19">
       <c r="A531" s="8" t="n">
@@ -16011,6 +16171,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>+54 11 4846-9245</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>https://www.docturno.com/gm/lirios-del-talar-grupo-medico</t>
+        </is>
+      </c>
     </row>
     <row r="532" ht="15.75" customHeight="1" s="19">
       <c r="A532" s="8" t="n">
@@ -16036,6 +16206,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>+54 11 4790-0614</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr"/>
     </row>
     <row r="533" ht="15.75" customHeight="1" s="19">
       <c r="A533" s="8" t="n">
@@ -16061,6 +16237,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F533" t="inlineStr"/>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nuestro.haedo/</t>
+        </is>
+      </c>
     </row>
     <row r="534" ht="15.75" customHeight="1" s="19">
       <c r="A534" s="8" t="n">
@@ -16086,6 +16268,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F534" t="inlineStr"/>
+      <c r="G534" t="inlineStr"/>
     </row>
     <row r="535" ht="15.75" customHeight="1" s="19">
       <c r="A535" s="8" t="n">
@@ -16111,6 +16295,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F535" t="inlineStr"/>
+      <c r="G535" t="inlineStr"/>
     </row>
     <row r="536" ht="15.75" customHeight="1" s="19">
       <c r="A536" s="8" t="n">
@@ -16136,6 +16322,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F536" t="inlineStr"/>
+      <c r="G536" t="inlineStr"/>
     </row>
     <row r="537" ht="15.75" customHeight="1" s="19">
       <c r="A537" s="8" t="n">
@@ -16161,6 +16349,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F537" t="inlineStr"/>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/osterbrocafe?igsh=NWVocHV0ZHBpdGFs</t>
+        </is>
+      </c>
     </row>
     <row r="538" ht="15.75" customHeight="1" s="19">
       <c r="A538" s="8" t="n">
@@ -16186,6 +16380,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F538" t="inlineStr"/>
+      <c r="G538" t="inlineStr"/>
     </row>
     <row r="539" ht="15.75" customHeight="1" s="19">
       <c r="A539" s="8" t="n">
@@ -16211,6 +16407,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F539" t="inlineStr"/>
+      <c r="G539" t="inlineStr"/>
     </row>
     <row r="540" ht="15.75" customHeight="1" s="19">
       <c r="A540" s="8" t="n">
@@ -16236,6 +16434,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>+54 2323 49-2230</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr"/>
     </row>
     <row r="541" ht="15.75" customHeight="1" s="19">
       <c r="A541" s="8" t="n">
@@ -16261,6 +16465,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F541" t="inlineStr"/>
+      <c r="G541" t="inlineStr"/>
     </row>
     <row r="542" ht="15.75" customHeight="1" s="19">
       <c r="A542" s="8" t="n">
@@ -16286,6 +16492,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F542" t="inlineStr"/>
+      <c r="G542" t="inlineStr"/>
     </row>
     <row r="543" ht="15.75" customHeight="1" s="19">
       <c r="A543" s="8" t="n">
@@ -16311,6 +16519,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F543" t="inlineStr"/>
+      <c r="G543" t="inlineStr"/>
     </row>
     <row r="544" ht="15.75" customHeight="1" s="19">
       <c r="A544" s="8" t="n">
@@ -16336,6 +16546,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>+54 11 7900-8954</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>https://www.vismileok.com/</t>
+        </is>
+      </c>
     </row>
     <row r="545" ht="15.75" customHeight="1" s="19">
       <c r="A545" s="8" t="n">
@@ -16361,6 +16581,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>+54 11 4756-4311</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr"/>
     </row>
     <row r="546" ht="15.75" customHeight="1" s="19">
       <c r="A546" s="8" t="n">
@@ -16386,6 +16612,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F546" t="inlineStr"/>
+      <c r="G546" t="inlineStr"/>
     </row>
     <row r="547" ht="15.75" customHeight="1" s="19">
       <c r="A547" s="8" t="n">
@@ -16411,6 +16639,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F547" t="inlineStr"/>
+      <c r="G547" t="inlineStr"/>
     </row>
     <row r="548" ht="15.75" customHeight="1" s="19">
       <c r="A548" s="8" t="n">
@@ -16436,6 +16666,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F548" t="inlineStr"/>
+      <c r="G548" t="inlineStr"/>
     </row>
     <row r="549" ht="15.75" customHeight="1" s="19">
       <c r="A549" s="8" t="n">
@@ -16461,6 +16693,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F549" t="inlineStr"/>
+      <c r="G549" t="inlineStr"/>
     </row>
     <row r="550" ht="15.75" customHeight="1" s="19">
       <c r="A550" s="8" t="n">
@@ -16486,6 +16720,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>+54 11 4790-2450</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr"/>
     </row>
     <row r="551" ht="15.75" customHeight="1" s="19">
       <c r="A551" s="8" t="n">
@@ -16511,6 +16751,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F551" t="inlineStr"/>
+      <c r="G551" t="inlineStr"/>
     </row>
     <row r="552" ht="15.75" customHeight="1" s="19">
       <c r="A552" s="8" t="n">
@@ -16536,6 +16778,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>+54 11 2257-3956</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr"/>
     </row>
     <row r="553" ht="15.75" customHeight="1" s="19">
       <c r="A553" s="8" t="n">
@@ -16561,6 +16809,16 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>+54 9 11 6971-0196</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>http://parquecabred.com.ar/%20-%20http://https://raizcriolla.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="554" ht="15.75" customHeight="1" s="19">
       <c r="A554" s="8" t="n">
@@ -16586,6 +16844,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F554" t="inlineStr"/>
+      <c r="G554" t="inlineStr"/>
     </row>
     <row r="555" ht="15.75" customHeight="1" s="19">
       <c r="A555" s="8" t="n">
@@ -16611,6 +16871,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F555" t="inlineStr"/>
+      <c r="G555" t="inlineStr"/>
     </row>
     <row r="556" ht="15.75" customHeight="1" s="19">
       <c r="A556" s="8" t="n">
@@ -16636,6 +16898,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>+54 11 3016-2593</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>https://newgarden.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="557" ht="15.75" customHeight="1" s="19">
       <c r="A557" s="8" t="n">
@@ -16661,6 +16933,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>+54 47467739</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr"/>
     </row>
     <row r="558" ht="15.75" customHeight="1" s="19">
       <c r="A558" s="8" t="n">
@@ -16686,6 +16964,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F558" t="inlineStr"/>
+      <c r="G558" t="inlineStr"/>
     </row>
     <row r="559" ht="15.75" customHeight="1" s="19">
       <c r="A559" s="8" t="n">
@@ -16711,6 +16991,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F559" t="inlineStr"/>
+      <c r="G559" t="inlineStr"/>
     </row>
     <row r="560" ht="15.75" customHeight="1" s="19">
       <c r="A560" s="8" t="n">
@@ -16736,6 +17018,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F560" t="inlineStr"/>
+      <c r="G560" t="inlineStr"/>
     </row>
     <row r="561" ht="15.75" customHeight="1" s="19">
       <c r="A561" s="8" t="n">
@@ -16761,6 +17045,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F561" t="inlineStr"/>
+      <c r="G561" t="inlineStr"/>
     </row>
     <row r="562" ht="15.75" customHeight="1" s="19">
       <c r="A562" s="8" t="n">
@@ -16786,6 +17072,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>+54 3487 68-4488</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>https://muebleriaconestilo.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="563" ht="15.75" customHeight="1" s="19">
       <c r="A563" s="8" t="n">
@@ -16811,6 +17107,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F563" t="inlineStr"/>
+      <c r="G563" t="inlineStr"/>
     </row>
     <row r="564" ht="15.75" customHeight="1" s="19">
       <c r="A564" s="8" t="n">
@@ -16836,6 +17134,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>+54 3487 44-0645</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>https://www.cemevetcentromedicoveterinario.com/</t>
+        </is>
+      </c>
     </row>
     <row r="565" ht="15.75" customHeight="1" s="19">
       <c r="A565" s="8" t="n">
@@ -16861,6 +17169,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F565" t="inlineStr"/>
+      <c r="G565" t="inlineStr"/>
     </row>
     <row r="566" ht="15.75" customHeight="1" s="19">
       <c r="A566" s="8" t="n">
@@ -16886,6 +17196,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F566" t="inlineStr"/>
+      <c r="G566" t="inlineStr"/>
     </row>
     <row r="567" ht="15.75" customHeight="1" s="19">
       <c r="A567" s="8" t="n">
@@ -16911,6 +17223,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>+54 3487 63-0563</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr"/>
     </row>
     <row r="568" ht="15.75" customHeight="1" s="19">
       <c r="A568" s="8" t="n">
@@ -16936,6 +17254,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F568" t="inlineStr"/>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>http://www.veterinariazarate.com/</t>
+        </is>
+      </c>
     </row>
     <row r="569" ht="15.75" customHeight="1" s="19">
       <c r="A569" s="8" t="n">
@@ -16961,6 +17285,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>+54 3487 30-7524</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr"/>
     </row>
     <row r="570" ht="15.75" customHeight="1" s="19">
       <c r="A570" s="8" t="n">
@@ -16986,6 +17316,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>+54 11 2465-4123</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr"/>
     </row>
     <row r="571" ht="15.75" customHeight="1" s="19">
       <c r="A571" s="8" t="n">
@@ -17011,6 +17347,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>+54 11 4723-2580</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr"/>
     </row>
     <row r="572" ht="15.75" customHeight="1" s="19">
       <c r="A572" s="8" t="n">
@@ -17036,6 +17378,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>+54 11 3085-3706</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>http://www.facebook.com/consultoriosmedicossanisidro</t>
+        </is>
+      </c>
     </row>
     <row r="573" ht="15.75" customHeight="1" s="19">
       <c r="A573" s="8" t="n">
@@ -17061,6 +17413,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F573" t="inlineStr"/>
+      <c r="G573" t="inlineStr"/>
     </row>
     <row r="574" ht="15.75" customHeight="1" s="19">
       <c r="A574" s="8" t="n">
@@ -17086,6 +17440,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>+54 11 4412-0148</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr"/>
     </row>
     <row r="575" ht="15.75" customHeight="1" s="19">
       <c r="A575" s="8" t="n">
@@ -17111,6 +17471,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F575" t="inlineStr"/>
+      <c r="G575" t="inlineStr"/>
     </row>
     <row r="576" ht="15.75" customHeight="1" s="19">
       <c r="A576" s="8" t="n">
@@ -17136,6 +17498,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F576" t="inlineStr"/>
+      <c r="G576" t="inlineStr"/>
     </row>
     <row r="577" ht="15.75" customHeight="1" s="19">
       <c r="A577" s="8" t="n">
@@ -17161,6 +17525,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>+54 348 442-1431</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr"/>
     </row>
     <row r="578" ht="15.75" customHeight="1" s="19">
       <c r="A578" s="8" t="n">
@@ -17186,6 +17556,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F578" t="inlineStr"/>
+      <c r="G578" t="inlineStr"/>
     </row>
     <row r="579" ht="15.75" customHeight="1" s="19">
       <c r="A579" s="8" t="n">
@@ -17211,6 +17583,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F579" t="inlineStr"/>
+      <c r="G579" t="inlineStr"/>
     </row>
     <row r="580" ht="15.75" customHeight="1" s="19">
       <c r="A580" s="8" t="n">
@@ -17236,6 +17610,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F580" t="inlineStr"/>
+      <c r="G580" t="inlineStr"/>
     </row>
     <row r="581" ht="15.75" customHeight="1" s="19">
       <c r="A581" s="8" t="n">
@@ -17261,6 +17637,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>+54 11 3141-4940</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>https://vetlandbaires.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="582" ht="15.75" customHeight="1" s="19">
       <c r="A582" s="8" t="n">
@@ -17286,6 +17672,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>+54 11 4709-1599</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr"/>
     </row>
     <row r="583" ht="15.75" customHeight="1" s="19">
       <c r="A583" s="8" t="n">
@@ -17311,6 +17703,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F583" t="inlineStr"/>
+      <c r="G583" t="inlineStr"/>
     </row>
     <row r="584" ht="15.75" customHeight="1" s="19">
       <c r="A584" s="8" t="n">
@@ -17336,6 +17730,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F584" t="inlineStr"/>
+      <c r="G584" t="inlineStr"/>
     </row>
     <row r="585" ht="15.75" customHeight="1" s="19">
       <c r="A585" s="8" t="n">
@@ -17361,6 +17757,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>+54 348 441-5006</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>https://taplink.cc/aikenlaundry</t>
+        </is>
+      </c>
     </row>
     <row r="586" ht="15.75" customHeight="1" s="19">
       <c r="A586" s="8" t="n">
@@ -17382,6 +17788,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>+54 9 11 3198-4300</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>http://www.rodriguezjurado.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="587" ht="15.75" customHeight="1" s="19">
       <c r="A587" s="8" t="n">
@@ -17407,6 +17823,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F587" t="inlineStr"/>
+      <c r="G587" t="inlineStr"/>
     </row>
     <row r="588" ht="15.75" customHeight="1" s="19">
       <c r="A588" s="8" t="n">
@@ -17432,6 +17850,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>+54 11 4791-0895</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr"/>
     </row>
     <row r="589" ht="15.75" customHeight="1" s="19">
       <c r="A589" s="8" t="n">
@@ -17457,6 +17881,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>+54 3489 43-6663</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>https://veterinarialuquez.mitiendanube.com/</t>
+        </is>
+      </c>
     </row>
     <row r="590" ht="15.75" customHeight="1" s="19">
       <c r="A590" s="8" t="n">
@@ -17482,6 +17916,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F590" t="inlineStr"/>
+      <c r="G590" t="inlineStr"/>
     </row>
     <row r="591" ht="15.75" customHeight="1" s="19">
       <c r="A591" s="8" t="n">
@@ -17507,6 +17943,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F591" t="inlineStr"/>
+      <c r="G591" t="inlineStr"/>
     </row>
     <row r="592" ht="15.75" customHeight="1" s="19">
       <c r="A592" s="8" t="n">
@@ -17532,6 +17970,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F592" t="inlineStr"/>
+      <c r="G592" t="inlineStr"/>
     </row>
     <row r="593" ht="15.75" customHeight="1" s="19">
       <c r="A593" s="8" t="n">
@@ -17557,6 +17997,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F593" t="inlineStr"/>
+      <c r="G593" t="inlineStr"/>
     </row>
     <row r="594" ht="15.75" customHeight="1" s="19">
       <c r="A594" s="8" t="n">
@@ -17582,6 +18024,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>+54 3489 42-0939</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/veterinarialabarthe/?hl=es</t>
+        </is>
+      </c>
     </row>
     <row r="595" ht="15.75" customHeight="1" s="19">
       <c r="A595" s="8" t="n">
@@ -17607,6 +18059,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F595" t="inlineStr"/>
+      <c r="G595" t="inlineStr"/>
     </row>
     <row r="596" ht="15.75" customHeight="1" s="19">
       <c r="A596" s="8" t="n">
@@ -17632,6 +18086,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F596" t="inlineStr"/>
+      <c r="G596" t="inlineStr"/>
     </row>
     <row r="597" ht="15.75" customHeight="1" s="19">
       <c r="A597" s="8" t="n">
@@ -17657,6 +18113,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>+54 11 5470-6642</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr"/>
     </row>
     <row r="598" ht="15.75" customHeight="1" s="19">
       <c r="A598" s="8" t="n">
@@ -17682,6 +18144,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>+54 3489 29-6736</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr"/>
     </row>
     <row r="599" ht="15.75" customHeight="1" s="19">
       <c r="A599" s="8" t="n">
@@ -17707,6 +18175,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F599" t="inlineStr"/>
+      <c r="G599" t="inlineStr"/>
     </row>
     <row r="600" ht="15.75" customHeight="1" s="19">
       <c r="A600" s="8" t="n">
@@ -17732,6 +18202,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F600" t="inlineStr"/>
+      <c r="G600" t="inlineStr"/>
     </row>
     <row r="601" ht="15.75" customHeight="1" s="19">
       <c r="A601" s="8" t="n">
@@ -17757,6 +18229,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F601" t="inlineStr"/>
+      <c r="G601" t="inlineStr"/>
     </row>
     <row r="602" ht="15.75" customHeight="1" s="19">
       <c r="A602" s="8" t="n">
@@ -17782,6 +18256,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F602" t="inlineStr"/>
+      <c r="G602" t="inlineStr"/>
     </row>
     <row r="603" ht="15.75" customHeight="1" s="19">
       <c r="A603" s="8" t="n">

--- a/PUNTOS_DE_VENTA_completado.xlsx
+++ b/PUNTOS_DE_VENTA_completado.xlsx
@@ -18283,6 +18283,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>+54 11 2249-8686</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr"/>
     </row>
     <row r="604" ht="15.75" customHeight="1" s="19">
       <c r="A604" s="8" t="n">
@@ -18308,6 +18314,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F604" t="inlineStr"/>
+      <c r="G604" t="inlineStr"/>
     </row>
     <row r="605" ht="15.75" customHeight="1" s="19">
       <c r="A605" s="8" t="n">
@@ -18333,6 +18341,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F605" t="inlineStr"/>
+      <c r="G605" t="inlineStr"/>
     </row>
     <row r="606" ht="15.75" customHeight="1" s="19">
       <c r="A606" s="8" t="n">
@@ -18358,6 +18368,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F606" t="inlineStr"/>
+      <c r="G606" t="inlineStr"/>
     </row>
     <row r="607" ht="15.75" customHeight="1" s="19">
       <c r="A607" s="8" t="n">
@@ -18383,6 +18395,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F607" t="inlineStr"/>
+      <c r="G607" t="inlineStr"/>
     </row>
     <row r="608" ht="15.75" customHeight="1" s="19">
       <c r="A608" s="8" t="n">
@@ -18408,6 +18422,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F608" t="inlineStr"/>
+      <c r="G608" t="inlineStr"/>
     </row>
     <row r="609" ht="15.75" customHeight="1" s="19">
       <c r="A609" s="8" t="n">
@@ -18433,6 +18449,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F609" t="inlineStr"/>
+      <c r="G609" t="inlineStr"/>
     </row>
     <row r="610" ht="15.75" customHeight="1" s="19">
       <c r="A610" s="8" t="n">
@@ -18458,6 +18476,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F610" t="inlineStr"/>
+      <c r="G610" t="inlineStr"/>
     </row>
     <row r="611" ht="15.75" customHeight="1" s="19">
       <c r="A611" s="8" t="n">
@@ -18483,6 +18503,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F611" t="inlineStr"/>
+      <c r="G611" t="inlineStr"/>
     </row>
     <row r="612" ht="15.75" customHeight="1" s="19">
       <c r="A612" s="8" t="n">
@@ -18508,6 +18530,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F612" t="inlineStr"/>
+      <c r="G612" t="inlineStr"/>
     </row>
     <row r="613" ht="15.75" customHeight="1" s="19">
       <c r="A613" s="8" t="n">
@@ -18533,6 +18557,12 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>+54 11 2281-2655</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr"/>
     </row>
     <row r="614" ht="15.75" customHeight="1" s="19">
       <c r="A614" s="8" t="n">
@@ -18558,6 +18588,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F614" t="inlineStr"/>
+      <c r="G614" t="inlineStr"/>
     </row>
     <row r="615" ht="15.75" customHeight="1" s="19">
       <c r="A615" s="8" t="n">
@@ -18583,6 +18615,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F615" t="inlineStr"/>
+      <c r="G615" t="inlineStr"/>
     </row>
     <row r="616" ht="15.75" customHeight="1" s="19">
       <c r="A616" s="8" t="n">
@@ -18608,6 +18642,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>+54 47778877</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vete.pets/</t>
+        </is>
+      </c>
     </row>
     <row r="617" ht="15.75" customHeight="1" s="19">
       <c r="A617" s="8" t="n">
@@ -18633,6 +18677,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F617" t="inlineStr"/>
+      <c r="G617" t="inlineStr"/>
     </row>
     <row r="618" ht="15.75" customHeight="1" s="19">
       <c r="A618" s="8" t="n">
@@ -18658,6 +18704,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F618" t="inlineStr"/>
+      <c r="G618" t="inlineStr"/>
     </row>
     <row r="619" ht="15.75" customHeight="1" s="19">
       <c r="A619" s="8" t="n">
@@ -18683,6 +18731,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F619" t="inlineStr"/>
+      <c r="G619" t="inlineStr"/>
     </row>
     <row r="620" ht="15.75" customHeight="1" s="19">
       <c r="A620" s="8" t="n">
@@ -18708,6 +18758,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>+54 11 5350-0205</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr"/>
     </row>
     <row r="621" ht="15.75" customHeight="1" s="19">
       <c r="A621" s="8" t="n">
@@ -18733,6 +18789,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>+54 11 6976-2819</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr"/>
     </row>
     <row r="622" ht="15.75" customHeight="1" s="19">
       <c r="A622" s="8" t="n">
@@ -18758,6 +18820,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F622" t="inlineStr"/>
+      <c r="G622" t="inlineStr"/>
     </row>
     <row r="623" ht="15.75" customHeight="1" s="19">
       <c r="A623" s="8" t="n">
@@ -18783,6 +18847,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F623" t="inlineStr"/>
+      <c r="G623" t="inlineStr"/>
     </row>
     <row r="624" ht="15.75" customHeight="1" s="19">
       <c r="A624" s="8" t="n">
@@ -18808,6 +18874,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F624" t="inlineStr"/>
+      <c r="G624" t="inlineStr"/>
     </row>
     <row r="625" ht="15.75" customHeight="1" s="19">
       <c r="A625" s="8" t="n">
@@ -18833,6 +18901,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>+54 11 2648-2524</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>http://www.chuna.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="626" ht="15.75" customHeight="1" s="19">
       <c r="A626" s="8" t="n">
@@ -18858,6 +18936,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F626" t="inlineStr"/>
+      <c r="G626" t="inlineStr"/>
     </row>
     <row r="627" ht="15.75" customHeight="1" s="19">
       <c r="A627" s="8" t="n">
@@ -18883,6 +18963,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F627" t="inlineStr"/>
+      <c r="G627" t="inlineStr"/>
     </row>
     <row r="628" ht="15.75" customHeight="1" s="19">
       <c r="A628" s="8" t="n">
@@ -18908,6 +18990,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F628" t="inlineStr"/>
+      <c r="G628" t="inlineStr"/>
     </row>
     <row r="629" ht="15.75" customHeight="1" s="19">
       <c r="A629" s="8" t="n">
@@ -18933,6 +19017,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F629" t="inlineStr"/>
+      <c r="G629" t="inlineStr"/>
     </row>
     <row r="630" ht="15.75" customHeight="1" s="19">
       <c r="A630" s="8" t="n">
@@ -18958,6 +19044,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F630" t="inlineStr"/>
+      <c r="G630" t="inlineStr"/>
     </row>
     <row r="631" ht="15.75" customHeight="1" s="19">
       <c r="A631" s="8" t="n">
@@ -18983,6 +19071,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>+54 2323 42-1070</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>https://santuariodelujan.org.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="632" ht="15.75" customHeight="1" s="19">
       <c r="A632" s="8" t="n">
@@ -19008,6 +19106,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F632" t="inlineStr"/>
+      <c r="G632" t="inlineStr"/>
     </row>
     <row r="633" ht="15.75" customHeight="1" s="19">
       <c r="A633" s="8" t="n">
@@ -19033,6 +19133,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F633" t="inlineStr"/>
+      <c r="G633" t="inlineStr"/>
     </row>
     <row r="634" ht="15.75" customHeight="1" s="19">
       <c r="A634" s="8" t="n">
@@ -19058,6 +19160,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>+54 2323 42-3733</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr"/>
     </row>
     <row r="635" ht="15.75" customHeight="1" s="19">
       <c r="A635" s="8" t="n">
@@ -19083,6 +19191,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>+54 2323 43-3990</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>http://agrimensortornatore.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="636" ht="15.75" customHeight="1" s="19">
       <c r="A636" s="8" t="n">
@@ -19108,6 +19226,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>+54 11 6090-3007</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>http://www.swissmedical.com/</t>
+        </is>
+      </c>
     </row>
     <row r="637" ht="15.75" customHeight="1" s="19">
       <c r="A637" s="8" t="n">
@@ -19133,6 +19261,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F637" t="inlineStr"/>
+      <c r="G637" t="inlineStr"/>
     </row>
     <row r="638" ht="15.75" customHeight="1" s="19">
       <c r="A638" s="8" t="n">
@@ -19158,6 +19288,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F638" t="inlineStr"/>
+      <c r="G638" t="inlineStr"/>
     </row>
     <row r="639" ht="15.75" customHeight="1" s="19">
       <c r="A639" s="8" t="n">
@@ -19183,6 +19315,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F639" t="inlineStr"/>
+      <c r="G639" t="inlineStr"/>
     </row>
     <row r="640" ht="15.75" customHeight="1" s="19">
       <c r="A640" s="8" t="n">
@@ -19208,6 +19342,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F640" t="inlineStr"/>
+      <c r="G640" t="inlineStr"/>
     </row>
     <row r="641" ht="15.75" customHeight="1" s="19">
       <c r="A641" s="8" t="n">
@@ -19233,6 +19369,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F641" t="inlineStr"/>
+      <c r="G641" t="inlineStr"/>
     </row>
     <row r="642" ht="15.75" customHeight="1" s="19">
       <c r="A642" s="8" t="n">
@@ -19258,6 +19396,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>+54 11 4703-2191</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr"/>
     </row>
     <row r="643" ht="15.75" customHeight="1" s="19">
       <c r="A643" s="8" t="n">
@@ -19283,6 +19427,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F643" t="inlineStr"/>
+      <c r="G643" t="inlineStr"/>
     </row>
     <row r="644" ht="15.75" customHeight="1" s="19">
       <c r="A644" s="8" t="n">
@@ -19308,6 +19454,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F644" t="inlineStr"/>
+      <c r="G644" t="inlineStr"/>
     </row>
     <row r="645" ht="15.75" customHeight="1" s="19">
       <c r="A645" s="8" t="n">
@@ -19333,6 +19481,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>+54 11 5356-2246</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vetsanbenito/</t>
+        </is>
+      </c>
     </row>
     <row r="646" ht="15.75" customHeight="1" s="19">
       <c r="A646" s="8" t="n">
@@ -19358,6 +19516,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F646" t="inlineStr"/>
+      <c r="G646" t="inlineStr"/>
     </row>
     <row r="647" ht="15.75" customHeight="1" s="19">
       <c r="A647" s="8" t="n">
@@ -19383,6 +19543,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>+54 2323 43-3318</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr"/>
     </row>
     <row r="648" ht="15.75" customHeight="1" s="19">
       <c r="A648" s="8" t="n">
@@ -19408,6 +19574,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>+54 2323 42-2776</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>http://www.rattohnos.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="649" ht="15.75" customHeight="1" s="19">
       <c r="A649" s="8" t="n">
@@ -19433,6 +19609,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>+54 11 4085-6083</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>https://www.pauladallochio.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="650" ht="15.75" customHeight="1" s="19">
       <c r="A650" s="8" t="n">
@@ -19458,6 +19644,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F650" t="inlineStr"/>
+      <c r="G650" t="inlineStr"/>
     </row>
     <row r="651" ht="15.75" customHeight="1" s="19">
       <c r="A651" s="8" t="n">
@@ -19483,6 +19671,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F651" t="inlineStr"/>
+      <c r="G651" t="inlineStr"/>
     </row>
     <row r="652" ht="15.75" customHeight="1" s="19">
       <c r="A652" s="8" t="n">
@@ -19508,6 +19698,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F652" t="inlineStr"/>
+      <c r="G652" t="inlineStr"/>
     </row>
     <row r="653" ht="15.75" customHeight="1" s="19">
       <c r="A653" s="8" t="n">
@@ -19533,6 +19725,12 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>+54 348 425-5936</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr"/>
     </row>
     <row r="654" ht="15.75" customHeight="1" s="19">
       <c r="A654" s="8" t="n">
@@ -19558,6 +19756,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F654" t="inlineStr"/>
+      <c r="G654" t="inlineStr"/>
     </row>
     <row r="655" ht="15.75" customHeight="1" s="19">
       <c r="A655" s="8" t="n">
@@ -19583,6 +19783,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F655" t="inlineStr"/>
+      <c r="G655" t="inlineStr"/>
     </row>
     <row r="656" ht="15.75" customHeight="1" s="19">
       <c r="A656" s="8" t="n">
@@ -19608,6 +19810,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>+54 11 4809-6300</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>http://hirsch.org.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="657" ht="15.75" customHeight="1" s="19">
       <c r="A657" s="8" t="n">
@@ -19633,6 +19845,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F657" t="inlineStr"/>
+      <c r="G657" t="inlineStr"/>
     </row>
     <row r="658" ht="15.75" customHeight="1" s="19">
       <c r="A658" s="8" t="n">
@@ -19658,6 +19872,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F658" t="inlineStr"/>
+      <c r="G658" t="inlineStr"/>
     </row>
     <row r="659" ht="15.75" customHeight="1" s="19">
       <c r="A659" s="8" t="n">
@@ -19683,6 +19899,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>+54 11 4782-9079</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>http://www.veterinarias.com.ar/centro-medico-veterinario-belgrano</t>
+        </is>
+      </c>
     </row>
     <row r="660" ht="15.75" customHeight="1" s="19">
       <c r="A660" s="8" t="n">
@@ -19708,6 +19934,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>+54 11 4770-9106</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>http://www.ecolux.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="661" ht="15.75" customHeight="1" s="19">
       <c r="A661" s="8" t="n">
@@ -19733,6 +19969,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>+54 11 4781-8886</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr"/>
     </row>
     <row r="662" ht="15.75" customHeight="1" s="19">
       <c r="A662" s="8" t="n">
@@ -19758,6 +20000,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F662" t="inlineStr"/>
+      <c r="G662" t="inlineStr"/>
     </row>
     <row r="663" ht="15.75" customHeight="1" s="19">
       <c r="A663" s="8" t="n">
@@ -19783,6 +20027,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F663" t="inlineStr"/>
+      <c r="G663" t="inlineStr"/>
     </row>
     <row r="664" ht="15.75" customHeight="1" s="19">
       <c r="A664" s="8" t="n">
@@ -19808,6 +20054,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F664" t="inlineStr"/>
+      <c r="G664" t="inlineStr"/>
     </row>
     <row r="665" ht="15.75" customHeight="1" s="19">
       <c r="A665" s="8" t="n">
@@ -19833,6 +20081,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F665" t="inlineStr"/>
+      <c r="G665" t="inlineStr"/>
     </row>
     <row r="666" ht="15.75" customHeight="1" s="19">
       <c r="A666" s="8" t="n">
@@ -19858,6 +20108,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>+54 11 2261-6733</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>http://vetturno.com/veterinaria-whippet/reservar</t>
+        </is>
+      </c>
     </row>
     <row r="667" ht="15.75" customHeight="1" s="19">
       <c r="A667" s="8" t="n">
@@ -19883,6 +20143,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>+54 11 4785-5566</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>http://www.leocan.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="668" ht="15.75" customHeight="1" s="19">
       <c r="A668" s="8" t="n">
@@ -19908,6 +20178,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F668" t="inlineStr"/>
+      <c r="G668" t="inlineStr"/>
     </row>
     <row r="669" ht="15.75" customHeight="1" s="19">
       <c r="A669" s="8" t="n">
@@ -19933,6 +20205,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F669" t="inlineStr"/>
+      <c r="G669" t="inlineStr"/>
     </row>
     <row r="670" ht="15.75" customHeight="1" s="19">
       <c r="A670" s="8" t="n">
@@ -19958,6 +20232,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F670" t="inlineStr"/>
+      <c r="G670" t="inlineStr"/>
     </row>
     <row r="671" ht="15.75" customHeight="1" s="19">
       <c r="A671" s="8" t="n">
@@ -19983,6 +20259,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F671" t="inlineStr"/>
+      <c r="G671" t="inlineStr"/>
     </row>
     <row r="672" ht="15.75" customHeight="1" s="19">
       <c r="A672" s="8" t="n">
@@ -20008,6 +20286,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F672" t="inlineStr"/>
+      <c r="G672" t="inlineStr"/>
     </row>
     <row r="673" ht="15.75" customHeight="1" s="19">
       <c r="A673" s="8" t="n">
@@ -20033,6 +20313,12 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>+54 11 6625-7594</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr"/>
     </row>
     <row r="674" ht="15.75" customHeight="1" s="19">
       <c r="A674" s="8" t="n">
@@ -20058,6 +20344,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F674" t="inlineStr"/>
+      <c r="G674" t="inlineStr"/>
     </row>
     <row r="675" ht="15.75" customHeight="1" s="19">
       <c r="A675" s="8" t="n">
@@ -20083,6 +20371,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F675" t="inlineStr"/>
+      <c r="G675" t="inlineStr"/>
     </row>
     <row r="676" ht="15.75" customHeight="1" s="19">
       <c r="A676" s="8" t="n">
@@ -20108,6 +20398,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F676" t="inlineStr"/>
+      <c r="G676" t="inlineStr"/>
     </row>
     <row r="677" ht="15.75" customHeight="1" s="19">
       <c r="A677" s="8" t="n">
@@ -20133,6 +20425,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F677" t="inlineStr"/>
+      <c r="G677" t="inlineStr"/>
     </row>
     <row r="678" ht="15.75" customHeight="1" s="19">
       <c r="A678" s="8" t="n">
@@ -20158,6 +20452,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F678" t="inlineStr"/>
+      <c r="G678" t="inlineStr"/>
     </row>
     <row r="679" ht="15.75" customHeight="1" s="19">
       <c r="A679" s="8" t="n">
@@ -20183,6 +20479,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F679" t="inlineStr"/>
+      <c r="G679" t="inlineStr"/>
     </row>
     <row r="680" ht="15.75" customHeight="1" s="19">
       <c r="A680" s="8" t="n">
@@ -20208,6 +20506,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F680" t="inlineStr"/>
+      <c r="G680" t="inlineStr"/>
     </row>
     <row r="681" ht="15.75" customHeight="1" s="19">
       <c r="A681" s="8" t="n">
@@ -20233,6 +20533,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>+54 11 4826-3552</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr"/>
     </row>
     <row r="682" ht="15.75" customHeight="1" s="19">
       <c r="A682" s="8" t="n">
@@ -20258,6 +20564,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>+54 11 5636-6495</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/veterinariabengolea</t>
+        </is>
+      </c>
     </row>
     <row r="683" ht="15.75" customHeight="1" s="19">
       <c r="A683" s="8" t="n">
@@ -20283,6 +20599,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F683" t="inlineStr"/>
+      <c r="G683" t="inlineStr"/>
     </row>
     <row r="684" ht="15.75" customHeight="1" s="19">
       <c r="A684" s="8" t="n">
@@ -20308,6 +20626,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F684" t="inlineStr"/>
+      <c r="G684" t="inlineStr"/>
     </row>
     <row r="685" ht="15.75" customHeight="1" s="19">
       <c r="A685" s="8" t="n">
@@ -20333,6 +20653,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>+54 11 2191-8679</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/veterinariorobertofara/</t>
+        </is>
+      </c>
     </row>
     <row r="686" ht="15.75" customHeight="1" s="19">
       <c r="A686" s="8" t="n">
@@ -20358,6 +20688,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>+54 11 4788-4167</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>https://odontologiaortodoncia-com-ar.webnode.page/</t>
+        </is>
+      </c>
     </row>
     <row r="687" ht="15.75" customHeight="1" s="19">
       <c r="A687" s="8" t="n">
@@ -20383,6 +20723,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F687" t="inlineStr"/>
+      <c r="G687" t="inlineStr"/>
     </row>
     <row r="688" ht="15.75" customHeight="1" s="19">
       <c r="A688" s="8" t="n">
@@ -20408,6 +20750,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F688" t="inlineStr"/>
+      <c r="G688" t="inlineStr"/>
     </row>
     <row r="689" ht="15.75" customHeight="1" s="19">
       <c r="A689" s="8" t="n">
@@ -20433,6 +20777,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F689" t="inlineStr"/>
+      <c r="G689" t="inlineStr"/>
     </row>
     <row r="690" ht="15.75" customHeight="1" s="19">
       <c r="A690" s="8" t="n">
@@ -20458,6 +20804,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>+54 9 11 3642-4030</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fisiovetpalermoba/?hl=es-la</t>
+        </is>
+      </c>
     </row>
     <row r="691" ht="15.75" customHeight="1" s="19">
       <c r="A691" s="8" t="n">
@@ -20479,6 +20835,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F691" t="inlineStr"/>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>http://www.argentina.gob.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="692" ht="15.75" customHeight="1" s="19">
       <c r="A692" s="8" t="n">
@@ -20504,6 +20866,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>+54 11 2137-8498</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>https://allsports.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="693" ht="15.75" customHeight="1" s="19">
       <c r="A693" s="8" t="n">
@@ -20529,6 +20901,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>+54 221 429-1000</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>https://www.laplata.gob.ar/#/</t>
+        </is>
+      </c>
     </row>
     <row r="694" ht="15.75" customHeight="1" s="19">
       <c r="A694" s="8" t="n">
@@ -20554,6 +20936,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>+54 11 4355-2263</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr"/>
     </row>
     <row r="695" ht="15.75" customHeight="1" s="19">
       <c r="A695" s="8" t="n">
@@ -20579,6 +20967,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>+54 221 423-4415</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr"/>
     </row>
     <row r="696" ht="15.75" customHeight="1" s="19">
       <c r="A696" s="8" t="n">
@@ -20604,6 +20998,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F696" t="inlineStr"/>
+      <c r="G696" t="inlineStr"/>
     </row>
     <row r="697" ht="15.75" customHeight="1" s="19">
       <c r="A697" s="8" t="n">
@@ -20629,6 +21025,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>+54 11 4216-7055</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>http://veterinariacalvo.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="698" ht="15.75" customHeight="1" s="19">
       <c r="A698" s="8" t="n">
@@ -20654,6 +21060,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F698" t="inlineStr"/>
+      <c r="G698" t="inlineStr"/>
     </row>
     <row r="699" ht="15.75" customHeight="1" s="19">
       <c r="A699" s="8" t="n">
@@ -20679,6 +21087,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F699" t="inlineStr"/>
+      <c r="G699" t="inlineStr"/>
     </row>
     <row r="700" ht="15.75" customHeight="1" s="19">
       <c r="A700" s="8" t="n">
@@ -20704,6 +21114,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F700" t="inlineStr"/>
+      <c r="G700" t="inlineStr"/>
     </row>
     <row r="701" ht="15.75" customHeight="1" s="19">
       <c r="A701" s="8" t="n">
@@ -20729,6 +21141,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F701" t="inlineStr"/>
+      <c r="G701" t="inlineStr"/>
     </row>
     <row r="702" ht="15.75" customHeight="1" s="19">
       <c r="A702" s="8" t="n">
@@ -20754,6 +21168,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F702" t="inlineStr"/>
+      <c r="G702" t="inlineStr"/>
     </row>
     <row r="703" ht="15.75" customHeight="1" s="19">
       <c r="A703" s="8" t="n">

--- a/PUNTOS_DE_VENTA_completado.xlsx
+++ b/PUNTOS_DE_VENTA_completado.xlsx
@@ -21195,6 +21195,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F703" t="inlineStr"/>
+      <c r="G703" t="inlineStr"/>
     </row>
     <row r="704" ht="15.75" customHeight="1" s="19">
       <c r="A704" s="8" t="n">
@@ -21220,6 +21222,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F704" t="inlineStr"/>
+      <c r="G704" t="inlineStr"/>
     </row>
     <row r="705" ht="15.75" customHeight="1" s="19">
       <c r="A705" s="8" t="n">
@@ -21245,6 +21249,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F705" t="inlineStr"/>
+      <c r="G705" t="inlineStr"/>
     </row>
     <row r="706" ht="15.75" customHeight="1" s="19">
       <c r="A706" s="8" t="n">
@@ -21270,6 +21276,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F706" t="inlineStr"/>
+      <c r="G706" t="inlineStr"/>
     </row>
     <row r="707" ht="15.75" customHeight="1" s="19">
       <c r="A707" s="8" t="n">
@@ -21295,6 +21303,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F707" t="inlineStr"/>
+      <c r="G707" t="inlineStr"/>
     </row>
     <row r="708" ht="15.75" customHeight="1" s="19">
       <c r="A708" s="8" t="n">
@@ -21320,6 +21330,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F708" t="inlineStr"/>
+      <c r="G708" t="inlineStr"/>
     </row>
     <row r="709" ht="15.75" customHeight="1" s="19">
       <c r="A709" s="8" t="n">
@@ -21345,6 +21357,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>+54 348 443-5700</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>https://www.google.com.ar/url?sa=t&amp;source=web&amp;rct=j&amp;url=https://www.jtekt.co.jp/e/company/global.html&amp;ved=0ahUKEwi6y7ugm-DRAhWCj5AKHepqDZEQFggkMAE&amp;usg=AFQjCNEYzzkQAjYHg-WKNXFpbBgPzPbdsA</t>
+        </is>
+      </c>
     </row>
     <row r="710" ht="15.75" customHeight="1" s="19">
       <c r="A710" s="8" t="n">
@@ -21370,6 +21392,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F710" t="inlineStr"/>
+      <c r="G710" t="inlineStr"/>
     </row>
     <row r="711" ht="15.75" customHeight="1" s="19">
       <c r="A711" s="8" t="n">
@@ -21395,6 +21419,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>+54 11 4765-8032</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr"/>
     </row>
     <row r="712" ht="15.75" customHeight="1" s="19">
       <c r="A712" s="8" t="n">
@@ -21420,6 +21450,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F712" t="inlineStr"/>
+      <c r="G712" t="inlineStr"/>
     </row>
     <row r="713" ht="15.75" customHeight="1" s="19">
       <c r="A713" s="8" t="n">
@@ -21445,6 +21477,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>+54 11 4867-3165</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr"/>
     </row>
     <row r="714" ht="15.75" customHeight="1" s="19">
       <c r="A714" s="8" t="n">
@@ -21470,6 +21508,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F714" t="inlineStr"/>
+      <c r="G714" t="inlineStr"/>
     </row>
     <row r="715" ht="15.75" customHeight="1" s="19">
       <c r="A715" s="8" t="n">
@@ -21495,6 +21535,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>+54 11 7894-7307</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>http://mariatranchida.vet/</t>
+        </is>
+      </c>
     </row>
     <row r="716" ht="15.75" customHeight="1" s="19">
       <c r="A716" s="8" t="n">
@@ -21520,6 +21570,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F716" t="inlineStr"/>
+      <c r="G716" t="inlineStr"/>
     </row>
     <row r="717" ht="15.75" customHeight="1" s="19">
       <c r="A717" s="8" t="n">
@@ -21545,6 +21597,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>+54 11 4556-5002</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>https://instagram.com/veterinaria.amvet?igshid=1nx33nslwwcas</t>
+        </is>
+      </c>
     </row>
     <row r="718" ht="15.75" customHeight="1" s="19">
       <c r="A718" s="8" t="n">
@@ -21570,6 +21632,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>+54 11 4553-4925</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr"/>
     </row>
     <row r="719" ht="15.75" customHeight="1" s="19">
       <c r="A719" s="8" t="n">
@@ -21595,6 +21663,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>+54 11 4574-1788</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr"/>
     </row>
     <row r="720" ht="15.75" customHeight="1" s="19">
       <c r="A720" s="8" t="n">
@@ -21620,6 +21694,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>+54 11 4927-0295</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr"/>
     </row>
     <row r="721" ht="15.75" customHeight="1" s="19">
       <c r="A721" s="8" t="n">
@@ -21645,6 +21725,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F721" t="inlineStr"/>
+      <c r="G721" t="inlineStr"/>
     </row>
     <row r="722" ht="15.75" customHeight="1" s="19">
       <c r="A722" s="8" t="n">
@@ -21670,6 +21752,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F722" t="inlineStr"/>
+      <c r="G722" t="inlineStr"/>
     </row>
     <row r="723" ht="15.75" customHeight="1" s="19">
       <c r="A723" s="8" t="n">
@@ -21695,6 +21779,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F723" t="inlineStr"/>
+      <c r="G723" t="inlineStr"/>
     </row>
     <row r="724" ht="15.75" customHeight="1" s="19">
       <c r="A724" s="8" t="n">
@@ -21720,6 +21806,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>+54 11 2068-1255</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr"/>
     </row>
     <row r="725" ht="15.75" customHeight="1" s="19">
       <c r="A725" s="8" t="n">
@@ -21745,6 +21837,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F725" t="inlineStr"/>
+      <c r="G725" t="inlineStr"/>
     </row>
     <row r="726" ht="15.75" customHeight="1" s="19">
       <c r="A726" s="8" t="n">
@@ -21770,6 +21864,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>+54 810-220-7276</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>https://www.gruposaporiti.com/</t>
+        </is>
+      </c>
     </row>
     <row r="727" ht="15.75" customHeight="1" s="19">
       <c r="A727" s="8" t="n">
@@ -21795,6 +21899,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>+54 11 6023-7922</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>https://menu.fu.do/planetroll</t>
+        </is>
+      </c>
     </row>
     <row r="728" ht="15.75" customHeight="1" s="19">
       <c r="A728" s="8" t="n">
@@ -21820,6 +21934,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F728" t="inlineStr"/>
+      <c r="G728" t="inlineStr"/>
     </row>
     <row r="729" ht="15.75" customHeight="1" s="19">
       <c r="A729" s="8" t="n">
@@ -21845,6 +21961,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>+54 11 4581-8771</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>http://www.veterinarias.com.ar/raggio-veterinaria</t>
+        </is>
+      </c>
     </row>
     <row r="730" ht="15.75" customHeight="1" s="19">
       <c r="A730" s="8" t="n">
@@ -21870,6 +21996,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F730" t="inlineStr"/>
+      <c r="G730" t="inlineStr"/>
     </row>
     <row r="731" ht="15.75" customHeight="1" s="19">
       <c r="A731" s="8" t="n">
@@ -21895,6 +22023,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F731" t="inlineStr"/>
+      <c r="G731" t="inlineStr"/>
     </row>
     <row r="732" ht="15.75" customHeight="1" s="19">
       <c r="A732" s="8" t="n">
@@ -21920,6 +22050,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F732" t="inlineStr"/>
+      <c r="G732" t="inlineStr"/>
     </row>
     <row r="733" ht="15.75" customHeight="1" s="19">
       <c r="A733" s="8" t="n">
@@ -21945,6 +22077,16 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>+34 671 48 22 51</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>https://www.institutobiologico.com/</t>
+        </is>
+      </c>
     </row>
     <row r="734" ht="15.75" customHeight="1" s="19">
       <c r="A734" s="8" t="n">
@@ -21970,6 +22112,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>+54 2954 66-4994</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>http://pintureriarossotto.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="735" ht="15.75" customHeight="1" s="19">
       <c r="A735" s="8" t="n">
@@ -21995,6 +22147,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F735" t="inlineStr"/>
+      <c r="G735" t="inlineStr"/>
     </row>
     <row r="736" ht="15.75" customHeight="1" s="19">
       <c r="A736" s="8" t="n">
@@ -22020,6 +22174,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F736" t="inlineStr"/>
+      <c r="G736" t="inlineStr"/>
     </row>
     <row r="737" ht="15.75" customHeight="1" s="19">
       <c r="A737" s="8" t="n">
@@ -22045,6 +22201,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F737" t="inlineStr"/>
+      <c r="G737" t="inlineStr"/>
     </row>
     <row r="738" ht="15.75" customHeight="1" s="19">
       <c r="A738" s="8" t="n">
@@ -22070,6 +22228,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>+54 11 4554-1849</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>http://www.veterinarias.com.ar/san-roque-veterinaria</t>
+        </is>
+      </c>
     </row>
     <row r="739" ht="15.75" customHeight="1" s="19">
       <c r="A739" s="8" t="n">
@@ -22095,6 +22263,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>+54 9 11 6511-0324</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>http://www.instintosveterinaria.com/</t>
+        </is>
+      </c>
     </row>
     <row r="740" ht="15.75" customHeight="1" s="19">
       <c r="A740" s="8" t="n">
@@ -22120,6 +22298,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>+54 11 4572-0094</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>http://www.veterinarias.com.ar/anzelini-natalia-veterinaria.html</t>
+        </is>
+      </c>
     </row>
     <row r="741" ht="15.75" customHeight="1" s="19">
       <c r="A741" s="8" t="n">
@@ -22145,6 +22333,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F741" t="inlineStr"/>
+      <c r="G741" t="inlineStr"/>
     </row>
     <row r="742" ht="15.75" customHeight="1" s="19">
       <c r="A742" s="8" t="n">
@@ -22170,6 +22360,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F742" t="inlineStr"/>
+      <c r="G742" t="inlineStr"/>
     </row>
     <row r="743" ht="15.75" customHeight="1" s="19">
       <c r="A743" s="8" t="n">
@@ -22195,6 +22387,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>+54 221 471-4388</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>https://trudys.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="744" ht="15.75" customHeight="1" s="19">
       <c r="A744" s="8" t="n">
@@ -22220,6 +22422,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F744" t="inlineStr"/>
+      <c r="G744" t="inlineStr"/>
     </row>
     <row r="745" ht="15.75" customHeight="1" s="19">
       <c r="A745" s="8" t="n">
@@ -22245,6 +22449,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F745" t="inlineStr"/>
+      <c r="G745" t="inlineStr"/>
     </row>
     <row r="746" ht="15.75" customHeight="1" s="19">
       <c r="A746" s="8" t="n">
@@ -22270,6 +22476,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F746" t="inlineStr"/>
+      <c r="G746" t="inlineStr"/>
     </row>
     <row r="747" ht="15.75" customHeight="1" s="19">
       <c r="A747" s="8" t="n">
@@ -22295,6 +22503,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>+54 221 471-4388</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>https://trudys.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="748" ht="15.75" customHeight="1" s="19">
       <c r="A748" s="8" t="n">
@@ -22320,6 +22538,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F748" t="inlineStr"/>
+      <c r="G748" t="inlineStr"/>
     </row>
     <row r="749" ht="15.75" customHeight="1" s="19">
       <c r="A749" s="8" t="n">
@@ -22345,6 +22565,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F749" t="inlineStr"/>
+      <c r="G749" t="inlineStr"/>
     </row>
     <row r="750" ht="15.75" customHeight="1" s="19">
       <c r="A750" s="8" t="n">
@@ -22370,6 +22592,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F750" t="inlineStr"/>
+      <c r="G750" t="inlineStr"/>
     </row>
     <row r="751" ht="15.75" customHeight="1" s="19">
       <c r="A751" s="8" t="n">
@@ -22395,6 +22619,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F751" t="inlineStr"/>
+      <c r="G751" t="inlineStr"/>
     </row>
     <row r="752" ht="15.75" customHeight="1" s="19">
       <c r="A752" s="8" t="n">
@@ -22418,6 +22644,16 @@
       <c r="E752" s="8" t="inlineStr">
         <is>
           <t>Veterinaria</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>+54 11 5574-5654</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>https://gabrielafernandez.com.ar/</t>
         </is>
       </c>
     </row>

--- a/PUNTOS_DE_VENTA_completado.xlsx
+++ b/PUNTOS_DE_VENTA_completado.xlsx
@@ -22681,6 +22681,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F753" t="inlineStr"/>
+      <c r="G753" t="inlineStr"/>
     </row>
     <row r="754" ht="15.75" customHeight="1" s="19">
       <c r="A754" s="8" t="n">
@@ -22706,6 +22708,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F754" t="inlineStr"/>
+      <c r="G754" t="inlineStr"/>
     </row>
     <row r="755" ht="15.75" customHeight="1" s="19">
       <c r="A755" s="8" t="n">
@@ -22731,6 +22735,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F755" t="inlineStr"/>
+      <c r="G755" t="inlineStr"/>
     </row>
     <row r="756" ht="15.75" customHeight="1" s="19">
       <c r="A756" s="8" t="n">
@@ -22756,6 +22762,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F756" t="inlineStr"/>
+      <c r="G756" t="inlineStr"/>
     </row>
     <row r="757" ht="15.75" customHeight="1" s="19">
       <c r="A757" s="8" t="n">
@@ -22781,6 +22789,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F757" t="inlineStr"/>
+      <c r="G757" t="inlineStr"/>
     </row>
     <row r="758" ht="15.75" customHeight="1" s="19">
       <c r="A758" s="8" t="n">
@@ -22806,6 +22816,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F758" t="inlineStr"/>
+      <c r="G758" t="inlineStr"/>
     </row>
     <row r="759" ht="15.75" customHeight="1" s="19">
       <c r="A759" s="8" t="n">
@@ -22831,6 +22843,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F759" t="inlineStr"/>
+      <c r="G759" t="inlineStr"/>
     </row>
     <row r="760" ht="15.75" customHeight="1" s="19">
       <c r="A760" s="8" t="n">
@@ -22856,6 +22870,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F760" t="inlineStr"/>
+      <c r="G760" t="inlineStr"/>
     </row>
     <row r="761" ht="15.75" customHeight="1" s="19">
       <c r="A761" s="8" t="n">
@@ -22881,6 +22897,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F761" t="inlineStr"/>
+      <c r="G761" t="inlineStr"/>
     </row>
     <row r="762" ht="15.75" customHeight="1" s="19">
       <c r="A762" s="8" t="n">
@@ -22906,6 +22924,16 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>+54 11 2095-0024</t>
+        </is>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>http://www.ammaturo.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="763" ht="15.75" customHeight="1" s="19">
       <c r="A763" s="8" t="n">
@@ -22931,6 +22959,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F763" t="inlineStr"/>
+      <c r="G763" t="inlineStr"/>
     </row>
     <row r="764" ht="15.75" customHeight="1" s="19">
       <c r="A764" s="8" t="n">
@@ -22956,6 +22986,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F764" t="inlineStr"/>
+      <c r="G764" t="inlineStr"/>
     </row>
     <row r="765" ht="15.75" customHeight="1" s="19">
       <c r="A765" s="8" t="n">
@@ -22981,6 +23013,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>+54 11 4568-9305</t>
+        </is>
+      </c>
+      <c r="G765" t="inlineStr"/>
     </row>
     <row r="766" ht="15.75" customHeight="1" s="19">
       <c r="A766" s="8" t="n">
@@ -23006,6 +23044,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F766" t="inlineStr"/>
+      <c r="G766" t="inlineStr"/>
     </row>
     <row r="767" ht="15.75" customHeight="1" s="19">
       <c r="A767" s="8" t="n">
@@ -23031,6 +23071,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F767" t="inlineStr"/>
+      <c r="G767" t="inlineStr"/>
     </row>
     <row r="768" ht="15.75" customHeight="1" s="19">
       <c r="A768" s="8" t="n">
@@ -23056,6 +23098,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>+54 11 4855-3629</t>
+        </is>
+      </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>https://www.veterinarias.com.ar/baamonde-veterinaria.html</t>
+        </is>
+      </c>
     </row>
     <row r="769" ht="15.75" customHeight="1" s="19">
       <c r="A769" s="8" t="n">
@@ -23081,6 +23133,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F769" t="inlineStr"/>
+      <c r="G769" t="inlineStr"/>
     </row>
     <row r="770" ht="15.75" customHeight="1" s="19">
       <c r="A770" s="8" t="n">
@@ -23106,6 +23160,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F770" t="inlineStr"/>
+      <c r="G770" t="inlineStr"/>
     </row>
     <row r="771" ht="15.75" customHeight="1" s="19">
       <c r="A771" s="8" t="n">
@@ -23131,6 +23187,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>+54 11 4632-5632</t>
+        </is>
+      </c>
+      <c r="G771" t="inlineStr"/>
     </row>
     <row r="772" ht="15.75" customHeight="1" s="19">
       <c r="A772" s="8" t="n">
@@ -23156,6 +23218,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>+54 9 11 2876-7545</t>
+        </is>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/espaciosimpleeventos/?hl=es</t>
+        </is>
+      </c>
     </row>
     <row r="773" ht="15.75" customHeight="1" s="19">
       <c r="A773" s="8" t="n">
@@ -23181,6 +23253,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F773" t="inlineStr"/>
+      <c r="G773" t="inlineStr"/>
     </row>
     <row r="774" ht="15.75" customHeight="1" s="19">
       <c r="A774" s="8" t="n">
@@ -23206,6 +23280,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>+54 387 421-0257</t>
+        </is>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>http://www.facundodezuviria8037.com/</t>
+        </is>
+      </c>
     </row>
     <row r="775" ht="15.75" customHeight="1" s="19">
       <c r="A775" s="8" t="n">
@@ -23231,6 +23315,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>+54 9 11 6879-9990</t>
+        </is>
+      </c>
+      <c r="G775" t="inlineStr"/>
     </row>
     <row r="776" ht="15.75" customHeight="1" s="19">
       <c r="A776" s="8" t="n">
@@ -23256,6 +23346,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F776" t="inlineStr"/>
+      <c r="G776" t="inlineStr"/>
     </row>
     <row r="777" ht="15.75" customHeight="1" s="19">
       <c r="A777" s="8" t="n">
@@ -23281,6 +23373,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>+54 11 4666-5972</t>
+        </is>
+      </c>
+      <c r="G777" t="inlineStr"/>
     </row>
     <row r="778" ht="15.75" customHeight="1" s="19">
       <c r="A778" s="8" t="n">
@@ -23306,6 +23404,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>+54 11 7063-9538</t>
+        </is>
+      </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>https://instagram.com/paunerovet?igshid=YmMyMTA2M2Y=</t>
+        </is>
+      </c>
     </row>
     <row r="779" ht="15.75" customHeight="1" s="19">
       <c r="A779" s="8" t="n">
@@ -23331,6 +23439,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F779" t="inlineStr"/>
+      <c r="G779" t="inlineStr"/>
     </row>
     <row r="780" ht="15.75" customHeight="1" s="19">
       <c r="A780" s="8" t="n">
@@ -23356,6 +23466,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F780" t="inlineStr"/>
+      <c r="G780" t="inlineStr"/>
     </row>
     <row r="781" ht="15.75" customHeight="1" s="19">
       <c r="A781" s="8" t="n">
@@ -23381,6 +23493,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>+54 11 6432-7602</t>
+        </is>
+      </c>
+      <c r="G781" t="inlineStr"/>
     </row>
     <row r="782" ht="15.75" customHeight="1" s="19">
       <c r="A782" s="8" t="n">
@@ -23406,6 +23524,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>+54 11 4625-2822</t>
+        </is>
+      </c>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vetecasanova?utm_source=ig_web_button_share_sheet&amp;igsh=ZDNlZDc0MzIxNw==</t>
+        </is>
+      </c>
     </row>
     <row r="783" ht="15.75" customHeight="1" s="19">
       <c r="A783" s="8" t="n">
@@ -23431,6 +23559,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>+54 11 3167-7237</t>
+        </is>
+      </c>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/larotisseriecastelar/</t>
+        </is>
+      </c>
     </row>
     <row r="784" ht="15.75" customHeight="1" s="19">
       <c r="A784" s="8" t="n">
@@ -23456,6 +23594,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F784" t="inlineStr"/>
+      <c r="G784" t="inlineStr"/>
     </row>
     <row r="785" ht="15.75" customHeight="1" s="19">
       <c r="A785" s="8" t="n">
@@ -23481,6 +23621,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>+54 11 4657-6871</t>
+        </is>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>http://www.hvo.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="786" ht="15.75" customHeight="1" s="19">
       <c r="A786" s="8" t="n">
@@ -23506,6 +23656,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F786" t="inlineStr"/>
+      <c r="G786" t="inlineStr"/>
     </row>
     <row r="787" ht="15.75" customHeight="1" s="19">
       <c r="A787" s="8" t="n">
@@ -23531,6 +23683,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>+54 11 4699-3364</t>
+        </is>
+      </c>
+      <c r="G787" t="inlineStr"/>
     </row>
     <row r="788" ht="15.75" customHeight="1" s="19">
       <c r="A788" s="8" t="n">
@@ -23556,6 +23714,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F788" t="inlineStr"/>
+      <c r="G788" t="inlineStr"/>
     </row>
     <row r="789" ht="15.75" customHeight="1" s="19">
       <c r="A789" s="8" t="n">
@@ -23581,6 +23741,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>+54 11 2362-2027</t>
+        </is>
+      </c>
+      <c r="G789" t="inlineStr"/>
     </row>
     <row r="790" ht="15.75" customHeight="1" s="19">
       <c r="A790" s="8" t="n">
@@ -23606,6 +23772,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F790" t="inlineStr"/>
+      <c r="G790" t="inlineStr"/>
     </row>
     <row r="791" ht="15.75" customHeight="1" s="19">
       <c r="A791" s="8" t="n">
@@ -23631,6 +23799,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F791" t="inlineStr"/>
+      <c r="G791" t="inlineStr"/>
     </row>
     <row r="792" ht="15.75" customHeight="1" s="19">
       <c r="A792" s="8" t="n">
@@ -23656,6 +23826,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F792" t="inlineStr"/>
+      <c r="G792" t="inlineStr"/>
     </row>
     <row r="793" ht="15.75" customHeight="1" s="19">
       <c r="A793" s="8" t="n">
@@ -23681,6 +23853,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F793" t="inlineStr"/>
+      <c r="G793" t="inlineStr"/>
     </row>
     <row r="794" ht="15.75" customHeight="1" s="19">
       <c r="A794" s="8" t="n">
@@ -23706,6 +23880,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F794" t="inlineStr"/>
+      <c r="G794" t="inlineStr"/>
     </row>
     <row r="795" ht="15.75" customHeight="1" s="19">
       <c r="A795" s="8" t="n">
@@ -23731,6 +23907,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>+54 11 3089-7291</t>
+        </is>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>https://m.facebook.com/aramisyolivia</t>
+        </is>
+      </c>
     </row>
     <row r="796" ht="15.75" customHeight="1" s="19">
       <c r="A796" s="8" t="n">
@@ -23756,6 +23942,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>+54 9 11 5952-8646</t>
+        </is>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>https://mariaachaval.com/</t>
+        </is>
+      </c>
     </row>
     <row r="797" ht="15.75" customHeight="1" s="19">
       <c r="A797" s="8" t="n">
@@ -23781,6 +23977,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F797" t="inlineStr"/>
+      <c r="G797" t="inlineStr"/>
     </row>
     <row r="798" ht="15.75" customHeight="1" s="19">
       <c r="A798" s="8" t="n">
@@ -23806,6 +24004,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>+54 11 4658-4232</t>
+        </is>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>https://clinicaveterinariarinaldividal.lovable.app/</t>
+        </is>
+      </c>
     </row>
     <row r="799" ht="15.75" customHeight="1" s="19">
       <c r="A799" s="8" t="n">
@@ -23831,6 +24039,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F799" t="inlineStr"/>
+      <c r="G799" t="inlineStr"/>
     </row>
     <row r="800" ht="15.75" customHeight="1" s="19">
       <c r="A800" s="8" t="n">
@@ -23856,6 +24066,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F800" t="inlineStr"/>
+      <c r="G800" t="inlineStr"/>
     </row>
     <row r="801" ht="15.75" customHeight="1" s="19">
       <c r="A801" s="8" t="n">
@@ -23881,6 +24093,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>+54 11 7079-1234</t>
+        </is>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>https://centro-pet.mercadoshops.com.ar/criadero</t>
+        </is>
+      </c>
     </row>
     <row r="802" ht="15.75" customHeight="1" s="19">
       <c r="A802" s="8" t="n">
@@ -23906,6 +24128,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>+54 11 4522-8103</t>
+        </is>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>https://www.profesionalvet.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="803" ht="15.75" customHeight="1" s="19">
       <c r="A803" s="8" t="n">
@@ -23931,6 +24163,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F803" t="inlineStr"/>
+      <c r="G803" t="inlineStr"/>
     </row>
     <row r="804" ht="15.75" customHeight="1" s="19">
       <c r="A804" s="8" t="n">
@@ -23956,6 +24190,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>+54 11 4521-5600</t>
+        </is>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>https://www.profesionalvet.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="805" ht="15.75" customHeight="1" s="19">
       <c r="A805" s="8" t="n">
@@ -23981,6 +24225,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F805" t="inlineStr"/>
+      <c r="G805" t="inlineStr"/>
     </row>
     <row r="806" ht="15.75" customHeight="1" s="19">
       <c r="A806" s="8" t="n">
@@ -24006,6 +24252,16 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>+54 11 5437-5471</t>
+        </is>
+      </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>http://www.trusoni.com/</t>
+        </is>
+      </c>
     </row>
     <row r="807" ht="15.75" customHeight="1" s="19">
       <c r="A807" s="8" t="n">
@@ -24031,6 +24287,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>+54 11 4806-4758</t>
+        </is>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>http://www.veterinariasebastian.com/</t>
+        </is>
+      </c>
     </row>
     <row r="808" ht="15.75" customHeight="1" s="19">
       <c r="A808" s="8" t="n">
@@ -24056,6 +24322,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F808" t="inlineStr"/>
+      <c r="G808" t="inlineStr"/>
     </row>
     <row r="809" ht="15.75" customHeight="1" s="19">
       <c r="A809" s="8" t="n">
@@ -24081,6 +24349,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F809" t="inlineStr"/>
+      <c r="G809" t="inlineStr"/>
     </row>
     <row r="810" ht="15.75" customHeight="1" s="19">
       <c r="A810" s="8" t="n">
@@ -24106,6 +24376,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F810" t="inlineStr"/>
+      <c r="G810" t="inlineStr"/>
     </row>
     <row r="811" ht="15.75" customHeight="1" s="19">
       <c r="A811" s="8" t="n">
@@ -24131,6 +24403,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>+54 11 4217-0969</t>
+        </is>
+      </c>
+      <c r="G811" t="inlineStr"/>
     </row>
     <row r="812" ht="15.75" customHeight="1" s="19">
       <c r="A812" s="8" t="n">
@@ -24156,6 +24434,12 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>+54 11 4222-0909</t>
+        </is>
+      </c>
+      <c r="G812" t="inlineStr"/>
     </row>
     <row r="813" ht="15.75" customHeight="1" s="19">
       <c r="A813" s="8" t="n">
@@ -24181,6 +24465,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>+54 11 3887-7207</t>
+        </is>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>https://www.nuevohanasono.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="814" ht="15.75" customHeight="1" s="19">
       <c r="A814" s="8" t="n">
@@ -24206,6 +24500,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>+54 11 6001-3894</t>
+        </is>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/asambleapetshop/</t>
+        </is>
+      </c>
     </row>
     <row r="815" ht="15.75" customHeight="1" s="19">
       <c r="A815" s="8" t="n">
@@ -24231,6 +24535,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F815" t="inlineStr"/>
+      <c r="G815" t="inlineStr"/>
     </row>
     <row r="816" ht="15.75" customHeight="1" s="19">
       <c r="A816" s="8" t="n">
@@ -24256,6 +24562,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F816" t="inlineStr"/>
+      <c r="G816" t="inlineStr"/>
     </row>
     <row r="817" ht="15.75" customHeight="1" s="19">
       <c r="A817" s="8" t="n">
@@ -24281,6 +24589,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F817" t="inlineStr"/>
+      <c r="G817" t="inlineStr"/>
     </row>
     <row r="818" ht="15.75" customHeight="1" s="19">
       <c r="A818" s="8" t="n">
@@ -24306,6 +24616,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F818" t="inlineStr"/>
+      <c r="G818" t="inlineStr"/>
     </row>
     <row r="819" ht="15.75" customHeight="1" s="19">
       <c r="A819" s="8" t="n">
@@ -24331,6 +24643,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F819" t="inlineStr"/>
+      <c r="G819" t="inlineStr"/>
     </row>
     <row r="820" ht="15.75" customHeight="1" s="19">
       <c r="A820" s="8" t="n">
@@ -24356,6 +24670,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F820" t="inlineStr"/>
+      <c r="G820" t="inlineStr"/>
     </row>
     <row r="821" ht="15.75" customHeight="1" s="19">
       <c r="A821" s="8" t="n">
@@ -24381,6 +24697,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>+54 11 6176-4069</t>
+        </is>
+      </c>
+      <c r="G821" t="inlineStr"/>
     </row>
     <row r="822" ht="15.75" customHeight="1" s="19">
       <c r="A822" s="8" t="n">
@@ -24406,6 +24728,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F822" t="inlineStr"/>
+      <c r="G822" t="inlineStr"/>
     </row>
     <row r="823" ht="15.75" customHeight="1" s="19">
       <c r="A823" s="8" t="n">
@@ -24431,6 +24755,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F823" t="inlineStr"/>
+      <c r="G823" t="inlineStr"/>
     </row>
     <row r="824" ht="15.75" customHeight="1" s="19">
       <c r="A824" s="8" t="n">
@@ -24456,6 +24782,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F824" t="inlineStr"/>
+      <c r="G824" t="inlineStr"/>
     </row>
     <row r="825" ht="15.75" customHeight="1" s="19">
       <c r="A825" s="8" t="n">
@@ -24477,6 +24805,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F825" t="inlineStr"/>
+      <c r="G825" t="inlineStr"/>
     </row>
     <row r="826" ht="15.75" customHeight="1" s="19">
       <c r="A826" s="8" t="n">
@@ -24502,6 +24832,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F826" t="inlineStr"/>
+      <c r="G826" t="inlineStr"/>
     </row>
     <row r="827" ht="15.75" customHeight="1" s="19">
       <c r="A827" s="8" t="n">
@@ -24527,6 +24859,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F827" t="inlineStr"/>
+      <c r="G827" t="inlineStr"/>
     </row>
     <row r="828" ht="15.75" customHeight="1" s="19">
       <c r="A828" s="8" t="n">
@@ -24552,6 +24886,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F828" t="inlineStr"/>
+      <c r="G828" t="inlineStr"/>
     </row>
     <row r="829" ht="15.75" customHeight="1" s="19">
       <c r="A829" s="8" t="n">
@@ -24577,6 +24913,12 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>+54 11 4381-2531</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr"/>
     </row>
     <row r="830" ht="15.75" customHeight="1" s="19">
       <c r="A830" s="8" t="n">
@@ -24602,6 +24944,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F830" t="inlineStr"/>
+      <c r="G830" t="inlineStr"/>
     </row>
     <row r="831" ht="15.75" customHeight="1" s="19">
       <c r="A831" s="8" t="n">
@@ -24627,6 +24971,12 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>+54 11 3789-3845</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr"/>
     </row>
     <row r="832" ht="15.75" customHeight="1" s="19">
       <c r="A832" s="8" t="n">
@@ -24652,6 +25002,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F832" t="inlineStr"/>
+      <c r="G832" t="inlineStr"/>
     </row>
     <row r="833" ht="15.75" customHeight="1" s="19">
       <c r="A833" s="8" t="n">
@@ -24677,6 +25029,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>+54 9 11 2390-1927</t>
+        </is>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>http://www.crazypet.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="834" ht="15.75" customHeight="1" s="19">
       <c r="A834" s="8" t="n">
@@ -24702,6 +25064,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>+54 9 11 2390-1927</t>
+        </is>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>http://www.crazypet.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="835" ht="15.75" customHeight="1" s="19">
       <c r="A835" s="8" t="n">
@@ -24727,6 +25099,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>+54 9 11 2390-1927</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>http://www.veterinariacrazypet.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="836" ht="15.75" customHeight="1" s="19">
       <c r="A836" s="8" t="n">
@@ -24752,6 +25134,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F836" t="inlineStr"/>
+      <c r="G836" t="inlineStr"/>
     </row>
     <row r="837" ht="15.75" customHeight="1" s="19">
       <c r="A837" s="8" t="n">
@@ -24777,6 +25161,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F837" t="inlineStr"/>
+      <c r="G837" t="inlineStr"/>
     </row>
     <row r="838" ht="15.75" customHeight="1" s="19">
       <c r="A838" s="8" t="n">
@@ -24802,6 +25188,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>+54 75289646</t>
+        </is>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>https://moiamodas.mitiendanube.com/</t>
+        </is>
+      </c>
     </row>
     <row r="839" ht="15.75" customHeight="1" s="19">
       <c r="A839" s="8" t="n">
@@ -24827,6 +25223,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F839" t="inlineStr"/>
+      <c r="G839" t="inlineStr"/>
     </row>
     <row r="840" ht="15.75" customHeight="1" s="19">
       <c r="A840" s="8" t="n">
@@ -24852,6 +25250,12 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>+54 11 6828-7717</t>
+        </is>
+      </c>
+      <c r="G840" t="inlineStr"/>
     </row>
     <row r="841" ht="15.75" customHeight="1" s="19">
       <c r="A841" s="8" t="n">
@@ -24877,6 +25281,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>+54 11 7079-1234</t>
+        </is>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>https://centro-pet.mercadoshops.com.ar/criadero</t>
+        </is>
+      </c>
     </row>
     <row r="842" ht="15.75" customHeight="1" s="19">
       <c r="A842" s="8" t="n">
@@ -24902,6 +25316,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>+54 11 7079-1234</t>
+        </is>
+      </c>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>https://centro-pet.mercadoshops.com.ar/criadero</t>
+        </is>
+      </c>
     </row>
     <row r="843" ht="15.75" customHeight="1" s="19">
       <c r="A843" s="8" t="n">
@@ -24927,6 +25351,12 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>+54 11 4242-8790</t>
+        </is>
+      </c>
+      <c r="G843" t="inlineStr"/>
     </row>
     <row r="844" ht="15.75" customHeight="1" s="19">
       <c r="A844" s="8" t="n">
@@ -24952,6 +25382,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F844" t="inlineStr"/>
+      <c r="G844" t="inlineStr"/>
     </row>
     <row r="845" ht="15.75" customHeight="1" s="19">
       <c r="A845" s="8" t="n">
@@ -24977,6 +25409,12 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>+54 11 6384-6406</t>
+        </is>
+      </c>
+      <c r="G845" t="inlineStr"/>
     </row>
     <row r="846" ht="15.75" customHeight="1" s="19">
       <c r="A846" s="8" t="n">
@@ -25002,6 +25440,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>+54 11 4962-3839</t>
+        </is>
+      </c>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>https://zoocopet.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="847" ht="15.75" customHeight="1" s="19">
       <c r="A847" s="8" t="n">
@@ -25027,6 +25475,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>+54 11 7079-1234</t>
+        </is>
+      </c>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>https://centro-pet.mercadoshops.com.ar/criadero</t>
+        </is>
+      </c>
     </row>
     <row r="848" ht="15.75" customHeight="1" s="19">
       <c r="A848" s="8" t="n">
@@ -25052,6 +25510,12 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>+54 11 7710-2887</t>
+        </is>
+      </c>
+      <c r="G848" t="inlineStr"/>
     </row>
     <row r="849" ht="15.75" customHeight="1" s="19">
       <c r="A849" s="8" t="n">
@@ -25077,6 +25541,12 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>+54 42432856</t>
+        </is>
+      </c>
+      <c r="G849" t="inlineStr"/>
     </row>
     <row r="850" ht="15.75" customHeight="1" s="19">
       <c r="A850" s="8" t="n">
@@ -25102,6 +25572,12 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>+54 11 7064-2536</t>
+        </is>
+      </c>
+      <c r="G850" t="inlineStr"/>
     </row>
     <row r="851" ht="15.75" customHeight="1" s="19">
       <c r="A851" s="8" t="n">
@@ -25127,6 +25603,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F851" t="inlineStr"/>
+      <c r="G851" t="inlineStr"/>
     </row>
     <row r="852" ht="15.75" customHeight="1" s="19">
       <c r="A852" s="8" t="n">
@@ -25152,6 +25630,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F852" t="inlineStr"/>
+      <c r="G852" t="inlineStr"/>
     </row>
     <row r="853" ht="15.75" customHeight="1" s="19">
       <c r="A853" s="8" t="n">

--- a/PUNTOS_DE_VENTA_completado.xlsx
+++ b/PUNTOS_DE_VENTA_completado.xlsx
@@ -25657,6 +25657,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F853" t="inlineStr"/>
+      <c r="G853" t="inlineStr"/>
     </row>
     <row r="854" ht="15.75" customHeight="1" s="19">
       <c r="A854" s="8" t="n">
@@ -25682,6 +25684,12 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>+54 11 4777-4981</t>
+        </is>
+      </c>
+      <c r="G854" t="inlineStr"/>
     </row>
     <row r="855" ht="15.75" customHeight="1" s="19">
       <c r="A855" s="8" t="n">
@@ -25707,6 +25715,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>+54 9 11 6101-2107</t>
+        </is>
+      </c>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>http://www.vet-life.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="856" ht="15.75" customHeight="1" s="19">
       <c r="A856" s="8" t="n">
@@ -25732,6 +25750,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>+54 810-220-6666</t>
+        </is>
+      </c>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>https://www.kangoopet.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="857" ht="15.75" customHeight="1" s="19">
       <c r="A857" s="8" t="n">
@@ -25757,6 +25785,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>+54 810-220-6666</t>
+        </is>
+      </c>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>https://www.kangoopet.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="858" ht="15.75" customHeight="1" s="19">
       <c r="A858" s="8" t="n">
@@ -25782,6 +25820,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>+54 11 4502-9798</t>
+        </is>
+      </c>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>http://www.consultoriosnazarre.com/</t>
+        </is>
+      </c>
     </row>
     <row r="859" ht="15.75" customHeight="1" s="19">
       <c r="A859" s="8" t="n">
@@ -25807,6 +25855,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>+54 11 4553-5821</t>
+        </is>
+      </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>http://www.totalpet.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="860" ht="15.75" customHeight="1" s="19">
       <c r="A860" s="8" t="n">
@@ -25832,6 +25890,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>+54 11 2554-5874</t>
+        </is>
+      </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>http://www.casperpetstore.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="861" ht="15.75" customHeight="1" s="19">
       <c r="A861" s="8" t="n">
@@ -25857,6 +25925,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F861" t="inlineStr"/>
+      <c r="G861" t="inlineStr"/>
     </row>
     <row r="862" ht="15.75" customHeight="1" s="19">
       <c r="A862" s="8" t="n">
@@ -25882,6 +25952,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>+54 810-220-8383</t>
+        </is>
+      </c>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>https://www.faunatikos.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="863" ht="15.75" customHeight="1" s="19">
       <c r="A863" s="8" t="n">
@@ -25907,6 +25987,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>+54 810-220-8383</t>
+        </is>
+      </c>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>https://www.faunatikos.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="864" ht="15.75" customHeight="1" s="19">
       <c r="A864" s="8" t="n">
@@ -25932,6 +26022,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F864" t="inlineStr">
+        <is>
+          <t>+54 810-220-6666</t>
+        </is>
+      </c>
+      <c r="G864" t="inlineStr">
+        <is>
+          <t>https://www.kangoopet.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="865" ht="15.75" customHeight="1" s="19">
       <c r="A865" s="8" t="n">
@@ -25957,6 +26057,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F865" t="inlineStr"/>
+      <c r="G865" t="inlineStr"/>
     </row>
     <row r="866" ht="15.75" customHeight="1" s="19">
       <c r="A866" s="8" t="n">
@@ -25982,6 +26084,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F866" t="inlineStr"/>
+      <c r="G866" t="inlineStr"/>
     </row>
     <row r="867" ht="15.75" customHeight="1" s="19">
       <c r="A867" s="8" t="n">
@@ -26007,6 +26111,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>+54 11 4089-8298</t>
+        </is>
+      </c>
+      <c r="G867" t="inlineStr"/>
     </row>
     <row r="868" ht="15.75" customHeight="1" s="19">
       <c r="A868" s="8" t="n">
@@ -26032,6 +26142,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>+54 810-220-8383</t>
+        </is>
+      </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>https://goo.su/1BN9snf</t>
+        </is>
+      </c>
     </row>
     <row r="869" ht="15.75" customHeight="1" s="19">
       <c r="A869" s="8" t="n">
@@ -26057,6 +26177,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>+54 11 4553-5821</t>
+        </is>
+      </c>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>http://www.totalpet.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="870" ht="15.75" customHeight="1" s="19">
       <c r="A870" s="8" t="n">
@@ -26082,6 +26212,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>+54 810-220-6666</t>
+        </is>
+      </c>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>http://www.kangoopet.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="871" ht="15.75" customHeight="1" s="19">
       <c r="A871" s="8" t="n">
@@ -26107,6 +26247,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F871" t="inlineStr"/>
+      <c r="G871" t="inlineStr"/>
     </row>
     <row r="872" ht="15.75" customHeight="1" s="19">
       <c r="A872" s="8" t="n">
@@ -26132,6 +26274,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>+54 810-220-8383</t>
+        </is>
+      </c>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>https://goo.su/1BN9snf</t>
+        </is>
+      </c>
     </row>
     <row r="873" ht="15.75" customHeight="1" s="19">
       <c r="A873" s="8" t="n">
@@ -26157,6 +26309,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>+54 810-220-6666</t>
+        </is>
+      </c>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>https://www.kangoopet.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="874" ht="15.75" customHeight="1" s="19">
       <c r="A874" s="8" t="n">
@@ -26182,6 +26344,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F874" t="inlineStr"/>
+      <c r="G874" t="inlineStr"/>
     </row>
     <row r="875" ht="15.75" customHeight="1" s="19">
       <c r="A875" s="8" t="n">
@@ -26207,6 +26371,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>+54 11 6335-0437</t>
+        </is>
+      </c>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>http://www.veterinariaclivet24hs.com/</t>
+        </is>
+      </c>
     </row>
     <row r="876" ht="15.75" customHeight="1" s="19">
       <c r="A876" s="8" t="n">
@@ -26232,6 +26406,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F876" t="inlineStr"/>
+      <c r="G876" t="inlineStr"/>
     </row>
     <row r="877" ht="15.75" customHeight="1" s="19">
       <c r="A877" s="8" t="n">
@@ -26257,6 +26433,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F877" t="inlineStr"/>
+      <c r="G877" t="inlineStr"/>
     </row>
     <row r="878" ht="15.75" customHeight="1" s="19">
       <c r="A878" s="8" t="n">
@@ -26282,6 +26460,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F878" t="inlineStr"/>
+      <c r="G878" t="inlineStr"/>
     </row>
     <row r="879" ht="15.75" customHeight="1" s="19">
       <c r="A879" s="8" t="n">
@@ -26307,6 +26487,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F879" t="inlineStr"/>
+      <c r="G879" t="inlineStr"/>
     </row>
     <row r="880" ht="15.75" customHeight="1" s="19">
       <c r="A880" s="8" t="n">
@@ -26332,6 +26514,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>+54 11 4976-0245</t>
+        </is>
+      </c>
+      <c r="G880" t="inlineStr"/>
     </row>
     <row r="881" ht="15.75" customHeight="1" s="19">
       <c r="A881" s="8" t="n">
@@ -26357,6 +26545,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>+54 9 11 6606-5674</t>
+        </is>
+      </c>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>http://vivianapetshop.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="882" ht="15.75" customHeight="1" s="19">
       <c r="A882" s="8" t="n">
@@ -26382,6 +26580,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F882" t="inlineStr"/>
+      <c r="G882" t="inlineStr"/>
     </row>
     <row r="883" ht="15.75" customHeight="1" s="19">
       <c r="A883" s="8" t="n">
@@ -26407,6 +26607,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>+54 11 5950-4343</t>
+        </is>
+      </c>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>https://www.pedidosya.com.ar/restaurantes/san-isidro/al-rayan-martinez-menu?origin=shop_list</t>
+        </is>
+      </c>
     </row>
     <row r="884" ht="15.75" customHeight="1" s="19">
       <c r="A884" s="8" t="n">
@@ -26432,6 +26642,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F884" t="inlineStr"/>
+      <c r="G884" t="inlineStr"/>
     </row>
     <row r="885" ht="15.75" customHeight="1" s="19">
       <c r="A885" s="8" t="n">
@@ -26457,6 +26669,12 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>+54 11 3497-3000</t>
+        </is>
+      </c>
+      <c r="G885" t="inlineStr"/>
     </row>
     <row r="886" ht="15.75" customHeight="1" s="19">
       <c r="A886" s="8" t="n">
@@ -26482,6 +26700,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F886" t="inlineStr"/>
+      <c r="G886" t="inlineStr"/>
     </row>
     <row r="887" ht="15.75" customHeight="1" s="19">
       <c r="A887" s="8" t="n">
@@ -26507,6 +26727,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F887" t="inlineStr"/>
+      <c r="G887" t="inlineStr"/>
     </row>
     <row r="888" ht="15.75" customHeight="1" s="19">
       <c r="A888" s="8" t="n">
@@ -26532,6 +26754,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F888" t="inlineStr"/>
+      <c r="G888" t="inlineStr"/>
     </row>
     <row r="889" ht="15.75" customHeight="1" s="19">
       <c r="A889" s="8" t="n">
@@ -26557,6 +26781,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>+54 11 5737-8221</t>
+        </is>
+      </c>
+      <c r="G889" t="inlineStr">
+        <is>
+          <t>https://www.puppis.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="890" ht="15.75" customHeight="1" s="19">
       <c r="A890" s="8" t="n">
@@ -26582,6 +26816,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F890" t="inlineStr"/>
+      <c r="G890" t="inlineStr"/>
     </row>
     <row r="891" ht="15.75" customHeight="1" s="19">
       <c r="A891" s="8" t="n">
@@ -26607,6 +26843,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F891" t="inlineStr"/>
+      <c r="G891" t="inlineStr"/>
     </row>
     <row r="892" ht="15.75" customHeight="1" s="19">
       <c r="A892" s="8" t="n">
@@ -26632,6 +26870,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F892" t="inlineStr"/>
+      <c r="G892" t="inlineStr"/>
     </row>
     <row r="893" ht="15.75" customHeight="1" s="19">
       <c r="A893" s="8" t="n">
@@ -26657,6 +26897,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F893" t="inlineStr"/>
+      <c r="G893" t="inlineStr"/>
     </row>
     <row r="894" ht="15.75" customHeight="1" s="19">
       <c r="A894" s="8" t="n">
@@ -26682,6 +26924,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F894" t="inlineStr"/>
+      <c r="G894" t="inlineStr"/>
     </row>
     <row r="895" ht="15.75" customHeight="1" s="19">
       <c r="A895" s="8" t="n">
@@ -26707,6 +26951,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>+54 11 3350-0255</t>
+        </is>
+      </c>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>https://nutrican.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="896" ht="15.75" customHeight="1" s="19">
       <c r="A896" s="8" t="n">
@@ -26732,6 +26986,12 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>+54 11 4887-9494</t>
+        </is>
+      </c>
+      <c r="G896" t="inlineStr"/>
     </row>
     <row r="897" ht="15.75" customHeight="1" s="19">
       <c r="A897" s="8" t="n">
@@ -26757,6 +27017,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F897" t="inlineStr"/>
+      <c r="G897" t="inlineStr"/>
     </row>
     <row r="898" ht="15.75" customHeight="1" s="19">
       <c r="A898" s="8" t="n">
@@ -26782,6 +27044,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>+54 9 11 2577-5217</t>
+        </is>
+      </c>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/brasitasresto?igsh=MWNjdm93bjBmaGpzMA==</t>
+        </is>
+      </c>
     </row>
     <row r="899" ht="15.75" customHeight="1" s="19">
       <c r="A899" s="8" t="n">
@@ -26807,6 +27079,12 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>+54 11 4451-4739</t>
+        </is>
+      </c>
+      <c r="G899" t="inlineStr"/>
     </row>
     <row r="900" ht="15.75" customHeight="1" s="19">
       <c r="A900" s="8" t="n">
@@ -26832,6 +27110,12 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F900" t="inlineStr"/>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>http://cmrawson.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="901" ht="15.75" customHeight="1" s="19">
       <c r="A901" s="8" t="n">
@@ -26857,6 +27141,12 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>+54 11 4798-6856</t>
+        </is>
+      </c>
+      <c r="G901" t="inlineStr"/>
     </row>
     <row r="902" ht="15.75" customHeight="1" s="19">
       <c r="A902" s="8" t="n">
@@ -26882,6 +27172,12 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>+54 11 3734-1210</t>
+        </is>
+      </c>
+      <c r="G902" t="inlineStr"/>
     </row>
     <row r="903" ht="15.75" customHeight="1" s="19">
       <c r="A903" s="8" t="n">
@@ -26907,6 +27203,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F903" t="inlineStr"/>
+      <c r="G903" t="inlineStr"/>
     </row>
     <row r="904" ht="15.75" customHeight="1" s="19">
       <c r="A904" s="8" t="n">
@@ -26932,6 +27230,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F904" t="inlineStr"/>
+      <c r="G904" t="inlineStr"/>
     </row>
     <row r="905" ht="15.75" customHeight="1" s="19">
       <c r="A905" s="8" t="n">
@@ -26957,6 +27257,12 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>+54 11 3350-4459</t>
+        </is>
+      </c>
+      <c r="G905" t="inlineStr"/>
     </row>
     <row r="906" ht="15.75" customHeight="1" s="19">
       <c r="A906" s="8" t="n">
@@ -26982,6 +27288,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>+54 11 4659-2011</t>
+        </is>
+      </c>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>https://www.ms.gba.gov.ar/sitios/hguemes/</t>
+        </is>
+      </c>
     </row>
     <row r="907" ht="15.75" customHeight="1" s="19">
       <c r="A907" s="8" t="n">
@@ -27007,6 +27323,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>+54 11 3350-0255</t>
+        </is>
+      </c>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>https://nutrican.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="908" ht="15.75" customHeight="1" s="19">
       <c r="A908" s="8" t="n">
@@ -27032,6 +27358,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F908" t="inlineStr"/>
+      <c r="G908" t="inlineStr"/>
     </row>
     <row r="909" ht="15.75" customHeight="1" s="19">
       <c r="A909" s="8" t="n">
@@ -27057,6 +27385,12 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>+54 810-444-6887</t>
+        </is>
+      </c>
+      <c r="G909" t="inlineStr"/>
     </row>
     <row r="910" ht="15.75" customHeight="1" s="19">
       <c r="A910" s="8" t="n">
@@ -27082,6 +27416,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>+54 11 2380-7278</t>
+        </is>
+      </c>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>https://basarian.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="911" ht="15.75" customHeight="1" s="19">
       <c r="A911" s="8" t="n">
@@ -27107,6 +27451,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>+54 9 11 2284-4259</t>
+        </is>
+      </c>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>http://www.daytona.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="912" ht="15.75" customHeight="1" s="19">
       <c r="A912" s="8" t="n">
@@ -27132,6 +27486,12 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F912" t="inlineStr"/>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>http://www.laaldea.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="913" ht="15.75" customHeight="1" s="19">
       <c r="A913" s="8" t="n">
@@ -27157,6 +27517,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>+54 11 3350-0255</t>
+        </is>
+      </c>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>https://nutrican.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="914" ht="15.75" customHeight="1" s="19">
       <c r="A914" s="8" t="n">
@@ -27182,6 +27552,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>+54 11 4630-4373</t>
+        </is>
+      </c>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>http://parquebrown.factoryshopping.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="915" ht="15.75" customHeight="1" s="19">
       <c r="A915" s="8" t="n">
@@ -27207,6 +27587,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F915" t="inlineStr"/>
+      <c r="G915" t="inlineStr"/>
     </row>
     <row r="916" ht="15.75" customHeight="1" s="19">
       <c r="A916" s="8" t="n">
@@ -27232,6 +27614,12 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>+54 11 7145-4500</t>
+        </is>
+      </c>
+      <c r="G916" t="inlineStr"/>
     </row>
     <row r="917" ht="15.75" customHeight="1" s="19">
       <c r="A917" s="8" t="n">
@@ -27257,6 +27645,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>+54 11 3350-0255</t>
+        </is>
+      </c>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>https://nutrican.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="918" ht="15.75" customHeight="1" s="19">
       <c r="A918" s="8" t="n">
@@ -27282,6 +27680,12 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>+54 221 425-1998</t>
+        </is>
+      </c>
+      <c r="G918" t="inlineStr"/>
     </row>
     <row r="919" ht="15.75" customHeight="1" s="19">
       <c r="A919" s="8" t="n">
@@ -27307,6 +27711,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>+54 11 4382-3451</t>
+        </is>
+      </c>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>http://www.andinavet.com/nosotros/nosotros.htm</t>
+        </is>
+      </c>
     </row>
     <row r="920" ht="15.75" customHeight="1" s="19">
       <c r="A920" s="8" t="n">
@@ -27332,6 +27746,16 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>+54 11 5723-9530</t>
+        </is>
+      </c>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>https://petland.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="921" ht="15.75" customHeight="1" s="19">
       <c r="A921" s="8" t="n">
@@ -27357,6 +27781,16 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>+54 11 5723-9530</t>
+        </is>
+      </c>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>https://petland.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="922" ht="15.75" customHeight="1" s="19">
       <c r="A922" s="8" t="n">
@@ -27382,6 +27816,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>+54 11 3350-0255</t>
+        </is>
+      </c>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>https://nutrican.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="923" ht="15.75" customHeight="1" s="19">
       <c r="A923" s="8" t="n">
@@ -27407,6 +27851,12 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>+54 11 2155-1425</t>
+        </is>
+      </c>
+      <c r="G923" t="inlineStr"/>
     </row>
     <row r="924" ht="15.75" customHeight="1" s="19">
       <c r="A924" s="8" t="n">
@@ -27432,6 +27882,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F924" t="inlineStr"/>
+      <c r="G924" t="inlineStr"/>
     </row>
     <row r="925" ht="15.75" customHeight="1" s="19">
       <c r="A925" s="8" t="n">
@@ -27457,6 +27909,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F925" t="inlineStr"/>
+      <c r="G925" t="inlineStr"/>
     </row>
     <row r="926" ht="15.75" customHeight="1" s="19">
       <c r="A926" s="8" t="n">
@@ -27482,6 +27936,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>+54 11 6910-6216</t>
+        </is>
+      </c>
+      <c r="G926" t="inlineStr">
+        <is>
+          <t>https://www.carrefour.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="927" ht="15.75" customHeight="1" s="19">
       <c r="A927" s="8" t="n">
@@ -27507,6 +27971,12 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>+54 11 2654-0074</t>
+        </is>
+      </c>
+      <c r="G927" t="inlineStr"/>
     </row>
     <row r="928" ht="15.75" customHeight="1" s="19">
       <c r="A928" s="8" t="n">
@@ -27532,6 +28002,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>+54 11 3350-0255</t>
+        </is>
+      </c>
+      <c r="G928" t="inlineStr">
+        <is>
+          <t>https://nutrican.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="929" ht="15.75" customHeight="1" s="19">
       <c r="A929" s="8" t="n">
@@ -27557,6 +28037,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F929" t="inlineStr"/>
+      <c r="G929" t="inlineStr"/>
     </row>
     <row r="930" ht="15.75" customHeight="1" s="19">
       <c r="A930" s="8" t="n">
@@ -27582,6 +28064,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>+54 11 4362-6622</t>
+        </is>
+      </c>
+      <c r="G930" t="inlineStr">
+        <is>
+          <t>http://multimascota.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="931" ht="15.75" customHeight="1" s="19">
       <c r="A931" s="8" t="n">
@@ -27607,6 +28099,12 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>+54 11 7145-4500</t>
+        </is>
+      </c>
+      <c r="G931" t="inlineStr"/>
     </row>
     <row r="932" ht="15.75" customHeight="1" s="19">
       <c r="A932" s="8" t="n">
@@ -27632,6 +28130,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F932" t="inlineStr"/>
+      <c r="G932" t="inlineStr"/>
     </row>
     <row r="933" ht="15.75" customHeight="1" s="19">
       <c r="A933" s="8" t="n">
@@ -27657,6 +28157,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>+54 810-220-2345</t>
+        </is>
+      </c>
+      <c r="G933" t="inlineStr">
+        <is>
+          <t>https://www.puppis.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="934" ht="15.75" customHeight="1" s="19">
       <c r="A934" s="8" t="n">
@@ -27682,6 +28192,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F934" t="inlineStr"/>
+      <c r="G934" t="inlineStr"/>
     </row>
     <row r="935" ht="15.75" customHeight="1" s="19">
       <c r="A935" s="8" t="n">
@@ -27707,6 +28219,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F935" t="inlineStr"/>
+      <c r="G935" t="inlineStr"/>
     </row>
     <row r="936" ht="15.75" customHeight="1" s="19">
       <c r="A936" s="8" t="n">
@@ -27732,6 +28246,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>+54 810-220-2345</t>
+        </is>
+      </c>
+      <c r="G936" t="inlineStr">
+        <is>
+          <t>https://www.puppis.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="937" ht="15.75" customHeight="1" s="19">
       <c r="A937" s="8" t="n">
@@ -27757,6 +28281,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>+1 859-353-5017</t>
+        </is>
+      </c>
+      <c r="G937" t="inlineStr">
+        <is>
+          <t>https://vivamexicolex.com/</t>
+        </is>
+      </c>
     </row>
     <row r="938" ht="15.75" customHeight="1" s="19">
       <c r="A938" s="8" t="n">
@@ -27782,6 +28316,12 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F938" t="inlineStr">
+        <is>
+          <t>+54 11 4798-6856</t>
+        </is>
+      </c>
+      <c r="G938" t="inlineStr"/>
     </row>
     <row r="939" ht="15.75" customHeight="1" s="19">
       <c r="A939" s="8" t="n">
@@ -27807,6 +28347,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F939" t="inlineStr"/>
+      <c r="G939" t="inlineStr"/>
     </row>
     <row r="940" ht="15.75" customHeight="1" s="19">
       <c r="A940" s="8" t="n">
@@ -27832,6 +28374,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F940" t="inlineStr">
+        <is>
+          <t>+54 11 5400-4084</t>
+        </is>
+      </c>
+      <c r="G940" t="inlineStr">
+        <is>
+          <t>https://www.natural-life.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="941" ht="15.75" customHeight="1" s="19">
       <c r="A941" s="8" t="n">
@@ -27857,6 +28409,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F941" t="inlineStr"/>
+      <c r="G941" t="inlineStr"/>
     </row>
     <row r="942" ht="15.75" customHeight="1" s="19">
       <c r="A942" s="8" t="n">
@@ -27882,6 +28436,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>+54 11 2339-2311</t>
+        </is>
+      </c>
+      <c r="G942" t="inlineStr">
+        <is>
+          <t>https://www.unipet.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="943" ht="15.75" customHeight="1" s="19">
       <c r="A943" s="8" t="n">
@@ -27907,6 +28471,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F943" t="inlineStr"/>
+      <c r="G943" t="inlineStr"/>
     </row>
     <row r="944" ht="15.75" customHeight="1" s="19">
       <c r="A944" s="8" t="n">
@@ -27932,6 +28498,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>+54 9 11 5924-2512</t>
+        </is>
+      </c>
+      <c r="G944" t="inlineStr">
+        <is>
+          <t>https://www.natural-life.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="945" ht="15.75" customHeight="1" s="19">
       <c r="A945" s="8" t="n">
@@ -27957,6 +28533,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>+54 11 4548-4594</t>
+        </is>
+      </c>
+      <c r="G945" t="inlineStr">
+        <is>
+          <t>https://viejomundo.meitre.com/</t>
+        </is>
+      </c>
     </row>
     <row r="946" ht="15.75" customHeight="1" s="19">
       <c r="A946" s="8" t="n">
@@ -27982,6 +28568,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F946" t="inlineStr"/>
+      <c r="G946" t="inlineStr"/>
     </row>
     <row r="947" ht="15.75" customHeight="1" s="19">
       <c r="A947" s="8" t="n">
@@ -28007,6 +28595,12 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>+54 11 4623-1256</t>
+        </is>
+      </c>
+      <c r="G947" t="inlineStr"/>
     </row>
     <row r="948" ht="15.75" customHeight="1" s="19">
       <c r="A948" s="8" t="n">
@@ -28032,6 +28626,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F948" t="inlineStr"/>
+      <c r="G948" t="inlineStr"/>
     </row>
     <row r="949" ht="15.75" customHeight="1" s="19">
       <c r="A949" s="8" t="n">
@@ -28057,6 +28653,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>+54 11 2767-7077</t>
+        </is>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>https://www.natural-life.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="950" ht="15.75" customHeight="1" s="19">
       <c r="A950" s="8" t="n">
@@ -28082,6 +28688,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>+54 11 4214-7191</t>
+        </is>
+      </c>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>http://www.gba.gob.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="951" ht="15.75" customHeight="1" s="19">
       <c r="A951" s="8" t="n">
@@ -28107,6 +28723,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F951" t="inlineStr"/>
+      <c r="G951" t="inlineStr"/>
     </row>
     <row r="952" ht="15.75" customHeight="1" s="19">
       <c r="A952" s="8" t="n">
@@ -28132,6 +28750,12 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>+54 11 4798-6856</t>
+        </is>
+      </c>
+      <c r="G952" t="inlineStr"/>
     </row>
     <row r="953" ht="15.75" customHeight="1" s="19">
       <c r="A953" s="8" t="n">

--- a/PUNTOS_DE_VENTA_completado.xlsx
+++ b/PUNTOS_DE_VENTA_completado.xlsx
@@ -28781,6 +28781,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>+54 11 3325-9607</t>
+        </is>
+      </c>
+      <c r="G953" t="inlineStr">
+        <is>
+          <t>https://www.natural-life.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="954" ht="15.75" customHeight="1" s="19">
       <c r="A954" s="8" t="n">
@@ -28806,6 +28816,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F954" t="inlineStr"/>
+      <c r="G954" t="inlineStr"/>
     </row>
     <row r="955" ht="15.75" customHeight="1" s="19">
       <c r="A955" s="8" t="n">
@@ -28831,6 +28843,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>+54 800-444-8484</t>
+        </is>
+      </c>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>https://www.carrefour.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="956" ht="15.75" customHeight="1" s="19">
       <c r="A956" s="8" t="n">
@@ -28856,6 +28878,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>+54 11 2339-2311</t>
+        </is>
+      </c>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>https://www.unipet.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="957" ht="15.75" customHeight="1" s="19">
       <c r="A957" s="8" t="n">
@@ -28881,6 +28913,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>+54 11 2339-2311</t>
+        </is>
+      </c>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>https://www.unipet.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="958" ht="15.75" customHeight="1" s="19">
       <c r="A958" s="8" t="n">
@@ -28906,6 +28948,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>+54 810-220-2345</t>
+        </is>
+      </c>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>http://www.puppis.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="959" ht="15.75" customHeight="1" s="19">
       <c r="A959" s="8" t="n">
@@ -28931,6 +28983,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F959" t="inlineStr"/>
+      <c r="G959" t="inlineStr"/>
     </row>
     <row r="960" ht="15.75" customHeight="1" s="19">
       <c r="A960" s="8" t="n">
@@ -28956,6 +29010,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>+54 11 4952-0857</t>
+        </is>
+      </c>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>https://www.depaso335.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="961" ht="15.75" customHeight="1" s="19">
       <c r="A961" s="8" t="n">
@@ -28981,6 +29045,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F961" t="inlineStr"/>
+      <c r="G961" t="inlineStr"/>
     </row>
     <row r="962" ht="15.75" customHeight="1" s="19">
       <c r="A962" s="8" t="n">
@@ -29006,6 +29072,12 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>+54 9 11 4400-2914</t>
+        </is>
+      </c>
+      <c r="G962" t="inlineStr"/>
     </row>
     <row r="963" ht="15.75" customHeight="1" s="19">
       <c r="A963" s="8" t="n">
@@ -29031,6 +29103,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>+54 11 4666-9092</t>
+        </is>
+      </c>
+      <c r="G963" t="inlineStr"/>
     </row>
     <row r="964" ht="15.75" customHeight="1" s="19">
       <c r="A964" s="8" t="n">
@@ -29056,6 +29134,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>+54 11 6197-3363</t>
+        </is>
+      </c>
+      <c r="G964" t="inlineStr">
+        <is>
+          <t>https://www.petpoint.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="965" ht="15.75" customHeight="1" s="19">
       <c r="A965" s="8" t="n">
@@ -29081,6 +29169,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F965" t="inlineStr">
+        <is>
+          <t>+54 9 11 3379-0077</t>
+        </is>
+      </c>
+      <c r="G965" t="inlineStr">
+        <is>
+          <t>http://www.demilamoresaccesorios.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="966" ht="15.75" customHeight="1" s="19">
       <c r="A966" s="8" t="n">
@@ -29106,6 +29204,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F966" t="inlineStr"/>
+      <c r="G966" t="inlineStr"/>
     </row>
     <row r="967" ht="15.75" customHeight="1" s="19">
       <c r="A967" s="8" t="n">
@@ -29131,6 +29231,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F967" t="inlineStr">
+        <is>
+          <t>+54 2320 47-3819</t>
+        </is>
+      </c>
+      <c r="G967" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/veterinariaindependencia.delviso/</t>
+        </is>
+      </c>
     </row>
     <row r="968" ht="15.75" customHeight="1" s="19">
       <c r="A968" s="8" t="n">
@@ -29156,6 +29266,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F968" t="inlineStr">
+        <is>
+          <t>+54 230 448-6179</t>
+        </is>
+      </c>
+      <c r="G968" t="inlineStr"/>
     </row>
     <row r="969" ht="15.75" customHeight="1" s="19">
       <c r="A969" s="8" t="n">
@@ -29181,6 +29297,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>+54 11 4741-0894</t>
+        </is>
+      </c>
+      <c r="G969" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/derentisvete?igsh=YnhiMm9rZDNyaTZs&amp;utm_source=qr</t>
+        </is>
+      </c>
     </row>
     <row r="970" ht="15.75" customHeight="1" s="19">
       <c r="A970" s="8" t="n">
@@ -29206,6 +29332,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F970" t="inlineStr"/>
+      <c r="G970" t="inlineStr"/>
     </row>
     <row r="971" ht="15.75" customHeight="1" s="19">
       <c r="A971" s="8" t="n">
@@ -29231,6 +29359,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>+54 11 4662-5510</t>
+        </is>
+      </c>
+      <c r="G971" t="inlineStr">
+        <is>
+          <t>http://www.hurlinghamclub.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="972" ht="15.75" customHeight="1" s="19">
       <c r="A972" s="8" t="n">
@@ -29256,6 +29394,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>+54 2320 43-2089</t>
+        </is>
+      </c>
+      <c r="G972" t="inlineStr"/>
     </row>
     <row r="973" ht="15.75" customHeight="1" s="19">
       <c r="A973" s="8" t="n">
@@ -29281,6 +29425,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F973" t="inlineStr">
+        <is>
+          <t>+54 2320 42-4537</t>
+        </is>
+      </c>
+      <c r="G973" t="inlineStr"/>
     </row>
     <row r="974" ht="15.75" customHeight="1" s="19">
       <c r="A974" s="8" t="n">
@@ -29306,6 +29456,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F974" t="inlineStr"/>
+      <c r="G974" t="inlineStr"/>
     </row>
     <row r="975" ht="15.75" customHeight="1" s="19">
       <c r="A975" s="8" t="n">
@@ -29331,6 +29483,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F975" t="inlineStr"/>
+      <c r="G975" t="inlineStr"/>
     </row>
     <row r="976" ht="15.75" customHeight="1" s="19">
       <c r="A976" s="8" t="n">
@@ -29356,6 +29510,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F976" t="inlineStr"/>
+      <c r="G976" t="inlineStr"/>
     </row>
     <row r="977" ht="15.75" customHeight="1" s="19">
       <c r="A977" s="8" t="n">
@@ -29381,6 +29537,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F977" t="inlineStr"/>
+      <c r="G977" t="inlineStr"/>
     </row>
     <row r="978" ht="15.75" customHeight="1" s="19">
       <c r="A978" s="8" t="n">
@@ -29406,6 +29564,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F978" t="inlineStr">
+        <is>
+          <t>+54 230 442-0709</t>
+        </is>
+      </c>
+      <c r="G978" t="inlineStr"/>
     </row>
     <row r="979" ht="15.75" customHeight="1" s="19">
       <c r="A979" s="8" t="n">
@@ -29431,6 +29595,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F979" t="inlineStr"/>
+      <c r="G979" t="inlineStr"/>
     </row>
     <row r="980" ht="15.75" customHeight="1" s="19">
       <c r="A980" s="8" t="n">
@@ -29454,6 +29620,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F980" t="inlineStr"/>
+      <c r="G980" t="inlineStr"/>
     </row>
     <row r="981" ht="15.75" customHeight="1" s="19">
       <c r="A981" s="8" t="n">
@@ -29479,6 +29647,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F981" t="inlineStr"/>
+      <c r="G981" t="inlineStr"/>
     </row>
     <row r="982" ht="15.75" customHeight="1" s="19">
       <c r="A982" s="8" t="n">
@@ -29504,6 +29674,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F982" t="inlineStr"/>
+      <c r="G982" t="inlineStr"/>
     </row>
     <row r="983" ht="15.75" customHeight="1" s="19">
       <c r="A983" s="8" t="n">
@@ -29529,6 +29701,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F983" t="inlineStr"/>
+      <c r="G983" t="inlineStr"/>
     </row>
     <row r="984" ht="15.75" customHeight="1" s="19">
       <c r="A984" s="8" t="n">
@@ -29554,6 +29728,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F984" t="inlineStr">
+        <is>
+          <t>+54 11 6785-9673</t>
+        </is>
+      </c>
+      <c r="G984" t="inlineStr">
+        <is>
+          <t>http://www.petpoint.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="985" ht="15.75" customHeight="1" s="19">
       <c r="A985" s="8" t="n">
@@ -29579,6 +29763,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F985" t="inlineStr">
+        <is>
+          <t>+54 11 4768-0428</t>
+        </is>
+      </c>
+      <c r="G985" t="inlineStr">
+        <is>
+          <t>https://www.veterinaria-paul.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="986" ht="15.75" customHeight="1" s="19">
       <c r="A986" s="8" t="n">
@@ -29604,6 +29798,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F986" t="inlineStr"/>
+      <c r="G986" t="inlineStr"/>
     </row>
     <row r="987" ht="15.75" customHeight="1" s="19">
       <c r="A987" s="8" t="n">
@@ -29629,6 +29825,12 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F987" t="inlineStr">
+        <is>
+          <t>+54 11 4764-1302</t>
+        </is>
+      </c>
+      <c r="G987" t="inlineStr"/>
     </row>
     <row r="988" ht="15.75" customHeight="1" s="19">
       <c r="A988" s="8" t="n">
@@ -29652,6 +29854,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F988" t="inlineStr"/>
+      <c r="G988" t="inlineStr">
+        <is>
+          <t>http://www.sanmartin.gov.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="989" ht="15.75" customHeight="1" s="19">
       <c r="A989" s="8" t="n">
@@ -29677,6 +29885,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F989" t="inlineStr">
+        <is>
+          <t>+54 11 4844-6392</t>
+        </is>
+      </c>
+      <c r="G989" t="inlineStr">
+        <is>
+          <t>http://petplanetshop.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="990" ht="15.75" customHeight="1" s="19">
       <c r="A990" s="8" t="n">
@@ -29702,6 +29920,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F990" t="inlineStr"/>
+      <c r="G990" t="inlineStr"/>
     </row>
     <row r="991" ht="15.75" customHeight="1" s="19">
       <c r="A991" s="8" t="n">
@@ -29727,6 +29947,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F991" t="inlineStr">
+        <is>
+          <t>+54 11 3396-1419</t>
+        </is>
+      </c>
+      <c r="G991" t="inlineStr"/>
     </row>
     <row r="992" ht="15.75" customHeight="1" s="19">
       <c r="A992" s="8" t="n">
@@ -29752,6 +29978,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F992" t="inlineStr"/>
+      <c r="G992" t="inlineStr"/>
     </row>
     <row r="993" ht="15.75" customHeight="1" s="19">
       <c r="A993" s="8" t="n">
@@ -29777,6 +30005,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F993" t="inlineStr">
+        <is>
+          <t>+54 11 4665-0983</t>
+        </is>
+      </c>
+      <c r="G993" t="inlineStr">
+        <is>
+          <t>https://instagram.com/veterinariaelmate?igshid=1r17pmqvg226c</t>
+        </is>
+      </c>
     </row>
     <row r="994" ht="15.75" customHeight="1" s="19">
       <c r="A994" s="8" t="n">
@@ -29802,6 +30040,12 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F994" t="inlineStr">
+        <is>
+          <t>+54 11 4725-3832</t>
+        </is>
+      </c>
+      <c r="G994" t="inlineStr"/>
     </row>
     <row r="995" ht="15.75" customHeight="1" s="19">
       <c r="A995" s="8" t="n">
@@ -29827,6 +30071,12 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F995" t="inlineStr">
+        <is>
+          <t>+54 11 5292-7707</t>
+        </is>
+      </c>
+      <c r="G995" t="inlineStr"/>
     </row>
     <row r="996" ht="15.75" customHeight="1" s="19">
       <c r="A996" s="8" t="n">
@@ -29852,6 +30102,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F996" t="inlineStr"/>
+      <c r="G996" t="inlineStr"/>
     </row>
     <row r="997" ht="15.75" customHeight="1" s="19">
       <c r="A997" s="8" t="n">
@@ -29877,6 +30129,12 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F997" t="inlineStr">
+        <is>
+          <t>+54 11 3488-6102</t>
+        </is>
+      </c>
+      <c r="G997" t="inlineStr"/>
     </row>
     <row r="998" ht="15.75" customHeight="1" s="19">
       <c r="A998" s="8" t="n">
@@ -29902,6 +30160,12 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F998" t="inlineStr">
+        <is>
+          <t>+54 11 4433-2545</t>
+        </is>
+      </c>
+      <c r="G998" t="inlineStr"/>
     </row>
     <row r="999" ht="15.75" customHeight="1" s="19">
       <c r="A999" s="8" t="n">
@@ -29927,6 +30191,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F999" t="inlineStr"/>
+      <c r="G999" t="inlineStr"/>
     </row>
     <row r="1000" ht="15.75" customHeight="1" s="19">
       <c r="A1000" s="8" t="n">
@@ -29952,6 +30218,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1000" t="inlineStr"/>
+      <c r="G1000" t="inlineStr"/>
     </row>
     <row r="1001" ht="15.75" customHeight="1" s="19">
       <c r="A1001" s="8" t="n">
@@ -29977,6 +30245,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1001" t="inlineStr"/>
+      <c r="G1001" t="inlineStr"/>
     </row>
     <row r="1002" ht="15.75" customHeight="1" s="19">
       <c r="A1002" s="8" t="n">
@@ -30002,6 +30272,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1002" t="inlineStr"/>
+      <c r="G1002" t="inlineStr"/>
     </row>
     <row r="1003" ht="15.75" customHeight="1" s="19">
       <c r="A1003" s="8" t="n">

--- a/PUNTOS_DE_VENTA_completado.xlsx
+++ b/PUNTOS_DE_VENTA_completado.xlsx
@@ -30299,6 +30299,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1003" t="inlineStr"/>
+      <c r="G1003" t="inlineStr"/>
     </row>
     <row r="1004" ht="15.75" customHeight="1" s="19">
       <c r="A1004" s="8" t="n">
@@ -30324,6 +30326,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1004" t="inlineStr"/>
+      <c r="G1004" t="inlineStr"/>
     </row>
     <row r="1005" ht="15.75" customHeight="1" s="19">
       <c r="A1005" s="8" t="n">
@@ -30349,6 +30353,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1005" t="inlineStr">
+        <is>
+          <t>+54 11 3779-2738</t>
+        </is>
+      </c>
+      <c r="G1005" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/elantojo_ok3</t>
+        </is>
+      </c>
     </row>
     <row r="1006" ht="15.75" customHeight="1" s="19">
       <c r="A1006" s="8" t="n">
@@ -30374,6 +30388,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1006" t="inlineStr"/>
+      <c r="G1006" t="inlineStr"/>
     </row>
     <row r="1007" ht="15.75" customHeight="1" s="19">
       <c r="A1007" s="8" t="n">
@@ -30399,6 +30415,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1007" t="inlineStr">
+        <is>
+          <t>+54 11 4943-5288</t>
+        </is>
+      </c>
+      <c r="G1007" t="inlineStr">
+        <is>
+          <t>http://www.osecac.org.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1008" ht="15.75" customHeight="1" s="19">
       <c r="A1008" s="8" t="n">
@@ -30424,6 +30450,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1008" t="inlineStr"/>
+      <c r="G1008" t="inlineStr"/>
     </row>
     <row r="1009" ht="15.75" customHeight="1" s="19">
       <c r="A1009" s="8" t="n">
@@ -30449,6 +30477,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1009" t="inlineStr"/>
+      <c r="G1009" t="inlineStr"/>
     </row>
     <row r="1010" ht="15.75" customHeight="1" s="19">
       <c r="A1010" s="8" t="n">
@@ -30474,6 +30504,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1010" t="inlineStr"/>
+      <c r="G1010" t="inlineStr"/>
     </row>
     <row r="1011" ht="15.75" customHeight="1" s="19">
       <c r="A1011" s="8" t="n">
@@ -30499,6 +30531,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F1011" t="inlineStr"/>
+      <c r="G1011" t="inlineStr"/>
     </row>
     <row r="1012" ht="15.75" customHeight="1" s="19">
       <c r="A1012" s="8" t="n">
@@ -30524,6 +30558,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1012" t="inlineStr"/>
+      <c r="G1012" t="inlineStr"/>
     </row>
     <row r="1013" ht="15.75" customHeight="1" s="19">
       <c r="A1013" s="8" t="n">
@@ -30549,6 +30585,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1013" t="inlineStr"/>
+      <c r="G1013" t="inlineStr"/>
     </row>
     <row r="1014" ht="15.75" customHeight="1" s="19">
       <c r="A1014" s="8" t="n">
@@ -30574,6 +30612,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1014" t="inlineStr"/>
+      <c r="G1014" t="inlineStr"/>
     </row>
     <row r="1015" ht="15.75" customHeight="1" s="19">
       <c r="A1015" s="8" t="n">
@@ -30599,6 +30639,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1015" t="inlineStr">
+        <is>
+          <t>+54 11 4632-0404</t>
+        </is>
+      </c>
+      <c r="G1015" t="inlineStr">
+        <is>
+          <t>https://lodefidelveterinaria.com/</t>
+        </is>
+      </c>
     </row>
     <row r="1016" ht="15.75" customHeight="1" s="19">
       <c r="A1016" s="8" t="n">
@@ -30624,6 +30674,12 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1016" t="inlineStr"/>
+      <c r="G1016" t="inlineStr">
+        <is>
+          <t>https://damelapatashop.com/</t>
+        </is>
+      </c>
     </row>
     <row r="1017" ht="15.75" customHeight="1" s="19">
       <c r="A1017" s="8" t="n">
@@ -30649,6 +30705,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1017" t="inlineStr"/>
+      <c r="G1017" t="inlineStr"/>
     </row>
     <row r="1018" ht="15.75" customHeight="1" s="19">
       <c r="A1018" s="8" t="n">
@@ -30674,6 +30732,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1018" t="inlineStr"/>
+      <c r="G1018" t="inlineStr"/>
     </row>
     <row r="1019" ht="15.75" customHeight="1" s="19">
       <c r="A1019" s="8" t="n">
@@ -30699,6 +30759,12 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1019" t="inlineStr">
+        <is>
+          <t>+54 11 4504-3004</t>
+        </is>
+      </c>
+      <c r="G1019" t="inlineStr"/>
     </row>
     <row r="1020" ht="15.75" customHeight="1" s="19">
       <c r="A1020" s="8" t="n">
@@ -30724,6 +30790,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1020" t="inlineStr">
+        <is>
+          <t>+54 11 4635-4080</t>
+        </is>
+      </c>
+      <c r="G1020" t="inlineStr">
+        <is>
+          <t>https://www.belcarautoelevador.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1021" ht="15.75" customHeight="1" s="19">
       <c r="A1021" s="8" t="n">
@@ -30749,6 +30825,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1021" t="inlineStr"/>
+      <c r="G1021" t="inlineStr"/>
     </row>
     <row r="1022" ht="15.75" customHeight="1" s="19">
       <c r="A1022" s="8" t="n">
@@ -30774,6 +30852,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1022" t="inlineStr"/>
+      <c r="G1022" t="inlineStr"/>
     </row>
     <row r="1023" ht="15.75" customHeight="1" s="19">
       <c r="A1023" s="8" t="n">
@@ -30795,6 +30875,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1023" t="inlineStr"/>
+      <c r="G1023" t="inlineStr"/>
     </row>
     <row r="1024" ht="15.75" customHeight="1" s="19">
       <c r="A1024" s="8" t="n">
@@ -30816,6 +30898,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1024" t="inlineStr"/>
+      <c r="G1024" t="inlineStr">
+        <is>
+          <t>http://www.argentina.gob.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1025" ht="15.75" customHeight="1" s="19">
       <c r="A1025" s="8" t="n">
@@ -30841,6 +30929,12 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1025" t="inlineStr">
+        <is>
+          <t>+54 11 4661-8540</t>
+        </is>
+      </c>
+      <c r="G1025" t="inlineStr"/>
     </row>
     <row r="1026" ht="15.75" customHeight="1" s="19">
       <c r="A1026" s="8" t="n">
@@ -30866,6 +30960,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1026" t="inlineStr">
+        <is>
+          <t>+54 35301213</t>
+        </is>
+      </c>
+      <c r="G1026" t="inlineStr">
+        <is>
+          <t>https://pilimascotas.shop/</t>
+        </is>
+      </c>
     </row>
     <row r="1027" ht="15.75" customHeight="1" s="19">
       <c r="A1027" s="8" t="n">
@@ -30891,6 +30995,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1027" t="inlineStr"/>
+      <c r="G1027" t="inlineStr"/>
     </row>
     <row r="1028" ht="15.75" customHeight="1" s="19">
       <c r="A1028" s="8" t="n">
@@ -30916,6 +31022,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1028" t="inlineStr"/>
+      <c r="G1028" t="inlineStr"/>
     </row>
     <row r="1029" ht="15.75" customHeight="1" s="19">
       <c r="A1029" s="8" t="n">
@@ -30941,6 +31049,12 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F1029" t="inlineStr">
+        <is>
+          <t>+54 11 5815-5172</t>
+        </is>
+      </c>
+      <c r="G1029" t="inlineStr"/>
     </row>
     <row r="1030" ht="15.75" customHeight="1" s="19">
       <c r="A1030" s="8" t="n">
@@ -30966,6 +31080,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1030" t="inlineStr"/>
+      <c r="G1030" t="inlineStr"/>
     </row>
     <row r="1031" ht="15.75" customHeight="1" s="19">
       <c r="A1031" s="8" t="n">
@@ -30991,6 +31107,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1031" t="inlineStr"/>
+      <c r="G1031" t="inlineStr"/>
     </row>
     <row r="1032" ht="15.75" customHeight="1" s="19">
       <c r="A1032" s="8" t="n">
@@ -31016,6 +31134,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1032" t="inlineStr"/>
+      <c r="G1032" t="inlineStr"/>
     </row>
     <row r="1033" ht="15.75" customHeight="1" s="19">
       <c r="A1033" s="8" t="n">
@@ -31041,6 +31161,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1033" t="inlineStr"/>
+      <c r="G1033" t="inlineStr"/>
     </row>
     <row r="1034" ht="15.75" customHeight="1" s="19">
       <c r="A1034" s="8" t="n">
@@ -31066,6 +31188,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1034" t="inlineStr"/>
+      <c r="G1034" t="inlineStr"/>
     </row>
     <row r="1035" ht="15.75" customHeight="1" s="19">
       <c r="A1035" s="8" t="n">
@@ -31091,6 +31215,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1035" t="inlineStr">
+        <is>
+          <t>+54 11 4222-1630</t>
+        </is>
+      </c>
+      <c r="G1035" t="inlineStr">
+        <is>
+          <t>https://www.veterinarias.com.ar/veterinaria-mascotitas</t>
+        </is>
+      </c>
     </row>
     <row r="1036" ht="15.75" customHeight="1" s="19">
       <c r="A1036" s="8" t="n">
@@ -31116,6 +31250,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1036" t="inlineStr">
+        <is>
+          <t>+54 42531233</t>
+        </is>
+      </c>
+      <c r="G1036" t="inlineStr">
+        <is>
+          <t>http://buloneraquilmes.com/</t>
+        </is>
+      </c>
     </row>
     <row r="1037" ht="15.75" customHeight="1" s="19">
       <c r="A1037" s="8" t="n">
@@ -31141,6 +31285,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1037" t="inlineStr">
+        <is>
+          <t>+54 11 3108-5049</t>
+        </is>
+      </c>
+      <c r="G1037" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bradocafewilde/</t>
+        </is>
+      </c>
     </row>
     <row r="1038" ht="15.75" customHeight="1" s="19">
       <c r="A1038" s="8" t="n">
@@ -31166,6 +31320,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F1038" t="inlineStr"/>
+      <c r="G1038" t="inlineStr"/>
     </row>
     <row r="1039" ht="15.75" customHeight="1" s="19">
       <c r="A1039" s="8" t="n">
@@ -31191,6 +31347,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1039" t="inlineStr">
+        <is>
+          <t>+54 11 4302-5724</t>
+        </is>
+      </c>
+      <c r="G1039" t="inlineStr">
+        <is>
+          <t>http://www.veterinariaburbuja.com/</t>
+        </is>
+      </c>
     </row>
     <row r="1040" ht="15.75" customHeight="1" s="19">
       <c r="A1040" s="8" t="n">
@@ -31216,6 +31382,12 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>+54 11 4805-8867</t>
+        </is>
+      </c>
+      <c r="G1040" t="inlineStr"/>
     </row>
     <row r="1041" ht="15.75" customHeight="1" s="19">
       <c r="A1041" s="8" t="n">
@@ -31241,6 +31413,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1041" t="inlineStr"/>
+      <c r="G1041" t="inlineStr"/>
     </row>
     <row r="1042" ht="15.75" customHeight="1" s="19">
       <c r="A1042" s="8" t="n">
@@ -31266,6 +31440,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>+54 11 4981-8978</t>
+        </is>
+      </c>
+      <c r="G1042" t="inlineStr">
+        <is>
+          <t>https://instagram.com/mcscota4500?utm_medium=copy_link</t>
+        </is>
+      </c>
     </row>
     <row r="1043" ht="15.75" customHeight="1" s="19">
       <c r="A1043" s="8" t="n">
@@ -31291,6 +31475,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1043" t="inlineStr"/>
+      <c r="G1043" t="inlineStr"/>
     </row>
     <row r="1044" ht="15.75" customHeight="1" s="19">
       <c r="A1044" s="8" t="n">
@@ -31316,6 +31502,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1044" t="inlineStr"/>
+      <c r="G1044" t="inlineStr"/>
     </row>
     <row r="1045" ht="15.75" customHeight="1" s="19">
       <c r="A1045" s="8" t="n">
@@ -31341,6 +31529,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1045" t="inlineStr"/>
+      <c r="G1045" t="inlineStr"/>
     </row>
     <row r="1046" ht="15.75" customHeight="1" s="19">
       <c r="A1046" s="8" t="n">
@@ -31366,6 +31556,12 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1046" t="inlineStr">
+        <is>
+          <t>+54 11 2598-6717</t>
+        </is>
+      </c>
+      <c r="G1046" t="inlineStr"/>
     </row>
     <row r="1047" ht="15.75" customHeight="1" s="19">
       <c r="A1047" s="8" t="n">
@@ -31391,6 +31587,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1047" t="inlineStr"/>
+      <c r="G1047" t="inlineStr"/>
     </row>
     <row r="1048" ht="15.75" customHeight="1" s="19">
       <c r="A1048" s="8" t="n">
@@ -31416,6 +31614,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1048" t="inlineStr"/>
+      <c r="G1048" t="inlineStr"/>
     </row>
     <row r="1049" ht="15.75" customHeight="1" s="19">
       <c r="A1049" s="8" t="n">
@@ -31441,6 +31641,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1049" t="inlineStr">
+        <is>
+          <t>+54 11 4864-9679</t>
+        </is>
+      </c>
+      <c r="G1049" t="inlineStr"/>
     </row>
     <row r="1050" ht="15.75" customHeight="1" s="19">
       <c r="A1050" s="8" t="n">
@@ -31466,6 +31672,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1050" t="inlineStr"/>
+      <c r="G1050" t="inlineStr"/>
     </row>
     <row r="1051" ht="15.75" customHeight="1" s="19">
       <c r="A1051" s="8" t="n">
@@ -31491,6 +31699,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1051" t="inlineStr"/>
+      <c r="G1051" t="inlineStr"/>
     </row>
     <row r="1052" ht="15.75" customHeight="1" s="19">
       <c r="A1052" s="8" t="n">
@@ -31514,6 +31724,16 @@
       <c r="E1052" s="9" t="inlineStr">
         <is>
           <t>Veterinaria</t>
+        </is>
+      </c>
+      <c r="F1052" t="inlineStr">
+        <is>
+          <t>+54 11 2238-1908</t>
+        </is>
+      </c>
+      <c r="G1052" t="inlineStr">
+        <is>
+          <t>http://www.sanjavucho.com.ar/</t>
         </is>
       </c>
     </row>

--- a/PUNTOS_DE_VENTA_completado.xlsx
+++ b/PUNTOS_DE_VENTA_completado.xlsx
@@ -31761,6 +31761,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1053" t="inlineStr"/>
+      <c r="G1053" t="inlineStr"/>
     </row>
     <row r="1054" ht="15.75" customHeight="1" s="19">
       <c r="A1054" s="8" t="n">
@@ -31786,6 +31788,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1054" t="inlineStr"/>
+      <c r="G1054" t="inlineStr"/>
     </row>
     <row r="1055" ht="15.75" customHeight="1" s="19">
       <c r="A1055" s="8" t="n">
@@ -31811,6 +31815,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1055" t="inlineStr">
+        <is>
+          <t>+54 11 4821-6894</t>
+        </is>
+      </c>
+      <c r="G1055" t="inlineStr">
+        <is>
+          <t>https://buscapeluqueria.com/comuna/buenos-aires/veterinaria-azcuenaga-peluqueria-canina-en-cdad-autonoma-de-buenos-aires/</t>
+        </is>
+      </c>
     </row>
     <row r="1056" ht="15.75" customHeight="1" s="19">
       <c r="A1056" s="8" t="n">
@@ -31836,6 +31850,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1056" t="inlineStr"/>
+      <c r="G1056" t="inlineStr"/>
     </row>
     <row r="1057" ht="15.75" customHeight="1" s="19">
       <c r="A1057" s="8" t="n">
@@ -31861,6 +31877,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1057" t="inlineStr">
+        <is>
+          <t>+54 11 6586-6681</t>
+        </is>
+      </c>
+      <c r="G1057" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mamanirest?igsh=MTJpM3ZuN3lqOXltdg==</t>
+        </is>
+      </c>
     </row>
     <row r="1058" ht="15.75" customHeight="1" s="19">
       <c r="A1058" s="8" t="n">
@@ -31886,6 +31912,16 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1058" t="inlineStr">
+        <is>
+          <t>+54 49413888</t>
+        </is>
+      </c>
+      <c r="G1058" t="inlineStr">
+        <is>
+          <t>http://www.discovery-pet.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1059" ht="15.75" customHeight="1" s="19">
       <c r="A1059" s="8" t="n">
@@ -31911,6 +31947,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1059" t="inlineStr"/>
+      <c r="G1059" t="inlineStr"/>
     </row>
     <row r="1060" ht="15.75" customHeight="1" s="19">
       <c r="A1060" s="8" t="n">
@@ -31936,6 +31974,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1060" t="inlineStr"/>
+      <c r="G1060" t="inlineStr"/>
     </row>
     <row r="1061" ht="15.75" customHeight="1" s="19">
       <c r="A1061" s="8" t="n">
@@ -31961,6 +32001,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1061" t="inlineStr"/>
+      <c r="G1061" t="inlineStr"/>
     </row>
     <row r="1062" ht="15.75" customHeight="1" s="19">
       <c r="A1062" s="8" t="n">
@@ -31986,6 +32028,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1062" t="inlineStr"/>
+      <c r="G1062" t="inlineStr"/>
     </row>
     <row r="1063" ht="15.75" customHeight="1" s="19">
       <c r="A1063" s="8" t="n">
@@ -32011,6 +32055,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1063" t="inlineStr"/>
+      <c r="G1063" t="inlineStr"/>
     </row>
     <row r="1064" ht="15.75" customHeight="1" s="19">
       <c r="A1064" s="8" t="n">
@@ -32036,6 +32082,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1064" t="inlineStr">
+        <is>
+          <t>+54 11 4361-0000</t>
+        </is>
+      </c>
+      <c r="G1064" t="inlineStr"/>
     </row>
     <row r="1065" ht="15.75" customHeight="1" s="19">
       <c r="A1065" s="8" t="n">
@@ -32061,6 +32113,16 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1065" t="inlineStr">
+        <is>
+          <t>+54 11 4772-7087</t>
+        </is>
+      </c>
+      <c r="G1065" t="inlineStr">
+        <is>
+          <t>http://www.institutogascon.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1066" ht="15.75" customHeight="1" s="19">
       <c r="A1066" s="8" t="n">
@@ -32086,6 +32148,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1066" t="inlineStr"/>
+      <c r="G1066" t="inlineStr"/>
     </row>
     <row r="1067" ht="15.75" customHeight="1" s="19">
       <c r="A1067" s="8" t="n">
@@ -32111,6 +32175,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1067" t="inlineStr"/>
+      <c r="G1067" t="inlineStr"/>
     </row>
     <row r="1068" ht="15.75" customHeight="1" s="19">
       <c r="A1068" s="8" t="n">
@@ -32136,6 +32202,12 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1068" t="inlineStr">
+        <is>
+          <t>+54 11 7064-2536</t>
+        </is>
+      </c>
+      <c r="G1068" t="inlineStr"/>
     </row>
     <row r="1069" ht="15.75" customHeight="1" s="19">
       <c r="A1069" s="8" t="n">
@@ -32161,6 +32233,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1069" t="inlineStr"/>
+      <c r="G1069" t="inlineStr"/>
     </row>
     <row r="1070" ht="15.75" customHeight="1" s="19">
       <c r="A1070" s="8" t="n">
@@ -32186,6 +32260,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1070" t="inlineStr">
+        <is>
+          <t>+54 11 4584-0194</t>
+        </is>
+      </c>
+      <c r="G1070" t="inlineStr">
+        <is>
+          <t>http://www.lapanerarosa.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1071" ht="15.75" customHeight="1" s="19">
       <c r="A1071" s="8" t="n">
@@ -32211,6 +32295,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1071" t="inlineStr"/>
+      <c r="G1071" t="inlineStr"/>
     </row>
     <row r="1072" ht="15.75" customHeight="1" s="19">
       <c r="A1072" s="8" t="n">
@@ -32236,6 +32322,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1072" t="inlineStr"/>
+      <c r="G1072" t="inlineStr"/>
     </row>
     <row r="1073" ht="15.75" customHeight="1" s="19">
       <c r="A1073" s="8" t="n">
@@ -32261,6 +32349,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1073" t="inlineStr"/>
+      <c r="G1073" t="inlineStr"/>
     </row>
     <row r="1074" ht="15.75" customHeight="1" s="19">
       <c r="A1074" s="8" t="n">
@@ -32286,6 +32376,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1074" t="inlineStr"/>
+      <c r="G1074" t="inlineStr"/>
     </row>
     <row r="1075" ht="15.75" customHeight="1" s="19">
       <c r="A1075" s="8" t="n">
@@ -32311,6 +32403,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1075" t="inlineStr"/>
+      <c r="G1075" t="inlineStr"/>
     </row>
     <row r="1076" ht="15.75" customHeight="1" s="19">
       <c r="A1076" s="8" t="n">
@@ -32336,6 +32430,12 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1076" t="inlineStr">
+        <is>
+          <t>+54 11 4767-1171</t>
+        </is>
+      </c>
+      <c r="G1076" t="inlineStr"/>
     </row>
     <row r="1077" ht="15.75" customHeight="1" s="19">
       <c r="A1077" s="8" t="n">
@@ -32359,6 +32459,12 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1077" t="inlineStr">
+        <is>
+          <t>+54 11 4993-5554</t>
+        </is>
+      </c>
+      <c r="G1077" t="inlineStr"/>
     </row>
     <row r="1078" ht="15.75" customHeight="1" s="19">
       <c r="A1078" s="8" t="n">
@@ -32384,6 +32490,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1078" t="inlineStr"/>
+      <c r="G1078" t="inlineStr"/>
     </row>
     <row r="1079" ht="15.75" customHeight="1" s="19">
       <c r="A1079" s="8" t="n">
@@ -32409,6 +32517,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1079" t="inlineStr"/>
+      <c r="G1079" t="inlineStr"/>
     </row>
     <row r="1080" ht="15.75" customHeight="1" s="19">
       <c r="A1080" s="8" t="n">
@@ -32434,6 +32544,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1080" t="inlineStr">
+        <is>
+          <t>+54 11 4241-9924</t>
+        </is>
+      </c>
+      <c r="G1080" t="inlineStr">
+        <is>
+          <t>http://www.foodmascotas.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1081" ht="15.75" customHeight="1" s="19">
       <c r="A1081" s="8" t="n">
@@ -32459,6 +32579,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1081" t="inlineStr">
+        <is>
+          <t>+54 11 4201-3274</t>
+        </is>
+      </c>
+      <c r="G1081" t="inlineStr">
+        <is>
+          <t>https://www.mundoanimalonline.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1082" ht="15.75" customHeight="1" s="19">
       <c r="A1082" s="8" t="n">
@@ -32484,6 +32614,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1082" t="inlineStr"/>
+      <c r="G1082" t="inlineStr"/>
     </row>
     <row r="1083" ht="15.75" customHeight="1" s="19">
       <c r="A1083" s="8" t="n">
@@ -32509,6 +32641,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1083" t="inlineStr"/>
+      <c r="G1083" t="inlineStr"/>
     </row>
     <row r="1084" ht="15.75" customHeight="1" s="19">
       <c r="A1084" s="8" t="n">
@@ -32534,6 +32668,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1084" t="inlineStr"/>
+      <c r="G1084" t="inlineStr"/>
     </row>
     <row r="1085" ht="15.75" customHeight="1" s="19">
       <c r="A1085" s="8" t="n">
@@ -32559,6 +32695,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1085" t="inlineStr"/>
+      <c r="G1085" t="inlineStr"/>
     </row>
     <row r="1086" ht="15.75" customHeight="1" s="19">
       <c r="A1086" s="8" t="n">
@@ -32584,6 +32722,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1086" t="inlineStr">
+        <is>
+          <t>+54 11 3802-4710</t>
+        </is>
+      </c>
+      <c r="G1086" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/petshopelmirador</t>
+        </is>
+      </c>
     </row>
     <row r="1087" ht="15.75" customHeight="1" s="19">
       <c r="A1087" s="8" t="n">
@@ -32609,6 +32757,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1087" t="inlineStr"/>
+      <c r="G1087" t="inlineStr"/>
     </row>
     <row r="1088" ht="15.75" customHeight="1" s="19">
       <c r="A1088" s="8" t="n">
@@ -32634,6 +32784,12 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1088" t="inlineStr">
+        <is>
+          <t>+54 11 5577-4540</t>
+        </is>
+      </c>
+      <c r="G1088" t="inlineStr"/>
     </row>
     <row r="1089" ht="15.75" customHeight="1" s="19">
       <c r="A1089" s="8" t="n">
@@ -32659,6 +32815,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1089" t="inlineStr"/>
+      <c r="G1089" t="inlineStr"/>
     </row>
     <row r="1090" ht="15.75" customHeight="1" s="19">
       <c r="A1090" s="8" t="n">
@@ -32684,6 +32842,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1090" t="inlineStr"/>
+      <c r="G1090" t="inlineStr"/>
     </row>
     <row r="1091" ht="15.75" customHeight="1" s="19">
       <c r="A1091" s="8" t="n">
@@ -32709,6 +32869,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1091" t="inlineStr"/>
+      <c r="G1091" t="inlineStr"/>
     </row>
     <row r="1092" ht="15.75" customHeight="1" s="19">
       <c r="A1092" s="8" t="n">
@@ -32734,6 +32896,12 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1092" t="inlineStr">
+        <is>
+          <t>+54 11 4750-0735</t>
+        </is>
+      </c>
+      <c r="G1092" t="inlineStr"/>
     </row>
     <row r="1093" ht="15.75" customHeight="1" s="19">
       <c r="A1093" s="8" t="n">
@@ -32759,6 +32927,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1093" t="inlineStr"/>
+      <c r="G1093" t="inlineStr"/>
     </row>
     <row r="1094" ht="15.75" customHeight="1" s="19">
       <c r="A1094" s="8" t="n">
@@ -32784,6 +32954,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1094" t="inlineStr">
+        <is>
+          <t>+54 11 4292-0484</t>
+        </is>
+      </c>
+      <c r="G1094" t="inlineStr">
+        <is>
+          <t>https://teamtecno.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1095" ht="15.75" customHeight="1" s="19">
       <c r="A1095" s="8" t="n">
@@ -32809,6 +32989,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1095" t="inlineStr"/>
+      <c r="G1095" t="inlineStr"/>
     </row>
     <row r="1096" ht="15.75" customHeight="1" s="19">
       <c r="A1096" s="8" t="n">
@@ -32834,6 +33016,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1096" t="inlineStr"/>
+      <c r="G1096" t="inlineStr"/>
     </row>
     <row r="1097" ht="15.75" customHeight="1" s="19">
       <c r="A1097" s="8" t="n">
@@ -32859,6 +33043,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1097" t="inlineStr"/>
+      <c r="G1097" t="inlineStr"/>
     </row>
     <row r="1098" ht="15.75" customHeight="1" s="19">
       <c r="A1098" s="8" t="n">
@@ -32884,6 +33070,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1098" t="inlineStr"/>
+      <c r="G1098" t="inlineStr"/>
     </row>
     <row r="1099" ht="15.75" customHeight="1" s="19">
       <c r="A1099" s="8" t="n">
@@ -32909,6 +33097,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1099" t="inlineStr"/>
+      <c r="G1099" t="inlineStr"/>
     </row>
     <row r="1100" ht="15.75" customHeight="1" s="19">
       <c r="A1100" s="8" t="n">
@@ -32934,6 +33124,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1100" t="inlineStr"/>
+      <c r="G1100" t="inlineStr"/>
     </row>
     <row r="1101" ht="15.75" customHeight="1" s="19">
       <c r="A1101" s="8" t="n">
@@ -32955,6 +33147,12 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1101" t="inlineStr"/>
+      <c r="G1101" t="inlineStr">
+        <is>
+          <t>http://www.argentina.gob.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1102" ht="15.75" customHeight="1" s="19">
       <c r="A1102" s="8" t="n">
@@ -32980,6 +33178,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1102" t="inlineStr"/>
+      <c r="G1102" t="inlineStr"/>
     </row>
     <row r="1103" ht="15.75" customHeight="1" s="19">
       <c r="A1103" s="8" t="n">

--- a/PUNTOS_DE_VENTA_completado.xlsx
+++ b/PUNTOS_DE_VENTA_completado.xlsx
@@ -33205,6 +33205,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F1103" t="inlineStr">
+        <is>
+          <t>+54 11 4702-7177</t>
+        </is>
+      </c>
+      <c r="G1103" t="inlineStr">
+        <is>
+          <t>http://www.faunatown.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1104" ht="15.75" customHeight="1" s="19">
       <c r="A1104" s="8" t="n">
@@ -33230,6 +33240,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1104" t="inlineStr"/>
+      <c r="G1104" t="inlineStr"/>
     </row>
     <row r="1105" ht="15.75" customHeight="1" s="19">
       <c r="A1105" s="8" t="n">
@@ -33255,6 +33267,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1105" t="inlineStr"/>
+      <c r="G1105" t="inlineStr"/>
     </row>
     <row r="1106" ht="15.75" customHeight="1" s="19">
       <c r="A1106" s="8" t="n">
@@ -33280,6 +33294,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1106" t="inlineStr"/>
+      <c r="G1106" t="inlineStr"/>
     </row>
     <row r="1107" ht="15.75" customHeight="1" s="19">
       <c r="A1107" s="8" t="n">
@@ -33305,6 +33321,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1107" t="inlineStr"/>
+      <c r="G1107" t="inlineStr"/>
     </row>
     <row r="1108" ht="15.75" customHeight="1" s="19">
       <c r="A1108" s="8" t="n">
@@ -33330,6 +33348,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1108" t="inlineStr"/>
+      <c r="G1108" t="inlineStr"/>
     </row>
     <row r="1109" ht="15.75" customHeight="1" s="19">
       <c r="A1109" s="8" t="n">
@@ -33355,6 +33375,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1109" t="inlineStr">
+        <is>
+          <t>+54 11 4488-7154</t>
+        </is>
+      </c>
+      <c r="G1109" t="inlineStr">
+        <is>
+          <t>http://www.elizalde.edu.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1110" ht="15.75" customHeight="1" s="19">
       <c r="A1110" s="8" t="n">
@@ -33380,6 +33410,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F1110" t="inlineStr">
+        <is>
+          <t>+54 11 4542-6610</t>
+        </is>
+      </c>
+      <c r="G1110" t="inlineStr">
+        <is>
+          <t>http://www.citypet.com.ar</t>
+        </is>
+      </c>
     </row>
     <row r="1111" ht="15.75" customHeight="1" s="19">
       <c r="A1111" s="8" t="n">
@@ -33405,6 +33445,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1111" t="inlineStr">
+        <is>
+          <t>+54 810-122-2424</t>
+        </is>
+      </c>
+      <c r="G1111" t="inlineStr">
+        <is>
+          <t>https://redbasa.com.ar/sanatorio-santa-clara-talar/</t>
+        </is>
+      </c>
     </row>
     <row r="1112" ht="15.75" customHeight="1" s="19">
       <c r="A1112" s="8" t="n">
@@ -33430,6 +33480,12 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F1112" t="inlineStr">
+        <is>
+          <t>+54 11 5250-9102</t>
+        </is>
+      </c>
+      <c r="G1112" t="inlineStr"/>
     </row>
     <row r="1113" ht="15.75" customHeight="1" s="19">
       <c r="A1113" s="8" t="n">
@@ -33455,6 +33511,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1113" t="inlineStr">
+        <is>
+          <t>+54 11 4711-9296</t>
+        </is>
+      </c>
+      <c r="G1113" t="inlineStr">
+        <is>
+          <t>https://vetegaray.mercadoshops.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1114" ht="15.75" customHeight="1" s="19">
       <c r="A1114" s="8" t="n">
@@ -33480,6 +33546,12 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F1114" t="inlineStr">
+        <is>
+          <t>+54 11 3679-5346</t>
+        </is>
+      </c>
+      <c r="G1114" t="inlineStr"/>
     </row>
     <row r="1115" ht="15.75" customHeight="1" s="19">
       <c r="A1115" s="8" t="n">
@@ -33505,6 +33577,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1115" t="inlineStr"/>
+      <c r="G1115" t="inlineStr"/>
     </row>
     <row r="1116" ht="15.75" customHeight="1" s="19">
       <c r="A1116" s="8" t="n">
@@ -33530,6 +33604,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1116" t="inlineStr"/>
+      <c r="G1116" t="inlineStr"/>
     </row>
     <row r="1117" ht="15.75" customHeight="1" s="19">
       <c r="A1117" s="8" t="n">
@@ -33555,6 +33631,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1117" t="inlineStr"/>
+      <c r="G1117" t="inlineStr"/>
     </row>
     <row r="1118" ht="15.75" customHeight="1" s="19">
       <c r="A1118" s="8" t="n">
@@ -33580,6 +33658,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1118" t="inlineStr"/>
+      <c r="G1118" t="inlineStr"/>
     </row>
     <row r="1119" ht="15.75" customHeight="1" s="19">
       <c r="A1119" s="8" t="n">
@@ -33605,6 +33685,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1119" t="inlineStr">
+        <is>
+          <t>+54 11 5637-4214</t>
+        </is>
+      </c>
+      <c r="G1119" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/veter.parana/</t>
+        </is>
+      </c>
     </row>
     <row r="1120" ht="15.75" customHeight="1" s="19">
       <c r="A1120" s="8" t="n">
@@ -33630,6 +33720,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1120" t="inlineStr"/>
+      <c r="G1120" t="inlineStr"/>
     </row>
     <row r="1121" ht="15.75" customHeight="1" s="19">
       <c r="A1121" s="8" t="n">
@@ -33655,6 +33747,12 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1121" t="inlineStr">
+        <is>
+          <t>+54 11 4763-9444</t>
+        </is>
+      </c>
+      <c r="G1121" t="inlineStr"/>
     </row>
     <row r="1122" ht="15.75" customHeight="1" s="19">
       <c r="A1122" s="8" t="n">
@@ -33680,6 +33778,12 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1122" t="inlineStr">
+        <is>
+          <t>+54 11 4709-9222</t>
+        </is>
+      </c>
+      <c r="G1122" t="inlineStr"/>
     </row>
     <row r="1123" ht="15.75" customHeight="1" s="19">
       <c r="A1123" s="8" t="n">
@@ -33705,6 +33809,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1123" t="inlineStr"/>
+      <c r="G1123" t="inlineStr"/>
     </row>
     <row r="1124" ht="15.75" customHeight="1" s="19">
       <c r="A1124" s="8" t="n">
@@ -33730,6 +33836,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1124" t="inlineStr">
+        <is>
+          <t>+54 11 4795-7918</t>
+        </is>
+      </c>
+      <c r="G1124" t="inlineStr">
+        <is>
+          <t>http://www.mivetshop.com.ar/shop/Danbar</t>
+        </is>
+      </c>
     </row>
     <row r="1125" ht="15.75" customHeight="1" s="19">
       <c r="A1125" s="8" t="n">
@@ -33755,6 +33871,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1125" t="inlineStr"/>
+      <c r="G1125" t="inlineStr"/>
     </row>
     <row r="1126" ht="15.75" customHeight="1" s="19">
       <c r="A1126" s="8" t="n">
@@ -33780,6 +33898,16 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1126" t="inlineStr">
+        <is>
+          <t>+54 11 2251-8118</t>
+        </is>
+      </c>
+      <c r="G1126" t="inlineStr">
+        <is>
+          <t>https://www.socialwapy.com/groovypets</t>
+        </is>
+      </c>
     </row>
     <row r="1127" ht="15.75" customHeight="1" s="19">
       <c r="A1127" s="8" t="n">
@@ -33805,6 +33933,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1127" t="inlineStr"/>
+      <c r="G1127" t="inlineStr"/>
     </row>
     <row r="1128" ht="15.75" customHeight="1" s="19">
       <c r="A1128" s="8" t="n">
@@ -33830,6 +33960,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1128" t="inlineStr">
+        <is>
+          <t>+54 9 11 2465-3582</t>
+        </is>
+      </c>
+      <c r="G1128" t="inlineStr">
+        <is>
+          <t>http://www.rehabilitacionvet.com/</t>
+        </is>
+      </c>
     </row>
     <row r="1129" ht="15.75" customHeight="1" s="19">
       <c r="A1129" s="8" t="n">
@@ -33855,6 +33995,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1129" t="inlineStr">
+        <is>
+          <t>+54 9 11 2675-6412</t>
+        </is>
+      </c>
+      <c r="G1129" t="inlineStr">
+        <is>
+          <t>http://www.vetmanchitas.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1130" ht="15.75" customHeight="1" s="19">
       <c r="A1130" s="8" t="n">
@@ -33880,6 +34030,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1130" t="inlineStr"/>
+      <c r="G1130" t="inlineStr"/>
     </row>
     <row r="1131" ht="15.75" customHeight="1" s="19">
       <c r="A1131" s="8" t="n">
@@ -33905,6 +34057,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1131" t="inlineStr"/>
+      <c r="G1131" t="inlineStr"/>
     </row>
     <row r="1132" ht="15.75" customHeight="1" s="19">
       <c r="A1132" s="8" t="n">
@@ -33930,6 +34084,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1132" t="inlineStr"/>
+      <c r="G1132" t="inlineStr"/>
     </row>
     <row r="1133" ht="15.75" customHeight="1" s="19">
       <c r="A1133" s="8" t="n">
@@ -33955,6 +34111,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1133" t="inlineStr">
+        <is>
+          <t>+54 11 4896-2813</t>
+        </is>
+      </c>
+      <c r="G1133" t="inlineStr">
+        <is>
+          <t>http://www.santaelenavet.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1134" ht="15.75" customHeight="1" s="19">
       <c r="A1134" s="8" t="n">
@@ -33980,6 +34146,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1134" t="inlineStr"/>
+      <c r="G1134" t="inlineStr"/>
     </row>
     <row r="1135" ht="15.75" customHeight="1" s="19">
       <c r="A1135" s="8" t="n">
@@ -34005,6 +34173,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1135" t="inlineStr"/>
+      <c r="G1135" t="inlineStr"/>
     </row>
     <row r="1136" ht="15.75" customHeight="1" s="19">
       <c r="A1136" s="8" t="n">
@@ -34030,6 +34200,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1136" t="inlineStr">
+        <is>
+          <t>+54 11 4770-9349</t>
+        </is>
+      </c>
+      <c r="G1136" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/veterinariapuchunis</t>
+        </is>
+      </c>
     </row>
     <row r="1137" ht="15.75" customHeight="1" s="19">
       <c r="A1137" s="8" t="n">
@@ -34055,6 +34235,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1137" t="inlineStr"/>
+      <c r="G1137" t="inlineStr"/>
     </row>
     <row r="1138" ht="15.75" customHeight="1" s="19">
       <c r="A1138" s="8" t="n">
@@ -34080,6 +34262,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1138" t="inlineStr"/>
+      <c r="G1138" t="inlineStr"/>
     </row>
     <row r="1139" ht="15.75" customHeight="1" s="19">
       <c r="A1139" s="8" t="n">
@@ -34105,6 +34289,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1139" t="inlineStr"/>
+      <c r="G1139" t="inlineStr"/>
     </row>
     <row r="1140" ht="15.75" customHeight="1" s="19">
       <c r="A1140" s="8" t="n">
@@ -34130,6 +34316,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1140" t="inlineStr"/>
+      <c r="G1140" t="inlineStr"/>
     </row>
     <row r="1141" ht="15.75" customHeight="1" s="19">
       <c r="A1141" s="8" t="n">
@@ -34155,6 +34343,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1141" t="inlineStr"/>
+      <c r="G1141" t="inlineStr"/>
     </row>
     <row r="1142" ht="15.75" customHeight="1" s="19">
       <c r="A1142" s="8" t="n">
@@ -34180,6 +34370,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1142" t="inlineStr"/>
+      <c r="G1142" t="inlineStr"/>
     </row>
     <row r="1143" ht="15.75" customHeight="1" s="19">
       <c r="A1143" s="8" t="n">
@@ -34205,6 +34397,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1143" t="inlineStr"/>
+      <c r="G1143" t="inlineStr"/>
     </row>
     <row r="1144" ht="15.75" customHeight="1" s="19">
       <c r="A1144" s="8" t="n">
@@ -34230,6 +34424,16 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1144" t="inlineStr">
+        <is>
+          <t>+54 11 5263-8786</t>
+        </is>
+      </c>
+      <c r="G1144" t="inlineStr">
+        <is>
+          <t>http://www.medclin.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1145" ht="15.75" customHeight="1" s="19">
       <c r="A1145" s="8" t="n">
@@ -34255,6 +34459,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1145" t="inlineStr"/>
+      <c r="G1145" t="inlineStr"/>
     </row>
     <row r="1146" ht="15.75" customHeight="1" s="19">
       <c r="A1146" s="8" t="n">
@@ -34276,6 +34482,12 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1146" t="inlineStr"/>
+      <c r="G1146" t="inlineStr">
+        <is>
+          <t>http://www.argentina.gob.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1147" ht="15.75" customHeight="1" s="19">
       <c r="A1147" s="8" t="n">
@@ -34301,6 +34513,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1147" t="inlineStr">
+        <is>
+          <t>+54 9 11 2391-7930</t>
+        </is>
+      </c>
+      <c r="G1147" t="inlineStr">
+        <is>
+          <t>https://msdientesblancos.wixsite.com/msod</t>
+        </is>
+      </c>
     </row>
     <row r="1148" ht="15.75" customHeight="1" s="19">
       <c r="A1148" s="8" t="n">
@@ -34326,6 +34548,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1148" t="inlineStr"/>
+      <c r="G1148" t="inlineStr"/>
     </row>
     <row r="1149" ht="15.75" customHeight="1" s="19">
       <c r="A1149" s="8" t="n">
@@ -34351,6 +34575,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F1149" t="inlineStr"/>
+      <c r="G1149" t="inlineStr"/>
     </row>
     <row r="1150" ht="15.75" customHeight="1" s="19">
       <c r="A1150" s="8" t="n">
@@ -34376,6 +34602,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1150" t="inlineStr"/>
+      <c r="G1150" t="inlineStr"/>
     </row>
     <row r="1151" ht="15.75" customHeight="1" s="19">
       <c r="A1151" s="8" t="n">
@@ -34401,6 +34629,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1151" t="inlineStr"/>
+      <c r="G1151" t="inlineStr"/>
     </row>
     <row r="1152" ht="15.75" customHeight="1" s="19">
       <c r="A1152" s="8" t="n">
@@ -34426,6 +34656,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1152" t="inlineStr">
+        <is>
+          <t>+54 11 4764-1302</t>
+        </is>
+      </c>
+      <c r="G1152" t="inlineStr"/>
     </row>
     <row r="1153" ht="15.75" customHeight="1" s="19">
       <c r="A1153" s="8" t="n">
@@ -34451,6 +34687,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1153" t="inlineStr"/>
+      <c r="G1153" t="inlineStr"/>
     </row>
     <row r="1154" ht="15.75" customHeight="1" s="19">
       <c r="A1154" s="8" t="n">
@@ -34476,6 +34714,12 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1154" t="inlineStr">
+        <is>
+          <t>+54 11 3515-4343</t>
+        </is>
+      </c>
+      <c r="G1154" t="inlineStr"/>
     </row>
     <row r="1155" ht="15.75" customHeight="1" s="19">
       <c r="A1155" s="8" t="n">
@@ -34501,6 +34745,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1155" t="inlineStr">
+        <is>
+          <t>+54 11 4855-3969</t>
+        </is>
+      </c>
+      <c r="G1155" t="inlineStr">
+        <is>
+          <t>https://instagram.com/veterinaria.pacalu?igshid=YmMyMTA2M2Y=</t>
+        </is>
+      </c>
     </row>
     <row r="1156" ht="15.75" customHeight="1" s="19">
       <c r="A1156" s="8" t="n">
@@ -34526,6 +34780,12 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1156" t="inlineStr">
+        <is>
+          <t>+54 11 4857-9111</t>
+        </is>
+      </c>
+      <c r="G1156" t="inlineStr"/>
     </row>
     <row r="1157" ht="15.75" customHeight="1" s="19">
       <c r="A1157" s="8" t="n">
@@ -34551,6 +34811,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1157" t="inlineStr"/>
+      <c r="G1157" t="inlineStr"/>
     </row>
     <row r="1158" ht="15.75" customHeight="1" s="19">
       <c r="A1158" s="8" t="n">
@@ -34576,6 +34838,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1158" t="inlineStr">
+        <is>
+          <t>+54 11 4437-4129</t>
+        </is>
+      </c>
+      <c r="G1158" t="inlineStr"/>
     </row>
     <row r="1159" ht="15.75" customHeight="1" s="19">
       <c r="A1159" s="8" t="n">
@@ -34601,6 +34869,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1159" t="inlineStr"/>
+      <c r="G1159" t="inlineStr"/>
     </row>
     <row r="1160" ht="15.75" customHeight="1" s="19">
       <c r="A1160" s="8" t="n">
@@ -34626,6 +34896,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1160" t="inlineStr"/>
+      <c r="G1160" t="inlineStr"/>
     </row>
     <row r="1161" ht="15.75" customHeight="1" s="19">
       <c r="A1161" s="8" t="n">
@@ -34651,6 +34923,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1161" t="inlineStr"/>
+      <c r="G1161" t="inlineStr"/>
     </row>
     <row r="1162" ht="15.75" customHeight="1" s="19">
       <c r="A1162" s="8" t="n">
@@ -34676,6 +34950,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1162" t="inlineStr"/>
+      <c r="G1162" t="inlineStr"/>
     </row>
     <row r="1163" ht="15.75" customHeight="1" s="19">
       <c r="A1163" s="8" t="n">
@@ -34701,6 +34977,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F1163" t="inlineStr"/>
+      <c r="G1163" t="inlineStr"/>
     </row>
     <row r="1164" ht="15.75" customHeight="1" s="19">
       <c r="A1164" s="8" t="n">
@@ -34726,6 +35004,12 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1164" t="inlineStr">
+        <is>
+          <t>+54 9 11 4037-9491</t>
+        </is>
+      </c>
+      <c r="G1164" t="inlineStr"/>
     </row>
     <row r="1165" ht="15.75" customHeight="1" s="19">
       <c r="A1165" s="8" t="n">
@@ -34751,6 +35035,12 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1165" t="inlineStr">
+        <is>
+          <t>+54 11 2596-4455</t>
+        </is>
+      </c>
+      <c r="G1165" t="inlineStr"/>
     </row>
     <row r="1166" ht="15.75" customHeight="1" s="19">
       <c r="A1166" s="8" t="n">
@@ -34776,6 +35066,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1166" t="inlineStr">
+        <is>
+          <t>+54 11 6601-0891</t>
+        </is>
+      </c>
+      <c r="G1166" t="inlineStr">
+        <is>
+          <t>https://viverpet2.mitiendanube.com/</t>
+        </is>
+      </c>
     </row>
     <row r="1167" ht="15.75" customHeight="1" s="19">
       <c r="A1167" s="8" t="n">
@@ -34801,6 +35101,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1167" t="inlineStr"/>
+      <c r="G1167" t="inlineStr"/>
     </row>
     <row r="1168" ht="15.75" customHeight="1" s="19">
       <c r="A1168" s="8" t="n">
@@ -34826,6 +35128,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1168" t="inlineStr">
+        <is>
+          <t>+54 11 4559-6094</t>
+        </is>
+      </c>
+      <c r="G1168" t="inlineStr"/>
     </row>
     <row r="1169" ht="15.75" customHeight="1" s="19">
       <c r="A1169" s="8" t="n">
@@ -34851,6 +35159,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1169" t="inlineStr"/>
+      <c r="G1169" t="inlineStr"/>
     </row>
     <row r="1170" ht="15.75" customHeight="1" s="19">
       <c r="A1170" s="8" t="n">
@@ -34876,6 +35186,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1170" t="inlineStr">
+        <is>
+          <t>+54 9 11 3239-9359</t>
+        </is>
+      </c>
+      <c r="G1170" t="inlineStr">
+        <is>
+          <t>https://www.forpet.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1171" ht="15.75" customHeight="1" s="19">
       <c r="A1171" s="8" t="n">
@@ -34901,6 +35221,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1171" t="inlineStr"/>
+      <c r="G1171" t="inlineStr"/>
     </row>
     <row r="1172" ht="15.75" customHeight="1" s="19">
       <c r="A1172" s="8" t="n">
@@ -34926,6 +35248,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1172" t="inlineStr">
+        <is>
+          <t>+54 11 2704-7274</t>
+        </is>
+      </c>
+      <c r="G1172" t="inlineStr">
+        <is>
+          <t>https://orthoea.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1173" ht="15.75" customHeight="1" s="19">
       <c r="A1173" s="8" t="n">
@@ -34951,6 +35283,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1173" t="inlineStr">
+        <is>
+          <t>+54 11 6848-0280</t>
+        </is>
+      </c>
+      <c r="G1173" t="inlineStr">
+        <is>
+          <t>https://instagram.com/veterinariashrek</t>
+        </is>
+      </c>
     </row>
     <row r="1174" ht="15.75" customHeight="1" s="19">
       <c r="A1174" s="8" t="n">
@@ -34976,6 +35318,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1174" t="inlineStr"/>
+      <c r="G1174" t="inlineStr"/>
     </row>
     <row r="1175" ht="15.75" customHeight="1" s="19">
       <c r="A1175" s="8" t="n">
@@ -35001,6 +35345,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1175" t="inlineStr">
+        <is>
+          <t>+54 9 11 5702-9942</t>
+        </is>
+      </c>
+      <c r="G1175" t="inlineStr">
+        <is>
+          <t>http://petsvelez.com/</t>
+        </is>
+      </c>
     </row>
     <row r="1176" ht="15.75" customHeight="1" s="19">
       <c r="A1176" s="8" t="n">
@@ -35026,6 +35380,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1176" t="inlineStr">
+        <is>
+          <t>+54 11 6089-0459</t>
+        </is>
+      </c>
+      <c r="G1176" t="inlineStr">
+        <is>
+          <t>https://traviesospetshop.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1177" ht="15.75" customHeight="1" s="19">
       <c r="A1177" s="8" t="n">
@@ -35051,6 +35415,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1177" t="inlineStr"/>
+      <c r="G1177" t="inlineStr"/>
     </row>
     <row r="1178" ht="15.75" customHeight="1" s="19">
       <c r="A1178" s="8" t="n">
@@ -35076,6 +35442,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1178" t="inlineStr"/>
+      <c r="G1178" t="inlineStr"/>
     </row>
     <row r="1179" ht="15.75" customHeight="1" s="19">
       <c r="A1179" s="8" t="n">
@@ -35101,6 +35469,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1179" t="inlineStr">
+        <is>
+          <t>+54 11 4664-5164</t>
+        </is>
+      </c>
+      <c r="G1179" t="inlineStr">
+        <is>
+          <t>https://instagram.com/petshopanimaladas?igshid=OGQ5ZDc2ODk2ZA==</t>
+        </is>
+      </c>
     </row>
     <row r="1180" ht="15.75" customHeight="1" s="19">
       <c r="A1180" s="8" t="n">
@@ -35126,6 +35504,12 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1180" t="inlineStr">
+        <is>
+          <t>+54 11 4243-2855</t>
+        </is>
+      </c>
+      <c r="G1180" t="inlineStr"/>
     </row>
     <row r="1181" ht="15.75" customHeight="1" s="19">
       <c r="A1181" s="8" t="n">
@@ -35151,6 +35535,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F1181" t="inlineStr">
+        <is>
+          <t>+54 221 504-2401</t>
+        </is>
+      </c>
+      <c r="G1181" t="inlineStr">
+        <is>
+          <t>https://www.epiventas.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1182" ht="15.75" customHeight="1" s="19">
       <c r="A1182" s="8" t="n">
@@ -35176,6 +35570,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1182" t="inlineStr">
+        <is>
+          <t>+54 11 3125-9467</t>
+        </is>
+      </c>
+      <c r="G1182" t="inlineStr">
+        <is>
+          <t>http://instagram.com/myfriendspalomar</t>
+        </is>
+      </c>
     </row>
     <row r="1183" ht="15.75" customHeight="1" s="19">
       <c r="A1183" s="8" t="n">
@@ -35201,6 +35605,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1183" t="inlineStr">
+        <is>
+          <t>+54 2202 42-2150</t>
+        </is>
+      </c>
+      <c r="G1183" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/instituto.larre/</t>
+        </is>
+      </c>
     </row>
     <row r="1184" ht="15.75" customHeight="1" s="19">
       <c r="A1184" s="8" t="n">
@@ -35226,6 +35640,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1184" t="inlineStr">
+        <is>
+          <t>+54 11 4659-6551</t>
+        </is>
+      </c>
+      <c r="G1184" t="inlineStr">
+        <is>
+          <t>http://www.mivetshop.com.ar/shop/vethaedo</t>
+        </is>
+      </c>
     </row>
     <row r="1185" ht="15.75" customHeight="1" s="19">
       <c r="A1185" s="8" t="n">
@@ -35251,6 +35675,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1185" t="inlineStr"/>
+      <c r="G1185" t="inlineStr"/>
     </row>
     <row r="1186" ht="15.75" customHeight="1" s="19">
       <c r="A1186" s="8" t="n">
@@ -35276,6 +35702,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1186" t="inlineStr"/>
+      <c r="G1186" t="inlineStr"/>
     </row>
     <row r="1187" ht="15.75" customHeight="1" s="19">
       <c r="A1187" s="8" t="n">
@@ -35301,6 +35729,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1187" t="inlineStr"/>
+      <c r="G1187" t="inlineStr"/>
     </row>
     <row r="1188" ht="15.75" customHeight="1" s="19">
       <c r="A1188" s="8" t="n">
@@ -35326,6 +35756,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1188" t="inlineStr"/>
+      <c r="G1188" t="inlineStr"/>
     </row>
     <row r="1189" ht="15.75" customHeight="1" s="19">
       <c r="A1189" s="8" t="n">
@@ -35351,6 +35783,12 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1189" t="inlineStr">
+        <is>
+          <t>+54 11 4629-9066</t>
+        </is>
+      </c>
+      <c r="G1189" t="inlineStr"/>
     </row>
     <row r="1190" ht="15.75" customHeight="1" s="19">
       <c r="A1190" s="8" t="n">
@@ -35376,6 +35814,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1190" t="inlineStr">
+        <is>
+          <t>+54 11 4658-0174</t>
+        </is>
+      </c>
+      <c r="G1190" t="inlineStr">
+        <is>
+          <t>http://www.proveter.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1191" ht="15.75" customHeight="1" s="19">
       <c r="A1191" s="8" t="n">
@@ -35401,6 +35849,12 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1191" t="inlineStr">
+        <is>
+          <t>+54 11 4484-6797</t>
+        </is>
+      </c>
+      <c r="G1191" t="inlineStr"/>
     </row>
     <row r="1192" ht="15.75" customHeight="1" s="19">
       <c r="A1192" s="8" t="n">
@@ -35426,6 +35880,12 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1192" t="inlineStr">
+        <is>
+          <t>+54 11 4656-8439</t>
+        </is>
+      </c>
+      <c r="G1192" t="inlineStr"/>
     </row>
     <row r="1193" ht="15.75" customHeight="1" s="19">
       <c r="A1193" s="8" t="n">
@@ -35451,6 +35911,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1193" t="inlineStr"/>
+      <c r="G1193" t="inlineStr"/>
     </row>
     <row r="1194" ht="15.75" customHeight="1" s="19">
       <c r="A1194" s="8" t="n">
@@ -35476,6 +35938,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1194" t="inlineStr"/>
+      <c r="G1194" t="inlineStr"/>
     </row>
     <row r="1195" ht="15.75" customHeight="1" s="19">
       <c r="A1195" s="8" t="n">
@@ -35501,6 +35965,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1195" t="inlineStr"/>
+      <c r="G1195" t="inlineStr"/>
     </row>
     <row r="1196" ht="15.75" customHeight="1" s="19">
       <c r="A1196" s="8" t="n">
@@ -35526,6 +35992,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1196" t="inlineStr"/>
+      <c r="G1196" t="inlineStr"/>
     </row>
     <row r="1197" ht="15.75" customHeight="1" s="19">
       <c r="A1197" s="8" t="n">
@@ -35551,6 +36019,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1197" t="inlineStr"/>
+      <c r="G1197" t="inlineStr"/>
     </row>
     <row r="1198" ht="15.75" customHeight="1" s="19">
       <c r="A1198" s="8" t="n">
@@ -35576,6 +36046,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1198" t="inlineStr"/>
+      <c r="G1198" t="inlineStr"/>
     </row>
     <row r="1199" ht="15.75" customHeight="1" s="19">
       <c r="A1199" s="8" t="n">
@@ -35601,6 +36073,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1199" t="inlineStr">
+        <is>
+          <t>+54 11 6397-1707</t>
+        </is>
+      </c>
+      <c r="G1199" t="inlineStr"/>
     </row>
     <row r="1200" ht="15.75" customHeight="1" s="19">
       <c r="A1200" s="8" t="n">
@@ -35626,6 +36104,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1200" t="inlineStr"/>
+      <c r="G1200" t="inlineStr"/>
     </row>
     <row r="1201" ht="15.75" customHeight="1" s="19">
       <c r="A1201" s="8" t="n">
@@ -35651,6 +36131,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1201" t="inlineStr"/>
+      <c r="G1201" t="inlineStr"/>
     </row>
     <row r="1202" ht="15.75" customHeight="1" s="19">
       <c r="A1202" s="8" t="n">
@@ -35676,6 +36158,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1202" t="inlineStr"/>
+      <c r="G1202" t="inlineStr"/>
     </row>
     <row r="1203" ht="15.75" customHeight="1" s="19">
       <c r="A1203" s="8" t="n">

--- a/PUNTOS_DE_VENTA_completado.xlsx
+++ b/PUNTOS_DE_VENTA_completado.xlsx
@@ -36185,6 +36185,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1203" t="inlineStr"/>
+      <c r="G1203" t="inlineStr"/>
     </row>
     <row r="1204" ht="15.75" customHeight="1" s="19">
       <c r="A1204" s="8" t="n">
@@ -36210,6 +36212,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1204" t="inlineStr"/>
+      <c r="G1204" t="inlineStr"/>
     </row>
     <row r="1205" ht="15.75" customHeight="1" s="19">
       <c r="A1205" s="8" t="n">
@@ -36235,6 +36239,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1205" t="inlineStr"/>
+      <c r="G1205" t="inlineStr"/>
     </row>
     <row r="1206" ht="15.75" customHeight="1" s="19">
       <c r="A1206" s="8" t="n">
@@ -36260,6 +36266,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1206" t="inlineStr"/>
+      <c r="G1206" t="inlineStr"/>
     </row>
     <row r="1207" ht="15.75" customHeight="1" s="19">
       <c r="A1207" s="8" t="n">
@@ -36285,6 +36293,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1207" t="inlineStr"/>
+      <c r="G1207" t="inlineStr"/>
     </row>
     <row r="1208" ht="15.75" customHeight="1" s="19">
       <c r="A1208" s="8" t="n">
@@ -36310,6 +36320,12 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F1208" t="inlineStr">
+        <is>
+          <t>+54 11 6837-4444</t>
+        </is>
+      </c>
+      <c r="G1208" t="inlineStr"/>
     </row>
     <row r="1209" ht="15.75" customHeight="1" s="19">
       <c r="A1209" s="8" t="n">
@@ -36335,6 +36351,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1209" t="inlineStr">
+        <is>
+          <t>+54 11 3511-2136</t>
+        </is>
+      </c>
+      <c r="G1209" t="inlineStr">
+        <is>
+          <t>http://www.mundoanimaldistribuidora.com/</t>
+        </is>
+      </c>
     </row>
     <row r="1210" ht="15.75" customHeight="1" s="19">
       <c r="A1210" s="8" t="n">
@@ -36360,6 +36386,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F1210" t="inlineStr"/>
+      <c r="G1210" t="inlineStr"/>
     </row>
     <row r="1211" ht="15.75" customHeight="1" s="19">
       <c r="A1211" s="8" t="n">
@@ -36385,6 +36413,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1211" t="inlineStr">
+        <is>
+          <t>+54 11 4629-3173</t>
+        </is>
+      </c>
+      <c r="G1211" t="inlineStr">
+        <is>
+          <t>https://cmmoron-bue.infd.edu.ar/sitio/</t>
+        </is>
+      </c>
     </row>
     <row r="1212" ht="15.75" customHeight="1" s="19">
       <c r="A1212" s="8" t="n">
@@ -36410,6 +36448,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1212" t="inlineStr"/>
+      <c r="G1212" t="inlineStr"/>
     </row>
     <row r="1213" ht="15.75" customHeight="1" s="19">
       <c r="A1213" s="8" t="n">
@@ -36435,6 +36475,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1213" t="inlineStr">
+        <is>
+          <t>+54 11 4408-2464</t>
+        </is>
+      </c>
+      <c r="G1213" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/petshopmimados/</t>
+        </is>
+      </c>
     </row>
     <row r="1214" ht="15.75" customHeight="1" s="19">
       <c r="A1214" s="8" t="n">
@@ -36460,6 +36510,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1214" t="inlineStr">
+        <is>
+          <t>+54 11 4003-4100</t>
+        </is>
+      </c>
+      <c r="G1214" t="inlineStr">
+        <is>
+          <t>https://www.bersa.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1215" ht="15.75" customHeight="1" s="19">
       <c r="A1215" s="8" t="n">
@@ -36485,6 +36545,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1215" t="inlineStr">
+        <is>
+          <t>+54 11 4422-3107</t>
+        </is>
+      </c>
+      <c r="G1215" t="inlineStr">
+        <is>
+          <t>http://sanatoriolatorresanjusto.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1216" ht="15.75" customHeight="1" s="19">
       <c r="A1216" s="8" t="n">
@@ -36510,6 +36580,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1216" t="inlineStr"/>
+      <c r="G1216" t="inlineStr"/>
     </row>
     <row r="1217" ht="15.75" customHeight="1" s="19">
       <c r="A1217" s="8" t="n">
@@ -36535,6 +36607,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1217" t="inlineStr">
+        <is>
+          <t>+54 11 4484-4991</t>
+        </is>
+      </c>
+      <c r="G1217" t="inlineStr"/>
     </row>
     <row r="1218" ht="15.75" customHeight="1" s="19">
       <c r="A1218" s="8" t="n">
@@ -36560,6 +36638,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F1218" t="inlineStr">
+        <is>
+          <t>+54 9 11 2390-1927</t>
+        </is>
+      </c>
+      <c r="G1218" t="inlineStr">
+        <is>
+          <t>http://www.crazypet.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1219" ht="15.75" customHeight="1" s="19">
       <c r="A1219" s="8" t="n">
@@ -36585,6 +36673,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F1219" t="inlineStr"/>
+      <c r="G1219" t="inlineStr"/>
     </row>
     <row r="1220" ht="15.75" customHeight="1" s="19">
       <c r="A1220" s="8" t="n">
@@ -36606,6 +36696,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1220" t="inlineStr"/>
+      <c r="G1220" t="inlineStr"/>
     </row>
     <row r="1221" ht="15.75" customHeight="1" s="19">
       <c r="A1221" s="8" t="n">
@@ -36631,6 +36723,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1221" t="inlineStr"/>
+      <c r="G1221" t="inlineStr"/>
     </row>
     <row r="1222" ht="15.75" customHeight="1" s="19">
       <c r="A1222" s="8" t="n">
@@ -36656,6 +36750,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1222" t="inlineStr"/>
+      <c r="G1222" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/optica_arlecchino/</t>
+        </is>
+      </c>
     </row>
     <row r="1223" ht="15.75" customHeight="1" s="19">
       <c r="A1223" s="8" t="n">
@@ -36681,6 +36781,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1223" t="inlineStr"/>
+      <c r="G1223" t="inlineStr"/>
     </row>
     <row r="1224" ht="15.75" customHeight="1" s="19">
       <c r="A1224" s="8" t="n">
@@ -36706,6 +36808,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1224" t="inlineStr">
+        <is>
+          <t>+54 11 6063-1404</t>
+        </is>
+      </c>
+      <c r="G1224" t="inlineStr"/>
     </row>
     <row r="1225" ht="15.75" customHeight="1" s="19">
       <c r="A1225" s="8" t="n">
@@ -36731,6 +36839,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1225" t="inlineStr"/>
+      <c r="G1225" t="inlineStr"/>
     </row>
     <row r="1226" ht="15.75" customHeight="1" s="19">
       <c r="A1226" s="8" t="n">
@@ -36756,6 +36866,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1226" t="inlineStr">
+        <is>
+          <t>+54 11 4484-9416</t>
+        </is>
+      </c>
+      <c r="G1226" t="inlineStr"/>
     </row>
     <row r="1227" ht="15.75" customHeight="1" s="19">
       <c r="A1227" s="8" t="n">
@@ -36781,6 +36897,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1227" t="inlineStr"/>
+      <c r="G1227" t="inlineStr"/>
     </row>
     <row r="1228" ht="15.75" customHeight="1" s="19">
       <c r="A1228" s="8" t="n">
@@ -36806,6 +36924,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1228" t="inlineStr"/>
+      <c r="G1228" t="inlineStr"/>
     </row>
     <row r="1229" ht="15.75" customHeight="1" s="19">
       <c r="A1229" s="8" t="n">
@@ -36831,6 +36951,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1229" t="inlineStr"/>
+      <c r="G1229" t="inlineStr"/>
     </row>
     <row r="1230" ht="15.75" customHeight="1" s="19">
       <c r="A1230" s="8" t="n">
@@ -36856,6 +36978,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1230" t="inlineStr"/>
+      <c r="G1230" t="inlineStr"/>
     </row>
     <row r="1231" ht="15.75" customHeight="1" s="19">
       <c r="A1231" s="8" t="n">
@@ -36881,6 +37005,16 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1231" t="inlineStr">
+        <is>
+          <t>+54 11 4203-8529</t>
+        </is>
+      </c>
+      <c r="G1231" t="inlineStr">
+        <is>
+          <t>http://www.dieguezehijos.com/</t>
+        </is>
+      </c>
     </row>
     <row r="1232" ht="15.75" customHeight="1" s="19">
       <c r="A1232" s="8" t="n">
@@ -36906,6 +37040,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F1232" t="inlineStr"/>
+      <c r="G1232" t="inlineStr"/>
     </row>
     <row r="1233" ht="15.75" customHeight="1" s="19">
       <c r="A1233" s="8" t="n">
@@ -36931,6 +37067,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1233" t="inlineStr"/>
+      <c r="G1233" t="inlineStr"/>
     </row>
     <row r="1234" ht="15.75" customHeight="1" s="19">
       <c r="A1234" s="8" t="n">
@@ -36956,6 +37094,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F1234" t="inlineStr"/>
+      <c r="G1234" t="inlineStr"/>
     </row>
     <row r="1235" ht="15.75" customHeight="1" s="19">
       <c r="A1235" s="8" t="n">
@@ -36981,6 +37121,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F1235" t="inlineStr"/>
+      <c r="G1235" t="inlineStr"/>
     </row>
     <row r="1236" ht="15.75" customHeight="1" s="19">
       <c r="A1236" s="8" t="n">
@@ -37006,6 +37148,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1236" t="inlineStr">
+        <is>
+          <t>+54 9 11 3685-5540</t>
+        </is>
+      </c>
+      <c r="G1236" t="inlineStr">
+        <is>
+          <t>http://estaciondebebidas.com/</t>
+        </is>
+      </c>
     </row>
     <row r="1237" ht="15.75" customHeight="1" s="19">
       <c r="A1237" s="8" t="n">
@@ -37031,6 +37183,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1237" t="inlineStr"/>
+      <c r="G1237" t="inlineStr"/>
     </row>
     <row r="1238" ht="15.75" customHeight="1" s="19">
       <c r="A1238" s="8" t="n">
@@ -37056,6 +37210,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1238" t="inlineStr"/>
+      <c r="G1238" t="inlineStr"/>
     </row>
     <row r="1239" ht="15.75" customHeight="1" s="19">
       <c r="A1239" s="8" t="n">
@@ -37081,6 +37237,16 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F1239" t="inlineStr">
+        <is>
+          <t>+54 11 4242-8776</t>
+        </is>
+      </c>
+      <c r="G1239" t="inlineStr">
+        <is>
+          <t>http://lamascotadeportes.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1240" ht="15.75" customHeight="1" s="19">
       <c r="A1240" s="8" t="n">
@@ -37106,6 +37272,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F1240" t="inlineStr"/>
+      <c r="G1240" t="inlineStr"/>
     </row>
     <row r="1241" ht="15.75" customHeight="1" s="19">
       <c r="A1241" s="8" t="n">
@@ -37131,6 +37299,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1241" t="inlineStr"/>
+      <c r="G1241" t="inlineStr"/>
     </row>
     <row r="1242" ht="15.75" customHeight="1" s="19">
       <c r="A1242" s="8" t="n">
@@ -37156,6 +37326,12 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F1242" t="inlineStr">
+        <is>
+          <t>+54 11 4629-8282</t>
+        </is>
+      </c>
+      <c r="G1242" t="inlineStr"/>
     </row>
     <row r="1243" ht="15.75" customHeight="1" s="19">
       <c r="A1243" s="8" t="n">
@@ -37181,6 +37357,16 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F1243" t="inlineStr">
+        <is>
+          <t>+54 11 4270-0305</t>
+        </is>
+      </c>
+      <c r="G1243" t="inlineStr">
+        <is>
+          <t>https://distrisuronline.com/</t>
+        </is>
+      </c>
     </row>
     <row r="1244" ht="15.75" customHeight="1" s="19">
       <c r="A1244" s="8" t="n">
@@ -37206,6 +37392,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1244" t="inlineStr"/>
+      <c r="G1244" t="inlineStr"/>
     </row>
     <row r="1245" ht="15.75" customHeight="1" s="19">
       <c r="A1245" s="8" t="n">
@@ -37231,6 +37419,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F1245" t="inlineStr"/>
+      <c r="G1245" t="inlineStr"/>
     </row>
     <row r="1246" ht="15.75" customHeight="1" s="19">
       <c r="A1246" s="8" t="n">
@@ -37256,6 +37446,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F1246" t="inlineStr"/>
+      <c r="G1246" t="inlineStr"/>
     </row>
     <row r="1247" ht="15.75" customHeight="1" s="19">
       <c r="A1247" s="8" t="n">
@@ -37281,6 +37473,12 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1247" t="inlineStr">
+        <is>
+          <t>+54 11 7711-9161</t>
+        </is>
+      </c>
+      <c r="G1247" t="inlineStr"/>
     </row>
     <row r="1248" ht="15.75" customHeight="1" s="19">
       <c r="A1248" s="8" t="n">
@@ -37306,6 +37504,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1248" t="inlineStr"/>
+      <c r="G1248" t="inlineStr"/>
     </row>
     <row r="1249" ht="15.75" customHeight="1" s="19">
       <c r="A1249" s="8" t="n">
@@ -37331,6 +37531,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1249" t="inlineStr"/>
+      <c r="G1249" t="inlineStr"/>
     </row>
     <row r="1250" ht="15.75" customHeight="1" s="19">
       <c r="A1250" s="8" t="n">
@@ -37356,6 +37558,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1250" t="inlineStr">
+        <is>
+          <t>+54 11 5700-0363</t>
+        </is>
+      </c>
+      <c r="G1250" t="inlineStr"/>
     </row>
     <row r="1251" ht="15.75" customHeight="1" s="19">
       <c r="A1251" s="8" t="n">
@@ -37381,6 +37589,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1251" t="inlineStr"/>
+      <c r="G1251" t="inlineStr"/>
     </row>
     <row r="1252" ht="15.75" customHeight="1" s="19">
       <c r="A1252" s="8" t="n">
@@ -37404,6 +37614,16 @@
       <c r="E1252" s="8" t="inlineStr">
         <is>
           <t>Pet Shop</t>
+        </is>
+      </c>
+      <c r="F1252" t="inlineStr">
+        <is>
+          <t>+54 9 11 2555-0230</t>
+        </is>
+      </c>
+      <c r="G1252" t="inlineStr">
+        <is>
+          <t>http://www.espacioactiva.com/</t>
         </is>
       </c>
     </row>

--- a/PUNTOS_DE_VENTA_completado.xlsx
+++ b/PUNTOS_DE_VENTA_completado.xlsx
@@ -37651,6 +37651,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1253" t="inlineStr"/>
+      <c r="G1253" t="inlineStr"/>
     </row>
     <row r="1254" ht="15.75" customHeight="1" s="19">
       <c r="A1254" s="8" t="n">
@@ -37676,6 +37678,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1254" t="inlineStr"/>
+      <c r="G1254" t="inlineStr"/>
     </row>
     <row r="1255" ht="15.75" customHeight="1" s="19">
       <c r="A1255" s="8" t="n">
@@ -37701,6 +37705,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1255" t="inlineStr"/>
+      <c r="G1255" t="inlineStr"/>
     </row>
     <row r="1256" ht="15.75" customHeight="1" s="19">
       <c r="A1256" s="8" t="n">
@@ -37726,6 +37732,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1256" t="inlineStr"/>
+      <c r="G1256" t="inlineStr"/>
     </row>
     <row r="1257" ht="15.75" customHeight="1" s="19">
       <c r="A1257" s="8" t="n">
@@ -37751,6 +37759,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1257" t="inlineStr"/>
+      <c r="G1257" t="inlineStr"/>
     </row>
     <row r="1258" ht="15.75" customHeight="1" s="19">
       <c r="A1258" s="8" t="n">
@@ -37776,6 +37786,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1258" t="inlineStr">
+        <is>
+          <t>+54 11 2319-2222</t>
+        </is>
+      </c>
+      <c r="G1258" t="inlineStr"/>
     </row>
     <row r="1259" ht="15.75" customHeight="1" s="19">
       <c r="A1259" s="8" t="n">
@@ -37801,6 +37817,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1259" t="inlineStr">
+        <is>
+          <t>+54 11 7174-6015</t>
+        </is>
+      </c>
+      <c r="G1259" t="inlineStr">
+        <is>
+          <t>https://www.topdoctors.com.ar/doctor/nicolas-avellaneda/</t>
+        </is>
+      </c>
     </row>
     <row r="1260" ht="15.75" customHeight="1" s="19">
       <c r="A1260" s="8" t="n">
@@ -37826,6 +37852,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1260" t="inlineStr"/>
+      <c r="G1260" t="inlineStr"/>
     </row>
     <row r="1261" ht="15.75" customHeight="1" s="19">
       <c r="A1261" s="8" t="n">
@@ -37851,6 +37879,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1261" t="inlineStr"/>
+      <c r="G1261" t="inlineStr"/>
     </row>
     <row r="1262" ht="15.75" customHeight="1" s="19">
       <c r="A1262" s="8" t="n">
@@ -37876,6 +37906,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1262" t="inlineStr"/>
+      <c r="G1262" t="inlineStr"/>
     </row>
     <row r="1263" ht="15.75" customHeight="1" s="19">
       <c r="A1263" s="8" t="n">
@@ -37901,6 +37933,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1263" t="inlineStr"/>
+      <c r="G1263" t="inlineStr"/>
     </row>
     <row r="1264" ht="15.75" customHeight="1" s="19">
       <c r="A1264" s="8" t="n">
@@ -37926,6 +37960,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1264" t="inlineStr"/>
+      <c r="G1264" t="inlineStr"/>
     </row>
     <row r="1265" ht="15.75" customHeight="1" s="19">
       <c r="A1265" s="8" t="n">
@@ -37951,6 +37987,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1265" t="inlineStr"/>
+      <c r="G1265" t="inlineStr"/>
     </row>
     <row r="1266" ht="15.75" customHeight="1" s="19">
       <c r="A1266" s="8" t="n">
@@ -37976,6 +38014,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1266" t="inlineStr"/>
+      <c r="G1266" t="inlineStr"/>
     </row>
     <row r="1267" ht="15.75" customHeight="1" s="19">
       <c r="A1267" s="8" t="n">
@@ -38001,6 +38041,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1267" t="inlineStr"/>
+      <c r="G1267" t="inlineStr"/>
     </row>
     <row r="1268" ht="15.75" customHeight="1" s="19">
       <c r="A1268" s="8" t="n">
@@ -38026,6 +38068,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1268" t="inlineStr"/>
+      <c r="G1268" t="inlineStr"/>
     </row>
     <row r="1269" ht="15.75" customHeight="1" s="19">
       <c r="A1269" s="8" t="n">
@@ -38051,6 +38095,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1269" t="inlineStr"/>
+      <c r="G1269" t="inlineStr"/>
     </row>
     <row r="1270" ht="15.75" customHeight="1" s="19">
       <c r="A1270" s="8" t="n">
@@ -38076,6 +38122,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1270" t="inlineStr">
+        <is>
+          <t>+54 221 451-9982</t>
+        </is>
+      </c>
+      <c r="G1270" t="inlineStr"/>
     </row>
     <row r="1271" ht="15.75" customHeight="1" s="19">
       <c r="A1271" s="8" t="n">
@@ -38101,6 +38153,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1271" t="inlineStr">
+        <is>
+          <t>+54 9 11 6517-8186</t>
+        </is>
+      </c>
+      <c r="G1271" t="inlineStr">
+        <is>
+          <t>https://www.salvajeydulce.com.ar/?utm_source=ig&amp;utm_medium=social&amp;utm_content=link_in_bio&amp;fbclid=PAdGRleAO-UApleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA8xMjQwMjQ1NzQyODc0MTQAAadj3RQzDdx81Kw2X3XS21J89W7dnWPmqHffhhd8sQZ7AWOK78FECbuA6Tzq2Q_aem_0z75KMoSROkI3nfLKc6fGA</t>
+        </is>
+      </c>
     </row>
     <row r="1272" ht="15.75" customHeight="1" s="19">
       <c r="A1272" s="8" t="n">
@@ -38126,6 +38188,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1272" t="inlineStr"/>
+      <c r="G1272" t="inlineStr"/>
     </row>
     <row r="1273" ht="15.75" customHeight="1" s="19">
       <c r="A1273" s="8" t="n">
@@ -38151,6 +38215,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1273" t="inlineStr"/>
+      <c r="G1273" t="inlineStr"/>
     </row>
     <row r="1274" ht="15.75" customHeight="1" s="19">
       <c r="A1274" s="8" t="n">
@@ -38176,6 +38242,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1274" t="inlineStr"/>
+      <c r="G1274" t="inlineStr"/>
     </row>
     <row r="1275" ht="15.75" customHeight="1" s="19">
       <c r="A1275" s="8" t="n">
@@ -38201,6 +38269,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1275" t="inlineStr"/>
+      <c r="G1275" t="inlineStr"/>
     </row>
     <row r="1276" ht="15.75" customHeight="1" s="19">
       <c r="A1276" s="8" t="n">
@@ -38226,6 +38296,12 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F1276" t="inlineStr">
+        <is>
+          <t>+54 11 4251-2416</t>
+        </is>
+      </c>
+      <c r="G1276" t="inlineStr"/>
     </row>
     <row r="1277" ht="15.75" customHeight="1" s="19">
       <c r="A1277" s="8" t="n">
@@ -38251,6 +38327,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1277" t="inlineStr">
+        <is>
+          <t>+54 11 3090-6175</t>
+        </is>
+      </c>
+      <c r="G1277" t="inlineStr"/>
     </row>
     <row r="1278" ht="15.75" customHeight="1" s="19">
       <c r="A1278" s="8" t="n">
@@ -38276,6 +38358,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1278" t="inlineStr"/>
+      <c r="G1278" t="inlineStr"/>
     </row>
     <row r="1279" ht="15.75" customHeight="1" s="19">
       <c r="A1279" s="8" t="n">
@@ -38297,6 +38381,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1279" t="inlineStr">
+        <is>
+          <t>+54 9 11 4409-0000</t>
+        </is>
+      </c>
+      <c r="G1279" t="inlineStr">
+        <is>
+          <t>http://www.laurafarias.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1280" ht="15.75" customHeight="1" s="19">
       <c r="A1280" s="8" t="n">
@@ -38322,6 +38416,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1280" t="inlineStr">
+        <is>
+          <t>+54 11 3038-4229</t>
+        </is>
+      </c>
+      <c r="G1280" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/brown.bodegonargentino?igsh=YnJ5bTdvMXR2ZXJ4</t>
+        </is>
+      </c>
     </row>
     <row r="1281" ht="15.75" customHeight="1" s="19">
       <c r="A1281" s="8" t="n">
@@ -38343,6 +38447,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1281" t="inlineStr"/>
+      <c r="G1281" t="inlineStr">
+        <is>
+          <t>http://www.argentina.gob.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1282" ht="15.75" customHeight="1" s="19">
       <c r="A1282" s="8" t="n">
@@ -38368,6 +38478,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1282" t="inlineStr"/>
+      <c r="G1282" t="inlineStr"/>
     </row>
     <row r="1283" ht="15.75" customHeight="1" s="19">
       <c r="A1283" s="8" t="n">
@@ -38393,6 +38505,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1283" t="inlineStr"/>
+      <c r="G1283" t="inlineStr"/>
     </row>
     <row r="1284" ht="15.75" customHeight="1" s="19">
       <c r="A1284" s="8" t="n">
@@ -38418,6 +38532,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1284" t="inlineStr"/>
+      <c r="G1284" t="inlineStr"/>
     </row>
     <row r="1285" ht="15.75" customHeight="1" s="19">
       <c r="A1285" s="8" t="n">
@@ -38443,6 +38559,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1285" t="inlineStr"/>
+      <c r="G1285" t="inlineStr"/>
     </row>
     <row r="1286" ht="15.75" customHeight="1" s="19">
       <c r="A1286" s="8" t="n">
@@ -38468,6 +38586,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1286" t="inlineStr"/>
+      <c r="G1286" t="inlineStr"/>
     </row>
     <row r="1287" ht="15.75" customHeight="1" s="19">
       <c r="A1287" s="8" t="n">
@@ -38493,6 +38613,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1287" t="inlineStr">
+        <is>
+          <t>+54 11 4635-4080</t>
+        </is>
+      </c>
+      <c r="G1287" t="inlineStr">
+        <is>
+          <t>https://www.belcarautoelevador.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1288" ht="15.75" customHeight="1" s="19">
       <c r="A1288" s="8" t="n">
@@ -38518,6 +38648,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1288" t="inlineStr"/>
+      <c r="G1288" t="inlineStr"/>
     </row>
     <row r="1289" ht="15.75" customHeight="1" s="19">
       <c r="A1289" s="8" t="n">
@@ -38543,6 +38675,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1289" t="inlineStr"/>
+      <c r="G1289" t="inlineStr"/>
     </row>
     <row r="1290" ht="15.75" customHeight="1" s="19">
       <c r="A1290" s="8" t="n">
@@ -38568,6 +38702,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1290" t="inlineStr"/>
+      <c r="G1290" t="inlineStr"/>
     </row>
     <row r="1291" ht="15.75" customHeight="1" s="19">
       <c r="A1291" s="8" t="n">
@@ -38589,6 +38725,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1291" t="inlineStr"/>
+      <c r="G1291" t="inlineStr">
+        <is>
+          <t>http://www.argentina.gob.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1292" ht="15.75" customHeight="1" s="19">
       <c r="A1292" s="8" t="n">
@@ -38614,6 +38756,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1292" t="inlineStr"/>
+      <c r="G1292" t="inlineStr"/>
     </row>
     <row r="1293" ht="15.75" customHeight="1" s="19">
       <c r="A1293" s="8" t="n">
@@ -38639,6 +38783,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1293" t="inlineStr"/>
+      <c r="G1293" t="inlineStr"/>
     </row>
     <row r="1294" ht="15.75" customHeight="1" s="19">
       <c r="A1294" s="8" t="n">
@@ -38664,6 +38810,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1294" t="inlineStr">
+        <is>
+          <t>+54 9 11 2511-7999</t>
+        </is>
+      </c>
+      <c r="G1294" t="inlineStr">
+        <is>
+          <t>https://bazarycia.com/</t>
+        </is>
+      </c>
     </row>
     <row r="1295" ht="15.75" customHeight="1" s="19">
       <c r="A1295" s="8" t="n">
@@ -38689,6 +38845,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1295" t="inlineStr"/>
+      <c r="G1295" t="inlineStr"/>
     </row>
     <row r="1296" ht="15.75" customHeight="1" s="19">
       <c r="A1296" s="8" t="n">
@@ -38714,6 +38872,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1296" t="inlineStr"/>
+      <c r="G1296" t="inlineStr"/>
     </row>
     <row r="1297" ht="15.75" customHeight="1" s="19">
       <c r="A1297" s="8" t="n">
@@ -38739,6 +38899,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1297" t="inlineStr"/>
+      <c r="G1297" t="inlineStr"/>
     </row>
     <row r="1298" ht="15.75" customHeight="1" s="19">
       <c r="A1298" s="8" t="n">
@@ -38764,6 +38926,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1298" t="inlineStr"/>
+      <c r="G1298" t="inlineStr"/>
     </row>
     <row r="1299" ht="15.75" customHeight="1" s="19">
       <c r="A1299" s="8" t="n">
@@ -38789,6 +38953,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1299" t="inlineStr"/>
+      <c r="G1299" t="inlineStr"/>
     </row>
     <row r="1300" ht="15.75" customHeight="1" s="19">
       <c r="A1300" s="8" t="n">
@@ -38814,6 +38980,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1300" t="inlineStr"/>
+      <c r="G1300" t="inlineStr"/>
     </row>
     <row r="1301" ht="15.75" customHeight="1" s="19">
       <c r="A1301" s="8" t="n">
@@ -38839,6 +39007,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1301" t="inlineStr"/>
+      <c r="G1301" t="inlineStr"/>
     </row>
     <row r="1302" ht="15.75" customHeight="1" s="19">
       <c r="A1302" s="8" t="n">
@@ -38864,6 +39034,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1302" t="inlineStr">
+        <is>
+          <t>+54 11 4656-8121</t>
+        </is>
+      </c>
+      <c r="G1302" t="inlineStr">
+        <is>
+          <t>https://instagram.com/panaderiarm?igshid=YmMyMTA2M2Y=</t>
+        </is>
+      </c>
     </row>
     <row r="1303" ht="15.75" customHeight="1" s="19">
       <c r="A1303" s="8" t="n">
@@ -38889,6 +39069,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1303" t="inlineStr">
+        <is>
+          <t>+54 11 4656-2398</t>
+        </is>
+      </c>
+      <c r="G1303" t="inlineStr"/>
     </row>
     <row r="1304" ht="15.75" customHeight="1" s="19">
       <c r="A1304" s="8" t="n">
@@ -38914,6 +39100,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1304" t="inlineStr"/>
+      <c r="G1304" t="inlineStr"/>
     </row>
     <row r="1305" ht="15.75" customHeight="1" s="19">
       <c r="A1305" s="8" t="n">
@@ -38939,6 +39127,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1305" t="inlineStr">
+        <is>
+          <t>+54 11 4003-4100</t>
+        </is>
+      </c>
+      <c r="G1305" t="inlineStr">
+        <is>
+          <t>https://www.bersa.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1306" ht="15.75" customHeight="1" s="19">
       <c r="A1306" s="8" t="n">
@@ -38964,6 +39162,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1306" t="inlineStr">
+        <is>
+          <t>+54 11 6211-6938</t>
+        </is>
+      </c>
+      <c r="G1306" t="inlineStr">
+        <is>
+          <t>https://tuturno.io/centrodesaludybelleza</t>
+        </is>
+      </c>
     </row>
     <row r="1307" ht="15.75" customHeight="1" s="19">
       <c r="A1307" s="8" t="n">
@@ -38989,6 +39197,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1307" t="inlineStr"/>
+      <c r="G1307" t="inlineStr"/>
     </row>
     <row r="1308" ht="15.75" customHeight="1" s="19">
       <c r="A1308" s="8" t="n">
@@ -39014,6 +39224,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1308" t="inlineStr"/>
+      <c r="G1308" t="inlineStr"/>
     </row>
     <row r="1309" ht="15.75" customHeight="1" s="19">
       <c r="A1309" s="8" t="n">
@@ -39039,6 +39251,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1309" t="inlineStr"/>
+      <c r="G1309" t="inlineStr"/>
     </row>
     <row r="1310" ht="15.75" customHeight="1" s="19">
       <c r="A1310" s="8" t="n">
@@ -39064,6 +39278,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1310" t="inlineStr"/>
+      <c r="G1310" t="inlineStr"/>
     </row>
     <row r="1311" ht="15.75" customHeight="1" s="19">
       <c r="A1311" s="8" t="n">
@@ -39085,6 +39301,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1311" t="inlineStr"/>
+      <c r="G1311" t="inlineStr">
+        <is>
+          <t>http://www.argentina.gob.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1312" ht="15.75" customHeight="1" s="19">
       <c r="A1312" s="8" t="n">
@@ -39106,6 +39328,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1312" t="inlineStr">
+        <is>
+          <t>+595 767 240 606</t>
+        </is>
+      </c>
+      <c r="G1312" t="inlineStr">
+        <is>
+          <t>http://www.lasaeta.com.py/</t>
+        </is>
+      </c>
     </row>
     <row r="1313" ht="15.75" customHeight="1" s="19">
       <c r="A1313" s="8" t="n">
@@ -39127,6 +39359,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1313" t="inlineStr"/>
+      <c r="G1313" t="inlineStr">
+        <is>
+          <t>http://www.argentina.gob.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1314" ht="15.75" customHeight="1" s="19">
       <c r="A1314" s="8" t="n">
@@ -39148,6 +39386,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1314" t="inlineStr"/>
+      <c r="G1314" t="inlineStr">
+        <is>
+          <t>http://www.argentina.gob.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1315" ht="15.75" customHeight="1" s="19">
       <c r="A1315" s="8" t="n">
@@ -39173,6 +39417,12 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1315" t="inlineStr">
+        <is>
+          <t>+54 11 4254-1885</t>
+        </is>
+      </c>
+      <c r="G1315" t="inlineStr"/>
     </row>
     <row r="1316" ht="15.75" customHeight="1" s="19">
       <c r="A1316" s="8" t="n">
@@ -39198,6 +39448,12 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1316" t="inlineStr">
+        <is>
+          <t>+54 11 3609-3548</t>
+        </is>
+      </c>
+      <c r="G1316" t="inlineStr"/>
     </row>
     <row r="1317" ht="15.75" customHeight="1" s="19">
       <c r="A1317" s="8" t="n">
@@ -39223,6 +39479,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1317" t="inlineStr"/>
+      <c r="G1317" t="inlineStr"/>
     </row>
     <row r="1318" ht="15.75" customHeight="1" s="19">
       <c r="A1318" s="8" t="n">
@@ -39248,6 +39506,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1318" t="inlineStr"/>
+      <c r="G1318" t="inlineStr"/>
     </row>
     <row r="1319" ht="15.75" customHeight="1" s="19">
       <c r="A1319" s="8" t="n">
@@ -39273,6 +39533,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1319" t="inlineStr"/>
+      <c r="G1319" t="inlineStr"/>
     </row>
     <row r="1320" ht="15.75" customHeight="1" s="19">
       <c r="A1320" s="8" t="n">
@@ -39298,6 +39560,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1320" t="inlineStr">
+        <is>
+          <t>+54 348 464-0719</t>
+        </is>
+      </c>
+      <c r="G1320" t="inlineStr"/>
     </row>
     <row r="1321" ht="15.75" customHeight="1" s="19">
       <c r="A1321" s="8" t="n">
@@ -39323,6 +39591,12 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F1321" t="inlineStr">
+        <is>
+          <t>+54 11 4251-2416</t>
+        </is>
+      </c>
+      <c r="G1321" t="inlineStr"/>
     </row>
     <row r="1322" ht="15.75" customHeight="1" s="19">
       <c r="A1322" s="8" t="n">
@@ -39348,6 +39622,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1322" t="inlineStr"/>
+      <c r="G1322" t="inlineStr"/>
     </row>
     <row r="1323" ht="15.75" customHeight="1" s="19">
       <c r="A1323" s="8" t="n">
@@ -39373,6 +39649,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1323" t="inlineStr">
+        <is>
+          <t>+54 3489 43-0433</t>
+        </is>
+      </c>
+      <c r="G1323" t="inlineStr">
+        <is>
+          <t>https://italpastdeli.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1324" ht="15.75" customHeight="1" s="19">
       <c r="A1324" s="8" t="n">
@@ -39398,6 +39684,12 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1324" t="inlineStr">
+        <is>
+          <t>+54 11 3653-0068</t>
+        </is>
+      </c>
+      <c r="G1324" t="inlineStr"/>
     </row>
     <row r="1325" ht="15.75" customHeight="1" s="19">
       <c r="A1325" s="8" t="n">
@@ -39423,6 +39715,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1325" t="inlineStr">
+        <is>
+          <t>+54 11 5830-3352</t>
+        </is>
+      </c>
+      <c r="G1325" t="inlineStr">
+        <is>
+          <t>http://facebook.com/Laesquinadelasmascotas</t>
+        </is>
+      </c>
     </row>
     <row r="1326" ht="15.75" customHeight="1" s="19">
       <c r="A1326" s="8" t="n">
@@ -39448,6 +39750,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1326" t="inlineStr">
+        <is>
+          <t>+54 348 444-1015</t>
+        </is>
+      </c>
+      <c r="G1326" t="inlineStr"/>
     </row>
     <row r="1327" ht="15.75" customHeight="1" s="19">
       <c r="A1327" s="8" t="n">
@@ -39473,6 +39781,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1327" t="inlineStr">
+        <is>
+          <t>+54 348 444-6497</t>
+        </is>
+      </c>
+      <c r="G1327" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/caro.drovenort.1</t>
+        </is>
+      </c>
     </row>
     <row r="1328" ht="15.75" customHeight="1" s="19">
       <c r="A1328" s="8" t="n">
@@ -39498,6 +39816,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1328" t="inlineStr">
+        <is>
+          <t>+54 3489 43-5555</t>
+        </is>
+      </c>
+      <c r="G1328" t="inlineStr">
+        <is>
+          <t>http://sofitel.accor.com/hotels/6519?merchantid=seo-maps-AR-6519&amp;sourceid=aw-cen&amp;utm_source=google+Maps&amp;utm_medium=seo+maps&amp;utm_campaign=seo+maps&amp;utm_term=Sofitel-Launch</t>
+        </is>
+      </c>
     </row>
     <row r="1329" ht="15.75" customHeight="1" s="19">
       <c r="A1329" s="8" t="n">
@@ -39523,6 +39851,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1329" t="inlineStr">
+        <is>
+          <t>+54 3489 43-5555</t>
+        </is>
+      </c>
+      <c r="G1329" t="inlineStr">
+        <is>
+          <t>http://sofitel.accor.com/hotels/6519?merchantid=seo-maps-AR-6519&amp;sourceid=aw-cen&amp;utm_source=google+Maps&amp;utm_medium=seo+maps&amp;utm_campaign=seo+maps&amp;utm_term=Sofitel-Launch</t>
+        </is>
+      </c>
     </row>
     <row r="1330" ht="15.75" customHeight="1" s="19">
       <c r="A1330" s="8" t="n">
@@ -39548,6 +39886,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1330" t="inlineStr"/>
+      <c r="G1330" t="inlineStr"/>
     </row>
     <row r="1331" ht="15.75" customHeight="1" s="19">
       <c r="A1331" s="8" t="n">
@@ -39573,6 +39913,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1331" t="inlineStr">
+        <is>
+          <t>+54 2323 68-1767</t>
+        </is>
+      </c>
+      <c r="G1331" t="inlineStr">
+        <is>
+          <t>http://www.orlrube.com/</t>
+        </is>
+      </c>
     </row>
     <row r="1332" ht="15.75" customHeight="1" s="19">
       <c r="A1332" s="8" t="n">
@@ -39598,6 +39948,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1332" t="inlineStr"/>
+      <c r="G1332" t="inlineStr"/>
     </row>
     <row r="1333" ht="15.75" customHeight="1" s="19">
       <c r="A1333" s="8" t="n">
@@ -39623,6 +39975,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1333" t="inlineStr"/>
+      <c r="G1333" t="inlineStr"/>
     </row>
     <row r="1334" ht="15.75" customHeight="1" s="19">
       <c r="A1334" s="8" t="n">
@@ -39648,6 +40002,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1334" t="inlineStr"/>
+      <c r="G1334" t="inlineStr"/>
     </row>
     <row r="1335" ht="15.75" customHeight="1" s="19">
       <c r="A1335" s="8" t="n">
@@ -39673,6 +40029,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1335" t="inlineStr"/>
+      <c r="G1335" t="inlineStr"/>
     </row>
     <row r="1336" ht="15.75" customHeight="1" s="19">
       <c r="A1336" s="8" t="n">
@@ -39698,6 +40056,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1336" t="inlineStr">
+        <is>
+          <t>+54 221 359-8898</t>
+        </is>
+      </c>
+      <c r="G1336" t="inlineStr"/>
     </row>
     <row r="1337" ht="15.75" customHeight="1" s="19">
       <c r="A1337" s="8" t="n">
@@ -39723,6 +40087,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1337" t="inlineStr">
+        <is>
+          <t>+54 11 4891-9191</t>
+        </is>
+      </c>
+      <c r="G1337" t="inlineStr">
+        <is>
+          <t>https://www.correoargentino.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1338" ht="15.75" customHeight="1" s="19">
       <c r="A1338" s="8" t="n">
@@ -39748,6 +40122,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1338" t="inlineStr"/>
+      <c r="G1338" t="inlineStr"/>
     </row>
     <row r="1339" ht="15.75" customHeight="1" s="19">
       <c r="A1339" s="8" t="n">
@@ -39773,6 +40149,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1339" t="inlineStr"/>
+      <c r="G1339" t="inlineStr"/>
     </row>
     <row r="1340" ht="15.75" customHeight="1" s="19">
       <c r="A1340" s="8" t="n">
@@ -39798,6 +40176,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1340" t="inlineStr"/>
+      <c r="G1340" t="inlineStr"/>
     </row>
     <row r="1341" ht="15.75" customHeight="1" s="19">
       <c r="A1341" s="8" t="n">
@@ -39823,6 +40203,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1341" t="inlineStr">
+        <is>
+          <t>+54 221 352-3642</t>
+        </is>
+      </c>
+      <c r="G1341" t="inlineStr"/>
     </row>
     <row r="1342" ht="15.75" customHeight="1" s="19">
       <c r="A1342" s="8" t="n">
@@ -39848,6 +40234,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1342" t="inlineStr"/>
+      <c r="G1342" t="inlineStr"/>
     </row>
     <row r="1343" ht="15.75" customHeight="1" s="19">
       <c r="A1343" s="8" t="n">
@@ -39873,6 +40261,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1343" t="inlineStr"/>
+      <c r="G1343" t="inlineStr"/>
     </row>
     <row r="1344" ht="15.75" customHeight="1" s="19">
       <c r="A1344" s="8" t="n">
@@ -39898,6 +40288,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1344" t="inlineStr"/>
+      <c r="G1344" t="inlineStr"/>
     </row>
     <row r="1345" ht="15.75" customHeight="1" s="19">
       <c r="A1345" s="8" t="n">
@@ -39923,6 +40315,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1345" t="inlineStr">
+        <is>
+          <t>+54 221 591-2965</t>
+        </is>
+      </c>
+      <c r="G1345" t="inlineStr"/>
     </row>
     <row r="1346" ht="15.75" customHeight="1" s="19">
       <c r="A1346" s="8" t="n">
@@ -39948,6 +40346,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1346" t="inlineStr"/>
+      <c r="G1346" t="inlineStr"/>
     </row>
     <row r="1347" ht="15.75" customHeight="1" s="19">
       <c r="A1347" s="8" t="n">
@@ -39973,6 +40373,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1347" t="inlineStr"/>
+      <c r="G1347" t="inlineStr"/>
     </row>
     <row r="1348" ht="15.75" customHeight="1" s="19">
       <c r="A1348" s="8" t="n">
@@ -39998,6 +40400,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1348" t="inlineStr"/>
+      <c r="G1348" t="inlineStr"/>
     </row>
     <row r="1349" ht="15.75" customHeight="1" s="19">
       <c r="A1349" s="8" t="n">
@@ -40023,6 +40427,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1349" t="inlineStr"/>
+      <c r="G1349" t="inlineStr"/>
     </row>
     <row r="1350" ht="15.75" customHeight="1" s="19">
       <c r="A1350" s="8" t="n">
@@ -40048,6 +40454,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1350" t="inlineStr"/>
+      <c r="G1350" t="inlineStr"/>
     </row>
     <row r="1351" ht="15.75" customHeight="1" s="19">
       <c r="A1351" s="8" t="n">
@@ -40073,6 +40481,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1351" t="inlineStr">
+        <is>
+          <t>+54 221 424-1063</t>
+        </is>
+      </c>
+      <c r="G1351" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/estantsur/</t>
+        </is>
+      </c>
     </row>
     <row r="1352" ht="15.75" customHeight="1" s="19">
       <c r="A1352" s="8" t="n">
@@ -40096,6 +40514,16 @@
       <c r="E1352" s="8" t="inlineStr">
         <is>
           <t>Pet Shop</t>
+        </is>
+      </c>
+      <c r="F1352" t="inlineStr">
+        <is>
+          <t>+54 47737220</t>
+        </is>
+      </c>
+      <c r="G1352" t="inlineStr">
+        <is>
+          <t>https://gualasd.com.ar/</t>
         </is>
       </c>
     </row>

--- a/PUNTOS_DE_VENTA_completado.xlsx
+++ b/PUNTOS_DE_VENTA_completado.xlsx
@@ -40551,6 +40551,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1353" t="inlineStr">
+        <is>
+          <t>+54 221 631-2222</t>
+        </is>
+      </c>
+      <c r="G1353" t="inlineStr"/>
     </row>
     <row r="1354" ht="15.75" customHeight="1" s="19">
       <c r="A1354" s="8" t="n">
@@ -40576,6 +40582,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1354" t="inlineStr"/>
+      <c r="G1354" t="inlineStr"/>
     </row>
     <row r="1355" ht="15.75" customHeight="1" s="19">
       <c r="A1355" s="8" t="n">
@@ -40601,6 +40609,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1355" t="inlineStr"/>
+      <c r="G1355" t="inlineStr"/>
     </row>
     <row r="1356" ht="15.75" customHeight="1" s="19">
       <c r="A1356" s="8" t="n">
@@ -40626,6 +40636,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1356" t="inlineStr"/>
+      <c r="G1356" t="inlineStr"/>
     </row>
     <row r="1357" ht="15.75" customHeight="1" s="19">
       <c r="A1357" s="8" t="n">
@@ -40651,6 +40663,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1357" t="inlineStr"/>
+      <c r="G1357" t="inlineStr"/>
     </row>
     <row r="1358" ht="15.75" customHeight="1" s="19">
       <c r="A1358" s="8" t="n">
@@ -40676,6 +40690,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1358" t="inlineStr"/>
+      <c r="G1358" t="inlineStr"/>
     </row>
     <row r="1359" ht="15.75" customHeight="1" s="19">
       <c r="A1359" s="8" t="n">
@@ -40701,6 +40717,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1359" t="inlineStr"/>
+      <c r="G1359" t="inlineStr"/>
     </row>
     <row r="1360" ht="15.75" customHeight="1" s="19">
       <c r="A1360" s="8" t="n">
@@ -40726,6 +40744,16 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1360" t="inlineStr">
+        <is>
+          <t>+54 11 2864-9333</t>
+        </is>
+      </c>
+      <c r="G1360" t="inlineStr">
+        <is>
+          <t>https://m.facebook.com/Repuestosnestorr</t>
+        </is>
+      </c>
     </row>
     <row r="1361" ht="15.75" customHeight="1" s="19">
       <c r="A1361" s="8" t="n">
@@ -40751,6 +40779,12 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1361" t="inlineStr">
+        <is>
+          <t>+54 11 4243-1314</t>
+        </is>
+      </c>
+      <c r="G1361" t="inlineStr"/>
     </row>
     <row r="1362" ht="15.75" customHeight="1" s="19">
       <c r="A1362" s="8" t="n">
@@ -40776,6 +40810,16 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1362" t="inlineStr">
+        <is>
+          <t>+54 11 5514-5805</t>
+        </is>
+      </c>
+      <c r="G1362" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lubricentercarlos?igsh=MTRnb2hxOXg1MnY1cg==</t>
+        </is>
+      </c>
     </row>
     <row r="1363" ht="15.75" customHeight="1" s="19">
       <c r="A1363" s="8" t="n">
@@ -40801,6 +40845,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1363" t="inlineStr"/>
+      <c r="G1363" t="inlineStr"/>
     </row>
     <row r="1364" ht="15.75" customHeight="1" s="19">
       <c r="A1364" s="8" t="n">
@@ -40826,6 +40872,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1364" t="inlineStr"/>
+      <c r="G1364" t="inlineStr"/>
     </row>
     <row r="1365" ht="15.75" customHeight="1" s="19">
       <c r="A1365" s="8" t="n">
@@ -40851,6 +40899,16 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1365" t="inlineStr">
+        <is>
+          <t>+54 42984510</t>
+        </is>
+      </c>
+      <c r="G1365" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/repuestospablo_?igsh=Mm1ibXpobnJrcmN6</t>
+        </is>
+      </c>
     </row>
     <row r="1366" ht="15.75" customHeight="1" s="19">
       <c r="A1366" s="8" t="n">
@@ -40876,6 +40934,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1366" t="inlineStr"/>
+      <c r="G1366" t="inlineStr"/>
     </row>
     <row r="1367" ht="15.75" customHeight="1" s="19">
       <c r="A1367" s="8" t="n">
@@ -40901,6 +40961,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1367" t="inlineStr">
+        <is>
+          <t>+54 11 4293-2742</t>
+        </is>
+      </c>
+      <c r="G1367" t="inlineStr"/>
     </row>
     <row r="1368" ht="15.75" customHeight="1" s="19">
       <c r="A1368" s="8" t="n">
@@ -40926,6 +40992,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1368" t="inlineStr">
+        <is>
+          <t>+54 11 2409-7986</t>
+        </is>
+      </c>
+      <c r="G1368" t="inlineStr">
+        <is>
+          <t>https://www.prefumo.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1369" ht="15.75" customHeight="1" s="19">
       <c r="A1369" s="8" t="n">
@@ -40951,6 +41027,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1369" t="inlineStr"/>
+      <c r="G1369" t="inlineStr"/>
     </row>
     <row r="1370" ht="15.75" customHeight="1" s="19">
       <c r="A1370" s="8" t="n">
@@ -40976,6 +41054,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1370" t="inlineStr"/>
+      <c r="G1370" t="inlineStr"/>
     </row>
     <row r="1371" ht="15.75" customHeight="1" s="19">
       <c r="A1371" s="8" t="n">
@@ -41001,6 +41081,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1371" t="inlineStr"/>
+      <c r="G1371" t="inlineStr"/>
     </row>
     <row r="1372" ht="15.75" customHeight="1" s="19">
       <c r="A1372" s="8" t="n">
@@ -41026,6 +41108,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1372" t="inlineStr"/>
+      <c r="G1372" t="inlineStr"/>
     </row>
     <row r="1373" ht="15.75" customHeight="1" s="19">
       <c r="A1373" s="8" t="n">
@@ -41051,6 +41135,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1373" t="inlineStr"/>
+      <c r="G1373" t="inlineStr"/>
     </row>
     <row r="1374" ht="15.75" customHeight="1" s="19">
       <c r="A1374" s="8" t="n">
@@ -41076,6 +41162,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1374" t="inlineStr">
+        <is>
+          <t>+54 11 4208-9860</t>
+        </is>
+      </c>
+      <c r="G1374" t="inlineStr">
+        <is>
+          <t>https://www.veterinarias.com.ar/pineyro.html</t>
+        </is>
+      </c>
     </row>
     <row r="1375" ht="15.75" customHeight="1" s="19">
       <c r="A1375" s="8" t="n">
@@ -41101,6 +41197,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1375" t="inlineStr"/>
+      <c r="G1375" t="inlineStr"/>
     </row>
     <row r="1376" ht="15.75" customHeight="1" s="19">
       <c r="A1376" s="8" t="n">
@@ -41126,6 +41224,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1376" t="inlineStr">
+        <is>
+          <t>+54 11 4210-1578</t>
+        </is>
+      </c>
+      <c r="G1376" t="inlineStr"/>
     </row>
     <row r="1377" ht="15.75" customHeight="1" s="19">
       <c r="A1377" s="8" t="n">
@@ -41151,6 +41255,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1377" t="inlineStr"/>
+      <c r="G1377" t="inlineStr"/>
     </row>
     <row r="1378" ht="15.75" customHeight="1" s="19">
       <c r="A1378" s="8" t="n">
@@ -41176,6 +41282,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1378" t="inlineStr"/>
+      <c r="G1378" t="inlineStr"/>
     </row>
     <row r="1379" ht="15.75" customHeight="1" s="19">
       <c r="A1379" s="8" t="n">
@@ -41201,6 +41309,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1379" t="inlineStr"/>
+      <c r="G1379" t="inlineStr"/>
     </row>
     <row r="1380" ht="15.75" customHeight="1" s="19">
       <c r="A1380" s="8" t="n">
@@ -41226,6 +41336,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1380" t="inlineStr"/>
+      <c r="G1380" t="inlineStr"/>
     </row>
     <row r="1381" ht="15.75" customHeight="1" s="19">
       <c r="A1381" s="8" t="n">
@@ -41251,6 +41363,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1381" t="inlineStr">
+        <is>
+          <t>+54 11 7525-0616</t>
+        </is>
+      </c>
+      <c r="G1381" t="inlineStr"/>
     </row>
     <row r="1382" ht="15.75" customHeight="1" s="19">
       <c r="A1382" s="8" t="n">
@@ -41276,6 +41394,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1382" t="inlineStr"/>
+      <c r="G1382" t="inlineStr"/>
     </row>
     <row r="1383" ht="15.75" customHeight="1" s="19">
       <c r="A1383" s="8" t="n">
@@ -41301,6 +41421,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1383" t="inlineStr"/>
+      <c r="G1383" t="inlineStr"/>
     </row>
     <row r="1384" ht="15.75" customHeight="1" s="19">
       <c r="A1384" s="8" t="n">
@@ -41326,6 +41448,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1384" t="inlineStr"/>
+      <c r="G1384" t="inlineStr"/>
     </row>
     <row r="1385" ht="15.75" customHeight="1" s="19">
       <c r="A1385" s="8" t="n">
@@ -41351,6 +41475,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1385" t="inlineStr"/>
+      <c r="G1385" t="inlineStr"/>
     </row>
     <row r="1386" ht="15.75" customHeight="1" s="19">
       <c r="A1386" s="8" t="n">
@@ -41376,6 +41502,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1386" t="inlineStr"/>
+      <c r="G1386" t="inlineStr"/>
     </row>
     <row r="1387" ht="15.75" customHeight="1" s="19">
       <c r="A1387" s="8" t="n">
@@ -41401,6 +41529,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1387" t="inlineStr"/>
+      <c r="G1387" t="inlineStr"/>
     </row>
     <row r="1388" ht="15.75" customHeight="1" s="19">
       <c r="A1388" s="8" t="n">
@@ -41426,6 +41556,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1388" t="inlineStr"/>
+      <c r="G1388" t="inlineStr"/>
     </row>
     <row r="1389" ht="15.75" customHeight="1" s="19">
       <c r="A1389" s="8" t="n">
@@ -41451,6 +41583,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1389" t="inlineStr"/>
+      <c r="G1389" t="inlineStr"/>
     </row>
     <row r="1390" ht="15.75" customHeight="1" s="19">
       <c r="A1390" s="8" t="n">
@@ -41476,6 +41610,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1390" t="inlineStr">
+        <is>
+          <t>+54 11 6232-7632</t>
+        </is>
+      </c>
+      <c r="G1390" t="inlineStr">
+        <is>
+          <t>http://www.delite.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1391" ht="15.75" customHeight="1" s="19">
       <c r="A1391" s="8" t="n">
@@ -41501,6 +41645,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1391" t="inlineStr"/>
+      <c r="G1391" t="inlineStr"/>
     </row>
     <row r="1392" ht="15.75" customHeight="1" s="19">
       <c r="A1392" s="8" t="n">
@@ -41526,6 +41672,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1392" t="inlineStr"/>
+      <c r="G1392" t="inlineStr"/>
     </row>
     <row r="1393" ht="15.75" customHeight="1" s="19">
       <c r="A1393" s="8" t="n">
@@ -41551,6 +41699,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1393" t="inlineStr">
+        <is>
+          <t>+54 3533 68-1523</t>
+        </is>
+      </c>
+      <c r="G1393" t="inlineStr">
+        <is>
+          <t>http://www.zanello.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1394" ht="15.75" customHeight="1" s="19">
       <c r="A1394" s="8" t="n">
@@ -41576,6 +41734,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1394" t="inlineStr"/>
+      <c r="G1394" t="inlineStr"/>
     </row>
     <row r="1395" ht="15.75" customHeight="1" s="19">
       <c r="A1395" s="8" t="n">
@@ -41601,6 +41761,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1395" t="inlineStr">
+        <is>
+          <t>+54 800-222-2299</t>
+        </is>
+      </c>
+      <c r="G1395" t="inlineStr">
+        <is>
+          <t>http://www.altoavellaneda.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1396" ht="15.75" customHeight="1" s="19">
       <c r="A1396" s="8" t="n">
@@ -41626,6 +41796,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1396" t="inlineStr"/>
+      <c r="G1396" t="inlineStr"/>
     </row>
     <row r="1397" ht="15.75" customHeight="1" s="19">
       <c r="A1397" s="8" t="n">
@@ -41651,6 +41823,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1397" t="inlineStr"/>
+      <c r="G1397" t="inlineStr"/>
     </row>
     <row r="1398" ht="15.75" customHeight="1" s="19">
       <c r="A1398" s="8" t="n">
@@ -41676,6 +41850,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1398" t="inlineStr"/>
+      <c r="G1398" t="inlineStr"/>
     </row>
     <row r="1399" ht="15.75" customHeight="1" s="19">
       <c r="A1399" s="8" t="n">
@@ -41701,6 +41877,16 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1399" t="inlineStr">
+        <is>
+          <t>+54 11 2642-9553</t>
+        </is>
+      </c>
+      <c r="G1399" t="inlineStr">
+        <is>
+          <t>https://menu.fu.do/pastaslacasadesara</t>
+        </is>
+      </c>
     </row>
     <row r="1400" ht="15.75" customHeight="1" s="19">
       <c r="A1400" s="8" t="n">
@@ -41726,6 +41912,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1400" t="inlineStr"/>
+      <c r="G1400" t="inlineStr"/>
     </row>
     <row r="1401" ht="15.75" customHeight="1" s="19">
       <c r="A1401" s="8" t="n">
@@ -41751,6 +41939,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1401" t="inlineStr"/>
+      <c r="G1401" t="inlineStr"/>
     </row>
     <row r="1402" ht="15.75" customHeight="1" s="19">
       <c r="A1402" s="8" t="n">
@@ -41776,6 +41966,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1402" t="inlineStr"/>
+      <c r="G1402" t="inlineStr"/>
     </row>
     <row r="1403" ht="15.75" customHeight="1" s="19">
       <c r="A1403" s="8" t="n">
@@ -41801,6 +41993,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1403" t="inlineStr"/>
+      <c r="G1403" t="inlineStr"/>
     </row>
     <row r="1404" ht="15.75" customHeight="1" s="19">
       <c r="A1404" s="8" t="n">
@@ -41826,6 +42020,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F1404" t="inlineStr"/>
+      <c r="G1404" t="inlineStr"/>
     </row>
     <row r="1405" ht="15.75" customHeight="1" s="19">
       <c r="A1405" s="8" t="n">
@@ -41851,6 +42047,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1405" t="inlineStr">
+        <is>
+          <t>+54 11 5845-2590</t>
+        </is>
+      </c>
+      <c r="G1405" t="inlineStr"/>
     </row>
     <row r="1406" ht="15.75" customHeight="1" s="19">
       <c r="A1406" s="8" t="n">
@@ -41876,6 +42078,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1406" t="inlineStr"/>
+      <c r="G1406" t="inlineStr"/>
     </row>
     <row r="1407" ht="15.75" customHeight="1" s="19">
       <c r="A1407" s="8" t="n">
@@ -41901,6 +42105,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F1407" t="inlineStr"/>
+      <c r="G1407" t="inlineStr"/>
     </row>
     <row r="1408" ht="15.75" customHeight="1" s="19">
       <c r="A1408" s="8" t="n">
@@ -41926,6 +42132,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1408" t="inlineStr"/>
+      <c r="G1408" t="inlineStr"/>
     </row>
     <row r="1409" ht="15.75" customHeight="1" s="19">
       <c r="A1409" s="8" t="n">
@@ -41951,6 +42159,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1409" t="inlineStr">
+        <is>
+          <t>+54 43045153</t>
+        </is>
+      </c>
+      <c r="G1409" t="inlineStr">
+        <is>
+          <t>https://buenosaires.gob.ar/comuna-3</t>
+        </is>
+      </c>
     </row>
     <row r="1410" ht="15.75" customHeight="1" s="19">
       <c r="A1410" s="8" t="n">
@@ -41976,6 +42194,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1410" t="inlineStr"/>
+      <c r="G1410" t="inlineStr"/>
     </row>
     <row r="1411" ht="15.75" customHeight="1" s="19">
       <c r="A1411" s="8" t="n">
@@ -42001,6 +42221,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1411" t="inlineStr"/>
+      <c r="G1411" t="inlineStr"/>
     </row>
     <row r="1412" ht="15.75" customHeight="1" s="19">
       <c r="A1412" s="8" t="n">
@@ -42026,6 +42248,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1412" t="inlineStr"/>
+      <c r="G1412" t="inlineStr"/>
     </row>
     <row r="1413" ht="15.75" customHeight="1" s="19">
       <c r="A1413" s="8" t="n">
@@ -42051,6 +42275,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1413" t="inlineStr">
+        <is>
+          <t>+54 11 4841-8188</t>
+        </is>
+      </c>
+      <c r="G1413" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/begonia.bar/</t>
+        </is>
+      </c>
     </row>
     <row r="1414" ht="15.75" customHeight="1" s="19">
       <c r="A1414" s="8" t="n">
@@ -42076,6 +42310,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1414" t="inlineStr">
+        <is>
+          <t>+54 42439687</t>
+        </is>
+      </c>
+      <c r="G1414" t="inlineStr">
+        <is>
+          <t>http://www.pascocomercial.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1415" ht="15.75" customHeight="1" s="19">
       <c r="A1415" s="8" t="n">
@@ -42101,6 +42345,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1415" t="inlineStr"/>
+      <c r="G1415" t="inlineStr"/>
     </row>
     <row r="1416" ht="15.75" customHeight="1" s="19">
       <c r="A1416" s="8" t="n">
@@ -42126,6 +42372,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1416" t="inlineStr"/>
+      <c r="G1416" t="inlineStr"/>
     </row>
     <row r="1417" ht="15.75" customHeight="1" s="19">
       <c r="A1417" s="8" t="n">
@@ -42151,6 +42399,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1417" t="inlineStr">
+        <is>
+          <t>+54 11 4243-3000</t>
+        </is>
+      </c>
+      <c r="G1417" t="inlineStr">
+        <is>
+          <t>http://loraypropiedades.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1418" ht="15.75" customHeight="1" s="19">
       <c r="A1418" s="8" t="n">
@@ -42176,6 +42434,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1418" t="inlineStr"/>
+      <c r="G1418" t="inlineStr"/>
     </row>
     <row r="1419" ht="15.75" customHeight="1" s="19">
       <c r="A1419" s="8" t="n">
@@ -42201,6 +42461,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1419" t="inlineStr"/>
+      <c r="G1419" t="inlineStr"/>
     </row>
     <row r="1420" ht="15.75" customHeight="1" s="19">
       <c r="A1420" s="8" t="n">
@@ -42226,6 +42488,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1420" t="inlineStr">
+        <is>
+          <t>+54 11 4932-3003</t>
+        </is>
+      </c>
+      <c r="G1420" t="inlineStr"/>
     </row>
     <row r="1421" ht="15.75" customHeight="1" s="19">
       <c r="A1421" s="8" t="n">
@@ -42251,6 +42519,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1421" t="inlineStr"/>
+      <c r="G1421" t="inlineStr"/>
     </row>
     <row r="1422" ht="15.75" customHeight="1" s="19">
       <c r="A1422" s="8" t="n">
@@ -42276,6 +42546,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1422" t="inlineStr">
+        <is>
+          <t>+54 11 4856-9132</t>
+        </is>
+      </c>
+      <c r="G1422" t="inlineStr"/>
     </row>
     <row r="1423" ht="15.75" customHeight="1" s="19">
       <c r="A1423" s="8" t="n">
@@ -42301,6 +42577,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1423" t="inlineStr"/>
+      <c r="G1423" t="inlineStr"/>
     </row>
     <row r="1424" ht="15.75" customHeight="1" s="19">
       <c r="A1424" s="8" t="n">
@@ -42326,6 +42604,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1424" t="inlineStr"/>
+      <c r="G1424" t="inlineStr"/>
     </row>
     <row r="1425" ht="15.75" customHeight="1" s="19">
       <c r="A1425" s="8" t="n">
@@ -42351,6 +42631,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1425" t="inlineStr"/>
+      <c r="G1425" t="inlineStr"/>
     </row>
     <row r="1426" ht="15.75" customHeight="1" s="19">
       <c r="A1426" s="8" t="n">
@@ -42376,6 +42658,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1426" t="inlineStr"/>
+      <c r="G1426" t="inlineStr"/>
     </row>
     <row r="1427" ht="15.75" customHeight="1" s="19">
       <c r="A1427" s="8" t="n">
@@ -42401,6 +42685,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1427" t="inlineStr"/>
+      <c r="G1427" t="inlineStr"/>
     </row>
     <row r="1428" ht="15.75" customHeight="1" s="19">
       <c r="A1428" s="8" t="n">
@@ -42426,6 +42712,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1428" t="inlineStr"/>
+      <c r="G1428" t="inlineStr"/>
     </row>
     <row r="1429" ht="15.75" customHeight="1" s="19">
       <c r="A1429" s="8" t="n">
@@ -42451,6 +42739,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1429" t="inlineStr"/>
+      <c r="G1429" t="inlineStr"/>
     </row>
     <row r="1430" ht="15.75" customHeight="1" s="19">
       <c r="A1430" s="8" t="n">
@@ -42476,6 +42766,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1430" t="inlineStr"/>
+      <c r="G1430" t="inlineStr"/>
     </row>
     <row r="1431" ht="15.75" customHeight="1" s="19">
       <c r="A1431" s="8" t="n">
@@ -42501,6 +42793,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1431" t="inlineStr">
+        <is>
+          <t>+39 0831 301462</t>
+        </is>
+      </c>
+      <c r="G1431" t="inlineStr">
+        <is>
+          <t>http://www.erricomaria.it/</t>
+        </is>
+      </c>
     </row>
     <row r="1432" ht="15.75" customHeight="1" s="19">
       <c r="A1432" s="8" t="n">
@@ -42526,6 +42828,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1432" t="inlineStr"/>
+      <c r="G1432" t="inlineStr"/>
     </row>
     <row r="1433" ht="15.75" customHeight="1" s="19">
       <c r="A1433" s="8" t="n">
@@ -42551,6 +42855,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1433" t="inlineStr"/>
+      <c r="G1433" t="inlineStr"/>
     </row>
     <row r="1434" ht="15.75" customHeight="1" s="19">
       <c r="A1434" s="8" t="n">
@@ -42576,6 +42882,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1434" t="inlineStr">
+        <is>
+          <t>+54 9 11 6515-3877</t>
+        </is>
+      </c>
+      <c r="G1434" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/forrajeria_el_gallo/?hl=en</t>
+        </is>
+      </c>
     </row>
     <row r="1435" ht="15.75" customHeight="1" s="19">
       <c r="A1435" s="8" t="n">
@@ -42601,6 +42917,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1435" t="inlineStr"/>
+      <c r="G1435" t="inlineStr"/>
     </row>
     <row r="1436" ht="15.75" customHeight="1" s="19">
       <c r="A1436" s="8" t="n">
@@ -42626,6 +42944,16 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F1436" t="inlineStr">
+        <is>
+          <t>+54 3327 48-1134</t>
+        </is>
+      </c>
+      <c r="G1436" t="inlineStr">
+        <is>
+          <t>http://www.distribuidoraeguibar.com/</t>
+        </is>
+      </c>
     </row>
     <row r="1437" ht="15.75" customHeight="1" s="19">
       <c r="A1437" s="8" t="n">
@@ -42651,6 +42979,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1437" t="inlineStr"/>
+      <c r="G1437" t="inlineStr"/>
     </row>
     <row r="1438" ht="15.75" customHeight="1" s="19">
       <c r="A1438" s="8" t="n">
@@ -42676,6 +43006,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1438" t="inlineStr">
+        <is>
+          <t>+54 348 447-1594</t>
+        </is>
+      </c>
+      <c r="G1438" t="inlineStr"/>
     </row>
     <row r="1439" ht="15.75" customHeight="1" s="19">
       <c r="A1439" s="8" t="n">
@@ -42701,6 +43037,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1439" t="inlineStr">
+        <is>
+          <t>+54 348 447-1594</t>
+        </is>
+      </c>
+      <c r="G1439" t="inlineStr"/>
     </row>
     <row r="1440" ht="15.75" customHeight="1" s="19">
       <c r="A1440" s="8" t="n">
@@ -42726,6 +43068,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1440" t="inlineStr"/>
+      <c r="G1440" t="inlineStr"/>
     </row>
     <row r="1441" ht="15.75" customHeight="1" s="19">
       <c r="A1441" s="8" t="n">
@@ -42751,6 +43095,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1441" t="inlineStr">
+        <is>
+          <t>+54 11 6981-1542</t>
+        </is>
+      </c>
+      <c r="G1441" t="inlineStr">
+        <is>
+          <t>https://www.marianaferrari.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1442" ht="15.75" customHeight="1" s="19">
       <c r="A1442" s="8" t="n">
@@ -42776,6 +43130,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F1442" t="inlineStr"/>
+      <c r="G1442" t="inlineStr"/>
     </row>
     <row r="1443" ht="15.75" customHeight="1" s="19">
       <c r="A1443" s="8" t="n">
@@ -42801,6 +43157,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1443" t="inlineStr"/>
+      <c r="G1443" t="inlineStr"/>
     </row>
     <row r="1444" ht="15.75" customHeight="1" s="19">
       <c r="A1444" s="8" t="n">
@@ -42826,6 +43184,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1444" t="inlineStr"/>
+      <c r="G1444" t="inlineStr"/>
     </row>
     <row r="1445" ht="15.75" customHeight="1" s="19">
       <c r="A1445" s="8" t="n">
@@ -42851,6 +43211,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1445" t="inlineStr">
+        <is>
+          <t>+54 11 4016-2620</t>
+        </is>
+      </c>
+      <c r="G1445" t="inlineStr">
+        <is>
+          <t>http://www.sanlorenzo.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1446" ht="15.75" customHeight="1" s="19">
       <c r="A1446" s="8" t="n">
@@ -42876,6 +43246,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1446" t="inlineStr"/>
+      <c r="G1446" t="inlineStr"/>
     </row>
     <row r="1447" ht="15.75" customHeight="1" s="19">
       <c r="A1447" s="8" t="n">
@@ -42901,6 +43273,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1447" t="inlineStr"/>
+      <c r="G1447" t="inlineStr"/>
     </row>
     <row r="1448" ht="15.75" customHeight="1" s="19">
       <c r="A1448" s="8" t="n">
@@ -42926,6 +43300,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1448" t="inlineStr"/>
+      <c r="G1448" t="inlineStr"/>
     </row>
     <row r="1449" ht="15.75" customHeight="1" s="19">
       <c r="A1449" s="8" t="n">
@@ -42951,6 +43327,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1449" t="inlineStr"/>
+      <c r="G1449" t="inlineStr"/>
     </row>
     <row r="1450" ht="15.75" customHeight="1" s="19">
       <c r="A1450" s="8" t="n">
@@ -42976,6 +43354,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1450" t="inlineStr"/>
+      <c r="G1450" t="inlineStr"/>
     </row>
     <row r="1451" ht="15.75" customHeight="1" s="19">
       <c r="A1451" s="8" t="n">
@@ -43001,6 +43381,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1451" t="inlineStr"/>
+      <c r="G1451" t="inlineStr"/>
     </row>
     <row r="1452" ht="15.75" customHeight="1" s="19">
       <c r="A1452" s="8" t="n">
@@ -43026,6 +43408,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1452" t="inlineStr">
+        <is>
+          <t>+54 11 6008-3887</t>
+        </is>
+      </c>
+      <c r="G1452" t="inlineStr"/>
     </row>
     <row r="1453" ht="15.75" customHeight="1" s="19">
       <c r="A1453" s="8" t="n">

--- a/PUNTOS_DE_VENTA_completado.xlsx
+++ b/PUNTOS_DE_VENTA_completado.xlsx
@@ -43439,6 +43439,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1453" t="inlineStr"/>
+      <c r="G1453" t="inlineStr"/>
     </row>
     <row r="1454" ht="15.75" customHeight="1" s="19">
       <c r="A1454" s="8" t="n">
@@ -43464,6 +43466,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1454" t="inlineStr"/>
+      <c r="G1454" t="inlineStr"/>
     </row>
     <row r="1455" ht="15.75" customHeight="1" s="19">
       <c r="A1455" s="8" t="n">
@@ -43489,6 +43493,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1455" t="inlineStr"/>
+      <c r="G1455" t="inlineStr"/>
     </row>
     <row r="1456" ht="15.75" customHeight="1" s="19">
       <c r="A1456" s="8" t="n">
@@ -43514,6 +43520,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1456" t="inlineStr"/>
+      <c r="G1456" t="inlineStr"/>
     </row>
     <row r="1457" ht="15.75" customHeight="1" s="19">
       <c r="A1457" s="8" t="n">
@@ -43539,6 +43547,12 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1457" t="inlineStr">
+        <is>
+          <t>+54 11 6443-8426</t>
+        </is>
+      </c>
+      <c r="G1457" t="inlineStr"/>
     </row>
     <row r="1458" ht="15.75" customHeight="1" s="19">
       <c r="A1458" s="8" t="n">
@@ -43564,6 +43578,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1458" t="inlineStr"/>
+      <c r="G1458" t="inlineStr"/>
     </row>
     <row r="1459" ht="15.75" customHeight="1" s="19">
       <c r="A1459" s="8" t="n">
@@ -43589,6 +43605,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1459" t="inlineStr"/>
+      <c r="G1459" t="inlineStr"/>
     </row>
     <row r="1460" ht="15.75" customHeight="1" s="19">
       <c r="A1460" s="8" t="n">
@@ -43614,6 +43632,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1460" t="inlineStr"/>
+      <c r="G1460" t="inlineStr"/>
     </row>
     <row r="1461" ht="15.75" customHeight="1" s="19">
       <c r="A1461" s="8" t="n">
@@ -43639,6 +43659,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1461" t="inlineStr"/>
+      <c r="G1461" t="inlineStr"/>
     </row>
     <row r="1462" ht="15.75" customHeight="1" s="19">
       <c r="A1462" s="8" t="n">
@@ -43664,6 +43686,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1462" t="inlineStr"/>
+      <c r="G1462" t="inlineStr"/>
     </row>
     <row r="1463" ht="15.75" customHeight="1" s="19">
       <c r="A1463" s="8" t="n">
@@ -43689,6 +43713,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1463" t="inlineStr"/>
+      <c r="G1463" t="inlineStr"/>
     </row>
     <row r="1464" ht="15.75" customHeight="1" s="19">
       <c r="A1464" s="8" t="n">
@@ -43714,6 +43740,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1464" t="inlineStr">
+        <is>
+          <t>+54 11 5485-5377</t>
+        </is>
+      </c>
+      <c r="G1464" t="inlineStr">
+        <is>
+          <t>https://instagram.com/tequerock.ar?utm_medium=copy_link</t>
+        </is>
+      </c>
     </row>
     <row r="1465" ht="15.75" customHeight="1" s="19">
       <c r="A1465" s="8" t="n">
@@ -43739,6 +43775,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1465" t="inlineStr"/>
+      <c r="G1465" t="inlineStr"/>
     </row>
     <row r="1466" ht="15.75" customHeight="1" s="19">
       <c r="A1466" s="8" t="n">
@@ -43764,6 +43802,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1466" t="inlineStr"/>
+      <c r="G1466" t="inlineStr"/>
     </row>
     <row r="1467" ht="15.75" customHeight="1" s="19">
       <c r="A1467" s="8" t="n">
@@ -43789,6 +43829,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1467" t="inlineStr"/>
+      <c r="G1467" t="inlineStr"/>
     </row>
     <row r="1468" ht="15.75" customHeight="1" s="19">
       <c r="A1468" s="8" t="n">
@@ -43814,6 +43856,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1468" t="inlineStr"/>
+      <c r="G1468" t="inlineStr"/>
     </row>
     <row r="1469" ht="15.75" customHeight="1" s="19">
       <c r="A1469" s="8" t="n">
@@ -43839,6 +43883,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1469" t="inlineStr"/>
+      <c r="G1469" t="inlineStr"/>
     </row>
     <row r="1470" ht="15.75" customHeight="1" s="19">
       <c r="A1470" s="8" t="n">
@@ -43864,6 +43910,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1470" t="inlineStr"/>
+      <c r="G1470" t="inlineStr"/>
     </row>
     <row r="1471" ht="15.75" customHeight="1" s="19">
       <c r="A1471" s="8" t="n">
@@ -43889,6 +43937,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1471" t="inlineStr"/>
+      <c r="G1471" t="inlineStr"/>
     </row>
     <row r="1472" ht="15.75" customHeight="1" s="19">
       <c r="A1472" s="8" t="n">
@@ -43914,6 +43964,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1472" t="inlineStr">
+        <is>
+          <t>+54 2320 43-0748</t>
+        </is>
+      </c>
+      <c r="G1472" t="inlineStr"/>
     </row>
     <row r="1473" ht="15.75" customHeight="1" s="19">
       <c r="A1473" s="8" t="n">
@@ -43939,6 +43995,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1473" t="inlineStr">
+        <is>
+          <t>+54 11 6800-2950</t>
+        </is>
+      </c>
+      <c r="G1473" t="inlineStr"/>
     </row>
     <row r="1474" ht="15.75" customHeight="1" s="19">
       <c r="A1474" s="8" t="n">
@@ -43964,6 +44026,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1474" t="inlineStr">
+        <is>
+          <t>+54 11 2405-3953</t>
+        </is>
+      </c>
+      <c r="G1474" t="inlineStr">
+        <is>
+          <t>https://pedi.app/ohquesushi/</t>
+        </is>
+      </c>
     </row>
     <row r="1475" ht="15.75" customHeight="1" s="19">
       <c r="A1475" s="8" t="n">
@@ -43989,6 +44061,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1475" t="inlineStr">
+        <is>
+          <t>+54 9 11 6962-7265</t>
+        </is>
+      </c>
+      <c r="G1475" t="inlineStr">
+        <is>
+          <t>http://printeco.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1476" ht="15.75" customHeight="1" s="19">
       <c r="A1476" s="8" t="n">
@@ -44014,6 +44096,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1476" t="inlineStr">
+        <is>
+          <t>+54 11 5263-7004</t>
+        </is>
+      </c>
+      <c r="G1476" t="inlineStr">
+        <is>
+          <t>http://www.mdyasociados.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1477" ht="15.75" customHeight="1" s="19">
       <c r="A1477" s="8" t="n">
@@ -44039,6 +44131,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1477" t="inlineStr"/>
+      <c r="G1477" t="inlineStr"/>
     </row>
     <row r="1478" ht="15.75" customHeight="1" s="19">
       <c r="A1478" s="8" t="n">
@@ -44064,6 +44158,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1478" t="inlineStr"/>
+      <c r="G1478" t="inlineStr"/>
     </row>
     <row r="1479" ht="15.75" customHeight="1" s="19">
       <c r="A1479" s="8" t="n">
@@ -44089,6 +44185,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1479" t="inlineStr"/>
+      <c r="G1479" t="inlineStr"/>
     </row>
     <row r="1480" ht="15.75" customHeight="1" s="19">
       <c r="A1480" s="8" t="n">
@@ -44114,6 +44212,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1480" t="inlineStr"/>
+      <c r="G1480" t="inlineStr"/>
     </row>
     <row r="1481" ht="15.75" customHeight="1" s="19">
       <c r="A1481" s="8" t="n">
@@ -44139,6 +44239,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1481" t="inlineStr"/>
+      <c r="G1481" t="inlineStr"/>
     </row>
     <row r="1482" ht="15.75" customHeight="1" s="19">
       <c r="A1482" s="8" t="n">
@@ -44164,6 +44266,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1482" t="inlineStr">
+        <is>
+          <t>+54 11 4718-2371</t>
+        </is>
+      </c>
+      <c r="G1482" t="inlineStr"/>
     </row>
     <row r="1483" ht="15.75" customHeight="1" s="19">
       <c r="A1483" s="8" t="n">
@@ -44189,6 +44297,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1483" t="inlineStr">
+        <is>
+          <t>+54 2320 64-9021</t>
+        </is>
+      </c>
+      <c r="G1483" t="inlineStr">
+        <is>
+          <t>http://www.unpaz.edu.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1484" ht="15.75" customHeight="1" s="19">
       <c r="A1484" s="8" t="n">
@@ -44214,6 +44332,12 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1484" t="inlineStr">
+        <is>
+          <t>+54 11 4741-5994</t>
+        </is>
+      </c>
+      <c r="G1484" t="inlineStr"/>
     </row>
     <row r="1485" ht="15.75" customHeight="1" s="19">
       <c r="A1485" s="8" t="n">
@@ -44239,6 +44363,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1485" t="inlineStr"/>
+      <c r="G1485" t="inlineStr"/>
     </row>
     <row r="1486" ht="15.75" customHeight="1" s="19">
       <c r="A1486" s="8" t="n">
@@ -44264,6 +44390,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1486" t="inlineStr"/>
+      <c r="G1486" t="inlineStr"/>
     </row>
     <row r="1487" ht="15.75" customHeight="1" s="19">
       <c r="A1487" s="8" t="n">
@@ -44289,6 +44417,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1487" t="inlineStr"/>
+      <c r="G1487" t="inlineStr"/>
     </row>
     <row r="1488" ht="15.75" customHeight="1" s="19">
       <c r="A1488" s="8" t="n">
@@ -44314,6 +44444,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1488" t="inlineStr"/>
+      <c r="G1488" t="inlineStr"/>
     </row>
     <row r="1489" ht="15.75" customHeight="1" s="19">
       <c r="A1489" s="8" t="n">
@@ -44339,6 +44471,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1489" t="inlineStr">
+        <is>
+          <t>+54 11 7079-1234</t>
+        </is>
+      </c>
+      <c r="G1489" t="inlineStr">
+        <is>
+          <t>https://centro-pet.mercadoshops.com.ar/criadero</t>
+        </is>
+      </c>
     </row>
     <row r="1490" ht="15.75" customHeight="1" s="19">
       <c r="A1490" s="8" t="n">
@@ -44364,6 +44506,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1490" t="inlineStr">
+        <is>
+          <t>+54 11 4421-1736</t>
+        </is>
+      </c>
+      <c r="G1490" t="inlineStr"/>
     </row>
     <row r="1491" ht="15.75" customHeight="1" s="19">
       <c r="A1491" s="8" t="n">
@@ -44389,6 +44537,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1491" t="inlineStr"/>
+      <c r="G1491" t="inlineStr"/>
     </row>
     <row r="1492" ht="15.75" customHeight="1" s="19">
       <c r="A1492" s="8" t="n">
@@ -44414,6 +44564,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1492" t="inlineStr">
+        <is>
+          <t>+54 11 5620-2158</t>
+        </is>
+      </c>
+      <c r="G1492" t="inlineStr">
+        <is>
+          <t>http://cuatropatascaseros.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1493" ht="15.75" customHeight="1" s="19">
       <c r="A1493" s="8" t="n">
@@ -44439,6 +44599,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1493" t="inlineStr"/>
+      <c r="G1493" t="inlineStr"/>
     </row>
     <row r="1494" ht="15.75" customHeight="1" s="19">
       <c r="A1494" s="8" t="n">
@@ -44464,6 +44626,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1494" t="inlineStr"/>
+      <c r="G1494" t="inlineStr"/>
     </row>
     <row r="1495" ht="15.75" customHeight="1" s="19">
       <c r="A1495" s="8" t="n">
@@ -44489,6 +44653,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1495" t="inlineStr"/>
+      <c r="G1495" t="inlineStr"/>
     </row>
     <row r="1496" ht="15.75" customHeight="1" s="19">
       <c r="A1496" s="8" t="n">
@@ -44514,6 +44680,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1496" t="inlineStr">
+        <is>
+          <t>+54 11 4308-1664</t>
+        </is>
+      </c>
+      <c r="G1496" t="inlineStr">
+        <is>
+          <t>http://www.catanese.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1497" ht="15.75" customHeight="1" s="19">
       <c r="A1497" s="8" t="n">
@@ -44539,6 +44715,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1497" t="inlineStr"/>
+      <c r="G1497" t="inlineStr"/>
     </row>
     <row r="1498" ht="15.75" customHeight="1" s="19">
       <c r="A1498" s="8" t="n">
@@ -44564,6 +44742,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1498" t="inlineStr"/>
+      <c r="G1498" t="inlineStr"/>
     </row>
     <row r="1499" ht="15.75" customHeight="1" s="19">
       <c r="A1499" s="8" t="n">
@@ -44589,6 +44769,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1499" t="inlineStr"/>
+      <c r="G1499" t="inlineStr"/>
     </row>
     <row r="1500" ht="15.75" customHeight="1" s="19">
       <c r="A1500" s="8" t="n">
@@ -44614,6 +44796,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1500" t="inlineStr"/>
+      <c r="G1500" t="inlineStr"/>
     </row>
     <row r="1501" ht="15.75" customHeight="1" s="19">
       <c r="A1501" s="8" t="n">
@@ -44639,6 +44823,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1501" t="inlineStr"/>
+      <c r="G1501" t="inlineStr"/>
     </row>
     <row r="1502" ht="15.75" customHeight="1" s="19">
       <c r="A1502" s="8" t="n">
@@ -44664,6 +44850,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1502" t="inlineStr"/>
+      <c r="G1502" t="inlineStr"/>
     </row>
     <row r="1503" ht="15.75" customHeight="1" s="19">
       <c r="A1503" s="8" t="n">
@@ -44689,6 +44877,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1503" t="inlineStr">
+        <is>
+          <t>+54 11 6428-3348</t>
+        </is>
+      </c>
+      <c r="G1503" t="inlineStr">
+        <is>
+          <t>http://www.luzbianca.com/</t>
+        </is>
+      </c>
     </row>
     <row r="1504" ht="15.75" customHeight="1" s="19">
       <c r="A1504" s="8" t="n">
@@ -44714,6 +44912,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1504" t="inlineStr">
+        <is>
+          <t>+54 11 4488-7154</t>
+        </is>
+      </c>
+      <c r="G1504" t="inlineStr">
+        <is>
+          <t>http://www.elizalde.edu.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1505" ht="15.75" customHeight="1" s="19">
       <c r="A1505" s="8" t="n">
@@ -44739,6 +44947,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1505" t="inlineStr">
+        <is>
+          <t>+54 11 6658-5029</t>
+        </is>
+      </c>
+      <c r="G1505" t="inlineStr">
+        <is>
+          <t>http://www.garrapatas.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1506" ht="15.75" customHeight="1" s="19">
       <c r="A1506" s="8" t="n">
@@ -44764,6 +44982,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1506" t="inlineStr"/>
+      <c r="G1506" t="inlineStr"/>
     </row>
     <row r="1507" ht="15.75" customHeight="1" s="19">
       <c r="A1507" s="8" t="n">
@@ -44789,6 +45009,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1507" t="inlineStr"/>
+      <c r="G1507" t="inlineStr"/>
     </row>
     <row r="1508" ht="15.75" customHeight="1" s="19">
       <c r="A1508" s="8" t="n">
@@ -44814,6 +45036,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1508" t="inlineStr"/>
+      <c r="G1508" t="inlineStr"/>
     </row>
     <row r="1509" ht="15.75" customHeight="1" s="19">
       <c r="A1509" s="8" t="n">
@@ -44839,6 +45063,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1509" t="inlineStr"/>
+      <c r="G1509" t="inlineStr"/>
     </row>
     <row r="1510" ht="15.75" customHeight="1" s="19">
       <c r="A1510" s="8" t="n">
@@ -44864,6 +45090,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1510" t="inlineStr"/>
+      <c r="G1510" t="inlineStr"/>
     </row>
     <row r="1511" ht="15.75" customHeight="1" s="19">
       <c r="A1511" s="8" t="n">
@@ -44889,6 +45117,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1511" t="inlineStr"/>
+      <c r="G1511" t="inlineStr"/>
     </row>
     <row r="1512" ht="15.75" customHeight="1" s="19">
       <c r="A1512" s="8" t="n">
@@ -44914,6 +45144,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1512" t="inlineStr"/>
+      <c r="G1512" t="inlineStr"/>
     </row>
     <row r="1513" ht="15.75" customHeight="1" s="19">
       <c r="A1513" s="8" t="n">
@@ -44939,6 +45171,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1513" t="inlineStr"/>
+      <c r="G1513" t="inlineStr"/>
     </row>
     <row r="1514" ht="15.75" customHeight="1" s="19">
       <c r="A1514" s="8" t="n">
@@ -44964,6 +45198,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1514" t="inlineStr"/>
+      <c r="G1514" t="inlineStr"/>
     </row>
     <row r="1515" ht="15.75" customHeight="1" s="19">
       <c r="A1515" s="8" t="n">
@@ -44989,6 +45225,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1515" t="inlineStr">
+        <is>
+          <t>+54 11 4003-4100</t>
+        </is>
+      </c>
+      <c r="G1515" t="inlineStr">
+        <is>
+          <t>https://www.bersa.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1516" ht="15.75" customHeight="1" s="19">
       <c r="A1516" s="8" t="n">
@@ -45014,6 +45260,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1516" t="inlineStr"/>
+      <c r="G1516" t="inlineStr"/>
     </row>
     <row r="1517" ht="15.75" customHeight="1" s="19">
       <c r="A1517" s="8" t="n">
@@ -45039,6 +45287,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1517" t="inlineStr"/>
+      <c r="G1517" t="inlineStr"/>
     </row>
     <row r="1518" ht="15.75" customHeight="1" s="19">
       <c r="A1518" s="8" t="n">
@@ -45064,6 +45314,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1518" t="inlineStr">
+        <is>
+          <t>+54 11 4712-6499</t>
+        </is>
+      </c>
+      <c r="G1518" t="inlineStr"/>
     </row>
     <row r="1519" ht="15.75" customHeight="1" s="19">
       <c r="A1519" s="8" t="n">
@@ -45089,6 +45345,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1519" t="inlineStr"/>
+      <c r="G1519" t="inlineStr"/>
     </row>
     <row r="1520" ht="15.75" customHeight="1" s="19">
       <c r="A1520" s="8" t="n">
@@ -45114,6 +45372,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1520" t="inlineStr">
+        <is>
+          <t>+54 11 4762-1191</t>
+        </is>
+      </c>
+      <c r="G1520" t="inlineStr">
+        <is>
+          <t>https://comercios.vicentelopez.gov.ar/comercio/libreria-saettone</t>
+        </is>
+      </c>
     </row>
     <row r="1521" ht="15.75" customHeight="1" s="19">
       <c r="A1521" s="8" t="n">
@@ -45139,6 +45407,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1521" t="inlineStr"/>
+      <c r="G1521" t="inlineStr"/>
     </row>
     <row r="1522" ht="15.75" customHeight="1" s="19">
       <c r="A1522" s="8" t="n">
@@ -45164,6 +45434,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1522" t="inlineStr">
+        <is>
+          <t>+54 230 440-1364</t>
+        </is>
+      </c>
+      <c r="G1522" t="inlineStr"/>
     </row>
     <row r="1523" ht="15.75" customHeight="1" s="19">
       <c r="A1523" s="8" t="n">
@@ -45189,6 +45465,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1523" t="inlineStr"/>
+      <c r="G1523" t="inlineStr"/>
     </row>
     <row r="1524" ht="15.75" customHeight="1" s="19">
       <c r="A1524" s="8" t="n">
@@ -45214,6 +45492,16 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1524" t="inlineStr">
+        <is>
+          <t>+54 11 3934-2111</t>
+        </is>
+      </c>
+      <c r="G1524" t="inlineStr">
+        <is>
+          <t>http://www.supermercadosdelta.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1525" ht="15.75" customHeight="1" s="19">
       <c r="A1525" s="8" t="n">
@@ -45239,6 +45527,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1525" t="inlineStr"/>
+      <c r="G1525" t="inlineStr"/>
     </row>
     <row r="1526" ht="15.75" customHeight="1" s="19">
       <c r="A1526" s="8" t="n">
@@ -45264,6 +45554,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1526" t="inlineStr"/>
+      <c r="G1526" t="inlineStr"/>
     </row>
     <row r="1527" ht="15.75" customHeight="1" s="19">
       <c r="A1527" s="8" t="n">
@@ -45289,6 +45581,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1527" t="inlineStr"/>
+      <c r="G1527" t="inlineStr"/>
     </row>
     <row r="1528" ht="15.75" customHeight="1" s="19">
       <c r="A1528" s="8" t="n">
@@ -45314,6 +45608,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1528" t="inlineStr">
+        <is>
+          <t>+54 11 4844-3722</t>
+        </is>
+      </c>
+      <c r="G1528" t="inlineStr"/>
     </row>
     <row r="1529" ht="15.75" customHeight="1" s="19">
       <c r="A1529" s="8" t="n">
@@ -45339,6 +45639,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1529" t="inlineStr">
+        <is>
+          <t>+54 11 3117-4267</t>
+        </is>
+      </c>
+      <c r="G1529" t="inlineStr"/>
     </row>
     <row r="1530" ht="15.75" customHeight="1" s="19">
       <c r="A1530" s="8" t="n">
@@ -45364,6 +45670,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1530" t="inlineStr"/>
+      <c r="G1530" t="inlineStr"/>
     </row>
     <row r="1531" ht="15.75" customHeight="1" s="19">
       <c r="A1531" s="8" t="n">
@@ -45389,6 +45697,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1531" t="inlineStr">
+        <is>
+          <t>+54 11 4755-1083</t>
+        </is>
+      </c>
+      <c r="G1531" t="inlineStr"/>
     </row>
     <row r="1532" ht="15.75" customHeight="1" s="19">
       <c r="A1532" s="8" t="n">
@@ -45414,6 +45728,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1532" t="inlineStr">
+        <is>
+          <t>+54 11 5832-5477</t>
+        </is>
+      </c>
+      <c r="G1532" t="inlineStr">
+        <is>
+          <t>https://germanpace.com/traumatologo-villa-urquiza</t>
+        </is>
+      </c>
     </row>
     <row r="1533" ht="15.75" customHeight="1" s="19">
       <c r="A1533" s="8" t="n">
@@ -45439,6 +45763,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1533" t="inlineStr">
+        <is>
+          <t>+54 11 3396-5937</t>
+        </is>
+      </c>
+      <c r="G1533" t="inlineStr">
+        <is>
+          <t>https://molinapanaderia.com.ar/?utm_source=google&amp;utm_medium=organico&amp;utm_campaign=ficha_gmb_molina_saenzpena</t>
+        </is>
+      </c>
     </row>
     <row r="1534" ht="15.75" customHeight="1" s="19">
       <c r="A1534" s="8" t="n">
@@ -45464,6 +45798,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1534" t="inlineStr"/>
+      <c r="G1534" t="inlineStr"/>
     </row>
     <row r="1535" ht="15.75" customHeight="1" s="19">
       <c r="A1535" s="8" t="n">
@@ -45489,6 +45825,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1535" t="inlineStr"/>
+      <c r="G1535" t="inlineStr"/>
     </row>
     <row r="1536" ht="15.75" customHeight="1" s="19">
       <c r="A1536" s="8" t="n">
@@ -45514,6 +45852,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1536" t="inlineStr"/>
+      <c r="G1536" t="inlineStr"/>
     </row>
     <row r="1537" ht="15.75" customHeight="1" s="19">
       <c r="A1537" s="8" t="n">
@@ -45539,6 +45879,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1537" t="inlineStr"/>
+      <c r="G1537" t="inlineStr"/>
     </row>
     <row r="1538" ht="15.75" customHeight="1" s="19">
       <c r="A1538" s="8" t="n">
@@ -45564,6 +45906,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1538" t="inlineStr"/>
+      <c r="G1538" t="inlineStr"/>
     </row>
     <row r="1539" ht="15.75" customHeight="1" s="19">
       <c r="A1539" s="8" t="n">
@@ -45589,6 +45933,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1539" t="inlineStr"/>
+      <c r="G1539" t="inlineStr"/>
     </row>
     <row r="1540" ht="15.75" customHeight="1" s="19">
       <c r="A1540" s="8" t="n">
@@ -45614,6 +45960,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1540" t="inlineStr"/>
+      <c r="G1540" t="inlineStr"/>
     </row>
     <row r="1541" ht="15.75" customHeight="1" s="19">
       <c r="A1541" s="8" t="n">
@@ -45639,6 +45987,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1541" t="inlineStr">
+        <is>
+          <t>+54 237 462-9467</t>
+        </is>
+      </c>
+      <c r="G1541" t="inlineStr"/>
     </row>
     <row r="1542" ht="15.75" customHeight="1" s="19">
       <c r="A1542" s="8" t="n">
@@ -45664,6 +46018,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1542" t="inlineStr">
+        <is>
+          <t>+54 11 3079-1788</t>
+        </is>
+      </c>
+      <c r="G1542" t="inlineStr"/>
     </row>
     <row r="1543" ht="15.75" customHeight="1" s="19">
       <c r="A1543" s="8" t="n">
@@ -45689,6 +46049,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1543" t="inlineStr">
+        <is>
+          <t>+54 11 4294-1914</t>
+        </is>
+      </c>
+      <c r="G1543" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/acetiendademascotas</t>
+        </is>
+      </c>
     </row>
     <row r="1544" ht="15.75" customHeight="1" s="19">
       <c r="A1544" s="8" t="n">
@@ -45714,6 +46084,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1544" t="inlineStr"/>
+      <c r="G1544" t="inlineStr"/>
     </row>
     <row r="1545" ht="15.75" customHeight="1" s="19">
       <c r="A1545" s="8" t="n">
@@ -45739,6 +46111,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1545" t="inlineStr"/>
+      <c r="G1545" t="inlineStr"/>
     </row>
     <row r="1546" ht="15.75" customHeight="1" s="19">
       <c r="A1546" s="8" t="n">
@@ -45764,6 +46138,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1546" t="inlineStr">
+        <is>
+          <t>+54 11 4206-2522</t>
+        </is>
+      </c>
+      <c r="G1546" t="inlineStr"/>
     </row>
     <row r="1547" ht="15.75" customHeight="1" s="19">
       <c r="A1547" s="8" t="n">
@@ -45789,6 +46169,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1547" t="inlineStr">
+        <is>
+          <t>+54 9 3489 29-3234</t>
+        </is>
+      </c>
+      <c r="G1547" t="inlineStr"/>
     </row>
     <row r="1548" ht="15.75" customHeight="1" s="19">
       <c r="A1548" s="8" t="n">
@@ -45814,6 +46200,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1548" t="inlineStr"/>
+      <c r="G1548" t="inlineStr"/>
     </row>
     <row r="1549" ht="15.75" customHeight="1" s="19">
       <c r="A1549" s="8" t="n">
@@ -45839,6 +46227,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1549" t="inlineStr"/>
+      <c r="G1549" t="inlineStr"/>
     </row>
     <row r="1550" ht="15.75" customHeight="1" s="19">
       <c r="A1550" s="8" t="n">
@@ -45864,6 +46254,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1550" t="inlineStr"/>
+      <c r="G1550" t="inlineStr"/>
     </row>
     <row r="1551" ht="15.75" customHeight="1" s="19">
       <c r="A1551" s="8" t="n">
@@ -45889,6 +46281,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1551" t="inlineStr">
+        <is>
+          <t>+54 11 3149-9490</t>
+        </is>
+      </c>
+      <c r="G1551" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pampanodevoto/?hl=es</t>
+        </is>
+      </c>
     </row>
     <row r="1552" ht="15.75" customHeight="1" s="19">
       <c r="A1552" s="8" t="n">
@@ -45914,6 +46316,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1552" t="inlineStr"/>
+      <c r="G1552" t="inlineStr"/>
     </row>
     <row r="1553" ht="15.75" customHeight="1" s="19">
       <c r="A1553" s="8" t="n">

--- a/PUNTOS_DE_VENTA_completado.xlsx
+++ b/PUNTOS_DE_VENTA_completado.xlsx
@@ -46343,6 +46343,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1553" t="inlineStr"/>
+      <c r="G1553" t="inlineStr"/>
     </row>
     <row r="1554" ht="15.75" customHeight="1" s="19">
       <c r="A1554" s="8" t="n">
@@ -46368,6 +46370,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1554" t="inlineStr"/>
+      <c r="G1554" t="inlineStr"/>
     </row>
     <row r="1555" ht="15.75" customHeight="1" s="19">
       <c r="A1555" s="8" t="n">
@@ -46393,6 +46397,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1555" t="inlineStr"/>
+      <c r="G1555" t="inlineStr"/>
     </row>
     <row r="1556" ht="15.75" customHeight="1" s="19">
       <c r="A1556" s="8" t="n">
@@ -46418,6 +46424,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1556" t="inlineStr">
+        <is>
+          <t>+54 11 4666-8229</t>
+        </is>
+      </c>
+      <c r="G1556" t="inlineStr"/>
     </row>
     <row r="1557" ht="15.75" customHeight="1" s="19">
       <c r="A1557" s="8" t="n">
@@ -46443,6 +46455,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1557" t="inlineStr"/>
+      <c r="G1557" t="inlineStr"/>
     </row>
     <row r="1558" ht="15.75" customHeight="1" s="19">
       <c r="A1558" s="8" t="n">
@@ -46468,6 +46482,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1558" t="inlineStr">
+        <is>
+          <t>+54 11 4666-0404</t>
+        </is>
+      </c>
+      <c r="G1558" t="inlineStr"/>
     </row>
     <row r="1559" ht="15.75" customHeight="1" s="19">
       <c r="A1559" s="8" t="n">
@@ -46493,6 +46513,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1559" t="inlineStr"/>
+      <c r="G1559" t="inlineStr"/>
     </row>
     <row r="1560" ht="15.75" customHeight="1" s="19">
       <c r="A1560" s="8" t="n">
@@ -46518,6 +46540,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1560" t="inlineStr"/>
+      <c r="G1560" t="inlineStr"/>
     </row>
     <row r="1561" ht="15.75" customHeight="1" s="19">
       <c r="A1561" s="8" t="n">
@@ -46543,6 +46567,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1561" t="inlineStr">
+        <is>
+          <t>+54 11 4214-7440</t>
+        </is>
+      </c>
+      <c r="G1561" t="inlineStr">
+        <is>
+          <t>https://m.facebook.com/BonAppetitMascotasOficial/</t>
+        </is>
+      </c>
     </row>
     <row r="1562" ht="15.75" customHeight="1" s="19">
       <c r="A1562" s="8" t="n">
@@ -46568,6 +46602,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1562" t="inlineStr"/>
+      <c r="G1562" t="inlineStr"/>
     </row>
     <row r="1563" ht="15.75" customHeight="1" s="19">
       <c r="A1563" s="8" t="n">
@@ -46593,6 +46629,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1563" t="inlineStr"/>
+      <c r="G1563" t="inlineStr"/>
     </row>
     <row r="1564" ht="15.75" customHeight="1" s="19">
       <c r="A1564" s="8" t="n">
@@ -46618,6 +46656,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1564" t="inlineStr"/>
+      <c r="G1564" t="inlineStr"/>
     </row>
     <row r="1565" ht="15.75" customHeight="1" s="19">
       <c r="A1565" s="8" t="n">
@@ -46643,6 +46683,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1565" t="inlineStr">
+        <is>
+          <t>+54 11 4214-4937</t>
+        </is>
+      </c>
+      <c r="G1565" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ferreteriabynnon?igsh=dDFoZzAxbWtweDF5</t>
+        </is>
+      </c>
     </row>
     <row r="1566" ht="15.75" customHeight="1" s="19">
       <c r="A1566" s="8" t="n">
@@ -46668,6 +46718,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1566" t="inlineStr"/>
+      <c r="G1566" t="inlineStr"/>
     </row>
     <row r="1567" ht="15.75" customHeight="1" s="19">
       <c r="A1567" s="8" t="n">
@@ -46693,6 +46745,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1567" t="inlineStr">
+        <is>
+          <t>+54 11 4233-5400</t>
+        </is>
+      </c>
+      <c r="G1567" t="inlineStr"/>
     </row>
     <row r="1568" ht="15.75" customHeight="1" s="19">
       <c r="A1568" s="8" t="n">
@@ -46718,6 +46776,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1568" t="inlineStr"/>
+      <c r="G1568" t="inlineStr"/>
     </row>
     <row r="1569" ht="15.75" customHeight="1" s="19">
       <c r="A1569" s="8" t="n">
@@ -46743,6 +46803,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1569" t="inlineStr"/>
+      <c r="G1569" t="inlineStr"/>
     </row>
     <row r="1570" ht="15.75" customHeight="1" s="19">
       <c r="A1570" s="8" t="n">
@@ -46768,6 +46830,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1570" t="inlineStr"/>
+      <c r="G1570" t="inlineStr"/>
     </row>
     <row r="1571" ht="15.75" customHeight="1" s="19">
       <c r="A1571" s="8" t="n">
@@ -46793,6 +46857,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1571" t="inlineStr"/>
+      <c r="G1571" t="inlineStr"/>
     </row>
     <row r="1572" ht="15.75" customHeight="1" s="19">
       <c r="A1572" s="8" t="n">
@@ -46818,6 +46884,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1572" t="inlineStr"/>
+      <c r="G1572" t="inlineStr"/>
     </row>
     <row r="1573" ht="15.75" customHeight="1" s="19">
       <c r="A1573" s="8" t="n">
@@ -46843,6 +46911,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1573" t="inlineStr"/>
+      <c r="G1573" t="inlineStr"/>
     </row>
     <row r="1574" ht="15.75" customHeight="1" s="19">
       <c r="A1574" s="8" t="n">
@@ -46868,6 +46938,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1574" t="inlineStr"/>
+      <c r="G1574" t="inlineStr"/>
     </row>
     <row r="1575" ht="15.75" customHeight="1" s="19">
       <c r="A1575" s="8" t="n">
@@ -46893,6 +46965,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1575" t="inlineStr"/>
+      <c r="G1575" t="inlineStr"/>
     </row>
     <row r="1576" ht="15.75" customHeight="1" s="19">
       <c r="A1576" s="8" t="n">
@@ -46918,6 +46992,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1576" t="inlineStr"/>
+      <c r="G1576" t="inlineStr"/>
     </row>
     <row r="1577" ht="15.75" customHeight="1" s="19">
       <c r="A1577" s="8" t="n">
@@ -46943,6 +47019,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1577" t="inlineStr"/>
+      <c r="G1577" t="inlineStr"/>
     </row>
     <row r="1578" ht="15.75" customHeight="1" s="19">
       <c r="A1578" s="8" t="n">
@@ -46968,6 +47046,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1578" t="inlineStr"/>
+      <c r="G1578" t="inlineStr"/>
     </row>
     <row r="1579" ht="15.75" customHeight="1" s="19">
       <c r="A1579" s="8" t="n">
@@ -46993,6 +47073,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1579" t="inlineStr"/>
+      <c r="G1579" t="inlineStr"/>
     </row>
     <row r="1580" ht="15.75" customHeight="1" s="19">
       <c r="A1580" s="8" t="n">
@@ -47018,6 +47100,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1580" t="inlineStr">
+        <is>
+          <t>+54 11 4233-5400</t>
+        </is>
+      </c>
+      <c r="G1580" t="inlineStr"/>
     </row>
     <row r="1581" ht="15.75" customHeight="1" s="19">
       <c r="A1581" s="8" t="n">
@@ -47043,6 +47131,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1581" t="inlineStr"/>
+      <c r="G1581" t="inlineStr"/>
     </row>
     <row r="1582" ht="15.75" customHeight="1" s="19">
       <c r="A1582" s="8" t="n">
@@ -47068,6 +47158,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1582" t="inlineStr"/>
+      <c r="G1582" t="inlineStr"/>
     </row>
     <row r="1583" ht="15.75" customHeight="1" s="19">
       <c r="A1583" s="8" t="n">
@@ -47093,6 +47185,12 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1583" t="inlineStr">
+        <is>
+          <t>+54 220 497-3999</t>
+        </is>
+      </c>
+      <c r="G1583" t="inlineStr"/>
     </row>
     <row r="1584" ht="15.75" customHeight="1" s="19">
       <c r="A1584" s="8" t="n">
@@ -47118,6 +47216,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1584" t="inlineStr"/>
+      <c r="G1584" t="inlineStr"/>
     </row>
     <row r="1585" ht="15.75" customHeight="1" s="19">
       <c r="A1585" s="8" t="n">
@@ -47143,6 +47243,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1585" t="inlineStr"/>
+      <c r="G1585" t="inlineStr"/>
     </row>
     <row r="1586" ht="15.75" customHeight="1" s="19">
       <c r="A1586" s="8" t="n">
@@ -47168,6 +47270,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1586" t="inlineStr"/>
+      <c r="G1586" t="inlineStr"/>
     </row>
     <row r="1587" ht="15.75" customHeight="1" s="19">
       <c r="A1587" s="8" t="n">
@@ -47193,6 +47297,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1587" t="inlineStr"/>
+      <c r="G1587" t="inlineStr"/>
     </row>
     <row r="1588" ht="15.75" customHeight="1" s="19">
       <c r="A1588" s="8" t="n">
@@ -47218,6 +47324,12 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1588" t="inlineStr">
+        <is>
+          <t>+54 11 5863-7629</t>
+        </is>
+      </c>
+      <c r="G1588" t="inlineStr"/>
     </row>
     <row r="1589" ht="15.75" customHeight="1" s="19">
       <c r="A1589" s="8" t="n">
@@ -47243,6 +47355,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1589" t="inlineStr">
+        <is>
+          <t>+54 11 5798-3013</t>
+        </is>
+      </c>
+      <c r="G1589" t="inlineStr">
+        <is>
+          <t>http://www.vercreativo.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1590" ht="15.75" customHeight="1" s="19">
       <c r="A1590" s="8" t="n">
@@ -47268,6 +47390,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1590" t="inlineStr"/>
+      <c r="G1590" t="inlineStr"/>
     </row>
     <row r="1591" ht="15.75" customHeight="1" s="19">
       <c r="A1591" s="8" t="n">
@@ -47293,6 +47417,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1591" t="inlineStr">
+        <is>
+          <t>+54 11 4891-9191</t>
+        </is>
+      </c>
+      <c r="G1591" t="inlineStr">
+        <is>
+          <t>https://www.correoargentino.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1592" ht="15.75" customHeight="1" s="19">
       <c r="A1592" s="8" t="n">
@@ -47318,6 +47452,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1592" t="inlineStr"/>
+      <c r="G1592" t="inlineStr"/>
     </row>
     <row r="1593" ht="15.75" customHeight="1" s="19">
       <c r="A1593" s="8" t="n">
@@ -47343,6 +47479,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1593" t="inlineStr"/>
+      <c r="G1593" t="inlineStr"/>
     </row>
     <row r="1594" ht="15.75" customHeight="1" s="19">
       <c r="A1594" s="8" t="n">
@@ -47368,6 +47506,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1594" t="inlineStr"/>
+      <c r="G1594" t="inlineStr"/>
     </row>
     <row r="1595" ht="15.75" customHeight="1" s="19">
       <c r="A1595" s="8" t="n">
@@ -47393,6 +47533,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1595" t="inlineStr"/>
+      <c r="G1595" t="inlineStr"/>
     </row>
     <row r="1596" ht="15.75" customHeight="1" s="19">
       <c r="A1596" s="8" t="n">
@@ -47418,6 +47560,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1596" t="inlineStr"/>
+      <c r="G1596" t="inlineStr"/>
     </row>
     <row r="1597" ht="15.75" customHeight="1" s="19">
       <c r="A1597" s="8" t="n">
@@ -47443,6 +47587,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1597" t="inlineStr"/>
+      <c r="G1597" t="inlineStr"/>
     </row>
     <row r="1598" ht="15.75" customHeight="1" s="19">
       <c r="A1598" s="8" t="n">
@@ -47468,6 +47614,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1598" t="inlineStr">
+        <is>
+          <t>+54 21265896</t>
+        </is>
+      </c>
+      <c r="G1598" t="inlineStr"/>
     </row>
     <row r="1599" ht="15.75" customHeight="1" s="19">
       <c r="A1599" s="8" t="n">
@@ -47493,6 +47645,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1599" t="inlineStr">
+        <is>
+          <t>+54 11 6271-8139</t>
+        </is>
+      </c>
+      <c r="G1599" t="inlineStr"/>
     </row>
     <row r="1600" ht="15.75" customHeight="1" s="19">
       <c r="A1600" s="8" t="n">
@@ -47518,6 +47676,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1600" t="inlineStr"/>
+      <c r="G1600" t="inlineStr"/>
     </row>
     <row r="1601" ht="15.75" customHeight="1" s="19">
       <c r="A1601" s="8" t="n">
@@ -47543,6 +47703,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1601" t="inlineStr"/>
+      <c r="G1601" t="inlineStr"/>
     </row>
     <row r="1602" ht="15.75" customHeight="1" s="19">
       <c r="A1602" s="8" t="n">
@@ -47566,6 +47728,16 @@
       <c r="E1602" s="9" t="inlineStr">
         <is>
           <t>Forrajeria</t>
+        </is>
+      </c>
+      <c r="F1602" t="inlineStr">
+        <is>
+          <t>+54 220 483-0954</t>
+        </is>
+      </c>
+      <c r="G1602" t="inlineStr">
+        <is>
+          <t>http://www.merlo.gob.ar/</t>
         </is>
       </c>
     </row>

--- a/PUNTOS_DE_VENTA_completado.xlsx
+++ b/PUNTOS_DE_VENTA_completado.xlsx
@@ -47765,6 +47765,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1603" t="inlineStr">
+        <is>
+          <t>+54 2656 47-3600</t>
+        </is>
+      </c>
+      <c r="G1603" t="inlineStr">
+        <is>
+          <t>https://www.wyndhamhotels.com/es-xl/hojo/merlo-argentina/howard-johnson-hotel-resort-villa-de-merlo/overview?CID=LC:q68ryvg9cq3avi8:15995&amp;iata=00093796</t>
+        </is>
+      </c>
     </row>
     <row r="1604" ht="15.75" customHeight="1" s="19">
       <c r="A1604" s="8" t="n">
@@ -47790,6 +47800,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1604" t="inlineStr"/>
+      <c r="G1604" t="inlineStr"/>
     </row>
     <row r="1605" ht="15.75" customHeight="1" s="19">
       <c r="A1605" s="8" t="n">
@@ -47815,6 +47827,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1605" t="inlineStr"/>
+      <c r="G1605" t="inlineStr"/>
     </row>
     <row r="1606" ht="15.75" customHeight="1" s="19">
       <c r="A1606" s="8" t="n">
@@ -47840,6 +47854,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1606" t="inlineStr"/>
+      <c r="G1606" t="inlineStr"/>
     </row>
     <row r="1607" ht="15.75" customHeight="1" s="19">
       <c r="A1607" s="8" t="n">
@@ -47865,6 +47881,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1607" t="inlineStr"/>
+      <c r="G1607" t="inlineStr"/>
     </row>
     <row r="1608" ht="15.75" customHeight="1" s="19">
       <c r="A1608" s="8" t="n">
@@ -47890,6 +47908,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1608" t="inlineStr">
+        <is>
+          <t>+54 230 448-5525</t>
+        </is>
+      </c>
+      <c r="G1608" t="inlineStr">
+        <is>
+          <t>https://forrajeriadelpuebloderqui.netlify.app/</t>
+        </is>
+      </c>
     </row>
     <row r="1609" ht="15.75" customHeight="1" s="19">
       <c r="A1609" s="8" t="n">
@@ -47915,6 +47943,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1609" t="inlineStr">
+        <is>
+          <t>+54 3487 42-3860</t>
+        </is>
+      </c>
+      <c r="G1609" t="inlineStr"/>
     </row>
     <row r="1610" ht="15.75" customHeight="1" s="19">
       <c r="A1610" s="8" t="n">
@@ -47940,6 +47974,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1610" t="inlineStr"/>
+      <c r="G1610" t="inlineStr"/>
     </row>
     <row r="1611" ht="15.75" customHeight="1" s="19">
       <c r="A1611" s="8" t="n">
@@ -47965,6 +48001,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F1611" t="inlineStr"/>
+      <c r="G1611" t="inlineStr"/>
     </row>
     <row r="1612" ht="15.75" customHeight="1" s="19">
       <c r="A1612" s="8" t="n">
@@ -47990,6 +48028,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1612" t="inlineStr"/>
+      <c r="G1612" t="inlineStr"/>
     </row>
     <row r="1613" ht="15.75" customHeight="1" s="19">
       <c r="A1613" s="8" t="n">
@@ -48015,6 +48055,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1613" t="inlineStr"/>
+      <c r="G1613" t="inlineStr"/>
     </row>
     <row r="1614" ht="15.75" customHeight="1" s="19">
       <c r="A1614" s="8" t="n">
@@ -48040,6 +48082,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1614" t="inlineStr"/>
+      <c r="G1614" t="inlineStr"/>
     </row>
     <row r="1615" ht="15.75" customHeight="1" s="19">
       <c r="A1615" s="8" t="n">
@@ -48065,6 +48109,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1615" t="inlineStr"/>
+      <c r="G1615" t="inlineStr"/>
     </row>
     <row r="1616" ht="15.75" customHeight="1" s="19">
       <c r="A1616" s="8" t="n">
@@ -48090,6 +48136,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1616" t="inlineStr"/>
+      <c r="G1616" t="inlineStr"/>
     </row>
     <row r="1617" ht="15.75" customHeight="1" s="19">
       <c r="A1617" s="8" t="n">
@@ -48115,6 +48163,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1617" t="inlineStr"/>
+      <c r="G1617" t="inlineStr"/>
     </row>
     <row r="1618" ht="15.75" customHeight="1" s="19">
       <c r="A1618" s="8" t="n">
@@ -48140,6 +48190,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1618" t="inlineStr"/>
+      <c r="G1618" t="inlineStr"/>
     </row>
     <row r="1619" ht="15.75" customHeight="1" s="19">
       <c r="A1619" s="8" t="n">
@@ -48165,6 +48217,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1619" t="inlineStr"/>
+      <c r="G1619" t="inlineStr"/>
     </row>
     <row r="1620" ht="15.75" customHeight="1" s="19">
       <c r="A1620" s="8" t="n">
@@ -48190,6 +48244,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1620" t="inlineStr"/>
+      <c r="G1620" t="inlineStr"/>
     </row>
     <row r="1621" ht="15.75" customHeight="1" s="19">
       <c r="A1621" s="8" t="n">
@@ -48215,6 +48271,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1621" t="inlineStr"/>
+      <c r="G1621" t="inlineStr"/>
     </row>
     <row r="1622" ht="15.75" customHeight="1" s="19">
       <c r="A1622" s="8" t="n">
@@ -48240,6 +48298,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1622" t="inlineStr"/>
+      <c r="G1622" t="inlineStr"/>
     </row>
     <row r="1623" ht="15.75" customHeight="1" s="19">
       <c r="A1623" s="8" t="n">
@@ -48265,6 +48325,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1623" t="inlineStr"/>
+      <c r="G1623" t="inlineStr"/>
     </row>
     <row r="1624" ht="15.75" customHeight="1" s="19">
       <c r="A1624" s="8" t="n">
@@ -48290,6 +48352,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1624" t="inlineStr"/>
+      <c r="G1624" t="inlineStr"/>
     </row>
     <row r="1625" ht="15.75" customHeight="1" s="19">
       <c r="A1625" s="8" t="n">
@@ -48315,6 +48379,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1625" t="inlineStr"/>
+      <c r="G1625" t="inlineStr"/>
     </row>
     <row r="1626" ht="15.75" customHeight="1" s="19">
       <c r="A1626" s="8" t="n">
@@ -48340,6 +48406,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1626" t="inlineStr"/>
+      <c r="G1626" t="inlineStr"/>
     </row>
     <row r="1627" ht="15.75" customHeight="1" s="19">
       <c r="A1627" s="8" t="n">
@@ -48365,6 +48433,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1627" t="inlineStr"/>
+      <c r="G1627" t="inlineStr"/>
     </row>
     <row r="1628" ht="15.75" customHeight="1" s="19">
       <c r="A1628" s="8" t="n">
@@ -48390,6 +48460,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1628" t="inlineStr"/>
+      <c r="G1628" t="inlineStr"/>
     </row>
     <row r="1629" ht="15.75" customHeight="1" s="19">
       <c r="A1629" s="8" t="n">
@@ -48415,6 +48487,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1629" t="inlineStr"/>
+      <c r="G1629" t="inlineStr"/>
     </row>
     <row r="1630" ht="15.75" customHeight="1" s="19">
       <c r="A1630" s="8" t="n">
@@ -48440,6 +48514,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1630" t="inlineStr"/>
+      <c r="G1630" t="inlineStr"/>
     </row>
     <row r="1631" ht="15.75" customHeight="1" s="19">
       <c r="A1631" s="8" t="n">
@@ -48465,6 +48541,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1631" t="inlineStr"/>
+      <c r="G1631" t="inlineStr"/>
     </row>
     <row r="1632" ht="15.75" customHeight="1" s="19">
       <c r="A1632" s="8" t="n">
@@ -48490,6 +48568,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1632" t="inlineStr"/>
+      <c r="G1632" t="inlineStr"/>
     </row>
     <row r="1633" ht="15.75" customHeight="1" s="19">
       <c r="A1633" s="8" t="n">
@@ -48515,6 +48595,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1633" t="inlineStr"/>
+      <c r="G1633" t="inlineStr"/>
     </row>
     <row r="1634" ht="15.75" customHeight="1" s="19">
       <c r="A1634" s="8" t="n">
@@ -48540,6 +48622,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1634" t="inlineStr">
+        <is>
+          <t>+54 220 482-3393</t>
+        </is>
+      </c>
+      <c r="G1634" t="inlineStr"/>
     </row>
     <row r="1635" ht="15.75" customHeight="1" s="19">
       <c r="A1635" s="8" t="n">
@@ -48565,6 +48653,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1635" t="inlineStr"/>
+      <c r="G1635" t="inlineStr"/>
     </row>
     <row r="1636" ht="15.75" customHeight="1" s="19">
       <c r="A1636" s="8" t="n">
@@ -48590,6 +48680,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1636" t="inlineStr"/>
+      <c r="G1636" t="inlineStr"/>
     </row>
     <row r="1637" ht="15.75" customHeight="1" s="19">
       <c r="A1637" s="8" t="n">
@@ -48615,6 +48707,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1637" t="inlineStr">
+        <is>
+          <t>+54 11 6272-8176</t>
+        </is>
+      </c>
+      <c r="G1637" t="inlineStr"/>
     </row>
     <row r="1638" ht="15.75" customHeight="1" s="19">
       <c r="A1638" s="8" t="n">
@@ -48640,6 +48738,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1638" t="inlineStr">
+        <is>
+          <t>+54 9 11 3342-8726</t>
+        </is>
+      </c>
+      <c r="G1638" t="inlineStr">
+        <is>
+          <t>http://www.elrusotiendademascotas.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1639" ht="15.75" customHeight="1" s="19">
       <c r="A1639" s="8" t="n">
@@ -48665,6 +48773,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1639" t="inlineStr"/>
+      <c r="G1639" t="inlineStr"/>
     </row>
     <row r="1640" ht="15.75" customHeight="1" s="19">
       <c r="A1640" s="8" t="n">
@@ -48690,6 +48800,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1640" t="inlineStr">
+        <is>
+          <t>+54 236 442-4618</t>
+        </is>
+      </c>
+      <c r="G1640" t="inlineStr"/>
     </row>
     <row r="1641" ht="15.75" customHeight="1" s="19">
       <c r="A1641" s="8" t="n">
@@ -48715,6 +48831,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1641" t="inlineStr"/>
+      <c r="G1641" t="inlineStr"/>
     </row>
     <row r="1642" ht="15.75" customHeight="1" s="19">
       <c r="A1642" s="8" t="n">
@@ -48740,6 +48858,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1642" t="inlineStr"/>
+      <c r="G1642" t="inlineStr"/>
     </row>
     <row r="1643" ht="15.75" customHeight="1" s="19">
       <c r="A1643" s="8" t="n">
@@ -48765,6 +48885,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1643" t="inlineStr"/>
+      <c r="G1643" t="inlineStr"/>
     </row>
     <row r="1644" ht="15.75" customHeight="1" s="19">
       <c r="A1644" s="8" t="n">
@@ -48786,6 +48908,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1644" t="inlineStr"/>
+      <c r="G1644" t="inlineStr">
+        <is>
+          <t>http://www.argentina.gob.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1645" ht="15.75" customHeight="1" s="19">
       <c r="A1645" s="8" t="n">
@@ -48811,6 +48939,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1645" t="inlineStr"/>
+      <c r="G1645" t="inlineStr"/>
     </row>
     <row r="1646" ht="15.75" customHeight="1" s="19">
       <c r="A1646" s="8" t="n">
@@ -48836,6 +48966,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F1646" t="inlineStr">
+        <is>
+          <t>+54 11 7079-1234</t>
+        </is>
+      </c>
+      <c r="G1646" t="inlineStr">
+        <is>
+          <t>https://centro-pet.mercadoshops.com.ar/criadero</t>
+        </is>
+      </c>
     </row>
     <row r="1647" ht="15.75" customHeight="1" s="19">
       <c r="A1647" s="8" t="n">
@@ -48861,6 +49001,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1647" t="inlineStr"/>
+      <c r="G1647" t="inlineStr"/>
     </row>
     <row r="1648" ht="15.75" customHeight="1" s="19">
       <c r="A1648" s="8" t="n">
@@ -48886,6 +49028,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1648" t="inlineStr"/>
+      <c r="G1648" t="inlineStr"/>
     </row>
     <row r="1649" ht="15.75" customHeight="1" s="19">
       <c r="A1649" s="8" t="n">
@@ -48911,6 +49055,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1649" t="inlineStr"/>
+      <c r="G1649" t="inlineStr"/>
     </row>
     <row r="1650" ht="15.75" customHeight="1" s="19">
       <c r="A1650" s="8" t="n">
@@ -48936,6 +49082,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1650" t="inlineStr"/>
+      <c r="G1650" t="inlineStr"/>
     </row>
     <row r="1651" ht="15.75" customHeight="1" s="19">
       <c r="A1651" s="8" t="n">
@@ -48961,6 +49109,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1651" t="inlineStr">
+        <is>
+          <t>+54 11 7195-0011</t>
+        </is>
+      </c>
+      <c r="G1651" t="inlineStr">
+        <is>
+          <t>http://www.coblapoint.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1652" ht="15.75" customHeight="1" s="19">
       <c r="A1652" s="8" t="n">
@@ -48986,6 +49144,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1652" t="inlineStr"/>
+      <c r="G1652" t="inlineStr"/>
     </row>
     <row r="1653" ht="15.75" customHeight="1" s="19">
       <c r="A1653" s="8" t="n">

--- a/PUNTOS_DE_VENTA_completado.xlsx
+++ b/PUNTOS_DE_VENTA_completado.xlsx
@@ -49171,6 +49171,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1653" t="inlineStr">
+        <is>
+          <t>+54 11 4082-8160</t>
+        </is>
+      </c>
+      <c r="G1653" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/eurekaentretenimientos/?utm_source=ig_web_button_share_sheet&amp;igshid=OGQ5ZDc2ODk2ZA==</t>
+        </is>
+      </c>
     </row>
     <row r="1654" ht="15.75" customHeight="1" s="19">
       <c r="A1654" s="8" t="n">
@@ -49196,6 +49206,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1654" t="inlineStr"/>
+      <c r="G1654" t="inlineStr"/>
     </row>
     <row r="1655" ht="15.75" customHeight="1" s="19">
       <c r="A1655" s="8" t="n">
@@ -49221,6 +49233,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1655" t="inlineStr"/>
+      <c r="G1655" t="inlineStr"/>
     </row>
     <row r="1656" ht="15.75" customHeight="1" s="19">
       <c r="A1656" s="8" t="n">
@@ -49246,6 +49260,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1656" t="inlineStr"/>
+      <c r="G1656" t="inlineStr"/>
     </row>
     <row r="1657" ht="15.75" customHeight="1" s="19">
       <c r="A1657" s="8" t="n">
@@ -49271,6 +49287,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1657" t="inlineStr">
+        <is>
+          <t>+54 11 5219-4444</t>
+        </is>
+      </c>
+      <c r="G1657" t="inlineStr">
+        <is>
+          <t>https://www.canrock.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1658" ht="15.75" customHeight="1" s="19">
       <c r="A1658" s="8" t="n">
@@ -49296,6 +49322,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1658" t="inlineStr"/>
+      <c r="G1658" t="inlineStr"/>
     </row>
     <row r="1659" ht="15.75" customHeight="1" s="19">
       <c r="A1659" s="8" t="n">
@@ -49321,6 +49349,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1659" t="inlineStr"/>
+      <c r="G1659" t="inlineStr"/>
     </row>
     <row r="1660" ht="15.75" customHeight="1" s="19">
       <c r="A1660" s="8" t="n">
@@ -49346,6 +49376,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1660" t="inlineStr">
+        <is>
+          <t>+54 11 2053-9852</t>
+        </is>
+      </c>
+      <c r="G1660" t="inlineStr">
+        <is>
+          <t>https://vetcenter.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1661" ht="15.75" customHeight="1" s="19">
       <c r="A1661" s="8" t="n">
@@ -49371,6 +49411,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1661" t="inlineStr">
+        <is>
+          <t>+54 343 467-5096</t>
+        </is>
+      </c>
+      <c r="G1661" t="inlineStr">
+        <is>
+          <t>http://www.vallemaria.gob.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1662" ht="15.75" customHeight="1" s="19">
       <c r="A1662" s="8" t="n">
@@ -49396,6 +49446,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1662" t="inlineStr"/>
+      <c r="G1662" t="inlineStr"/>
     </row>
     <row r="1663" ht="15.75" customHeight="1" s="19">
       <c r="A1663" s="8" t="n">
@@ -49421,6 +49473,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1663" t="inlineStr">
+        <is>
+          <t>+54 11 3144-4198</t>
+        </is>
+      </c>
+      <c r="G1663" t="inlineStr">
+        <is>
+          <t>https://www.gpquality.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1664" ht="15.75" customHeight="1" s="19">
       <c r="A1664" s="8" t="n">
@@ -49446,6 +49508,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1664" t="inlineStr"/>
+      <c r="G1664" t="inlineStr"/>
     </row>
     <row r="1665" ht="15.75" customHeight="1" s="19">
       <c r="A1665" s="8" t="n">
@@ -49471,6 +49535,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1665" t="inlineStr"/>
+      <c r="G1665" t="inlineStr"/>
     </row>
     <row r="1666" ht="15.75" customHeight="1" s="19">
       <c r="A1666" s="8" t="n">
@@ -49496,6 +49562,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1666" t="inlineStr">
+        <is>
+          <t>+54 9 11 5479-5371</t>
+        </is>
+      </c>
+      <c r="G1666" t="inlineStr"/>
     </row>
     <row r="1667" ht="15.75" customHeight="1" s="19">
       <c r="A1667" s="8" t="n">
@@ -49521,6 +49593,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1667" t="inlineStr"/>
+      <c r="G1667" t="inlineStr"/>
     </row>
     <row r="1668" ht="15.75" customHeight="1" s="19">
       <c r="A1668" s="8" t="n">
@@ -49546,6 +49620,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1668" t="inlineStr"/>
+      <c r="G1668" t="inlineStr"/>
     </row>
     <row r="1669" ht="15.75" customHeight="1" s="19">
       <c r="A1669" s="8" t="n">
@@ -49571,6 +49647,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1669" t="inlineStr">
+        <is>
+          <t>+54 11 7738-7665</t>
+        </is>
+      </c>
+      <c r="G1669" t="inlineStr">
+        <is>
+          <t>https://electromaxel.com.ar/#!/-maxel/</t>
+        </is>
+      </c>
     </row>
     <row r="1670" ht="15.75" customHeight="1" s="19">
       <c r="A1670" s="8" t="n">
@@ -49596,6 +49682,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1670" t="inlineStr"/>
+      <c r="G1670" t="inlineStr"/>
     </row>
     <row r="1671" ht="15.75" customHeight="1" s="19">
       <c r="A1671" s="8" t="n">
@@ -49621,6 +49709,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1671" t="inlineStr"/>
+      <c r="G1671" t="inlineStr"/>
     </row>
     <row r="1672" ht="15.75" customHeight="1" s="19">
       <c r="A1672" s="8" t="n">
@@ -49646,6 +49736,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1672" t="inlineStr">
+        <is>
+          <t>+54 11 4836-2459</t>
+        </is>
+      </c>
+      <c r="G1672" t="inlineStr">
+        <is>
+          <t>https://www.mivetshop.com.ar/shop/selpypet</t>
+        </is>
+      </c>
     </row>
     <row r="1673" ht="15.75" customHeight="1" s="19">
       <c r="A1673" s="8" t="n">
@@ -49671,6 +49771,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1673" t="inlineStr">
+        <is>
+          <t>+54 11 5566-8052</t>
+        </is>
+      </c>
+      <c r="G1673" t="inlineStr"/>
     </row>
     <row r="1674" ht="15.75" customHeight="1" s="19">
       <c r="A1674" s="8" t="n">
@@ -49696,6 +49802,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F1674" t="inlineStr">
+        <is>
+          <t>+54 11 4776-0477</t>
+        </is>
+      </c>
+      <c r="G1674" t="inlineStr">
+        <is>
+          <t>https://carpescheider.com/</t>
+        </is>
+      </c>
     </row>
     <row r="1675" ht="15.75" customHeight="1" s="19">
       <c r="A1675" s="8" t="n">
@@ -49721,6 +49837,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F1675" t="inlineStr">
+        <is>
+          <t>+54 9 11 6897-5659</t>
+        </is>
+      </c>
+      <c r="G1675" t="inlineStr">
+        <is>
+          <t>http://www.totalpet.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1676" ht="15.75" customHeight="1" s="19">
       <c r="A1676" s="8" t="n">
@@ -49746,6 +49872,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F1676" t="inlineStr">
+        <is>
+          <t>+54 11 4553-5821</t>
+        </is>
+      </c>
+      <c r="G1676" t="inlineStr">
+        <is>
+          <t>http://www.totalpet.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1677" ht="15.75" customHeight="1" s="19">
       <c r="A1677" s="8" t="n">
@@ -49771,6 +49907,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1677" t="inlineStr"/>
+      <c r="G1677" t="inlineStr"/>
     </row>
     <row r="1678" ht="15.75" customHeight="1" s="19">
       <c r="A1678" s="8" t="n">
@@ -49796,6 +49934,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F1678" t="inlineStr"/>
+      <c r="G1678" t="inlineStr"/>
     </row>
     <row r="1679" ht="15.75" customHeight="1" s="19">
       <c r="A1679" s="8" t="n">
@@ -49817,6 +49957,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F1679" t="inlineStr">
+        <is>
+          <t>+54 11 4588-6500</t>
+        </is>
+      </c>
+      <c r="G1679" t="inlineStr">
+        <is>
+          <t>http://www.amarintech.com/</t>
+        </is>
+      </c>
     </row>
     <row r="1680" ht="15.75" customHeight="1" s="19">
       <c r="A1680" s="8" t="n">
@@ -49842,6 +49992,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1680" t="inlineStr"/>
+      <c r="G1680" t="inlineStr"/>
     </row>
     <row r="1681" ht="15.75" customHeight="1" s="19">
       <c r="A1681" s="8" t="n">
@@ -49867,6 +50019,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1681" t="inlineStr"/>
+      <c r="G1681" t="inlineStr"/>
     </row>
     <row r="1682" ht="15.75" customHeight="1" s="19">
       <c r="A1682" s="8" t="n">
@@ -49892,6 +50046,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1682" t="inlineStr"/>
+      <c r="G1682" t="inlineStr"/>
     </row>
     <row r="1683" ht="15.75" customHeight="1" s="19">
       <c r="A1683" s="8" t="n">
@@ -49917,6 +50073,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1683" t="inlineStr">
+        <is>
+          <t>+54 11 4701-7697</t>
+        </is>
+      </c>
+      <c r="G1683" t="inlineStr"/>
     </row>
     <row r="1684" ht="15.75" customHeight="1" s="19">
       <c r="A1684" s="8" t="n">
@@ -49942,6 +50104,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1684" t="inlineStr">
+        <is>
+          <t>+54 11 4122-6000</t>
+        </is>
+      </c>
+      <c r="G1684" t="inlineStr">
+        <is>
+          <t>https://www.garrahan.gov.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1685" ht="15.75" customHeight="1" s="19">
       <c r="A1685" s="8" t="n">
@@ -49967,6 +50139,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1685" t="inlineStr"/>
+      <c r="G1685" t="inlineStr"/>
     </row>
     <row r="1686" ht="15.75" customHeight="1" s="19">
       <c r="A1686" s="8" t="n">
@@ -49992,6 +50166,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1686" t="inlineStr"/>
+      <c r="G1686" t="inlineStr"/>
     </row>
     <row r="1687" ht="15.75" customHeight="1" s="19">
       <c r="A1687" s="8" t="n">
@@ -50017,6 +50193,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1687" t="inlineStr"/>
+      <c r="G1687" t="inlineStr"/>
     </row>
     <row r="1688" ht="15.75" customHeight="1" s="19">
       <c r="A1688" s="8" t="n">
@@ -50042,6 +50220,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1688" t="inlineStr">
+        <is>
+          <t>+54 11 4744-0553</t>
+        </is>
+      </c>
+      <c r="G1688" t="inlineStr"/>
     </row>
     <row r="1689" ht="15.75" customHeight="1" s="19">
       <c r="A1689" s="8" t="n">
@@ -50067,6 +50251,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1689" t="inlineStr"/>
+      <c r="G1689" t="inlineStr"/>
     </row>
     <row r="1690" ht="15.75" customHeight="1" s="19">
       <c r="A1690" s="8" t="n">
@@ -50092,6 +50278,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1690" t="inlineStr"/>
+      <c r="G1690" t="inlineStr"/>
     </row>
     <row r="1691" ht="15.75" customHeight="1" s="19">
       <c r="A1691" s="8" t="n">
@@ -50117,6 +50305,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1691" t="inlineStr"/>
+      <c r="G1691" t="inlineStr"/>
     </row>
     <row r="1692" ht="15.75" customHeight="1" s="19">
       <c r="A1692" s="8" t="n">
@@ -50142,6 +50332,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1692" t="inlineStr"/>
+      <c r="G1692" t="inlineStr"/>
     </row>
     <row r="1693" ht="15.75" customHeight="1" s="19">
       <c r="A1693" s="8" t="n">
@@ -50167,6 +50359,16 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1693" t="inlineStr">
+        <is>
+          <t>+54 9 11 6982-9191</t>
+        </is>
+      </c>
+      <c r="G1693" t="inlineStr">
+        <is>
+          <t>https://www.48fitcycle.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1694" ht="15.75" customHeight="1" s="19">
       <c r="A1694" s="8" t="n">
@@ -50192,6 +50394,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1694" t="inlineStr"/>
+      <c r="G1694" t="inlineStr"/>
     </row>
     <row r="1695" ht="15.75" customHeight="1" s="19">
       <c r="A1695" s="8" t="n">
@@ -50217,6 +50421,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1695" t="inlineStr"/>
+      <c r="G1695" t="inlineStr"/>
     </row>
     <row r="1696" ht="15.75" customHeight="1" s="19">
       <c r="A1696" s="8" t="n">
@@ -50242,6 +50448,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1696" t="inlineStr">
+        <is>
+          <t>+54 11 3521-6162</t>
+        </is>
+      </c>
+      <c r="G1696" t="inlineStr"/>
     </row>
     <row r="1697" ht="15.75" customHeight="1" s="19">
       <c r="A1697" s="8" t="n">
@@ -50267,6 +50479,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1697" t="inlineStr"/>
+      <c r="G1697" t="inlineStr"/>
     </row>
     <row r="1698" ht="15.75" customHeight="1" s="19">
       <c r="A1698" s="8" t="n">
@@ -50292,6 +50506,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1698" t="inlineStr">
+        <is>
+          <t>+54 11 4745-3841</t>
+        </is>
+      </c>
+      <c r="G1698" t="inlineStr"/>
     </row>
     <row r="1699" ht="15.75" customHeight="1" s="19">
       <c r="A1699" s="8" t="n">
@@ -50317,6 +50537,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1699" t="inlineStr"/>
+      <c r="G1699" t="inlineStr"/>
     </row>
     <row r="1700" ht="15.75" customHeight="1" s="19">
       <c r="A1700" s="8" t="n">
@@ -50342,6 +50564,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1700" t="inlineStr">
+        <is>
+          <t>+54 11 3795-6509</t>
+        </is>
+      </c>
+      <c r="G1700" t="inlineStr">
+        <is>
+          <t>https://pedidos.petshopdonmario.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1701" ht="15.75" customHeight="1" s="19">
       <c r="A1701" s="8" t="n">
@@ -50367,6 +50599,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1701" t="inlineStr">
+        <is>
+          <t>+54 9 11 6284-5800</t>
+        </is>
+      </c>
+      <c r="G1701" t="inlineStr">
+        <is>
+          <t>https://www.mivetshop.com.ar/shop/animalshop?utm_source=ig&amp;utm_medium=social&amp;utm_content=link_in_bio&amp;brid=uYX7UjnU10PQtuQqQT-kJw</t>
+        </is>
+      </c>
     </row>
     <row r="1702" ht="15.75" customHeight="1" s="19">
       <c r="A1702" s="8" t="n">
@@ -50392,6 +50634,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1702" t="inlineStr"/>
+      <c r="G1702" t="inlineStr"/>
     </row>
     <row r="1703" ht="15.75" customHeight="1" s="19">
       <c r="A1703" s="8" t="n">
@@ -50417,6 +50661,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1703" t="inlineStr">
+        <is>
+          <t>+54 11 6844-2502</t>
+        </is>
+      </c>
+      <c r="G1703" t="inlineStr">
+        <is>
+          <t>http://www.thebarberjob.com/</t>
+        </is>
+      </c>
     </row>
     <row r="1704" ht="15.75" customHeight="1" s="19">
       <c r="A1704" s="8" t="n">
@@ -50442,6 +50696,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1704" t="inlineStr"/>
+      <c r="G1704" t="inlineStr"/>
     </row>
     <row r="1705" ht="15.75" customHeight="1" s="19">
       <c r="A1705" s="8" t="n">
@@ -50467,6 +50723,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1705" t="inlineStr">
+        <is>
+          <t>+54 11 4947-9321</t>
+        </is>
+      </c>
+      <c r="G1705" t="inlineStr"/>
     </row>
     <row r="1706" ht="15.75" customHeight="1" s="19">
       <c r="A1706" s="8" t="n">
@@ -50492,6 +50754,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1706" t="inlineStr"/>
+      <c r="G1706" t="inlineStr"/>
     </row>
     <row r="1707" ht="15.75" customHeight="1" s="19">
       <c r="A1707" s="8" t="n">
@@ -50517,6 +50781,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1707" t="inlineStr"/>
+      <c r="G1707" t="inlineStr"/>
     </row>
     <row r="1708" ht="15.75" customHeight="1" s="19">
       <c r="A1708" s="8" t="n">
@@ -50542,6 +50808,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1708" t="inlineStr"/>
+      <c r="G1708" t="inlineStr"/>
     </row>
     <row r="1709" ht="15.75" customHeight="1" s="19">
       <c r="A1709" s="8" t="n">
@@ -50567,6 +50835,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1709" t="inlineStr"/>
+      <c r="G1709" t="inlineStr"/>
     </row>
     <row r="1710" ht="15.75" customHeight="1" s="19">
       <c r="A1710" s="8" t="n">
@@ -50592,6 +50862,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1710" t="inlineStr"/>
+      <c r="G1710" t="inlineStr"/>
     </row>
     <row r="1711" ht="15.75" customHeight="1" s="19">
       <c r="A1711" s="8" t="n">
@@ -50617,6 +50889,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1711" t="inlineStr">
+        <is>
+          <t>+54 11 4546-3250</t>
+        </is>
+      </c>
+      <c r="G1711" t="inlineStr"/>
     </row>
     <row r="1712" ht="15.75" customHeight="1" s="19">
       <c r="A1712" s="8" t="n">
@@ -50642,6 +50920,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1712" t="inlineStr"/>
+      <c r="G1712" t="inlineStr"/>
     </row>
     <row r="1713" ht="15.75" customHeight="1" s="19">
       <c r="A1713" s="8" t="n">
@@ -50667,6 +50947,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1713" t="inlineStr"/>
+      <c r="G1713" t="inlineStr"/>
     </row>
     <row r="1714" ht="15.75" customHeight="1" s="19">
       <c r="A1714" s="8" t="n">
@@ -50692,6 +50974,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1714" t="inlineStr"/>
+      <c r="G1714" t="inlineStr"/>
     </row>
     <row r="1715" ht="15.75" customHeight="1" s="19">
       <c r="A1715" s="8" t="n">
@@ -50717,6 +51001,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1715" t="inlineStr">
+        <is>
+          <t>+54 11 4553-4456</t>
+        </is>
+      </c>
+      <c r="G1715" t="inlineStr">
+        <is>
+          <t>http://www.spacan.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1716" ht="15.75" customHeight="1" s="19">
       <c r="A1716" s="8" t="n">
@@ -50742,6 +51036,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1716" t="inlineStr"/>
+      <c r="G1716" t="inlineStr"/>
     </row>
     <row r="1717" ht="15.75" customHeight="1" s="19">
       <c r="A1717" s="8" t="n">
@@ -50767,6 +51063,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1717" t="inlineStr"/>
+      <c r="G1717" t="inlineStr"/>
     </row>
     <row r="1718" ht="15.75" customHeight="1" s="19">
       <c r="A1718" s="8" t="n">
@@ -50792,6 +51090,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1718" t="inlineStr"/>
+      <c r="G1718" t="inlineStr"/>
     </row>
     <row r="1719" ht="15.75" customHeight="1" s="19">
       <c r="A1719" s="8" t="n">
@@ -50817,6 +51117,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1719" t="inlineStr"/>
+      <c r="G1719" t="inlineStr"/>
     </row>
     <row r="1720" ht="15.75" customHeight="1" s="19">
       <c r="A1720" s="8" t="n">
@@ -50842,6 +51144,12 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F1720" t="inlineStr">
+        <is>
+          <t>+54 11 4566-5114</t>
+        </is>
+      </c>
+      <c r="G1720" t="inlineStr"/>
     </row>
     <row r="1721" ht="15.75" customHeight="1" s="19">
       <c r="A1721" s="8" t="n">
@@ -50867,6 +51175,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1721" t="inlineStr">
+        <is>
+          <t>+54 11 4773-5974</t>
+        </is>
+      </c>
+      <c r="G1721" t="inlineStr"/>
     </row>
     <row r="1722" ht="15.75" customHeight="1" s="19">
       <c r="A1722" s="8" t="n">
@@ -50892,6 +51206,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1722" t="inlineStr"/>
+      <c r="G1722" t="inlineStr"/>
     </row>
     <row r="1723" ht="15.75" customHeight="1" s="19">
       <c r="A1723" s="8" t="n">
@@ -50917,6 +51233,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1723" t="inlineStr"/>
+      <c r="G1723" t="inlineStr"/>
     </row>
     <row r="1724" ht="15.75" customHeight="1" s="19">
       <c r="A1724" s="8" t="n">
@@ -50942,6 +51260,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1724" t="inlineStr"/>
+      <c r="G1724" t="inlineStr"/>
     </row>
     <row r="1725" ht="15.75" customHeight="1" s="19">
       <c r="A1725" s="8" t="n">
@@ -50967,6 +51287,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1725" t="inlineStr"/>
+      <c r="G1725" t="inlineStr"/>
     </row>
     <row r="1726" ht="15.75" customHeight="1" s="19">
       <c r="A1726" s="8" t="n">
@@ -50992,6 +51314,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1726" t="inlineStr"/>
+      <c r="G1726" t="inlineStr"/>
     </row>
     <row r="1727" ht="15.75" customHeight="1" s="19">
       <c r="A1727" s="8" t="n">
@@ -51017,6 +51341,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1727" t="inlineStr"/>
+      <c r="G1727" t="inlineStr"/>
     </row>
     <row r="1728" ht="15.75" customHeight="1" s="19">
       <c r="A1728" s="8" t="n">
@@ -51042,6 +51368,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1728" t="inlineStr"/>
+      <c r="G1728" t="inlineStr"/>
     </row>
     <row r="1729" ht="15.75" customHeight="1" s="19">
       <c r="A1729" s="8" t="n">
@@ -51067,6 +51395,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1729" t="inlineStr"/>
+      <c r="G1729" t="inlineStr"/>
     </row>
     <row r="1730" ht="15.75" customHeight="1" s="19">
       <c r="A1730" s="8" t="n">
@@ -51092,6 +51422,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1730" t="inlineStr">
+        <is>
+          <t>+54 11 4237-8155</t>
+        </is>
+      </c>
+      <c r="G1730" t="inlineStr"/>
     </row>
     <row r="1731" ht="15.75" customHeight="1" s="19">
       <c r="A1731" s="8" t="n">
@@ -51117,6 +51453,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1731" t="inlineStr"/>
+      <c r="G1731" t="inlineStr"/>
     </row>
     <row r="1732" ht="15.75" customHeight="1" s="19">
       <c r="A1732" s="8" t="n">
@@ -51142,6 +51480,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1732" t="inlineStr"/>
+      <c r="G1732" t="inlineStr"/>
     </row>
     <row r="1733" ht="15.75" customHeight="1" s="19">
       <c r="A1733" s="8" t="n">
@@ -51167,6 +51507,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1733" t="inlineStr"/>
+      <c r="G1733" t="inlineStr"/>
     </row>
     <row r="1734" ht="15.75" customHeight="1" s="19">
       <c r="A1734" s="8" t="n">
@@ -51192,6 +51534,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1734" t="inlineStr"/>
+      <c r="G1734" t="inlineStr"/>
     </row>
     <row r="1735" ht="15.75" customHeight="1" s="19">
       <c r="A1735" s="8" t="n">
@@ -51217,6 +51561,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1735" t="inlineStr"/>
+      <c r="G1735" t="inlineStr"/>
     </row>
     <row r="1736" ht="15.75" customHeight="1" s="19">
       <c r="A1736" s="8" t="n">
@@ -51242,6 +51588,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1736" t="inlineStr">
+        <is>
+          <t>+54 810-666-4444</t>
+        </is>
+      </c>
+      <c r="G1736" t="inlineStr">
+        <is>
+          <t>http://www.bna.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1737" ht="15.75" customHeight="1" s="19">
       <c r="A1737" s="8" t="n">
@@ -51267,6 +51623,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1737" t="inlineStr"/>
+      <c r="G1737" t="inlineStr"/>
     </row>
     <row r="1738" ht="15.75" customHeight="1" s="19">
       <c r="A1738" s="8" t="n">
@@ -51292,6 +51650,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1738" t="inlineStr"/>
+      <c r="G1738" t="inlineStr"/>
     </row>
     <row r="1739" ht="15.75" customHeight="1" s="19">
       <c r="A1739" s="8" t="n">
@@ -51317,6 +51677,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1739" t="inlineStr"/>
+      <c r="G1739" t="inlineStr"/>
     </row>
     <row r="1740" ht="15.75" customHeight="1" s="19">
       <c r="A1740" s="8" t="n">
@@ -51342,6 +51704,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1740" t="inlineStr"/>
+      <c r="G1740" t="inlineStr"/>
     </row>
     <row r="1741" ht="15.75" customHeight="1" s="19">
       <c r="A1741" s="8" t="n">
@@ -51367,6 +51731,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F1741" t="inlineStr"/>
+      <c r="G1741" t="inlineStr"/>
     </row>
     <row r="1742" ht="15.75" customHeight="1" s="19">
       <c r="A1742" s="8" t="n">
@@ -51392,6 +51758,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1742" t="inlineStr"/>
+      <c r="G1742" t="inlineStr"/>
     </row>
     <row r="1743" ht="15.75" customHeight="1" s="19">
       <c r="A1743" s="8" t="n">
@@ -51417,6 +51785,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F1743" t="inlineStr">
+        <is>
+          <t>+54 11 2339-2311</t>
+        </is>
+      </c>
+      <c r="G1743" t="inlineStr">
+        <is>
+          <t>https://www.unipet.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1744" ht="15.75" customHeight="1" s="19">
       <c r="A1744" s="8" t="n">
@@ -51442,6 +51820,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1744" t="inlineStr"/>
+      <c r="G1744" t="inlineStr"/>
     </row>
     <row r="1745" ht="15.75" customHeight="1" s="19">
       <c r="A1745" s="8" t="n">
@@ -51467,6 +51847,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1745" t="inlineStr"/>
+      <c r="G1745" t="inlineStr"/>
     </row>
     <row r="1746" ht="15.75" customHeight="1" s="19">
       <c r="A1746" s="8" t="n">
@@ -51492,6 +51874,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1746" t="inlineStr"/>
+      <c r="G1746" t="inlineStr"/>
     </row>
     <row r="1747" ht="15.75" customHeight="1" s="19">
       <c r="A1747" s="8" t="n">
@@ -51517,6 +51901,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1747" t="inlineStr"/>
+      <c r="G1747" t="inlineStr"/>
     </row>
     <row r="1748" ht="15.75" customHeight="1" s="19">
       <c r="A1748" s="8" t="n">
@@ -51542,6 +51928,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1748" t="inlineStr"/>
+      <c r="G1748" t="inlineStr"/>
     </row>
     <row r="1749" ht="15.75" customHeight="1" s="19">
       <c r="A1749" s="8" t="n">
@@ -51567,6 +51955,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1749" t="inlineStr">
+        <is>
+          <t>+54 11 4483-0156</t>
+        </is>
+      </c>
+      <c r="G1749" t="inlineStr"/>
     </row>
     <row r="1750" ht="15.75" customHeight="1" s="19">
       <c r="A1750" s="8" t="n">
@@ -51592,6 +51986,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1750" t="inlineStr"/>
+      <c r="G1750" t="inlineStr"/>
     </row>
     <row r="1751" ht="15.75" customHeight="1" s="19">
       <c r="A1751" s="8" t="n">
@@ -51617,6 +52013,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1751" t="inlineStr"/>
+      <c r="G1751" t="inlineStr"/>
     </row>
     <row r="1752" ht="15.75" customHeight="1" s="19">
       <c r="A1752" s="8" t="n">
@@ -51642,6 +52040,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1752" t="inlineStr"/>
+      <c r="G1752" t="inlineStr"/>
     </row>
     <row r="1753" ht="15.75" customHeight="1" s="19">
       <c r="A1753" s="8" t="n">

--- a/PUNTOS_DE_VENTA_completado.xlsx
+++ b/PUNTOS_DE_VENTA_completado.xlsx
@@ -52067,6 +52067,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1753" t="inlineStr"/>
+      <c r="G1753" t="inlineStr"/>
     </row>
     <row r="1754" ht="15.75" customHeight="1" s="19">
       <c r="A1754" s="8" t="n">
@@ -52092,6 +52094,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1754" t="inlineStr"/>
+      <c r="G1754" t="inlineStr"/>
     </row>
     <row r="1755" ht="15.75" customHeight="1" s="19">
       <c r="A1755" s="8" t="n">
@@ -52117,6 +52121,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1755" t="inlineStr">
+        <is>
+          <t>+54 11 3334-0166</t>
+        </is>
+      </c>
+      <c r="G1755" t="inlineStr"/>
     </row>
     <row r="1756" ht="15.75" customHeight="1" s="19">
       <c r="A1756" s="8" t="n">
@@ -52142,6 +52152,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1756" t="inlineStr"/>
+      <c r="G1756" t="inlineStr"/>
     </row>
     <row r="1757" ht="15.75" customHeight="1" s="19">
       <c r="A1757" s="8" t="n">
@@ -52167,6 +52179,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1757" t="inlineStr"/>
+      <c r="G1757" t="inlineStr"/>
     </row>
     <row r="1758" ht="15.75" customHeight="1" s="19">
       <c r="A1758" s="8" t="n">
@@ -52192,6 +52206,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1758" t="inlineStr"/>
+      <c r="G1758" t="inlineStr"/>
     </row>
     <row r="1759" ht="15.75" customHeight="1" s="19">
       <c r="A1759" s="8" t="n">
@@ -52217,6 +52233,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1759" t="inlineStr">
+        <is>
+          <t>+54 11 4662-5510</t>
+        </is>
+      </c>
+      <c r="G1759" t="inlineStr">
+        <is>
+          <t>http://www.hurlinghamclub.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1760" ht="15.75" customHeight="1" s="19">
       <c r="A1760" s="8" t="n">
@@ -52242,6 +52268,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1760" t="inlineStr">
+        <is>
+          <t>+54 11 5805-2450</t>
+        </is>
+      </c>
+      <c r="G1760" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/masajesartemisas?utm_source=ig_web_button_share_sheet&amp;igsh=ZDNlZDc0MzIxNw==</t>
+        </is>
+      </c>
     </row>
     <row r="1761" ht="15.75" customHeight="1" s="19">
       <c r="A1761" s="8" t="n">
@@ -52267,6 +52303,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1761" t="inlineStr"/>
+      <c r="G1761" t="inlineStr"/>
     </row>
     <row r="1762" ht="15.75" customHeight="1" s="19">
       <c r="A1762" s="8" t="n">
@@ -52292,6 +52330,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1762" t="inlineStr"/>
+      <c r="G1762" t="inlineStr"/>
     </row>
     <row r="1763" ht="15.75" customHeight="1" s="19">
       <c r="A1763" s="8" t="n">
@@ -52317,6 +52357,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1763" t="inlineStr"/>
+      <c r="G1763" t="inlineStr"/>
     </row>
     <row r="1764" ht="15.75" customHeight="1" s="19">
       <c r="A1764" s="8" t="n">
@@ -52342,6 +52384,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1764" t="inlineStr"/>
+      <c r="G1764" t="inlineStr"/>
     </row>
     <row r="1765" ht="15.75" customHeight="1" s="19">
       <c r="A1765" s="8" t="n">
@@ -52367,6 +52411,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1765" t="inlineStr">
+        <is>
+          <t>+54 11 7612-3468</t>
+        </is>
+      </c>
+      <c r="G1765" t="inlineStr"/>
     </row>
     <row r="1766" ht="15.75" customHeight="1" s="19">
       <c r="A1766" s="8" t="n">
@@ -52392,6 +52442,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1766" t="inlineStr"/>
+      <c r="G1766" t="inlineStr"/>
     </row>
     <row r="1767" ht="15.75" customHeight="1" s="19">
       <c r="A1767" s="8" t="n">
@@ -52417,6 +52469,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1767" t="inlineStr"/>
+      <c r="G1767" t="inlineStr"/>
     </row>
     <row r="1768" ht="15.75" customHeight="1" s="19">
       <c r="A1768" s="8" t="n">
@@ -52442,6 +52496,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1768" t="inlineStr">
+        <is>
+          <t>+54 46459000</t>
+        </is>
+      </c>
+      <c r="G1768" t="inlineStr">
+        <is>
+          <t>http://www.imasalud.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1769" ht="15.75" customHeight="1" s="19">
       <c r="A1769" s="8" t="n">
@@ -52467,6 +52531,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1769" t="inlineStr"/>
+      <c r="G1769" t="inlineStr"/>
     </row>
     <row r="1770" ht="15.75" customHeight="1" s="19">
       <c r="A1770" s="8" t="n">
@@ -52492,6 +52558,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1770" t="inlineStr"/>
+      <c r="G1770" t="inlineStr"/>
     </row>
     <row r="1771" ht="15.75" customHeight="1" s="19">
       <c r="A1771" s="8" t="n">
@@ -52517,6 +52585,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1771" t="inlineStr"/>
+      <c r="G1771" t="inlineStr"/>
     </row>
     <row r="1772" ht="15.75" customHeight="1" s="19">
       <c r="A1772" s="8" t="n">
@@ -52542,6 +52612,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1772" t="inlineStr"/>
+      <c r="G1772" t="inlineStr"/>
     </row>
     <row r="1773" ht="15.75" customHeight="1" s="19">
       <c r="A1773" s="8" t="n">
@@ -52567,6 +52639,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1773" t="inlineStr"/>
+      <c r="G1773" t="inlineStr"/>
     </row>
     <row r="1774" ht="15.75" customHeight="1" s="19">
       <c r="A1774" s="8" t="n">
@@ -52592,6 +52666,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1774" t="inlineStr"/>
+      <c r="G1774" t="inlineStr"/>
     </row>
     <row r="1775" ht="15.75" customHeight="1" s="19">
       <c r="A1775" s="8" t="n">
@@ -52617,6 +52693,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1775" t="inlineStr"/>
+      <c r="G1775" t="inlineStr"/>
     </row>
     <row r="1776" ht="15.75" customHeight="1" s="19">
       <c r="A1776" s="8" t="n">
@@ -52642,6 +52720,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1776" t="inlineStr"/>
+      <c r="G1776" t="inlineStr"/>
     </row>
     <row r="1777" ht="15.75" customHeight="1" s="19">
       <c r="A1777" s="8" t="n">
@@ -52667,6 +52747,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1777" t="inlineStr">
+        <is>
+          <t>+54 52637145</t>
+        </is>
+      </c>
+      <c r="G1777" t="inlineStr">
+        <is>
+          <t>http://www.centraloeste.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1778" ht="15.75" customHeight="1" s="19">
       <c r="A1778" s="8" t="n">
@@ -52692,6 +52782,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1778" t="inlineStr"/>
+      <c r="G1778" t="inlineStr"/>
     </row>
     <row r="1779" ht="15.75" customHeight="1" s="19">
       <c r="A1779" s="8" t="n">
@@ -52717,6 +52809,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1779" t="inlineStr">
+        <is>
+          <t>+54 9 11 3085-1117</t>
+        </is>
+      </c>
+      <c r="G1779" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maderasbelo</t>
+        </is>
+      </c>
     </row>
     <row r="1780" ht="15.75" customHeight="1" s="19">
       <c r="A1780" s="8" t="n">
@@ -52742,6 +52844,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1780" t="inlineStr">
+        <is>
+          <t>+54 11 3122-8406</t>
+        </is>
+      </c>
+      <c r="G1780" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/elgalpon2124?igsh=MTNsb2Y4bWRnZXAzbQ==</t>
+        </is>
+      </c>
     </row>
     <row r="1781" ht="15.75" customHeight="1" s="19">
       <c r="A1781" s="8" t="n">
@@ -52767,6 +52879,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1781" t="inlineStr"/>
+      <c r="G1781" t="inlineStr"/>
     </row>
     <row r="1782" ht="15.75" customHeight="1" s="19">
       <c r="A1782" s="8" t="n">
@@ -52792,6 +52906,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1782" t="inlineStr"/>
+      <c r="G1782" t="inlineStr"/>
     </row>
     <row r="1783" ht="15.75" customHeight="1" s="19">
       <c r="A1783" s="8" t="n">
@@ -52815,6 +52931,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1783" t="inlineStr"/>
+      <c r="G1783" t="inlineStr"/>
     </row>
     <row r="1784" ht="15.75" customHeight="1" s="19">
       <c r="A1784" s="8" t="n">
@@ -52836,6 +52954,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1784" t="inlineStr"/>
+      <c r="G1784" t="inlineStr">
+        <is>
+          <t>http://www.argentina.gob.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1785" ht="15.75" customHeight="1" s="19">
       <c r="A1785" s="8" t="n">
@@ -52861,6 +52985,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1785" t="inlineStr"/>
+      <c r="G1785" t="inlineStr"/>
     </row>
     <row r="1786" ht="15.75" customHeight="1" s="19">
       <c r="A1786" s="8" t="n">
@@ -52886,6 +53012,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1786" t="inlineStr"/>
+      <c r="G1786" t="inlineStr"/>
     </row>
     <row r="1787" ht="15.75" customHeight="1" s="19">
       <c r="A1787" s="8" t="n">
@@ -52907,6 +53035,12 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F1787" t="inlineStr">
+        <is>
+          <t>+54 11 4238-7163</t>
+        </is>
+      </c>
+      <c r="G1787" t="inlineStr"/>
     </row>
     <row r="1788" ht="15.75" customHeight="1" s="19">
       <c r="A1788" s="8" t="n">
@@ -52932,6 +53066,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1788" t="inlineStr"/>
+      <c r="G1788" t="inlineStr"/>
     </row>
     <row r="1789" ht="15.75" customHeight="1" s="19">
       <c r="A1789" s="8" t="n">
@@ -52957,6 +53093,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1789" t="inlineStr">
+        <is>
+          <t>+54 11 4298-4376</t>
+        </is>
+      </c>
+      <c r="G1789" t="inlineStr">
+        <is>
+          <t>http://www.boedo55.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1790" ht="15.75" customHeight="1" s="19">
       <c r="A1790" s="8" t="n">
@@ -52982,6 +53128,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1790" t="inlineStr"/>
+      <c r="G1790" t="inlineStr"/>
     </row>
     <row r="1791" ht="15.75" customHeight="1" s="19">
       <c r="A1791" s="8" t="n">
@@ -53007,6 +53155,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1791" t="inlineStr"/>
+      <c r="G1791" t="inlineStr"/>
     </row>
     <row r="1792" ht="15.75" customHeight="1" s="19">
       <c r="A1792" s="8" t="n">
@@ -53032,6 +53182,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1792" t="inlineStr"/>
+      <c r="G1792" t="inlineStr"/>
     </row>
     <row r="1793" ht="15.75" customHeight="1" s="19">
       <c r="A1793" s="8" t="n">
@@ -53057,6 +53209,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1793" t="inlineStr">
+        <is>
+          <t>+54 11 4513-2783</t>
+        </is>
+      </c>
+      <c r="G1793" t="inlineStr"/>
     </row>
     <row r="1794" ht="15.75" customHeight="1" s="19">
       <c r="A1794" s="8" t="n">
@@ -53082,6 +53240,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1794" t="inlineStr"/>
+      <c r="G1794" t="inlineStr"/>
     </row>
     <row r="1795" ht="15.75" customHeight="1" s="19">
       <c r="A1795" s="8" t="n">
@@ -53107,6 +53267,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1795" t="inlineStr"/>
+      <c r="G1795" t="inlineStr"/>
     </row>
     <row r="1796" ht="15.75" customHeight="1" s="19">
       <c r="A1796" s="8" t="n">
@@ -53132,6 +53294,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1796" t="inlineStr">
+        <is>
+          <t>+54 9 11 2165-6418</t>
+        </is>
+      </c>
+      <c r="G1796" t="inlineStr">
+        <is>
+          <t>http://www.bacanes.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1797" ht="15.75" customHeight="1" s="19">
       <c r="A1797" s="8" t="n">
@@ -53157,6 +53329,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1797" t="inlineStr"/>
+      <c r="G1797" t="inlineStr"/>
     </row>
     <row r="1798" ht="15.75" customHeight="1" s="19">
       <c r="A1798" s="8" t="n">
@@ -53182,6 +53356,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1798" t="inlineStr"/>
+      <c r="G1798" t="inlineStr"/>
     </row>
     <row r="1799" ht="15.75" customHeight="1" s="19">
       <c r="A1799" s="8" t="n">
@@ -53207,6 +53383,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1799" t="inlineStr"/>
+      <c r="G1799" t="inlineStr"/>
     </row>
     <row r="1800" ht="15.75" customHeight="1" s="19">
       <c r="A1800" s="8" t="n">
@@ -53232,6 +53410,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1800" t="inlineStr"/>
+      <c r="G1800" t="inlineStr"/>
     </row>
     <row r="1801" ht="15.75" customHeight="1" s="19">
       <c r="A1801" s="8" t="n">
@@ -53257,6 +53437,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1801" t="inlineStr">
+        <is>
+          <t>+54 11 2314-4557</t>
+        </is>
+      </c>
+      <c r="G1801" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vivatrainingclub?igsh=bXA5bXJnZGVkbGE5</t>
+        </is>
+      </c>
     </row>
     <row r="1802" ht="15.75" customHeight="1" s="19">
       <c r="A1802" s="8" t="n">
@@ -53282,6 +53472,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1802" t="inlineStr">
+        <is>
+          <t>+54 11 2300-1187</t>
+        </is>
+      </c>
+      <c r="G1802" t="inlineStr"/>
     </row>
     <row r="1803" ht="15.75" customHeight="1" s="19">
       <c r="A1803" s="8" t="n">
@@ -53307,6 +53503,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1803" t="inlineStr"/>
+      <c r="G1803" t="inlineStr"/>
     </row>
     <row r="1804" ht="15.75" customHeight="1" s="19">
       <c r="A1804" s="8" t="n">
@@ -53332,6 +53530,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1804" t="inlineStr"/>
+      <c r="G1804" t="inlineStr"/>
     </row>
     <row r="1805" ht="15.75" customHeight="1" s="19">
       <c r="A1805" s="8" t="n">
@@ -53357,6 +53557,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1805" t="inlineStr"/>
+      <c r="G1805" t="inlineStr"/>
     </row>
     <row r="1806" ht="15.75" customHeight="1" s="19">
       <c r="A1806" s="8" t="n">
@@ -53382,6 +53584,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1806" t="inlineStr"/>
+      <c r="G1806" t="inlineStr"/>
     </row>
     <row r="1807" ht="15.75" customHeight="1" s="19">
       <c r="A1807" s="8" t="n">
@@ -53407,6 +53611,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1807" t="inlineStr">
+        <is>
+          <t>+54 11 4743-2166</t>
+        </is>
+      </c>
+      <c r="G1807" t="inlineStr"/>
     </row>
     <row r="1808" ht="15.75" customHeight="1" s="19">
       <c r="A1808" s="8" t="n">
@@ -53432,6 +53642,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1808" t="inlineStr"/>
+      <c r="G1808" t="inlineStr"/>
     </row>
     <row r="1809" ht="15.75" customHeight="1" s="19">
       <c r="A1809" s="8" t="n">
@@ -53457,6 +53669,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1809" t="inlineStr">
+        <is>
+          <t>+54 11 4664-4187</t>
+        </is>
+      </c>
+      <c r="G1809" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/elhogardetumascotapetshop</t>
+        </is>
+      </c>
     </row>
     <row r="1810" ht="15.75" customHeight="1" s="19">
       <c r="A1810" s="8" t="n">
@@ -53482,6 +53704,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1810" t="inlineStr">
+        <is>
+          <t>+54 44516310</t>
+        </is>
+      </c>
+      <c r="G1810" t="inlineStr"/>
     </row>
     <row r="1811" ht="15.75" customHeight="1" s="19">
       <c r="A1811" s="8" t="n">
@@ -53507,6 +53735,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1811" t="inlineStr"/>
+      <c r="G1811" t="inlineStr"/>
     </row>
     <row r="1812" ht="15.75" customHeight="1" s="19">
       <c r="A1812" s="8" t="n">
@@ -53532,6 +53762,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1812" t="inlineStr">
+        <is>
+          <t>+54 11 4664-9701</t>
+        </is>
+      </c>
+      <c r="G1812" t="inlineStr">
+        <is>
+          <t>http://www.chatelet.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1813" ht="15.75" customHeight="1" s="19">
       <c r="A1813" s="8" t="n">
@@ -53557,6 +53797,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1813" t="inlineStr">
+        <is>
+          <t>+54 11 6047-0467</t>
+        </is>
+      </c>
+      <c r="G1813" t="inlineStr">
+        <is>
+          <t>http://bellezatecnia.com/</t>
+        </is>
+      </c>
     </row>
     <row r="1814" ht="15.75" customHeight="1" s="19">
       <c r="A1814" s="8" t="n">
@@ -53582,6 +53832,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1814" t="inlineStr">
+        <is>
+          <t>+54 3404 57-5331</t>
+        </is>
+      </c>
+      <c r="G1814" t="inlineStr">
+        <is>
+          <t>https://gaviglio.com/</t>
+        </is>
+      </c>
     </row>
     <row r="1815" ht="15.75" customHeight="1" s="19">
       <c r="A1815" s="8" t="n">
@@ -53607,6 +53867,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1815" t="inlineStr">
+        <is>
+          <t>+54 11 4862-9517</t>
+        </is>
+      </c>
+      <c r="G1815" t="inlineStr"/>
     </row>
     <row r="1816" ht="15.75" customHeight="1" s="19">
       <c r="A1816" s="8" t="n">
@@ -53632,6 +53898,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1816" t="inlineStr"/>
+      <c r="G1816" t="inlineStr"/>
     </row>
     <row r="1817" ht="15.75" customHeight="1" s="19">
       <c r="A1817" s="8" t="n">
@@ -53657,6 +53925,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1817" t="inlineStr"/>
+      <c r="G1817" t="inlineStr"/>
     </row>
     <row r="1818" ht="15.75" customHeight="1" s="19">
       <c r="A1818" s="8" t="n">
@@ -53682,6 +53952,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1818" t="inlineStr">
+        <is>
+          <t>+54 11 4864-1223</t>
+        </is>
+      </c>
+      <c r="G1818" t="inlineStr"/>
     </row>
     <row r="1819" ht="15.75" customHeight="1" s="19">
       <c r="A1819" s="8" t="n">
@@ -53707,6 +53983,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1819" t="inlineStr"/>
+      <c r="G1819" t="inlineStr"/>
     </row>
     <row r="1820" ht="15.75" customHeight="1" s="19">
       <c r="A1820" s="8" t="n">
@@ -53732,6 +54010,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1820" t="inlineStr"/>
+      <c r="G1820" t="inlineStr"/>
     </row>
     <row r="1821" ht="15.75" customHeight="1" s="19">
       <c r="A1821" s="8" t="n">
@@ -53757,6 +54037,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1821" t="inlineStr"/>
+      <c r="G1821" t="inlineStr"/>
     </row>
     <row r="1822" ht="15.75" customHeight="1" s="19">
       <c r="A1822" s="8" t="n">
@@ -53782,6 +54064,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1822" t="inlineStr"/>
+      <c r="G1822" t="inlineStr"/>
     </row>
     <row r="1823" ht="15.75" customHeight="1" s="19">
       <c r="A1823" s="8" t="n">
@@ -53807,6 +54091,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1823" t="inlineStr"/>
+      <c r="G1823" t="inlineStr"/>
     </row>
     <row r="1824" ht="15.75" customHeight="1" s="19">
       <c r="A1824" s="8" t="n">
@@ -53832,6 +54118,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F1824" t="inlineStr"/>
+      <c r="G1824" t="inlineStr"/>
     </row>
     <row r="1825" ht="15.75" customHeight="1" s="19">
       <c r="A1825" s="8" t="n">
@@ -53857,6 +54145,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1825" t="inlineStr"/>
+      <c r="G1825" t="inlineStr"/>
     </row>
     <row r="1826" ht="15.75" customHeight="1" s="19">
       <c r="A1826" s="8" t="n">
@@ -53882,6 +54172,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1826" t="inlineStr"/>
+      <c r="G1826" t="inlineStr"/>
     </row>
     <row r="1827" ht="15.75" customHeight="1" s="19">
       <c r="A1827" s="8" t="n">
@@ -53907,6 +54199,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1827" t="inlineStr"/>
+      <c r="G1827" t="inlineStr"/>
     </row>
     <row r="1828" ht="15.75" customHeight="1" s="19">
       <c r="A1828" s="8" t="n">
@@ -53932,6 +54226,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1828" t="inlineStr"/>
+      <c r="G1828" t="inlineStr"/>
     </row>
     <row r="1829" ht="15.75" customHeight="1" s="19">
       <c r="A1829" s="8" t="n">
@@ -53957,6 +54253,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1829" t="inlineStr"/>
+      <c r="G1829" t="inlineStr"/>
     </row>
     <row r="1830" ht="15.75" customHeight="1" s="19">
       <c r="A1830" s="8" t="n">
@@ -53982,6 +54280,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1830" t="inlineStr"/>
+      <c r="G1830" t="inlineStr"/>
     </row>
     <row r="1831" ht="15.75" customHeight="1" s="19">
       <c r="A1831" s="8" t="n">
@@ -54007,6 +54307,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1831" t="inlineStr"/>
+      <c r="G1831" t="inlineStr"/>
     </row>
     <row r="1832" ht="15.75" customHeight="1" s="19">
       <c r="A1832" s="8" t="n">
@@ -54032,6 +54334,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1832" t="inlineStr"/>
+      <c r="G1832" t="inlineStr"/>
     </row>
     <row r="1833" ht="15.75" customHeight="1" s="19">
       <c r="A1833" s="8" t="n">
@@ -54057,6 +54361,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1833" t="inlineStr">
+        <is>
+          <t>+54 11 3008-4749</t>
+        </is>
+      </c>
+      <c r="G1833" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/familia.aufieri?fbclid=PAZXh0bgNhZW0CMTEAAaYYKdrrUExlKHTyeMVCoFfvyRE1G3EsSKzwbhmo9mlroB4LOWZBR8HAbj4_aem_SZL8Fc5TuAabmHZ5tBPJWQ</t>
+        </is>
+      </c>
     </row>
     <row r="1834" ht="15.75" customHeight="1" s="19">
       <c r="A1834" s="8" t="n">
@@ -54082,6 +54396,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1834" t="inlineStr"/>
+      <c r="G1834" t="inlineStr"/>
     </row>
     <row r="1835" ht="15.75" customHeight="1" s="19">
       <c r="A1835" s="8" t="n">
@@ -54107,6 +54423,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1835" t="inlineStr"/>
+      <c r="G1835" t="inlineStr">
+        <is>
+          <t>http://chui.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1836" ht="15.75" customHeight="1" s="19">
       <c r="A1836" s="8" t="n">
@@ -54132,6 +54454,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1836" t="inlineStr"/>
+      <c r="G1836" t="inlineStr"/>
     </row>
     <row r="1837" ht="15.75" customHeight="1" s="19">
       <c r="A1837" s="8" t="n">
@@ -54157,6 +54481,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1837" t="inlineStr"/>
+      <c r="G1837" t="inlineStr"/>
     </row>
     <row r="1838" ht="15.75" customHeight="1" s="19">
       <c r="A1838" s="8" t="n">
@@ -54182,6 +54508,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1838" t="inlineStr"/>
+      <c r="G1838" t="inlineStr"/>
     </row>
     <row r="1839" ht="15.75" customHeight="1" s="19">
       <c r="A1839" s="8" t="n">
@@ -54207,6 +54535,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1839" t="inlineStr">
+        <is>
+          <t>+54 11 4504-5197</t>
+        </is>
+      </c>
+      <c r="G1839" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/huesosyburbujas</t>
+        </is>
+      </c>
     </row>
     <row r="1840" ht="15.75" customHeight="1" s="19">
       <c r="A1840" s="8" t="n">
@@ -54232,6 +54570,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1840" t="inlineStr"/>
+      <c r="G1840" t="inlineStr"/>
     </row>
     <row r="1841" ht="15.75" customHeight="1" s="19">
       <c r="A1841" s="8" t="n">
@@ -54257,6 +54597,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1841" t="inlineStr"/>
+      <c r="G1841" t="inlineStr"/>
     </row>
     <row r="1842" ht="15.75" customHeight="1" s="19">
       <c r="A1842" s="8" t="n">
@@ -54282,6 +54624,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1842" t="inlineStr">
+        <is>
+          <t>+54 11 5310-1780</t>
+        </is>
+      </c>
+      <c r="G1842" t="inlineStr">
+        <is>
+          <t>https://www.estudiosalaromero.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1843" ht="15.75" customHeight="1" s="19">
       <c r="A1843" s="8" t="n">
@@ -54307,6 +54659,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1843" t="inlineStr"/>
+      <c r="G1843" t="inlineStr"/>
     </row>
     <row r="1844" ht="15.75" customHeight="1" s="19">
       <c r="A1844" s="8" t="n">
@@ -54332,6 +54686,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1844" t="inlineStr"/>
+      <c r="G1844" t="inlineStr"/>
     </row>
     <row r="1845" ht="15.75" customHeight="1" s="19">
       <c r="A1845" s="8" t="n">
@@ -54357,6 +54713,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1845" t="inlineStr"/>
+      <c r="G1845" t="inlineStr"/>
     </row>
     <row r="1846" ht="15.75" customHeight="1" s="19">
       <c r="A1846" s="8" t="n">
@@ -54382,6 +54740,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1846" t="inlineStr"/>
+      <c r="G1846" t="inlineStr"/>
     </row>
     <row r="1847" ht="15.75" customHeight="1" s="19">
       <c r="A1847" s="8" t="n">
@@ -54407,6 +54767,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1847" t="inlineStr"/>
+      <c r="G1847" t="inlineStr"/>
     </row>
     <row r="1848" ht="15.75" customHeight="1" s="19">
       <c r="A1848" s="8" t="n">
@@ -54432,6 +54794,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1848" t="inlineStr"/>
+      <c r="G1848" t="inlineStr"/>
     </row>
     <row r="1849" ht="15.75" customHeight="1" s="19">
       <c r="A1849" s="8" t="n">
@@ -54457,6 +54821,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1849" t="inlineStr"/>
+      <c r="G1849" t="inlineStr"/>
     </row>
     <row r="1850" ht="15.75" customHeight="1" s="19">
       <c r="A1850" s="8" t="n">
@@ -54482,6 +54848,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1850" t="inlineStr"/>
+      <c r="G1850" t="inlineStr"/>
     </row>
     <row r="1851" ht="15.75" customHeight="1" s="19">
       <c r="A1851" s="8" t="n">
@@ -54507,6 +54875,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1851" t="inlineStr"/>
+      <c r="G1851" t="inlineStr"/>
     </row>
     <row r="1852" ht="15.75" customHeight="1" s="19">
       <c r="A1852" s="8" t="n">
@@ -54532,6 +54902,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1852" t="inlineStr"/>
+      <c r="G1852" t="inlineStr"/>
     </row>
     <row r="1853" ht="15.75" customHeight="1" s="19">
       <c r="A1853" s="8" t="n">

--- a/PUNTOS_DE_VENTA_completado.xlsx
+++ b/PUNTOS_DE_VENTA_completado.xlsx
@@ -54929,6 +54929,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1853" t="inlineStr"/>
+      <c r="G1853" t="inlineStr"/>
     </row>
     <row r="1854" ht="15.75" customHeight="1" s="19">
       <c r="A1854" s="8" t="n">
@@ -54954,6 +54956,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1854" t="inlineStr"/>
+      <c r="G1854" t="inlineStr"/>
     </row>
     <row r="1855" ht="15.75" customHeight="1" s="19">
       <c r="A1855" s="8" t="n">
@@ -54979,6 +54983,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1855" t="inlineStr"/>
+      <c r="G1855" t="inlineStr"/>
     </row>
     <row r="1856" ht="15.75" customHeight="1" s="19">
       <c r="A1856" s="8" t="n">
@@ -55004,6 +55010,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1856" t="inlineStr"/>
+      <c r="G1856" t="inlineStr"/>
     </row>
     <row r="1857" ht="15.75" customHeight="1" s="19">
       <c r="A1857" s="8" t="n">
@@ -55029,6 +55037,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1857" t="inlineStr"/>
+      <c r="G1857" t="inlineStr"/>
     </row>
     <row r="1858" ht="15.75" customHeight="1" s="19">
       <c r="A1858" s="8" t="n">
@@ -55054,6 +55064,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1858" t="inlineStr"/>
+      <c r="G1858" t="inlineStr"/>
     </row>
     <row r="1859" ht="15.75" customHeight="1" s="19">
       <c r="A1859" s="8" t="n">
@@ -55075,6 +55087,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1859" t="inlineStr"/>
+      <c r="G1859" t="inlineStr">
+        <is>
+          <t>http://www.argentina.gob.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1860" ht="15.75" customHeight="1" s="19">
       <c r="A1860" s="8" t="n">
@@ -55100,6 +55118,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1860" t="inlineStr"/>
+      <c r="G1860" t="inlineStr"/>
     </row>
     <row r="1861" ht="15.75" customHeight="1" s="19">
       <c r="A1861" s="8" t="n">
@@ -55125,6 +55145,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1861" t="inlineStr"/>
+      <c r="G1861" t="inlineStr"/>
     </row>
     <row r="1862" ht="15.75" customHeight="1" s="19">
       <c r="A1862" s="8" t="n">
@@ -55150,6 +55172,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1862" t="inlineStr"/>
+      <c r="G1862" t="inlineStr"/>
     </row>
     <row r="1863" ht="15.75" customHeight="1" s="19">
       <c r="A1863" s="8" t="n">
@@ -55175,6 +55199,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1863" t="inlineStr"/>
+      <c r="G1863" t="inlineStr"/>
     </row>
     <row r="1864" ht="15.75" customHeight="1" s="19">
       <c r="A1864" s="8" t="n">
@@ -55200,6 +55226,16 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F1864" t="inlineStr">
+        <is>
+          <t>+54 11 4822-7733</t>
+        </is>
+      </c>
+      <c r="G1864" t="inlineStr">
+        <is>
+          <t>http://www.fehgra.org.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1865" ht="15.75" customHeight="1" s="19">
       <c r="A1865" s="8" t="n">
@@ -55225,6 +55261,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1865" t="inlineStr"/>
+      <c r="G1865" t="inlineStr"/>
     </row>
     <row r="1866" ht="15.75" customHeight="1" s="19">
       <c r="A1866" s="8" t="n">
@@ -55250,6 +55288,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1866" t="inlineStr"/>
+      <c r="G1866" t="inlineStr"/>
     </row>
     <row r="1867" ht="15.75" customHeight="1" s="19">
       <c r="A1867" s="8" t="n">
@@ -55275,6 +55315,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1867" t="inlineStr"/>
+      <c r="G1867" t="inlineStr"/>
     </row>
     <row r="1868" ht="15.75" customHeight="1" s="19">
       <c r="A1868" s="8" t="n">
@@ -55300,6 +55342,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1868" t="inlineStr">
+        <is>
+          <t>+54 11 2450-2584</t>
+        </is>
+      </c>
+      <c r="G1868" t="inlineStr">
+        <is>
+          <t>http://www.tiendasavarin.com/</t>
+        </is>
+      </c>
     </row>
     <row r="1869" ht="15.75" customHeight="1" s="19">
       <c r="A1869" s="8" t="n">
@@ -55325,6 +55377,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1869" t="inlineStr"/>
+      <c r="G1869" t="inlineStr"/>
     </row>
     <row r="1870" ht="15.75" customHeight="1" s="19">
       <c r="A1870" s="8" t="n">
@@ -55346,6 +55400,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1870" t="inlineStr"/>
+      <c r="G1870" t="inlineStr">
+        <is>
+          <t>http://www.argentina.gob.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1871" ht="15.75" customHeight="1" s="19">
       <c r="A1871" s="8" t="n">
@@ -55367,6 +55427,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1871" t="inlineStr"/>
+      <c r="G1871" t="inlineStr">
+        <is>
+          <t>http://www.argentina.gob.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1872" ht="15.75" customHeight="1" s="19">
       <c r="A1872" s="8" t="n">
@@ -55392,6 +55458,16 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F1872" t="inlineStr">
+        <is>
+          <t>+54 11 6708-1332</t>
+        </is>
+      </c>
+      <c r="G1872" t="inlineStr">
+        <is>
+          <t>http://www.universomascota.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1873" ht="15.75" customHeight="1" s="19">
       <c r="A1873" s="8" t="n">
@@ -55417,6 +55493,16 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F1873" t="inlineStr">
+        <is>
+          <t>+54 11 3149-1810</t>
+        </is>
+      </c>
+      <c r="G1873" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Pescader%C3%ADa-Alta-Mar-2023023951250509/</t>
+        </is>
+      </c>
     </row>
     <row r="1874" ht="15.75" customHeight="1" s="19">
       <c r="A1874" s="8" t="n">
@@ -55442,6 +55528,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1874" t="inlineStr"/>
+      <c r="G1874" t="inlineStr"/>
     </row>
     <row r="1875" ht="15.75" customHeight="1" s="19">
       <c r="A1875" s="8" t="n">
@@ -55467,6 +55555,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1875" t="inlineStr"/>
+      <c r="G1875" t="inlineStr"/>
     </row>
     <row r="1876" ht="15.75" customHeight="1" s="19">
       <c r="A1876" s="8" t="n">
@@ -55492,6 +55582,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1876" t="inlineStr"/>
+      <c r="G1876" t="inlineStr"/>
     </row>
     <row r="1877" ht="15.75" customHeight="1" s="19">
       <c r="A1877" s="8" t="n">
@@ -55517,6 +55609,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1877" t="inlineStr">
+        <is>
+          <t>+54 11 4554-7542</t>
+        </is>
+      </c>
+      <c r="G1877" t="inlineStr">
+        <is>
+          <t>http://comiccenterstore.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1878" ht="15.75" customHeight="1" s="19">
       <c r="A1878" s="8" t="n">
@@ -55542,6 +55644,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1878" t="inlineStr"/>
+      <c r="G1878" t="inlineStr"/>
     </row>
     <row r="1879" ht="15.75" customHeight="1" s="19">
       <c r="A1879" s="8" t="n">
@@ -55567,6 +55671,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1879" t="inlineStr"/>
+      <c r="G1879" t="inlineStr"/>
     </row>
     <row r="1880" ht="15.75" customHeight="1" s="19">
       <c r="A1880" s="8" t="n">
@@ -55592,6 +55698,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1880" t="inlineStr">
+        <is>
+          <t>+54 11 4902-9975</t>
+        </is>
+      </c>
+      <c r="G1880" t="inlineStr"/>
     </row>
     <row r="1881" ht="15.75" customHeight="1" s="19">
       <c r="A1881" s="8" t="n">
@@ -55617,6 +55729,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1881" t="inlineStr"/>
+      <c r="G1881" t="inlineStr"/>
     </row>
     <row r="1882" ht="15.75" customHeight="1" s="19">
       <c r="A1882" s="8" t="n">
@@ -55642,6 +55756,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1882" t="inlineStr"/>
+      <c r="G1882" t="inlineStr"/>
     </row>
     <row r="1883" ht="15.75" customHeight="1" s="19">
       <c r="A1883" s="8" t="n">
@@ -55667,6 +55783,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1883" t="inlineStr">
+        <is>
+          <t>+54 11 4046-1548</t>
+        </is>
+      </c>
+      <c r="G1883" t="inlineStr">
+        <is>
+          <t>https://animalandia.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1884" ht="15.75" customHeight="1" s="19">
       <c r="A1884" s="8" t="n">
@@ -55692,6 +55818,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1884" t="inlineStr"/>
+      <c r="G1884" t="inlineStr"/>
     </row>
     <row r="1885" ht="15.75" customHeight="1" s="19">
       <c r="A1885" s="8" t="n">
@@ -55717,6 +55845,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1885" t="inlineStr"/>
+      <c r="G1885" t="inlineStr"/>
     </row>
     <row r="1886" ht="15.75" customHeight="1" s="19">
       <c r="A1886" s="8" t="n">
@@ -55742,6 +55872,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1886" t="inlineStr"/>
+      <c r="G1886" t="inlineStr"/>
     </row>
     <row r="1887" ht="15.75" customHeight="1" s="19">
       <c r="A1887" s="8" t="n">
@@ -55767,6 +55899,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1887" t="inlineStr"/>
+      <c r="G1887" t="inlineStr"/>
     </row>
     <row r="1888" ht="15.75" customHeight="1" s="19">
       <c r="A1888" s="8" t="n">
@@ -55792,6 +55926,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1888" t="inlineStr"/>
+      <c r="G1888" t="inlineStr"/>
     </row>
     <row r="1889" ht="15.75" customHeight="1" s="19">
       <c r="A1889" s="8" t="n">
@@ -55817,6 +55953,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1889" t="inlineStr"/>
+      <c r="G1889" t="inlineStr"/>
     </row>
     <row r="1890" ht="15.75" customHeight="1" s="19">
       <c r="A1890" s="8" t="n">
@@ -55842,6 +55980,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1890" t="inlineStr"/>
+      <c r="G1890" t="inlineStr"/>
     </row>
     <row r="1891" ht="15.75" customHeight="1" s="19">
       <c r="A1891" s="8" t="n">
@@ -55867,6 +56007,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1891" t="inlineStr"/>
+      <c r="G1891" t="inlineStr"/>
     </row>
     <row r="1892" ht="15.75" customHeight="1" s="19">
       <c r="A1892" s="8" t="n">
@@ -55892,6 +56034,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1892" t="inlineStr"/>
+      <c r="G1892" t="inlineStr"/>
     </row>
     <row r="1893" ht="15.75" customHeight="1" s="19">
       <c r="A1893" s="8" t="n">
@@ -55917,6 +56061,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1893" t="inlineStr"/>
+      <c r="G1893" t="inlineStr"/>
     </row>
     <row r="1894" ht="15.75" customHeight="1" s="19">
       <c r="A1894" s="8" t="n">
@@ -55942,6 +56088,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1894" t="inlineStr"/>
+      <c r="G1894" t="inlineStr"/>
     </row>
     <row r="1895" ht="15.75" customHeight="1" s="19">
       <c r="A1895" s="8" t="n">
@@ -55967,6 +56115,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1895" t="inlineStr"/>
+      <c r="G1895" t="inlineStr"/>
     </row>
     <row r="1896" ht="15.75" customHeight="1" s="19">
       <c r="A1896" s="8" t="n">
@@ -55992,6 +56142,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1896" t="inlineStr"/>
+      <c r="G1896" t="inlineStr"/>
     </row>
     <row r="1897" ht="15.75" customHeight="1" s="19">
       <c r="A1897" s="8" t="n">
@@ -56017,6 +56169,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1897" t="inlineStr">
+        <is>
+          <t>+54 11 4637-7330</t>
+        </is>
+      </c>
+      <c r="G1897" t="inlineStr"/>
     </row>
     <row r="1898" ht="15.75" customHeight="1" s="19">
       <c r="A1898" s="8" t="n">
@@ -56042,6 +56200,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1898" t="inlineStr"/>
+      <c r="G1898" t="inlineStr"/>
     </row>
     <row r="1899" ht="15.75" customHeight="1" s="19">
       <c r="A1899" s="8" t="n">
@@ -56067,6 +56227,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1899" t="inlineStr"/>
+      <c r="G1899" t="inlineStr"/>
     </row>
     <row r="1900" ht="15.75" customHeight="1" s="19">
       <c r="A1900" s="8" t="n">
@@ -56092,6 +56254,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1900" t="inlineStr"/>
+      <c r="G1900" t="inlineStr"/>
     </row>
     <row r="1901" ht="15.75" customHeight="1" s="19">
       <c r="A1901" s="8" t="n">
@@ -56117,6 +56281,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1901" t="inlineStr"/>
+      <c r="G1901" t="inlineStr"/>
     </row>
     <row r="1902" ht="15.75" customHeight="1" s="19">
       <c r="A1902" s="8" t="n">
@@ -56142,6 +56308,12 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F1902" t="inlineStr">
+        <is>
+          <t>+54 11 4734-9587</t>
+        </is>
+      </c>
+      <c r="G1902" t="inlineStr"/>
     </row>
     <row r="1903" ht="15.75" customHeight="1" s="19">
       <c r="A1903" s="8" t="n">

--- a/PUNTOS_DE_VENTA_completado.xlsx
+++ b/PUNTOS_DE_VENTA_completado.xlsx
@@ -56339,6 +56339,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F1903" t="inlineStr">
+        <is>
+          <t>+54 810-999-3279</t>
+        </is>
+      </c>
+      <c r="G1903" t="inlineStr">
+        <is>
+          <t>https://www.easy.com.ar/?utm_source=google&amp;utm_medium=organic&amp;utm_campaign=google-my-business&amp;utm_content=branding_easy-constituyentes_sitio-web&amp;utm_term=perfil</t>
+        </is>
+      </c>
     </row>
     <row r="1904" ht="15.75" customHeight="1" s="19">
       <c r="A1904" s="8" t="n">
@@ -56364,6 +56374,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1904" t="inlineStr">
+        <is>
+          <t>+54 11 4483-3042</t>
+        </is>
+      </c>
+      <c r="G1904" t="inlineStr">
+        <is>
+          <t>https://ayfer.empretienda.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1905" ht="15.75" customHeight="1" s="19">
       <c r="A1905" s="8" t="n">
@@ -56389,6 +56409,8 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F1905" t="inlineStr"/>
+      <c r="G1905" t="inlineStr"/>
     </row>
     <row r="1906" ht="15.75" customHeight="1" s="19">
       <c r="A1906" s="8" t="n">
@@ -56414,6 +56436,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1906" t="inlineStr">
+        <is>
+          <t>+54 11 2835-6839</t>
+        </is>
+      </c>
+      <c r="G1906" t="inlineStr">
+        <is>
+          <t>https://hipermascota.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1907" ht="15.75" customHeight="1" s="19">
       <c r="A1907" s="8" t="n">
@@ -56439,6 +56471,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1907" t="inlineStr">
+        <is>
+          <t>+54 11 4741-9118</t>
+        </is>
+      </c>
+      <c r="G1907" t="inlineStr"/>
     </row>
     <row r="1908" ht="15.75" customHeight="1" s="19">
       <c r="A1908" s="8" t="n">
@@ -56464,6 +56502,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1908" t="inlineStr"/>
+      <c r="G1908" t="inlineStr"/>
     </row>
     <row r="1909" ht="15.75" customHeight="1" s="19">
       <c r="A1909" s="8" t="n">
@@ -56489,6 +56529,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1909" t="inlineStr"/>
+      <c r="G1909" t="inlineStr"/>
     </row>
     <row r="1910" ht="15.75" customHeight="1" s="19">
       <c r="A1910" s="8" t="n">
@@ -56514,6 +56556,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1910" t="inlineStr"/>
+      <c r="G1910" t="inlineStr"/>
     </row>
     <row r="1911" ht="15.75" customHeight="1" s="19">
       <c r="A1911" s="8" t="n">
@@ -56539,6 +56583,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1911" t="inlineStr"/>
+      <c r="G1911" t="inlineStr"/>
     </row>
     <row r="1912" ht="15.75" customHeight="1" s="19">
       <c r="A1912" s="8" t="n">
@@ -56564,6 +56610,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1912" t="inlineStr"/>
+      <c r="G1912" t="inlineStr"/>
     </row>
     <row r="1913" ht="15.75" customHeight="1" s="19">
       <c r="A1913" s="8" t="n">
@@ -56589,6 +56637,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1913" t="inlineStr"/>
+      <c r="G1913" t="inlineStr"/>
     </row>
     <row r="1914" ht="15.75" customHeight="1" s="19">
       <c r="A1914" s="8" t="n">
@@ -56614,6 +56664,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1914" t="inlineStr"/>
+      <c r="G1914" t="inlineStr"/>
     </row>
     <row r="1915" ht="15.75" customHeight="1" s="19">
       <c r="A1915" s="8" t="n">
@@ -56639,6 +56691,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1915" t="inlineStr">
+        <is>
+          <t>+54 220 483-3759</t>
+        </is>
+      </c>
+      <c r="G1915" t="inlineStr"/>
     </row>
     <row r="1916" ht="15.75" customHeight="1" s="19">
       <c r="A1916" s="8" t="n">
@@ -56664,6 +56722,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1916" t="inlineStr">
+        <is>
+          <t>+54 11 4464-5600</t>
+        </is>
+      </c>
+      <c r="G1916" t="inlineStr"/>
     </row>
     <row r="1917" ht="15.75" customHeight="1" s="19">
       <c r="A1917" s="8" t="n">
@@ -56689,6 +56753,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1917" t="inlineStr">
+        <is>
+          <t>+54 11 2496-2300</t>
+        </is>
+      </c>
+      <c r="G1917" t="inlineStr"/>
     </row>
     <row r="1918" ht="15.75" customHeight="1" s="19">
       <c r="A1918" s="8" t="n">
@@ -56714,6 +56784,16 @@
           <t>Pet Supermarket</t>
         </is>
       </c>
+      <c r="F1918" t="inlineStr">
+        <is>
+          <t>+54 11 3990-9770</t>
+        </is>
+      </c>
+      <c r="G1918" t="inlineStr">
+        <is>
+          <t>http://www.kamik.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1919" ht="15.75" customHeight="1" s="19">
       <c r="A1919" s="8" t="n">
@@ -56739,6 +56819,16 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1919" t="inlineStr">
+        <is>
+          <t>+54 47446176</t>
+        </is>
+      </c>
+      <c r="G1919" t="inlineStr">
+        <is>
+          <t>https://consultoriosrubinich.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1920" ht="15.75" customHeight="1" s="19">
       <c r="A1920" s="8" t="n">
@@ -56764,6 +56854,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F1920" t="inlineStr"/>
+      <c r="G1920" t="inlineStr"/>
     </row>
     <row r="1921" ht="15.75" customHeight="1" s="19">
       <c r="A1921" s="8" t="n">
@@ -56789,6 +56881,12 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F1921" t="inlineStr">
+        <is>
+          <t>+54 9 11 3077-4500</t>
+        </is>
+      </c>
+      <c r="G1921" t="inlineStr"/>
     </row>
     <row r="1922" ht="15.75" customHeight="1" s="19">
       <c r="A1922" s="8" t="n">
@@ -56814,6 +56912,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1922" t="inlineStr"/>
+      <c r="G1922" t="inlineStr"/>
     </row>
     <row r="1923" ht="15.75" customHeight="1" s="19">
       <c r="A1923" s="8" t="n">
@@ -56839,6 +56939,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1923" t="inlineStr"/>
+      <c r="G1923" t="inlineStr"/>
     </row>
     <row r="1924" ht="15.75" customHeight="1" s="19">
       <c r="A1924" s="8" t="n">
@@ -56864,6 +56966,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1924" t="inlineStr"/>
+      <c r="G1924" t="inlineStr"/>
     </row>
     <row r="1925" ht="15.75" customHeight="1" s="19">
       <c r="A1925" s="8" t="n">
@@ -56889,6 +56993,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1925" t="inlineStr">
+        <is>
+          <t>+54 11 6787-4004</t>
+        </is>
+      </c>
+      <c r="G1925" t="inlineStr">
+        <is>
+          <t>https://marielaclothes.mitiendanube.com/</t>
+        </is>
+      </c>
     </row>
     <row r="1926" ht="15.75" customHeight="1" s="19">
       <c r="A1926" s="8" t="n">
@@ -56914,6 +57028,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1926" t="inlineStr"/>
+      <c r="G1926" t="inlineStr"/>
     </row>
     <row r="1927" ht="15.75" customHeight="1" s="19">
       <c r="A1927" s="8" t="n">
@@ -56939,6 +57055,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1927" t="inlineStr">
+        <is>
+          <t>+54 11 4247-9925</t>
+        </is>
+      </c>
+      <c r="G1927" t="inlineStr"/>
     </row>
     <row r="1928" ht="15.75" customHeight="1" s="19">
       <c r="A1928" s="8" t="n">
@@ -56964,6 +57086,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1928" t="inlineStr">
+        <is>
+          <t>+54 11 4286-9591</t>
+        </is>
+      </c>
+      <c r="G1928" t="inlineStr"/>
     </row>
     <row r="1929" ht="15.75" customHeight="1" s="19">
       <c r="A1929" s="8" t="n">
@@ -56989,6 +57117,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1929" t="inlineStr">
+        <is>
+          <t>+54 11 4225-7535</t>
+        </is>
+      </c>
+      <c r="G1929" t="inlineStr">
+        <is>
+          <t>https://compakjetrodados.com/</t>
+        </is>
+      </c>
     </row>
     <row r="1930" ht="15.75" customHeight="1" s="19">
       <c r="A1930" s="8" t="n">
@@ -57014,6 +57152,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1930" t="inlineStr">
+        <is>
+          <t>+54 11 6795-4942</t>
+        </is>
+      </c>
+      <c r="G1930" t="inlineStr"/>
     </row>
     <row r="1931" ht="15.75" customHeight="1" s="19">
       <c r="A1931" s="8" t="n">
@@ -57039,6 +57183,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1931" t="inlineStr"/>
+      <c r="G1931" t="inlineStr"/>
     </row>
     <row r="1932" ht="15.75" customHeight="1" s="19">
       <c r="A1932" s="8" t="n">
@@ -57064,6 +57210,16 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F1932" t="inlineStr">
+        <is>
+          <t>+54 11 4216-5800</t>
+        </is>
+      </c>
+      <c r="G1932" t="inlineStr">
+        <is>
+          <t>http://www.ossum.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1933" ht="15.75" customHeight="1" s="19">
       <c r="A1933" s="8" t="n">
@@ -57089,6 +57245,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1933" t="inlineStr"/>
+      <c r="G1933" t="inlineStr"/>
     </row>
     <row r="1934" ht="15.75" customHeight="1" s="19">
       <c r="A1934" s="8" t="n">
@@ -57114,6 +57272,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1934" t="inlineStr"/>
+      <c r="G1934" t="inlineStr"/>
     </row>
     <row r="1935" ht="15.75" customHeight="1" s="19">
       <c r="A1935" s="8" t="n">
@@ -57139,6 +57299,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1935" t="inlineStr"/>
+      <c r="G1935" t="inlineStr"/>
     </row>
     <row r="1936" ht="15.75" customHeight="1" s="19">
       <c r="A1936" s="8" t="n">
@@ -57164,6 +57326,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1936" t="inlineStr"/>
+      <c r="G1936" t="inlineStr"/>
     </row>
     <row r="1937" ht="15.75" customHeight="1" s="19">
       <c r="A1937" s="8" t="n">
@@ -57189,6 +57353,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1937" t="inlineStr"/>
+      <c r="G1937" t="inlineStr"/>
     </row>
     <row r="1938" ht="15.75" customHeight="1" s="19">
       <c r="A1938" s="8" t="n">
@@ -57214,6 +57380,16 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1938" t="inlineStr">
+        <is>
+          <t>+54 11 4258-2042</t>
+        </is>
+      </c>
+      <c r="G1938" t="inlineStr">
+        <is>
+          <t>https://www.super-losangeles.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1939" ht="15.75" customHeight="1" s="19">
       <c r="A1939" s="8" t="n">
@@ -57239,6 +57415,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1939" t="inlineStr"/>
+      <c r="G1939" t="inlineStr"/>
     </row>
     <row r="1940" ht="15.75" customHeight="1" s="19">
       <c r="A1940" s="8" t="n">
@@ -57264,6 +57442,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1940" t="inlineStr"/>
+      <c r="G1940" t="inlineStr"/>
     </row>
     <row r="1941" ht="15.75" customHeight="1" s="19">
       <c r="A1941" s="8" t="n">
@@ -57289,6 +57469,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1941" t="inlineStr">
+        <is>
+          <t>+54 11 4220-8542</t>
+        </is>
+      </c>
+      <c r="G1941" t="inlineStr">
+        <is>
+          <t>https://www.correoargentino.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1942" ht="15.75" customHeight="1" s="19">
       <c r="A1942" s="8" t="n">
@@ -57314,6 +57504,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1942" t="inlineStr"/>
+      <c r="G1942" t="inlineStr"/>
     </row>
     <row r="1943" ht="15.75" customHeight="1" s="19">
       <c r="A1943" s="8" t="n">
@@ -57339,6 +57531,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1943" t="inlineStr"/>
+      <c r="G1943" t="inlineStr"/>
     </row>
     <row r="1944" ht="15.75" customHeight="1" s="19">
       <c r="A1944" s="8" t="n">
@@ -57364,6 +57558,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1944" t="inlineStr"/>
+      <c r="G1944" t="inlineStr"/>
     </row>
     <row r="1945" ht="15.75" customHeight="1" s="19">
       <c r="A1945" s="8" t="n">
@@ -57389,6 +57585,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1945" t="inlineStr"/>
+      <c r="G1945" t="inlineStr"/>
     </row>
     <row r="1946" ht="15.75" customHeight="1" s="19">
       <c r="A1946" s="8" t="n">
@@ -57414,6 +57612,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1946" t="inlineStr"/>
+      <c r="G1946" t="inlineStr"/>
     </row>
     <row r="1947" ht="15.75" customHeight="1" s="19">
       <c r="A1947" s="8" t="n">
@@ -57439,6 +57639,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1947" t="inlineStr"/>
+      <c r="G1947" t="inlineStr"/>
     </row>
     <row r="1948" ht="15.75" customHeight="1" s="19">
       <c r="A1948" s="8" t="n">
@@ -57464,6 +57666,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1948" t="inlineStr">
+        <is>
+          <t>+54 11 2789-1882</t>
+        </is>
+      </c>
+      <c r="G1948" t="inlineStr"/>
     </row>
     <row r="1949" ht="15.75" customHeight="1" s="19">
       <c r="A1949" s="8" t="n">
@@ -57489,6 +57697,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1949" t="inlineStr"/>
+      <c r="G1949" t="inlineStr"/>
     </row>
     <row r="1950" ht="15.75" customHeight="1" s="19">
       <c r="A1950" s="8" t="n">
@@ -57514,6 +57724,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1950" t="inlineStr"/>
+      <c r="G1950" t="inlineStr"/>
     </row>
     <row r="1951" ht="15.75" customHeight="1" s="19">
       <c r="A1951" s="8" t="n">
@@ -57539,6 +57751,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1951" t="inlineStr"/>
+      <c r="G1951" t="inlineStr"/>
     </row>
     <row r="1952" ht="15.75" customHeight="1" s="19">
       <c r="A1952" s="8" t="n">
@@ -57564,6 +57778,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1952" t="inlineStr"/>
+      <c r="G1952" t="inlineStr"/>
     </row>
     <row r="1953" ht="15.75" customHeight="1" s="19">
       <c r="A1953" s="8" t="n">
@@ -57589,6 +57805,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1953" t="inlineStr"/>
+      <c r="G1953" t="inlineStr"/>
     </row>
     <row r="1954" ht="15.75" customHeight="1" s="19">
       <c r="A1954" s="8" t="n">
@@ -57614,6 +57832,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1954" t="inlineStr">
+        <is>
+          <t>+54 800-777-3472</t>
+        </is>
+      </c>
+      <c r="G1954" t="inlineStr">
+        <is>
+          <t>https://www.fincasdehudson.com/</t>
+        </is>
+      </c>
     </row>
     <row r="1955" ht="15.75" customHeight="1" s="19">
       <c r="A1955" s="8" t="n">
@@ -57639,6 +57867,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1955" t="inlineStr">
+        <is>
+          <t>+54 11 4249-5037</t>
+        </is>
+      </c>
+      <c r="G1955" t="inlineStr"/>
     </row>
     <row r="1956" ht="15.75" customHeight="1" s="19">
       <c r="A1956" s="8" t="n">
@@ -57664,6 +57898,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1956" t="inlineStr"/>
+      <c r="G1956" t="inlineStr"/>
     </row>
     <row r="1957" ht="15.75" customHeight="1" s="19">
       <c r="A1957" s="8" t="n">
@@ -57689,6 +57925,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1957" t="inlineStr">
+        <is>
+          <t>+54 11 6469-2233</t>
+        </is>
+      </c>
+      <c r="G1957" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/labirreria_banfield/saved/?hl=es-la</t>
+        </is>
+      </c>
     </row>
     <row r="1958" ht="15.75" customHeight="1" s="19">
       <c r="A1958" s="8" t="n">
@@ -57714,6 +57960,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1958" t="inlineStr"/>
+      <c r="G1958" t="inlineStr"/>
     </row>
     <row r="1959" ht="15.75" customHeight="1" s="19">
       <c r="A1959" s="8" t="n">
@@ -57739,6 +57987,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1959" t="inlineStr"/>
+      <c r="G1959" t="inlineStr"/>
     </row>
     <row r="1960" ht="15.75" customHeight="1" s="19">
       <c r="A1960" s="8" t="n">
@@ -57764,6 +58014,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1960" t="inlineStr"/>
+      <c r="G1960" t="inlineStr"/>
     </row>
     <row r="1961" ht="15.75" customHeight="1" s="19">
       <c r="A1961" s="8" t="n">
@@ -57789,6 +58041,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1961" t="inlineStr"/>
+      <c r="G1961" t="inlineStr"/>
     </row>
     <row r="1962" ht="15.75" customHeight="1" s="19">
       <c r="A1962" s="8" t="n">
@@ -57814,6 +58068,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1962" t="inlineStr">
+        <is>
+          <t>+54 11 4242-1125</t>
+        </is>
+      </c>
+      <c r="G1962" t="inlineStr">
+        <is>
+          <t>https://www.vetcenterescalada.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1963" ht="15.75" customHeight="1" s="19">
       <c r="A1963" s="8" t="n">
@@ -57839,6 +58103,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1963" t="inlineStr"/>
+      <c r="G1963" t="inlineStr"/>
     </row>
     <row r="1964" ht="15.75" customHeight="1" s="19">
       <c r="A1964" s="8" t="n">
@@ -57864,6 +58130,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1964" t="inlineStr">
+        <is>
+          <t>+54 11 6086-3975</t>
+        </is>
+      </c>
+      <c r="G1964" t="inlineStr">
+        <is>
+          <t>http://www.mah.org.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1965" ht="15.75" customHeight="1" s="19">
       <c r="A1965" s="8" t="n">
@@ -57889,6 +58165,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1965" t="inlineStr">
+        <is>
+          <t>+54 11 2293-6969</t>
+        </is>
+      </c>
+      <c r="G1965" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/casamascotaslanus/</t>
+        </is>
+      </c>
     </row>
     <row r="1966" ht="15.75" customHeight="1" s="19">
       <c r="A1966" s="8" t="n">
@@ -57914,6 +58200,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1966" t="inlineStr"/>
+      <c r="G1966" t="inlineStr"/>
     </row>
     <row r="1967" ht="15.75" customHeight="1" s="19">
       <c r="A1967" s="8" t="n">
@@ -57939,6 +58227,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1967" t="inlineStr"/>
+      <c r="G1967" t="inlineStr"/>
     </row>
     <row r="1968" ht="15.75" customHeight="1" s="19">
       <c r="A1968" s="8" t="n">
@@ -57964,6 +58254,16 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F1968" t="inlineStr">
+        <is>
+          <t>+54 11 4116-4723</t>
+        </is>
+      </c>
+      <c r="G1968" t="inlineStr">
+        <is>
+          <t>http://nutricega.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1969" ht="15.75" customHeight="1" s="19">
       <c r="A1969" s="8" t="n">
@@ -57989,6 +58289,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1969" t="inlineStr"/>
+      <c r="G1969" t="inlineStr"/>
     </row>
     <row r="1970" ht="15.75" customHeight="1" s="19">
       <c r="A1970" s="8" t="n">
@@ -58014,6 +58316,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1970" t="inlineStr">
+        <is>
+          <t>+54 11 4229-5500</t>
+        </is>
+      </c>
+      <c r="G1970" t="inlineStr"/>
     </row>
     <row r="1971" ht="15.75" customHeight="1" s="19">
       <c r="A1971" s="8" t="n">
@@ -58039,6 +58347,16 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1971" t="inlineStr">
+        <is>
+          <t>+54 11 6011-5300</t>
+        </is>
+      </c>
+      <c r="G1971" t="inlineStr">
+        <is>
+          <t>http://www.santamariasa.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1972" ht="15.75" customHeight="1" s="19">
       <c r="A1972" s="8" t="n">
@@ -58064,6 +58382,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1972" t="inlineStr">
+        <is>
+          <t>+54 11 5897-0604</t>
+        </is>
+      </c>
+      <c r="G1972" t="inlineStr">
+        <is>
+          <t>https://www.estudiojuridicoforciniti.com/</t>
+        </is>
+      </c>
     </row>
     <row r="1973" ht="15.75" customHeight="1" s="19">
       <c r="A1973" s="8" t="n">
@@ -58089,6 +58417,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1973" t="inlineStr"/>
+      <c r="G1973" t="inlineStr"/>
     </row>
     <row r="1974" ht="15.75" customHeight="1" s="19">
       <c r="A1974" s="8" t="n">
@@ -58114,6 +58444,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1974" t="inlineStr"/>
+      <c r="G1974" t="inlineStr"/>
     </row>
     <row r="1975" ht="15.75" customHeight="1" s="19">
       <c r="A1975" s="8" t="n">
@@ -58139,6 +58471,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1975" t="inlineStr"/>
+      <c r="G1975" t="inlineStr"/>
     </row>
     <row r="1976" ht="15.75" customHeight="1" s="19">
       <c r="A1976" s="8" t="n">
@@ -58164,6 +58498,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1976" t="inlineStr"/>
+      <c r="G1976" t="inlineStr"/>
     </row>
     <row r="1977" ht="15.75" customHeight="1" s="19">
       <c r="A1977" s="8" t="n">
@@ -58189,6 +58525,16 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1977" t="inlineStr">
+        <is>
+          <t>+54 42507496</t>
+        </is>
+      </c>
+      <c r="G1977" t="inlineStr">
+        <is>
+          <t>http://www.santamariasa.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1978" ht="15.75" customHeight="1" s="19">
       <c r="A1978" s="8" t="n">
@@ -58214,6 +58560,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1978" t="inlineStr"/>
+      <c r="G1978" t="inlineStr"/>
     </row>
     <row r="1979" ht="15.75" customHeight="1" s="19">
       <c r="A1979" s="8" t="n">
@@ -58239,6 +58587,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1979" t="inlineStr">
+        <is>
+          <t>+54 11 4241-5100</t>
+        </is>
+      </c>
+      <c r="G1979" t="inlineStr">
+        <is>
+          <t>https://www.remax-titanium.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1980" ht="15.75" customHeight="1" s="19">
       <c r="A1980" s="8" t="n">
@@ -58264,6 +58622,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1980" t="inlineStr"/>
+      <c r="G1980" t="inlineStr"/>
     </row>
     <row r="1981" ht="15.75" customHeight="1" s="19">
       <c r="A1981" s="8" t="n">
@@ -58289,6 +58649,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1981" t="inlineStr">
+        <is>
+          <t>+54 11 4208-5507</t>
+        </is>
+      </c>
+      <c r="G1981" t="inlineStr">
+        <is>
+          <t>https://www.correoargentino.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1982" ht="15.75" customHeight="1" s="19">
       <c r="A1982" s="8" t="n">
@@ -58314,6 +58684,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1982" t="inlineStr"/>
+      <c r="G1982" t="inlineStr"/>
     </row>
     <row r="1983" ht="15.75" customHeight="1" s="19">
       <c r="A1983" s="8" t="n">
@@ -58339,6 +58711,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1983" t="inlineStr"/>
+      <c r="G1983" t="inlineStr">
+        <is>
+          <t>https://obradorcraft.mitiendanube.com/?utm_source=ig&amp;utm_medium=social&amp;utm_content=link_in_bio&amp;fbclid=PAb21jcARCVplleHRuA2FlbQIxMQBzcnRjBmFwcF9pZA81NjcwNjczNDMzNTI0MjcAAafHgVDVLCJE6lfO0UM20ZOfEdA_30L9UmROYquqzKkZgoTQSg-EhaKXHnAvlQ_aem__BJ3zEYY01Oua7f6QfAr8g</t>
+        </is>
+      </c>
     </row>
     <row r="1984" ht="15.75" customHeight="1" s="19">
       <c r="A1984" s="8" t="n">
@@ -58364,6 +58742,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1984" t="inlineStr"/>
+      <c r="G1984" t="inlineStr"/>
     </row>
     <row r="1985" ht="15.75" customHeight="1" s="19">
       <c r="A1985" s="8" t="n">
@@ -58389,6 +58769,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1985" t="inlineStr"/>
+      <c r="G1985" t="inlineStr"/>
     </row>
     <row r="1986" ht="15.75" customHeight="1" s="19">
       <c r="A1986" s="8" t="n">
@@ -58414,6 +58796,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1986" t="inlineStr"/>
+      <c r="G1986" t="inlineStr"/>
     </row>
     <row r="1987" ht="15.75" customHeight="1" s="19">
       <c r="A1987" s="8" t="n">
@@ -58439,6 +58823,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1987" t="inlineStr"/>
+      <c r="G1987" t="inlineStr"/>
     </row>
     <row r="1988" ht="15.75" customHeight="1" s="19">
       <c r="A1988" s="8" t="n">
@@ -58464,6 +58850,16 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F1988" t="inlineStr">
+        <is>
+          <t>+54 11 6354-9122</t>
+        </is>
+      </c>
+      <c r="G1988" t="inlineStr">
+        <is>
+          <t>https://www.centromedicomonteagudo.com/ubicacion.html</t>
+        </is>
+      </c>
     </row>
     <row r="1989" ht="15.75" customHeight="1" s="19">
       <c r="A1989" s="8" t="n">
@@ -58489,6 +58885,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1989" t="inlineStr"/>
+      <c r="G1989" t="inlineStr"/>
     </row>
     <row r="1990" ht="15.75" customHeight="1" s="19">
       <c r="A1990" s="8" t="n">
@@ -58514,6 +58912,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1990" t="inlineStr"/>
+      <c r="G1990" t="inlineStr"/>
     </row>
     <row r="1991" ht="15.75" customHeight="1" s="19">
       <c r="A1991" s="8" t="n">
@@ -58539,6 +58939,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1991" t="inlineStr"/>
+      <c r="G1991" t="inlineStr"/>
     </row>
     <row r="1992" ht="15.75" customHeight="1" s="19">
       <c r="A1992" s="8" t="n">
@@ -58564,6 +58966,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1992" t="inlineStr"/>
+      <c r="G1992" t="inlineStr"/>
     </row>
     <row r="1993" ht="15.75" customHeight="1" s="19">
       <c r="A1993" s="8" t="n">
@@ -58589,6 +58993,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1993" t="inlineStr">
+        <is>
+          <t>+54 2202 43-5213</t>
+        </is>
+      </c>
+      <c r="G1993" t="inlineStr"/>
     </row>
     <row r="1994" ht="15.75" customHeight="1" s="19">
       <c r="A1994" s="8" t="n">
@@ -58614,6 +59024,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1994" t="inlineStr"/>
+      <c r="G1994" t="inlineStr"/>
     </row>
     <row r="1995" ht="15.75" customHeight="1" s="19">
       <c r="A1995" s="8" t="n">
@@ -58639,6 +59051,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1995" t="inlineStr">
+        <is>
+          <t>+54 11 4626-7472</t>
+        </is>
+      </c>
+      <c r="G1995" t="inlineStr"/>
     </row>
     <row r="1996" ht="15.75" customHeight="1" s="19">
       <c r="A1996" s="8" t="n">
@@ -58664,6 +59082,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1996" t="inlineStr"/>
+      <c r="G1996" t="inlineStr"/>
     </row>
     <row r="1997" ht="15.75" customHeight="1" s="19">
       <c r="A1997" s="8" t="n">
@@ -58689,6 +59109,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1997" t="inlineStr">
+        <is>
+          <t>+54 11 3129-5595</t>
+        </is>
+      </c>
+      <c r="G1997" t="inlineStr">
+        <is>
+          <t>http://fabioreyes.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="1998" ht="15.75" customHeight="1" s="19">
       <c r="A1998" s="8" t="n">
@@ -58714,6 +59144,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F1998" t="inlineStr"/>
+      <c r="G1998" t="inlineStr"/>
     </row>
     <row r="1999" ht="15.75" customHeight="1" s="19">
       <c r="A1999" s="8" t="n">
@@ -58739,6 +59171,16 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F1999" t="inlineStr">
+        <is>
+          <t>+54 11 6332-3353</t>
+        </is>
+      </c>
+      <c r="G1999" t="inlineStr">
+        <is>
+          <t>http://www.chevanne.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="2000" ht="15.75" customHeight="1" s="19">
       <c r="A2000" s="8" t="n">
@@ -58764,6 +59206,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2000" t="inlineStr"/>
+      <c r="G2000" t="inlineStr"/>
     </row>
     <row r="2001" ht="15.75" customHeight="1" s="19">
       <c r="A2001" s="8" t="n">
@@ -58789,6 +59233,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2001" t="inlineStr"/>
+      <c r="G2001" t="inlineStr"/>
     </row>
     <row r="2002" ht="15.75" customHeight="1" s="19">
       <c r="A2002" s="8" t="n">
@@ -58814,6 +59260,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2002" t="inlineStr"/>
+      <c r="G2002" t="inlineStr"/>
     </row>
     <row r="2003" ht="15.75" customHeight="1" s="19">
       <c r="A2003" s="8" t="n">

--- a/PUNTOS_DE_VENTA_completado.xlsx
+++ b/PUNTOS_DE_VENTA_completado.xlsx
@@ -59287,6 +59287,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2003" t="inlineStr"/>
+      <c r="G2003" t="inlineStr"/>
     </row>
     <row r="2004" ht="15.75" customHeight="1" s="19">
       <c r="A2004" s="8" t="n">
@@ -59312,6 +59314,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2004" t="inlineStr"/>
+      <c r="G2004" t="inlineStr"/>
     </row>
     <row r="2005" ht="15.75" customHeight="1" s="19">
       <c r="A2005" s="8" t="n">
@@ -59337,6 +59341,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2005" t="inlineStr"/>
+      <c r="G2005" t="inlineStr"/>
     </row>
     <row r="2006" ht="15.75" customHeight="1" s="19">
       <c r="A2006" s="8" t="n">
@@ -59362,6 +59368,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2006" t="inlineStr"/>
+      <c r="G2006" t="inlineStr"/>
     </row>
     <row r="2007" ht="15.75" customHeight="1" s="19">
       <c r="A2007" s="8" t="n">
@@ -59387,6 +59395,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2007" t="inlineStr"/>
+      <c r="G2007" t="inlineStr"/>
     </row>
     <row r="2008" ht="15.75" customHeight="1" s="19">
       <c r="A2008" s="8" t="n">
@@ -59412,6 +59422,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2008" t="inlineStr"/>
+      <c r="G2008" t="inlineStr"/>
     </row>
     <row r="2009" ht="15.75" customHeight="1" s="19">
       <c r="A2009" s="8" t="n">
@@ -59437,6 +59449,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2009" t="inlineStr"/>
+      <c r="G2009" t="inlineStr"/>
     </row>
     <row r="2010" ht="15.75" customHeight="1" s="19">
       <c r="A2010" s="8" t="n">
@@ -59462,6 +59476,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2010" t="inlineStr"/>
+      <c r="G2010" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/john.doyer?igsh=MTN3czhuajFnZ2g3Zw==</t>
+        </is>
+      </c>
     </row>
     <row r="2011" ht="15.75" customHeight="1" s="19">
       <c r="A2011" s="8" t="n">
@@ -59487,6 +59507,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2011" t="inlineStr"/>
+      <c r="G2011" t="inlineStr"/>
     </row>
     <row r="2012" ht="15.75" customHeight="1" s="19">
       <c r="A2012" s="8" t="n">
@@ -59512,6 +59534,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2012" t="inlineStr">
+        <is>
+          <t>+54 11 4441-9992</t>
+        </is>
+      </c>
+      <c r="G2012" t="inlineStr">
+        <is>
+          <t>http://animalbrothers.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="2013" ht="15.75" customHeight="1" s="19">
       <c r="A2013" s="8" t="n">
@@ -59537,6 +59569,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2013" t="inlineStr"/>
+      <c r="G2013" t="inlineStr"/>
     </row>
     <row r="2014" ht="15.75" customHeight="1" s="19">
       <c r="A2014" s="8" t="n">
@@ -59562,6 +59596,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2014" t="inlineStr"/>
+      <c r="G2014" t="inlineStr"/>
     </row>
     <row r="2015" ht="15.75" customHeight="1" s="19">
       <c r="A2015" s="8" t="n">
@@ -59587,6 +59623,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2015" t="inlineStr"/>
+      <c r="G2015" t="inlineStr"/>
     </row>
     <row r="2016" ht="15.75" customHeight="1" s="19">
       <c r="A2016" s="8" t="n">
@@ -59612,6 +59650,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2016" t="inlineStr"/>
+      <c r="G2016" t="inlineStr"/>
     </row>
     <row r="2017" ht="15.75" customHeight="1" s="19">
       <c r="A2017" s="8" t="n">
@@ -59637,6 +59677,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2017" t="inlineStr"/>
+      <c r="G2017" t="inlineStr"/>
     </row>
     <row r="2018" ht="15.75" customHeight="1" s="19">
       <c r="A2018" s="8" t="n">
@@ -59662,6 +59704,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2018" t="inlineStr"/>
+      <c r="G2018" t="inlineStr"/>
     </row>
     <row r="2019" ht="15.75" customHeight="1" s="19">
       <c r="A2019" s="8" t="n">
@@ -59687,6 +59731,16 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2019" t="inlineStr">
+        <is>
+          <t>+54 11 4216-5130</t>
+        </is>
+      </c>
+      <c r="G2019" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dongatobegui?igsh=eDJlNjVybjMwNjl1</t>
+        </is>
+      </c>
     </row>
     <row r="2020" ht="15.75" customHeight="1" s="19">
       <c r="A2020" s="8" t="n">
@@ -59712,6 +59766,16 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2020" t="inlineStr">
+        <is>
+          <t>+54 11 4216-5130</t>
+        </is>
+      </c>
+      <c r="G2020" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dongatobegui?igsh=eDJlNjVybjMwNjl1</t>
+        </is>
+      </c>
     </row>
     <row r="2021" ht="15.75" customHeight="1" s="19">
       <c r="A2021" s="8" t="n">
@@ -59737,6 +59801,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2021" t="inlineStr">
+        <is>
+          <t>+54 11 2606-9110</t>
+        </is>
+      </c>
+      <c r="G2021" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/gabrielverazay</t>
+        </is>
+      </c>
     </row>
     <row r="2022" ht="15.75" customHeight="1" s="19">
       <c r="A2022" s="8" t="n">
@@ -59762,6 +59836,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2022" t="inlineStr"/>
+      <c r="G2022" t="inlineStr"/>
     </row>
     <row r="2023" ht="15.75" customHeight="1" s="19">
       <c r="A2023" s="8" t="n">
@@ -59787,6 +59863,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F2023" t="inlineStr"/>
+      <c r="G2023" t="inlineStr"/>
     </row>
     <row r="2024" ht="15.75" customHeight="1" s="19">
       <c r="A2024" s="8" t="n">
@@ -59812,6 +59890,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F2024" t="inlineStr"/>
+      <c r="G2024" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/veterinariaplus?igsh=NzI5Z3Z0Mzh5NHFu</t>
+        </is>
+      </c>
     </row>
     <row r="2025" ht="15.75" customHeight="1" s="19">
       <c r="A2025" s="8" t="n">
@@ -59837,6 +59921,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2025" t="inlineStr"/>
+      <c r="G2025" t="inlineStr"/>
     </row>
     <row r="2026" ht="15.75" customHeight="1" s="19">
       <c r="A2026" s="8" t="n">
@@ -59862,6 +59948,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2026" t="inlineStr"/>
+      <c r="G2026" t="inlineStr"/>
     </row>
     <row r="2027" ht="15.75" customHeight="1" s="19">
       <c r="A2027" s="8" t="n">
@@ -59887,6 +59975,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F2027" t="inlineStr"/>
+      <c r="G2027" t="inlineStr"/>
     </row>
     <row r="2028" ht="15.75" customHeight="1" s="19">
       <c r="A2028" s="8" t="n">
@@ -59912,6 +60002,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F2028" t="inlineStr"/>
+      <c r="G2028" t="inlineStr"/>
     </row>
     <row r="2029" ht="15.75" customHeight="1" s="19">
       <c r="A2029" s="8" t="n">
@@ -59937,6 +60029,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F2029" t="inlineStr"/>
+      <c r="G2029" t="inlineStr"/>
     </row>
     <row r="2030" ht="15.75" customHeight="1" s="19">
       <c r="A2030" s="8" t="n">
@@ -59962,6 +60056,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2030" t="inlineStr">
+        <is>
+          <t>+54 11 2885-4780</t>
+        </is>
+      </c>
+      <c r="G2030" t="inlineStr"/>
     </row>
     <row r="2031" ht="15.75" customHeight="1" s="19">
       <c r="A2031" s="8" t="n">
@@ -59987,6 +60087,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F2031" t="inlineStr"/>
+      <c r="G2031" t="inlineStr"/>
     </row>
     <row r="2032" ht="15.75" customHeight="1" s="19">
       <c r="A2032" s="8" t="n">
@@ -60012,6 +60114,8 @@
           <t>pet shop</t>
         </is>
       </c>
+      <c r="F2032" t="inlineStr"/>
+      <c r="G2032" t="inlineStr"/>
     </row>
     <row r="2033" ht="15.75" customHeight="1" s="19">
       <c r="A2033" s="8" t="n">
@@ -60037,6 +60141,12 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F2033" t="inlineStr">
+        <is>
+          <t>+54 11 4208-0796</t>
+        </is>
+      </c>
+      <c r="G2033" t="inlineStr"/>
     </row>
     <row r="2034" ht="15.75" customHeight="1" s="19">
       <c r="A2034" s="8" t="n">
@@ -60062,6 +60172,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F2034" t="inlineStr"/>
+      <c r="G2034" t="inlineStr"/>
     </row>
     <row r="2035" ht="15.75" customHeight="1" s="19">
       <c r="A2035" s="8" t="n">
@@ -60087,6 +60199,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F2035" t="inlineStr"/>
+      <c r="G2035" t="inlineStr"/>
     </row>
     <row r="2036" ht="15.75" customHeight="1" s="19">
       <c r="A2036" s="8" t="n">
@@ -60112,6 +60226,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F2036" t="inlineStr">
+        <is>
+          <t>+54 11 4216-7771</t>
+        </is>
+      </c>
+      <c r="G2036" t="inlineStr"/>
     </row>
     <row r="2037" ht="15.75" customHeight="1" s="19">
       <c r="A2037" s="8" t="n">
@@ -60137,6 +60257,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2037" t="inlineStr">
+        <is>
+          <t>+54 220 476-1911</t>
+        </is>
+      </c>
+      <c r="G2037" t="inlineStr"/>
     </row>
     <row r="2038" ht="15.75" customHeight="1" s="19">
       <c r="A2038" s="8" t="n">
@@ -60162,6 +60288,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2038" t="inlineStr"/>
+      <c r="G2038" t="inlineStr"/>
     </row>
     <row r="2039" ht="15.75" customHeight="1" s="19">
       <c r="A2039" s="8" t="n">
@@ -60187,6 +60315,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2039" t="inlineStr">
+        <is>
+          <t>+54 11 5454-3260</t>
+        </is>
+      </c>
+      <c r="G2039" t="inlineStr"/>
     </row>
     <row r="2040" ht="15.75" customHeight="1" s="19">
       <c r="A2040" s="8" t="n">
@@ -60212,6 +60346,12 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2040" t="inlineStr">
+        <is>
+          <t>+54 11 3924-5468</t>
+        </is>
+      </c>
+      <c r="G2040" t="inlineStr"/>
     </row>
     <row r="2041" ht="15.75" customHeight="1" s="19">
       <c r="A2041" s="8" t="n">
@@ -60237,6 +60377,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2041" t="inlineStr">
+        <is>
+          <t>+54 9 11 6700-9400</t>
+        </is>
+      </c>
+      <c r="G2041" t="inlineStr">
+        <is>
+          <t>http://www.estudioaire.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="2042" ht="15.75" customHeight="1" s="19">
       <c r="A2042" s="8" t="n">
@@ -60262,6 +60412,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2042" t="inlineStr"/>
+      <c r="G2042" t="inlineStr"/>
     </row>
     <row r="2043" ht="15.75" customHeight="1" s="19">
       <c r="A2043" s="8" t="n">
@@ -60287,6 +60439,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2043" t="inlineStr"/>
+      <c r="G2043" t="inlineStr"/>
     </row>
     <row r="2044" ht="15.75" customHeight="1" s="19">
       <c r="A2044" s="8" t="n">
@@ -60312,6 +60466,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2044" t="inlineStr"/>
+      <c r="G2044" t="inlineStr"/>
     </row>
     <row r="2045" ht="15.75" customHeight="1" s="19">
       <c r="A2045" s="8" t="n">
@@ -60337,6 +60493,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2045" t="inlineStr"/>
+      <c r="G2045" t="inlineStr"/>
     </row>
     <row r="2046" ht="15.75" customHeight="1" s="19">
       <c r="A2046" s="8" t="n">
@@ -60362,6 +60520,8 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F2046" t="inlineStr"/>
+      <c r="G2046" t="inlineStr"/>
     </row>
     <row r="2047" ht="15.75" customHeight="1" s="19">
       <c r="A2047" s="8" t="n">
@@ -60387,6 +60547,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F2047" t="inlineStr">
+        <is>
+          <t>+54 11 2788-1845</t>
+        </is>
+      </c>
+      <c r="G2047" t="inlineStr"/>
     </row>
     <row r="2048" ht="15.75" customHeight="1" s="19">
       <c r="A2048" s="8" t="n">
@@ -60412,6 +60578,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2048" t="inlineStr">
+        <is>
+          <t>+54 341 531-2514</t>
+        </is>
+      </c>
+      <c r="G2048" t="inlineStr">
+        <is>
+          <t>http://www.carniceriatomasello.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="2049" ht="15.75" customHeight="1" s="19">
       <c r="A2049" s="8" t="n">
@@ -60437,6 +60613,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2049" t="inlineStr"/>
+      <c r="G2049" t="inlineStr"/>
     </row>
     <row r="2050" ht="15.75" customHeight="1" s="19">
       <c r="A2050" s="8" t="n">
@@ -60462,6 +60640,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2050" t="inlineStr"/>
+      <c r="G2050" t="inlineStr"/>
     </row>
     <row r="2051" ht="15.75" customHeight="1" s="19">
       <c r="A2051" s="8" t="n">
@@ -60487,6 +60667,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2051" t="inlineStr">
+        <is>
+          <t>+54 11 2801-8490</t>
+        </is>
+      </c>
+      <c r="G2051" t="inlineStr">
+        <is>
+          <t>https://www.argentina.gob.ar/cisi</t>
+        </is>
+      </c>
     </row>
     <row r="2052" ht="15.75" customHeight="1" s="19">
       <c r="A2052" s="8" t="n">
@@ -60512,6 +60702,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2052" t="inlineStr">
+        <is>
+          <t>+54 3487 42-2277</t>
+        </is>
+      </c>
+      <c r="G2052" t="inlineStr"/>
     </row>
     <row r="2053" ht="15.75" customHeight="1" s="19">
       <c r="A2053" s="8" t="n">
@@ -60537,6 +60733,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2053" t="inlineStr"/>
+      <c r="G2053" t="inlineStr"/>
     </row>
     <row r="2054" ht="15.75" customHeight="1" s="19">
       <c r="A2054" s="8" t="n">
@@ -60562,6 +60760,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2054" t="inlineStr">
+        <is>
+          <t>+54 9 11 6981-0194</t>
+        </is>
+      </c>
+      <c r="G2054" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/GranjaAraiwa/</t>
+        </is>
+      </c>
     </row>
     <row r="2055" ht="15.75" customHeight="1" s="19">
       <c r="A2055" s="8" t="n">
@@ -60587,6 +60795,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2055" t="inlineStr">
+        <is>
+          <t>+54 9 11 6981-0194</t>
+        </is>
+      </c>
+      <c r="G2055" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/GranjaAraiwa/</t>
+        </is>
+      </c>
     </row>
     <row r="2056" ht="15.75" customHeight="1" s="19">
       <c r="A2056" s="8" t="n">
@@ -60612,6 +60830,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2056" t="inlineStr"/>
+      <c r="G2056" t="inlineStr"/>
     </row>
     <row r="2057" ht="15.75" customHeight="1" s="19">
       <c r="A2057" s="8" t="n">
@@ -60637,6 +60857,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2057" t="inlineStr">
+        <is>
+          <t>+54 348 430-3024</t>
+        </is>
+      </c>
+      <c r="G2057" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/natividaddeescobar</t>
+        </is>
+      </c>
     </row>
     <row r="2058" ht="15.75" customHeight="1" s="19">
       <c r="A2058" s="8" t="n">
@@ -60662,6 +60892,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F2058" t="inlineStr">
+        <is>
+          <t>+54 11 4739-2926</t>
+        </is>
+      </c>
+      <c r="G2058" t="inlineStr"/>
     </row>
     <row r="2059" ht="15.75" customHeight="1" s="19">
       <c r="A2059" s="8" t="n">
@@ -60687,6 +60923,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2059" t="inlineStr"/>
+      <c r="G2059" t="inlineStr"/>
     </row>
     <row r="2060" ht="15.75" customHeight="1" s="19">
       <c r="A2060" s="8" t="n">
@@ -60712,6 +60950,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2060" t="inlineStr"/>
+      <c r="G2060" t="inlineStr"/>
     </row>
     <row r="2061" ht="15.75" customHeight="1" s="19">
       <c r="A2061" s="8" t="n">
@@ -60737,6 +60977,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2061" t="inlineStr"/>
+      <c r="G2061" t="inlineStr"/>
     </row>
     <row r="2062" ht="15.75" customHeight="1" s="19">
       <c r="A2062" s="8" t="n">
@@ -60762,6 +61004,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2062" t="inlineStr"/>
+      <c r="G2062" t="inlineStr"/>
     </row>
     <row r="2063" ht="15.75" customHeight="1" s="19">
       <c r="A2063" s="8" t="n">
@@ -60787,6 +61031,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2063" t="inlineStr"/>
+      <c r="G2063" t="inlineStr"/>
     </row>
     <row r="2064" ht="15.75" customHeight="1" s="19">
       <c r="A2064" s="8" t="n">
@@ -60812,6 +61058,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2064" t="inlineStr"/>
+      <c r="G2064" t="inlineStr"/>
     </row>
     <row r="2065" ht="15.75" customHeight="1" s="19">
       <c r="A2065" s="8" t="n">
@@ -60837,6 +61085,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2065" t="inlineStr"/>
+      <c r="G2065" t="inlineStr"/>
     </row>
     <row r="2066" ht="15.75" customHeight="1" s="19">
       <c r="A2066" s="8" t="n">
@@ -60862,6 +61112,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2066" t="inlineStr"/>
+      <c r="G2066" t="inlineStr"/>
     </row>
     <row r="2067" ht="15.75" customHeight="1" s="19">
       <c r="A2067" s="8" t="n">
@@ -60887,6 +61139,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2067" t="inlineStr"/>
+      <c r="G2067" t="inlineStr"/>
     </row>
     <row r="2068" ht="15.75" customHeight="1" s="19">
       <c r="A2068" s="8" t="n">
@@ -60912,6 +61166,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2068" t="inlineStr"/>
+      <c r="G2068" t="inlineStr"/>
     </row>
     <row r="2069" ht="15.75" customHeight="1" s="19">
       <c r="A2069" s="8" t="n">
@@ -60937,6 +61193,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2069" t="inlineStr">
+        <is>
+          <t>+54 800-220-7748</t>
+        </is>
+      </c>
+      <c r="G2069" t="inlineStr">
+        <is>
+          <t>http://www.priva.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="2070" ht="15.75" customHeight="1" s="19">
       <c r="A2070" s="8" t="n">
@@ -60962,6 +61228,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2070" t="inlineStr"/>
+      <c r="G2070" t="inlineStr"/>
     </row>
     <row r="2071" ht="15.75" customHeight="1" s="19">
       <c r="A2071" s="8" t="n">
@@ -60987,6 +61255,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2071" t="inlineStr">
+        <is>
+          <t>+54 348 444-1015</t>
+        </is>
+      </c>
+      <c r="G2071" t="inlineStr"/>
     </row>
     <row r="2072" ht="15.75" customHeight="1" s="19">
       <c r="A2072" s="8" t="n">
@@ -61012,6 +61286,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2072" t="inlineStr"/>
+      <c r="G2072" t="inlineStr"/>
     </row>
     <row r="2073" ht="15.75" customHeight="1" s="19">
       <c r="A2073" s="8" t="n">
@@ -61037,6 +61313,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2073" t="inlineStr"/>
+      <c r="G2073" t="inlineStr"/>
     </row>
     <row r="2074" ht="15.75" customHeight="1" s="19">
       <c r="A2074" s="8" t="n">
@@ -61062,6 +61340,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2074" t="inlineStr">
+        <is>
+          <t>+54 9 230 431-9072</t>
+        </is>
+      </c>
+      <c r="G2074" t="inlineStr">
+        <is>
+          <t>https://treviloscardales.shop/</t>
+        </is>
+      </c>
     </row>
     <row r="2075" ht="15.75" customHeight="1" s="19">
       <c r="A2075" s="8" t="n">
@@ -61087,6 +61375,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2075" t="inlineStr">
+        <is>
+          <t>+54 2323 42-2264</t>
+        </is>
+      </c>
+      <c r="G2075" t="inlineStr"/>
     </row>
     <row r="2076" ht="15.75" customHeight="1" s="19">
       <c r="A2076" s="8" t="n">
@@ -61112,6 +61406,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2076" t="inlineStr"/>
+      <c r="G2076" t="inlineStr"/>
     </row>
     <row r="2077" ht="15.75" customHeight="1" s="19">
       <c r="A2077" s="8" t="n">
@@ -61137,6 +61433,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2077" t="inlineStr">
+        <is>
+          <t>+54 2323 42-0551</t>
+        </is>
+      </c>
+      <c r="G2077" t="inlineStr"/>
     </row>
     <row r="2078" ht="15.75" customHeight="1" s="19">
       <c r="A2078" s="8" t="n">
@@ -61162,6 +61464,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2078" t="inlineStr"/>
+      <c r="G2078" t="inlineStr"/>
     </row>
     <row r="2079" ht="15.75" customHeight="1" s="19">
       <c r="A2079" s="8" t="n">
@@ -61187,6 +61491,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2079" t="inlineStr"/>
+      <c r="G2079" t="inlineStr"/>
     </row>
     <row r="2080" ht="15.75" customHeight="1" s="19">
       <c r="A2080" s="8" t="n">
@@ -61212,6 +61518,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2080" t="inlineStr">
+        <is>
+          <t>+54 2323 42-1070</t>
+        </is>
+      </c>
+      <c r="G2080" t="inlineStr">
+        <is>
+          <t>https://santuariodelujan.org.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="2081" ht="15.75" customHeight="1" s="19">
       <c r="A2081" s="8" t="n">
@@ -61237,6 +61553,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2081" t="inlineStr"/>
+      <c r="G2081" t="inlineStr"/>
     </row>
     <row r="2082" ht="15.75" customHeight="1" s="19">
       <c r="A2082" s="8" t="n">
@@ -61262,6 +61580,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2082" t="inlineStr">
+        <is>
+          <t>+54 2323 42-1070</t>
+        </is>
+      </c>
+      <c r="G2082" t="inlineStr">
+        <is>
+          <t>https://santuariodelujan.org.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="2083" ht="15.75" customHeight="1" s="19">
       <c r="A2083" s="8" t="n">
@@ -61287,6 +61615,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2083" t="inlineStr"/>
+      <c r="G2083" t="inlineStr"/>
     </row>
     <row r="2084" ht="15.75" customHeight="1" s="19">
       <c r="A2084" s="8" t="n">
@@ -61312,6 +61642,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2084" t="inlineStr"/>
+      <c r="G2084" t="inlineStr"/>
     </row>
     <row r="2085" ht="15.75" customHeight="1" s="19">
       <c r="A2085" s="8" t="n">
@@ -61337,6 +61669,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2085" t="inlineStr">
+        <is>
+          <t>+54 2323 47-3692</t>
+        </is>
+      </c>
+      <c r="G2085" t="inlineStr">
+        <is>
+          <t>http://www.forrajeriamartin.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="2086" ht="15.75" customHeight="1" s="19">
       <c r="A2086" s="8" t="n">
@@ -61362,6 +61704,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2086" t="inlineStr">
+        <is>
+          <t>+54 221 464-4701</t>
+        </is>
+      </c>
+      <c r="G2086" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/riccicalzados/</t>
+        </is>
+      </c>
     </row>
     <row r="2087" ht="15.75" customHeight="1" s="19">
       <c r="A2087" s="8" t="n">
@@ -61387,6 +61739,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2087" t="inlineStr"/>
+      <c r="G2087" t="inlineStr"/>
     </row>
     <row r="2088" ht="15.75" customHeight="1" s="19">
       <c r="A2088" s="8" t="n">
@@ -61412,6 +61766,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2088" t="inlineStr"/>
+      <c r="G2088" t="inlineStr"/>
     </row>
     <row r="2089" ht="15.75" customHeight="1" s="19">
       <c r="A2089" s="8" t="n">
@@ -61437,6 +61793,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2089" t="inlineStr"/>
+      <c r="G2089" t="inlineStr"/>
     </row>
     <row r="2090" ht="15.75" customHeight="1" s="19">
       <c r="A2090" s="8" t="n">
@@ -61462,6 +61820,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2090" t="inlineStr"/>
+      <c r="G2090" t="inlineStr"/>
     </row>
     <row r="2091" ht="15.75" customHeight="1" s="19">
       <c r="A2091" s="8" t="n">
@@ -61487,6 +61847,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2091" t="inlineStr">
+        <is>
+          <t>+39 011 024 3211</t>
+        </is>
+      </c>
+      <c r="G2091" t="inlineStr"/>
     </row>
     <row r="2092" ht="15.75" customHeight="1" s="19">
       <c r="A2092" s="8" t="n">
@@ -61512,6 +61878,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2092" t="inlineStr"/>
+      <c r="G2092" t="inlineStr"/>
     </row>
     <row r="2093" ht="15.75" customHeight="1" s="19">
       <c r="A2093" s="8" t="n">
@@ -61537,6 +61905,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2093" t="inlineStr"/>
+      <c r="G2093" t="inlineStr"/>
     </row>
     <row r="2094" ht="15.75" customHeight="1" s="19">
       <c r="A2094" s="8" t="n">
@@ -61562,6 +61932,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2094" t="inlineStr"/>
+      <c r="G2094" t="inlineStr"/>
     </row>
     <row r="2095" ht="15.75" customHeight="1" s="19">
       <c r="A2095" s="8" t="n">
@@ -61587,6 +61959,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2095" t="inlineStr">
+        <is>
+          <t>+54 11 4280-3454</t>
+        </is>
+      </c>
+      <c r="G2095" t="inlineStr">
+        <is>
+          <t>http://www.crecchio.com/</t>
+        </is>
+      </c>
     </row>
     <row r="2096" ht="15.75" customHeight="1" s="19">
       <c r="A2096" s="8" t="n">
@@ -61612,6 +61994,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2096" t="inlineStr"/>
+      <c r="G2096" t="inlineStr"/>
     </row>
     <row r="2097" ht="15.75" customHeight="1" s="19">
       <c r="A2097" s="8" t="n">
@@ -61637,6 +62021,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2097" t="inlineStr"/>
+      <c r="G2097" t="inlineStr"/>
     </row>
     <row r="2098" ht="15.75" customHeight="1" s="19">
       <c r="A2098" s="8" t="n">
@@ -61662,6 +62048,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2098" t="inlineStr"/>
+      <c r="G2098" t="inlineStr"/>
     </row>
     <row r="2099" ht="15.75" customHeight="1" s="19">
       <c r="A2099" s="8" t="n">
@@ -61687,6 +62075,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2099" t="inlineStr"/>
+      <c r="G2099" t="inlineStr"/>
     </row>
     <row r="2100" ht="15.75" customHeight="1" s="19">
       <c r="A2100" s="8" t="n">
@@ -61712,6 +62102,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2100" t="inlineStr">
+        <is>
+          <t>+54 11 7729-4728</t>
+        </is>
+      </c>
+      <c r="G2100" t="inlineStr">
+        <is>
+          <t>http://casafirpo.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="2101" ht="15.75" customHeight="1" s="19">
       <c r="A2101" s="8" t="n">
@@ -61737,6 +62137,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2101" t="inlineStr"/>
+      <c r="G2101" t="inlineStr"/>
     </row>
     <row r="2102" ht="15.75" customHeight="1" s="19">
       <c r="A2102" s="8" t="n">
@@ -61762,6 +62164,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2102" t="inlineStr"/>
+      <c r="G2102" t="inlineStr"/>
     </row>
     <row r="2103" ht="15.75" customHeight="1" s="19">
       <c r="A2103" s="8" t="n">

--- a/PUNTOS_DE_VENTA_completado.xlsx
+++ b/PUNTOS_DE_VENTA_completado.xlsx
@@ -62191,6 +62191,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2103" t="inlineStr"/>
+      <c r="G2103" t="inlineStr"/>
     </row>
     <row r="2104" ht="15.75" customHeight="1" s="19">
       <c r="A2104" s="8" t="n">
@@ -62216,6 +62218,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2104" t="inlineStr"/>
+      <c r="G2104" t="inlineStr"/>
     </row>
     <row r="2105" ht="15.75" customHeight="1" s="19">
       <c r="A2105" s="8" t="n">
@@ -62241,6 +62245,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2105" t="inlineStr">
+        <is>
+          <t>+54 11 5434-3503</t>
+        </is>
+      </c>
+      <c r="G2105" t="inlineStr"/>
     </row>
     <row r="2106" ht="15.75" customHeight="1" s="19">
       <c r="A2106" s="8" t="n">
@@ -62266,6 +62276,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2106" t="inlineStr"/>
+      <c r="G2106" t="inlineStr"/>
     </row>
     <row r="2107" ht="15.75" customHeight="1" s="19">
       <c r="A2107" s="8" t="n">
@@ -62291,6 +62303,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2107" t="inlineStr"/>
+      <c r="G2107" t="inlineStr"/>
     </row>
     <row r="2108" ht="15.75" customHeight="1" s="19">
       <c r="A2108" s="8" t="n">
@@ -62316,6 +62330,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2108" t="inlineStr"/>
+      <c r="G2108" t="inlineStr"/>
     </row>
     <row r="2109" ht="15.75" customHeight="1" s="19">
       <c r="A2109" s="8" t="n">
@@ -62341,6 +62357,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2109" t="inlineStr"/>
+      <c r="G2109" t="inlineStr"/>
     </row>
     <row r="2110" ht="15.75" customHeight="1" s="19">
       <c r="A2110" s="8" t="n">
@@ -62366,6 +62384,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2110" t="inlineStr"/>
+      <c r="G2110" t="inlineStr"/>
     </row>
     <row r="2111" ht="15.75" customHeight="1" s="19">
       <c r="A2111" s="8" t="n">
@@ -62391,6 +62411,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2111" t="inlineStr"/>
+      <c r="G2111" t="inlineStr"/>
     </row>
     <row r="2112" ht="15.75" customHeight="1" s="19">
       <c r="A2112" s="8" t="n">
@@ -62416,6 +62438,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2112" t="inlineStr"/>
+      <c r="G2112" t="inlineStr"/>
     </row>
     <row r="2113" ht="15.75" customHeight="1" s="19">
       <c r="A2113" s="8" t="n">
@@ -62441,6 +62465,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2113" t="inlineStr"/>
+      <c r="G2113" t="inlineStr"/>
     </row>
     <row r="2114" ht="15.75" customHeight="1" s="19">
       <c r="A2114" s="8" t="n">
@@ -62466,6 +62492,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2114" t="inlineStr"/>
+      <c r="G2114" t="inlineStr"/>
     </row>
     <row r="2115" ht="15.75" customHeight="1" s="19">
       <c r="A2115" s="8" t="n">
@@ -62491,6 +62519,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2115" t="inlineStr"/>
+      <c r="G2115" t="inlineStr"/>
     </row>
     <row r="2116" ht="15.75" customHeight="1" s="19">
       <c r="A2116" s="8" t="n">
@@ -62516,6 +62546,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2116" t="inlineStr"/>
+      <c r="G2116" t="inlineStr"/>
     </row>
     <row r="2117" ht="15.75" customHeight="1" s="19">
       <c r="A2117" s="8" t="n">
@@ -62541,6 +62573,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2117" t="inlineStr"/>
+      <c r="G2117" t="inlineStr"/>
     </row>
     <row r="2118" ht="15.75" customHeight="1" s="19">
       <c r="A2118" s="8" t="n">
@@ -62566,6 +62600,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F2118" t="inlineStr"/>
+      <c r="G2118" t="inlineStr"/>
     </row>
     <row r="2119" ht="15.75" customHeight="1" s="19">
       <c r="A2119" s="8" t="n">
@@ -62591,6 +62627,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2119" t="inlineStr"/>
+      <c r="G2119" t="inlineStr"/>
     </row>
     <row r="2120" ht="15.75" customHeight="1" s="19">
       <c r="A2120" s="8" t="n">
@@ -62616,6 +62654,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2120" t="inlineStr"/>
+      <c r="G2120" t="inlineStr"/>
     </row>
     <row r="2121" ht="15.75" customHeight="1" s="19">
       <c r="A2121" s="8" t="n">
@@ -62641,6 +62681,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2121" t="inlineStr"/>
+      <c r="G2121" t="inlineStr"/>
     </row>
     <row r="2122" ht="15.75" customHeight="1" s="19">
       <c r="A2122" s="8" t="n">
@@ -62666,6 +62708,12 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F2122" t="inlineStr">
+        <is>
+          <t>+54 11 4629-2457</t>
+        </is>
+      </c>
+      <c r="G2122" t="inlineStr"/>
     </row>
     <row r="2123" ht="15.75" customHeight="1" s="19">
       <c r="A2123" s="8" t="n">
@@ -62691,6 +62739,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2123" t="inlineStr">
+        <is>
+          <t>+54 11 5296-5200</t>
+        </is>
+      </c>
+      <c r="G2123" t="inlineStr">
+        <is>
+          <t>http://argentina.bosch.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="2124" ht="15.75" customHeight="1" s="19">
       <c r="A2124" s="8" t="n">
@@ -62716,6 +62774,12 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2124" t="inlineStr">
+        <is>
+          <t>+54 11 3201-7519</t>
+        </is>
+      </c>
+      <c r="G2124" t="inlineStr"/>
     </row>
     <row r="2125" ht="15.75" customHeight="1" s="19">
       <c r="A2125" s="8" t="n">
@@ -62741,6 +62805,12 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2125" t="inlineStr">
+        <is>
+          <t>+54 11 4627-4833</t>
+        </is>
+      </c>
+      <c r="G2125" t="inlineStr"/>
     </row>
     <row r="2126" ht="15.75" customHeight="1" s="19">
       <c r="A2126" s="8" t="n">
@@ -62766,6 +62836,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2126" t="inlineStr"/>
+      <c r="G2126" t="inlineStr"/>
     </row>
     <row r="2127" ht="15.75" customHeight="1" s="19">
       <c r="A2127" s="8" t="n">
@@ -62791,6 +62863,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2127" t="inlineStr"/>
+      <c r="G2127" t="inlineStr"/>
     </row>
     <row r="2128" ht="15.75" customHeight="1" s="19">
       <c r="A2128" s="8" t="n">
@@ -62816,6 +62890,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2128" t="inlineStr">
+        <is>
+          <t>+54 11 4840-2039</t>
+        </is>
+      </c>
+      <c r="G2128" t="inlineStr">
+        <is>
+          <t>http://www.sanitariosgabriel.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="2129" ht="15.75" customHeight="1" s="19">
       <c r="A2129" s="8" t="n">
@@ -62841,6 +62925,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2129" t="inlineStr"/>
+      <c r="G2129" t="inlineStr"/>
     </row>
     <row r="2130" ht="15.75" customHeight="1" s="19">
       <c r="A2130" s="8" t="n">
@@ -62866,6 +62952,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2130" t="inlineStr"/>
+      <c r="G2130" t="inlineStr"/>
     </row>
     <row r="2131" ht="15.75" customHeight="1" s="19">
       <c r="A2131" s="8" t="n">
@@ -62891,6 +62979,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2131" t="inlineStr"/>
+      <c r="G2131" t="inlineStr"/>
     </row>
     <row r="2132" ht="15.75" customHeight="1" s="19">
       <c r="A2132" s="8" t="n">
@@ -62916,6 +63006,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2132" t="inlineStr"/>
+      <c r="G2132" t="inlineStr"/>
     </row>
     <row r="2133" ht="15.75" customHeight="1" s="19">
       <c r="A2133" s="8" t="n">
@@ -62941,6 +63033,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2133" t="inlineStr"/>
+      <c r="G2133" t="inlineStr"/>
     </row>
     <row r="2134" ht="15.75" customHeight="1" s="19">
       <c r="A2134" s="8" t="n">
@@ -62966,6 +63060,12 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2134" t="inlineStr">
+        <is>
+          <t>+54 11 4443-0513</t>
+        </is>
+      </c>
+      <c r="G2134" t="inlineStr"/>
     </row>
     <row r="2135" ht="15.75" customHeight="1" s="19">
       <c r="A2135" s="8" t="n">
@@ -62991,6 +63091,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F2135" t="inlineStr"/>
+      <c r="G2135" t="inlineStr"/>
     </row>
     <row r="2136" ht="15.75" customHeight="1" s="19">
       <c r="A2136" s="8" t="n">
@@ -63016,6 +63118,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2136" t="inlineStr"/>
+      <c r="G2136" t="inlineStr"/>
     </row>
     <row r="2137" ht="15.75" customHeight="1" s="19">
       <c r="A2137" s="8" t="n">
@@ -63041,6 +63145,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2137" t="inlineStr"/>
+      <c r="G2137" t="inlineStr"/>
     </row>
     <row r="2138" ht="15.75" customHeight="1" s="19">
       <c r="A2138" s="8" t="n">
@@ -63066,6 +63172,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2138" t="inlineStr"/>
+      <c r="G2138" t="inlineStr"/>
     </row>
     <row r="2139" ht="15.75" customHeight="1" s="19">
       <c r="A2139" s="8" t="n">
@@ -63091,6 +63199,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2139" t="inlineStr"/>
+      <c r="G2139" t="inlineStr"/>
     </row>
     <row r="2140" ht="15.75" customHeight="1" s="19">
       <c r="A2140" s="8" t="n">
@@ -63116,6 +63226,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2140" t="inlineStr"/>
+      <c r="G2140" t="inlineStr"/>
     </row>
     <row r="2141" ht="15.75" customHeight="1" s="19">
       <c r="A2141" s="8" t="n">
@@ -63141,6 +63253,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2141" t="inlineStr"/>
+      <c r="G2141" t="inlineStr"/>
     </row>
     <row r="2142" ht="15.75" customHeight="1" s="19">
       <c r="A2142" s="8" t="n">
@@ -63166,6 +63280,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2142" t="inlineStr"/>
+      <c r="G2142" t="inlineStr"/>
     </row>
     <row r="2143" ht="15.75" customHeight="1" s="19">
       <c r="A2143" s="8" t="n">
@@ -63191,6 +63307,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2143" t="inlineStr"/>
+      <c r="G2143" t="inlineStr"/>
     </row>
     <row r="2144" ht="15.75" customHeight="1" s="19">
       <c r="A2144" s="8" t="n">
@@ -63216,6 +63334,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2144" t="inlineStr"/>
+      <c r="G2144" t="inlineStr"/>
     </row>
     <row r="2145" ht="15.75" customHeight="1" s="19">
       <c r="A2145" s="8" t="n">
@@ -63241,6 +63361,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2145" t="inlineStr"/>
+      <c r="G2145" t="inlineStr"/>
     </row>
     <row r="2146" ht="15.75" customHeight="1" s="19">
       <c r="A2146" s="8" t="n">
@@ -63266,6 +63388,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2146" t="inlineStr"/>
+      <c r="G2146" t="inlineStr"/>
     </row>
     <row r="2147" ht="15.75" customHeight="1" s="19">
       <c r="A2147" s="8" t="n">
@@ -63291,6 +63415,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2147" t="inlineStr"/>
+      <c r="G2147" t="inlineStr"/>
     </row>
     <row r="2148" ht="15.75" customHeight="1" s="19">
       <c r="A2148" s="8" t="n">
@@ -63316,6 +63442,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2148" t="inlineStr"/>
+      <c r="G2148" t="inlineStr"/>
     </row>
     <row r="2149" ht="15.75" customHeight="1" s="19">
       <c r="A2149" s="8" t="n">
@@ -63341,6 +63469,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2149" t="inlineStr"/>
+      <c r="G2149" t="inlineStr"/>
     </row>
     <row r="2150" ht="15.75" customHeight="1" s="19">
       <c r="A2150" s="8" t="n">
@@ -63366,6 +63496,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2150" t="inlineStr">
+        <is>
+          <t>+54 11 2463-7514</t>
+        </is>
+      </c>
+      <c r="G2150" t="inlineStr"/>
     </row>
     <row r="2151" ht="15.75" customHeight="1" s="19">
       <c r="A2151" s="8" t="n">
@@ -63391,6 +63527,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2151" t="inlineStr"/>
+      <c r="G2151" t="inlineStr"/>
     </row>
     <row r="2152" ht="15.75" customHeight="1" s="19">
       <c r="A2152" s="8" t="n">
@@ -63416,6 +63554,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2152" t="inlineStr"/>
+      <c r="G2152" t="inlineStr"/>
     </row>
     <row r="2153" ht="15.75" customHeight="1" s="19">
       <c r="A2153" s="8" t="n">

--- a/PUNTOS_DE_VENTA_completado.xlsx
+++ b/PUNTOS_DE_VENTA_completado.xlsx
@@ -63581,6 +63581,12 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2153" t="inlineStr">
+        <is>
+          <t>+54 11 4662-3307</t>
+        </is>
+      </c>
+      <c r="G2153" t="inlineStr"/>
     </row>
     <row r="2154" ht="15.75" customHeight="1" s="19">
       <c r="A2154" s="8" t="n">
@@ -63606,6 +63612,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2154" t="inlineStr"/>
+      <c r="G2154" t="inlineStr"/>
     </row>
     <row r="2155" ht="15.75" customHeight="1" s="19">
       <c r="A2155" s="8" t="n">
@@ -63631,6 +63639,16 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2155" t="inlineStr">
+        <is>
+          <t>+54 11 4452-6046</t>
+        </is>
+      </c>
+      <c r="G2155" t="inlineStr">
+        <is>
+          <t>http://facebook.com/aidayadriana</t>
+        </is>
+      </c>
     </row>
     <row r="2156" ht="15.75" customHeight="1" s="19">
       <c r="A2156" s="8" t="n">
@@ -63656,6 +63674,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2156" t="inlineStr"/>
+      <c r="G2156" t="inlineStr"/>
     </row>
     <row r="2157" ht="15.75" customHeight="1" s="19">
       <c r="A2157" s="8" t="n">
@@ -63681,6 +63701,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F2157" t="inlineStr"/>
+      <c r="G2157" t="inlineStr"/>
     </row>
     <row r="2158" ht="15.75" customHeight="1" s="19">
       <c r="A2158" s="8" t="n">
@@ -63706,6 +63728,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F2158" t="inlineStr"/>
+      <c r="G2158" t="inlineStr"/>
     </row>
     <row r="2159" ht="15.75" customHeight="1" s="19">
       <c r="A2159" s="8" t="n">
@@ -63731,6 +63755,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2159" t="inlineStr"/>
+      <c r="G2159" t="inlineStr"/>
     </row>
     <row r="2160" ht="15.75" customHeight="1" s="19">
       <c r="A2160" s="8" t="n">
@@ -63756,6 +63782,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2160" t="inlineStr"/>
+      <c r="G2160" t="inlineStr"/>
     </row>
     <row r="2161" ht="15.75" customHeight="1" s="19">
       <c r="A2161" s="8" t="n">
@@ -63781,6 +63809,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2161" t="inlineStr"/>
+      <c r="G2161" t="inlineStr"/>
     </row>
     <row r="2162" ht="15.75" customHeight="1" s="19">
       <c r="A2162" s="8" t="n">
@@ -63806,6 +63836,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2162" t="inlineStr"/>
+      <c r="G2162" t="inlineStr"/>
     </row>
     <row r="2163" ht="15.75" customHeight="1" s="19">
       <c r="A2163" s="8" t="n">
@@ -63831,6 +63863,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2163" t="inlineStr">
+        <is>
+          <t>+54 11 2463-7514</t>
+        </is>
+      </c>
+      <c r="G2163" t="inlineStr"/>
     </row>
     <row r="2164" ht="15.75" customHeight="1" s="19">
       <c r="A2164" s="8" t="n">
@@ -63856,6 +63894,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2164" t="inlineStr">
+        <is>
+          <t>+54 11 4231-5950</t>
+        </is>
+      </c>
+      <c r="G2164" t="inlineStr">
+        <is>
+          <t>https://www.laboratorioarregui.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="2165" ht="15.75" customHeight="1" s="19">
       <c r="A2165" s="8" t="n">
@@ -63881,6 +63929,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2165" t="inlineStr">
+        <is>
+          <t>+54 11 5625-4003</t>
+        </is>
+      </c>
+      <c r="G2165" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vivero.loscipreses</t>
+        </is>
+      </c>
     </row>
     <row r="2166" ht="15.75" customHeight="1" s="19">
       <c r="A2166" s="8" t="n">
@@ -63906,6 +63964,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2166" t="inlineStr"/>
+      <c r="G2166" t="inlineStr"/>
     </row>
     <row r="2167" ht="15.75" customHeight="1" s="19">
       <c r="A2167" s="8" t="n">
@@ -63931,6 +63991,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2167" t="inlineStr"/>
+      <c r="G2167" t="inlineStr"/>
     </row>
     <row r="2168" ht="15.75" customHeight="1" s="19">
       <c r="A2168" s="8" t="n">
@@ -63956,6 +64018,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2168" t="inlineStr"/>
+      <c r="G2168" t="inlineStr"/>
     </row>
     <row r="2169" ht="15.75" customHeight="1" s="19">
       <c r="A2169" s="8" t="n">
@@ -63981,6 +64045,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2169" t="inlineStr">
+        <is>
+          <t>+54 11 4260-5125</t>
+        </is>
+      </c>
+      <c r="G2169" t="inlineStr"/>
     </row>
     <row r="2170" ht="15.75" customHeight="1" s="19">
       <c r="A2170" s="8" t="n">
@@ -64006,6 +64076,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2170" t="inlineStr">
+        <is>
+          <t>+54 11 3029-8443</t>
+        </is>
+      </c>
+      <c r="G2170" t="inlineStr">
+        <is>
+          <t>http://dra-analiaveronicaruizdiaz.com/</t>
+        </is>
+      </c>
     </row>
     <row r="2171" ht="15.75" customHeight="1" s="19">
       <c r="A2171" s="8" t="n">
@@ -64031,6 +64111,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2171" t="inlineStr"/>
+      <c r="G2171" t="inlineStr"/>
     </row>
     <row r="2172" ht="15.75" customHeight="1" s="19">
       <c r="A2172" s="8" t="n">
@@ -64056,6 +64138,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2172" t="inlineStr"/>
+      <c r="G2172" t="inlineStr"/>
     </row>
     <row r="2173" ht="15.75" customHeight="1" s="19">
       <c r="A2173" s="8" t="n">
@@ -64081,6 +64165,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2173" t="inlineStr"/>
+      <c r="G2173" t="inlineStr"/>
     </row>
     <row r="2174" ht="15.75" customHeight="1" s="19">
       <c r="A2174" s="8" t="n">
@@ -64106,6 +64192,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2174" t="inlineStr"/>
+      <c r="G2174" t="inlineStr"/>
     </row>
     <row r="2175" ht="15.75" customHeight="1" s="19">
       <c r="A2175" s="8" t="n">
@@ -64131,6 +64219,16 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2175" t="inlineStr">
+        <is>
+          <t>+54 46459000</t>
+        </is>
+      </c>
+      <c r="G2175" t="inlineStr">
+        <is>
+          <t>http://www.imasalud.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="2176" ht="15.75" customHeight="1" s="19">
       <c r="A2176" s="8" t="n">
@@ -64156,6 +64254,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2176" t="inlineStr"/>
+      <c r="G2176" t="inlineStr"/>
     </row>
     <row r="2177" ht="15.75" customHeight="1" s="19">
       <c r="A2177" s="8" t="n">
@@ -64181,6 +64281,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2177" t="inlineStr"/>
+      <c r="G2177" t="inlineStr"/>
     </row>
     <row r="2178" ht="15.75" customHeight="1" s="19">
       <c r="A2178" s="8" t="n">
@@ -64206,6 +64308,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2178" t="inlineStr"/>
+      <c r="G2178" t="inlineStr"/>
     </row>
     <row r="2179" ht="15.75" customHeight="1" s="19">
       <c r="A2179" s="8" t="n">
@@ -64231,6 +64335,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2179" t="inlineStr"/>
+      <c r="G2179" t="inlineStr"/>
     </row>
     <row r="2180" ht="15.75" customHeight="1" s="19">
       <c r="A2180" s="8" t="n">
@@ -64256,6 +64362,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2180" t="inlineStr"/>
+      <c r="G2180" t="inlineStr"/>
     </row>
     <row r="2181" ht="15.75" customHeight="1" s="19">
       <c r="A2181" s="8" t="n">
@@ -64281,6 +64389,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2181" t="inlineStr"/>
+      <c r="G2181" t="inlineStr"/>
     </row>
     <row r="2182" ht="15.75" customHeight="1" s="19">
       <c r="A2182" s="8" t="n">
@@ -64306,6 +64416,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2182" t="inlineStr"/>
+      <c r="G2182" t="inlineStr"/>
     </row>
     <row r="2183" ht="15.75" customHeight="1" s="19">
       <c r="A2183" s="8" t="n">
@@ -64331,6 +64443,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2183" t="inlineStr">
+        <is>
+          <t>+54 11 6082-9621</t>
+        </is>
+      </c>
+      <c r="G2183" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_lasrecetasdesofia?igsh=cmZ0MGk4d2p5d2J1&amp;utm_source=qr</t>
+        </is>
+      </c>
     </row>
     <row r="2184" ht="15.75" customHeight="1" s="19">
       <c r="A2184" s="8" t="n">
@@ -64356,6 +64478,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2184" t="inlineStr"/>
+      <c r="G2184" t="inlineStr"/>
     </row>
     <row r="2185" ht="15.75" customHeight="1" s="19">
       <c r="A2185" s="8" t="n">
@@ -64381,6 +64505,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2185" t="inlineStr"/>
+      <c r="G2185" t="inlineStr"/>
     </row>
     <row r="2186" ht="15.75" customHeight="1" s="19">
       <c r="A2186" s="8" t="n">
@@ -64406,6 +64532,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2186" t="inlineStr">
+        <is>
+          <t>+54 11 4243-1297</t>
+        </is>
+      </c>
+      <c r="G2186" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sixtofernandez614/</t>
+        </is>
+      </c>
     </row>
     <row r="2187" ht="15.75" customHeight="1" s="19">
       <c r="A2187" s="8" t="n">
@@ -64431,6 +64567,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2187" t="inlineStr"/>
+      <c r="G2187" t="inlineStr"/>
     </row>
     <row r="2188" ht="15.75" customHeight="1" s="19">
       <c r="A2188" s="8" t="n">
@@ -64456,6 +64594,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2188" t="inlineStr"/>
+      <c r="G2188" t="inlineStr"/>
     </row>
     <row r="2189" ht="15.75" customHeight="1" s="19">
       <c r="A2189" s="8" t="n">
@@ -64481,6 +64621,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2189" t="inlineStr"/>
+      <c r="G2189" t="inlineStr"/>
     </row>
     <row r="2190" ht="15.75" customHeight="1" s="19">
       <c r="A2190" s="8" t="n">
@@ -64506,6 +64648,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2190" t="inlineStr"/>
+      <c r="G2190" t="inlineStr"/>
     </row>
     <row r="2191" ht="15.75" customHeight="1" s="19">
       <c r="A2191" s="8" t="n">
@@ -64531,6 +64675,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2191" t="inlineStr"/>
+      <c r="G2191" t="inlineStr"/>
     </row>
     <row r="2192" ht="15.75" customHeight="1" s="19">
       <c r="A2192" s="8" t="n">
@@ -64556,6 +64702,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2192" t="inlineStr">
+        <is>
+          <t>+54 3327 48-1134</t>
+        </is>
+      </c>
+      <c r="G2192" t="inlineStr">
+        <is>
+          <t>http://www.distribuidoraeguibar.com/</t>
+        </is>
+      </c>
     </row>
     <row r="2193" ht="15.75" customHeight="1" s="19">
       <c r="A2193" s="8" t="n">
@@ -64581,6 +64737,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2193" t="inlineStr"/>
+      <c r="G2193" t="inlineStr"/>
     </row>
     <row r="2194" ht="15.75" customHeight="1" s="19">
       <c r="A2194" s="8" t="n">
@@ -64606,6 +64764,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2194" t="inlineStr"/>
+      <c r="G2194" t="inlineStr"/>
     </row>
     <row r="2195" ht="15.75" customHeight="1" s="19">
       <c r="A2195" s="8" t="n">
@@ -64631,6 +64791,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2195" t="inlineStr"/>
+      <c r="G2195" t="inlineStr"/>
     </row>
     <row r="2196" ht="15.75" customHeight="1" s="19">
       <c r="A2196" s="8" t="n">
@@ -64656,6 +64818,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2196" t="inlineStr"/>
+      <c r="G2196" t="inlineStr"/>
     </row>
     <row r="2197" ht="15.75" customHeight="1" s="19">
       <c r="A2197" s="8" t="n">
@@ -64681,6 +64845,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F2197" t="inlineStr"/>
+      <c r="G2197" t="inlineStr"/>
     </row>
     <row r="2198" ht="15.75" customHeight="1" s="19">
       <c r="A2198" s="8" t="n">
@@ -64706,6 +64872,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2198" t="inlineStr"/>
+      <c r="G2198" t="inlineStr"/>
     </row>
     <row r="2199" ht="15.75" customHeight="1" s="19">
       <c r="A2199" s="8" t="n">
@@ -64731,6 +64899,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2199" t="inlineStr">
+        <is>
+          <t>+54 11 3134-0905</t>
+        </is>
+      </c>
+      <c r="G2199" t="inlineStr"/>
     </row>
     <row r="2200" ht="15.75" customHeight="1" s="19">
       <c r="A2200" s="8" t="n">
@@ -64756,6 +64930,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2200" t="inlineStr"/>
+      <c r="G2200" t="inlineStr"/>
     </row>
     <row r="2201" ht="15.75" customHeight="1" s="19">
       <c r="A2201" s="8" t="n">
@@ -64781,6 +64957,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2201" t="inlineStr"/>
+      <c r="G2201" t="inlineStr"/>
     </row>
     <row r="2202" ht="15.75" customHeight="1" s="19">
       <c r="A2202" s="8" t="n">
@@ -64806,6 +64984,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2202" t="inlineStr">
+        <is>
+          <t>+54 348 447-1594</t>
+        </is>
+      </c>
+      <c r="G2202" t="inlineStr"/>
     </row>
     <row r="2203" ht="15.75" customHeight="1" s="19">
       <c r="A2203" s="8" t="n">

--- a/PUNTOS_DE_VENTA_completado.xlsx
+++ b/PUNTOS_DE_VENTA_completado.xlsx
@@ -65015,6 +65015,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2203" t="inlineStr"/>
+      <c r="G2203" t="inlineStr"/>
     </row>
     <row r="2204" ht="15.75" customHeight="1" s="19">
       <c r="A2204" s="8" t="n">
@@ -65040,6 +65042,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2204" t="inlineStr"/>
+      <c r="G2204" t="inlineStr"/>
     </row>
     <row r="2205" ht="15.75" customHeight="1" s="19">
       <c r="A2205" s="8" t="n">
@@ -65065,6 +65069,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2205" t="inlineStr">
+        <is>
+          <t>+54 11 2193-2654</t>
+        </is>
+      </c>
+      <c r="G2205" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lacuevacell?igsh=cWxxOTU2bnV5N3ho</t>
+        </is>
+      </c>
     </row>
     <row r="2206" ht="15.75" customHeight="1" s="19">
       <c r="A2206" s="8" t="n">
@@ -65090,6 +65104,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2206" t="inlineStr">
+        <is>
+          <t>+54 11 5693-6220</t>
+        </is>
+      </c>
+      <c r="G2206" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/repuestos1199/</t>
+        </is>
+      </c>
     </row>
     <row r="2207" ht="15.75" customHeight="1" s="19">
       <c r="A2207" s="8" t="n">
@@ -65115,6 +65139,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2207" t="inlineStr"/>
+      <c r="G2207" t="inlineStr"/>
     </row>
     <row r="2208" ht="15.75" customHeight="1" s="19">
       <c r="A2208" s="8" t="n">
@@ -65140,6 +65166,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2208" t="inlineStr"/>
+      <c r="G2208" t="inlineStr">
+        <is>
+          <t>http://www.pmi.com/</t>
+        </is>
+      </c>
     </row>
     <row r="2209" ht="15.75" customHeight="1" s="19">
       <c r="A2209" s="8" t="n">
@@ -65165,6 +65197,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2209" t="inlineStr"/>
+      <c r="G2209" t="inlineStr"/>
     </row>
     <row r="2210" ht="15.75" customHeight="1" s="19">
       <c r="A2210" s="8" t="n">
@@ -65190,6 +65224,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2210" t="inlineStr">
+        <is>
+          <t>+54 2320 64-9021</t>
+        </is>
+      </c>
+      <c r="G2210" t="inlineStr">
+        <is>
+          <t>http://www.unpaz.edu.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="2211" ht="15.75" customHeight="1" s="19">
       <c r="A2211" s="8" t="n">
@@ -65215,6 +65259,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2211" t="inlineStr">
+        <is>
+          <t>+54 2320 64-9021</t>
+        </is>
+      </c>
+      <c r="G2211" t="inlineStr">
+        <is>
+          <t>http://www.unpaz.edu.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="2212" ht="15.75" customHeight="1" s="19">
       <c r="A2212" s="8" t="n">
@@ -65240,6 +65294,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2212" t="inlineStr"/>
+      <c r="G2212" t="inlineStr"/>
     </row>
     <row r="2213" ht="15.75" customHeight="1" s="19">
       <c r="A2213" s="8" t="n">
@@ -65265,6 +65321,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2213" t="inlineStr">
+        <is>
+          <t>+54 2320 64-9021</t>
+        </is>
+      </c>
+      <c r="G2213" t="inlineStr">
+        <is>
+          <t>http://www.unpaz.edu.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="2214" ht="15.75" customHeight="1" s="19">
       <c r="A2214" s="8" t="n">
@@ -65290,6 +65356,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2214" t="inlineStr"/>
+      <c r="G2214" t="inlineStr"/>
     </row>
     <row r="2215" ht="15.75" customHeight="1" s="19">
       <c r="A2215" s="8" t="n">
@@ -65315,6 +65383,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2215" t="inlineStr"/>
+      <c r="G2215" t="inlineStr"/>
     </row>
     <row r="2216" ht="15.75" customHeight="1" s="19">
       <c r="A2216" s="8" t="n">
@@ -65340,6 +65410,16 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F2216" t="inlineStr">
+        <is>
+          <t>+54 11 5010-9795</t>
+        </is>
+      </c>
+      <c r="G2216" t="inlineStr">
+        <is>
+          <t>http://www.estebanecheverria.gob.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="2217" ht="15.75" customHeight="1" s="19">
       <c r="A2217" s="8" t="n">
@@ -65365,6 +65445,12 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2217" t="inlineStr">
+        <is>
+          <t>+54 11 6098-4948</t>
+        </is>
+      </c>
+      <c r="G2217" t="inlineStr"/>
     </row>
     <row r="2218" ht="15.75" customHeight="1" s="19">
       <c r="A2218" s="8" t="n">
@@ -65390,6 +65476,12 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2218" t="inlineStr">
+        <is>
+          <t>+54 11 4272-8663</t>
+        </is>
+      </c>
+      <c r="G2218" t="inlineStr"/>
     </row>
     <row r="2219" ht="15.75" customHeight="1" s="19">
       <c r="A2219" s="8" t="n">
@@ -65415,6 +65507,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2219" t="inlineStr"/>
+      <c r="G2219" t="inlineStr"/>
     </row>
     <row r="2220" ht="15.75" customHeight="1" s="19">
       <c r="A2220" s="8" t="n">
@@ -65440,6 +65534,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2220" t="inlineStr"/>
+      <c r="G2220" t="inlineStr"/>
     </row>
     <row r="2221" ht="15.75" customHeight="1" s="19">
       <c r="A2221" s="8" t="n">
@@ -65465,6 +65561,16 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2221" t="inlineStr">
+        <is>
+          <t>+54 11 4744-4263</t>
+        </is>
+      </c>
+      <c r="G2221" t="inlineStr">
+        <is>
+          <t>https://floreriahector.wixsite.com/floreshectorvictoria</t>
+        </is>
+      </c>
     </row>
     <row r="2222" ht="15.75" customHeight="1" s="19">
       <c r="A2222" s="8" t="n">
@@ -65490,6 +65596,16 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2222" t="inlineStr">
+        <is>
+          <t>+54 11 3155-0983</t>
+        </is>
+      </c>
+      <c r="G2222" t="inlineStr">
+        <is>
+          <t>https://wa.me/5491131550983</t>
+        </is>
+      </c>
     </row>
     <row r="2223" ht="15.75" customHeight="1" s="19">
       <c r="A2223" s="8" t="n">
@@ -65515,6 +65631,12 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2223" t="inlineStr">
+        <is>
+          <t>+54 2225 42-7070</t>
+        </is>
+      </c>
+      <c r="G2223" t="inlineStr"/>
     </row>
     <row r="2224" ht="15.75" customHeight="1" s="19">
       <c r="A2224" s="8" t="n">
@@ -65540,6 +65662,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2224" t="inlineStr"/>
+      <c r="G2224" t="inlineStr"/>
     </row>
     <row r="2225" ht="15.75" customHeight="1" s="19">
       <c r="A2225" s="8" t="n">
@@ -65565,6 +65689,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2225" t="inlineStr"/>
+      <c r="G2225" t="inlineStr"/>
     </row>
     <row r="2226" ht="15.75" customHeight="1" s="19">
       <c r="A2226" s="8" t="n">
@@ -65590,6 +65716,12 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2226" t="inlineStr"/>
+      <c r="G2226" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/elgranerodeburzaco/</t>
+        </is>
+      </c>
     </row>
     <row r="2227" ht="15.75" customHeight="1" s="19">
       <c r="A2227" s="8" t="n">
@@ -65615,6 +65747,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2227" t="inlineStr"/>
+      <c r="G2227" t="inlineStr"/>
     </row>
     <row r="2228" ht="15.75" customHeight="1" s="19">
       <c r="A2228" s="8" t="n">
@@ -65640,6 +65774,16 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2228" t="inlineStr">
+        <is>
+          <t>+54 11 7145-5420</t>
+        </is>
+      </c>
+      <c r="G2228" t="inlineStr">
+        <is>
+          <t>https://www.iluminacioncastex.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="2229" ht="15.75" customHeight="1" s="19">
       <c r="A2229" s="8" t="n">
@@ -65665,6 +65809,12 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2229" t="inlineStr">
+        <is>
+          <t>+54 2224 43-2311</t>
+        </is>
+      </c>
+      <c r="G2229" t="inlineStr"/>
     </row>
     <row r="2230" ht="15.75" customHeight="1" s="19">
       <c r="A2230" s="8" t="n">
@@ -65690,6 +65840,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F2230" t="inlineStr"/>
+      <c r="G2230" t="inlineStr"/>
     </row>
     <row r="2231" ht="15.75" customHeight="1" s="19">
       <c r="A2231" s="8" t="n">
@@ -65715,6 +65867,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2231" t="inlineStr"/>
+      <c r="G2231" t="inlineStr"/>
     </row>
     <row r="2232" ht="15.75" customHeight="1" s="19">
       <c r="A2232" s="8" t="n">
@@ -65740,6 +65894,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2232" t="inlineStr"/>
+      <c r="G2232" t="inlineStr"/>
     </row>
     <row r="2233" ht="15.75" customHeight="1" s="19">
       <c r="A2233" s="8" t="n">
@@ -65765,6 +65921,12 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F2233" t="inlineStr">
+        <is>
+          <t>+54 2224 47-8791</t>
+        </is>
+      </c>
+      <c r="G2233" t="inlineStr"/>
     </row>
     <row r="2234" ht="15.75" customHeight="1" s="19">
       <c r="A2234" s="8" t="n">
@@ -65790,6 +65952,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2234" t="inlineStr"/>
+      <c r="G2234" t="inlineStr"/>
     </row>
     <row r="2235" ht="15.75" customHeight="1" s="19">
       <c r="A2235" s="8" t="n">
@@ -65815,6 +65979,16 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F2235" t="inlineStr">
+        <is>
+          <t>+54 11 2673-2145</t>
+        </is>
+      </c>
+      <c r="G2235" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/p/Frigor%25C3%25ADfico-fas-100028127245632/</t>
+        </is>
+      </c>
     </row>
     <row r="2236" ht="15.75" customHeight="1" s="19">
       <c r="A2236" s="8" t="n">
@@ -65840,6 +66014,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2236" t="inlineStr"/>
+      <c r="G2236" t="inlineStr"/>
     </row>
     <row r="2237" ht="15.75" customHeight="1" s="19">
       <c r="A2237" s="8" t="n">
@@ -65865,6 +66041,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2237" t="inlineStr">
+        <is>
+          <t>+54 11 3850-6869</t>
+        </is>
+      </c>
+      <c r="G2237" t="inlineStr">
+        <is>
+          <t>https://heladosdaniel.com/</t>
+        </is>
+      </c>
     </row>
     <row r="2238" ht="15.75" customHeight="1" s="19">
       <c r="A2238" s="8" t="n">
@@ -65890,6 +66076,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2238" t="inlineStr">
+        <is>
+          <t>+54 11 4201-1166</t>
+        </is>
+      </c>
+      <c r="G2238" t="inlineStr">
+        <is>
+          <t>http://www.centromoya.com/</t>
+        </is>
+      </c>
     </row>
     <row r="2239" ht="15.75" customHeight="1" s="19">
       <c r="A2239" s="8" t="n">
@@ -65915,6 +66111,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2239" t="inlineStr"/>
+      <c r="G2239" t="inlineStr"/>
     </row>
     <row r="2240" ht="15.75" customHeight="1" s="19">
       <c r="A2240" s="8" t="n">
@@ -65940,6 +66138,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2240" t="inlineStr"/>
+      <c r="G2240" t="inlineStr"/>
     </row>
     <row r="2241" ht="15.75" customHeight="1" s="19">
       <c r="A2241" s="8" t="n">
@@ -65965,6 +66165,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2241" t="inlineStr"/>
+      <c r="G2241" t="inlineStr"/>
     </row>
     <row r="2242" ht="15.75" customHeight="1" s="19">
       <c r="A2242" s="8" t="n">
@@ -65990,6 +66192,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2242" t="inlineStr"/>
+      <c r="G2242" t="inlineStr"/>
     </row>
     <row r="2243" ht="15.75" customHeight="1" s="19">
       <c r="A2243" s="8" t="n">
@@ -66015,6 +66219,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2243" t="inlineStr"/>
+      <c r="G2243" t="inlineStr"/>
     </row>
     <row r="2244" ht="15.75" customHeight="1" s="19">
       <c r="A2244" s="8" t="n">
@@ -66040,6 +66246,16 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2244" t="inlineStr">
+        <is>
+          <t>+54 11 2154-1049</t>
+        </is>
+      </c>
+      <c r="G2244" t="inlineStr">
+        <is>
+          <t>https://www.twinlok-abrojo.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="2245" ht="15.75" customHeight="1" s="19">
       <c r="A2245" s="8" t="n">
@@ -66065,6 +66281,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2245" t="inlineStr"/>
+      <c r="G2245" t="inlineStr"/>
     </row>
     <row r="2246" ht="15.75" customHeight="1" s="19">
       <c r="A2246" s="8" t="n">
@@ -66090,6 +66308,12 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F2246" t="inlineStr">
+        <is>
+          <t>+54 2224 52-4323</t>
+        </is>
+      </c>
+      <c r="G2246" t="inlineStr"/>
     </row>
     <row r="2247" ht="15.75" customHeight="1" s="19">
       <c r="A2247" s="8" t="n">
@@ -66115,6 +66339,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F2247" t="inlineStr"/>
+      <c r="G2247" t="inlineStr"/>
     </row>
     <row r="2248" ht="15.75" customHeight="1" s="19">
       <c r="A2248" s="8" t="n">
@@ -66140,6 +66366,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2248" t="inlineStr"/>
+      <c r="G2248" t="inlineStr"/>
     </row>
     <row r="2249" ht="15.75" customHeight="1" s="19">
       <c r="A2249" s="8" t="n">
@@ -66165,6 +66393,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2249" t="inlineStr"/>
+      <c r="G2249" t="inlineStr"/>
     </row>
     <row r="2250" ht="15.75" customHeight="1" s="19">
       <c r="A2250" s="8" t="n">
@@ -66190,6 +66420,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2250" t="inlineStr">
+        <is>
+          <t>+54 11 3464-2959</t>
+        </is>
+      </c>
+      <c r="G2250" t="inlineStr"/>
     </row>
     <row r="2251" ht="15.75" customHeight="1" s="19">
       <c r="A2251" s="8" t="n">
@@ -66215,6 +66451,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2251" t="inlineStr"/>
+      <c r="G2251" t="inlineStr"/>
     </row>
     <row r="2252" ht="15.75" customHeight="1" s="19">
       <c r="A2252" s="8" t="n">
@@ -66240,6 +66478,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2252" t="inlineStr"/>
+      <c r="G2252" t="inlineStr"/>
     </row>
     <row r="2253" ht="15.75" customHeight="1" s="19">
       <c r="A2253" s="8" t="n">
@@ -66265,6 +66505,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2253" t="inlineStr"/>
+      <c r="G2253" t="inlineStr"/>
     </row>
     <row r="2254" ht="15.75" customHeight="1" s="19">
       <c r="A2254" s="8" t="n">
@@ -66290,6 +66532,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F2254" t="inlineStr"/>
+      <c r="G2254" t="inlineStr"/>
     </row>
     <row r="2255" ht="15.75" customHeight="1" s="19">
       <c r="A2255" s="8" t="n">
@@ -66315,6 +66559,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2255" t="inlineStr"/>
+      <c r="G2255" t="inlineStr"/>
     </row>
     <row r="2256" ht="15.75" customHeight="1" s="19">
       <c r="A2256" s="8" t="n">
@@ -66340,6 +66586,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2256" t="inlineStr"/>
+      <c r="G2256" t="inlineStr"/>
     </row>
     <row r="2257" ht="15.75" customHeight="1" s="19">
       <c r="A2257" s="8" t="n">
@@ -66365,6 +66613,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2257" t="inlineStr"/>
+      <c r="G2257" t="inlineStr"/>
     </row>
     <row r="2258" ht="15.75" customHeight="1" s="19">
       <c r="A2258" s="8" t="n">
@@ -66390,6 +66640,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2258" t="inlineStr"/>
+      <c r="G2258" t="inlineStr"/>
     </row>
     <row r="2259" ht="15.75" customHeight="1" s="19">
       <c r="A2259" s="8" t="n">
@@ -66415,6 +66667,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2259" t="inlineStr">
+        <is>
+          <t>+54 11 2152-4200</t>
+        </is>
+      </c>
+      <c r="G2259" t="inlineStr">
+        <is>
+          <t>https://www.tortugasopenmall.com/</t>
+        </is>
+      </c>
     </row>
     <row r="2260" ht="15.75" customHeight="1" s="19">
       <c r="A2260" s="8" t="n">
@@ -66440,6 +66702,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F2260" t="inlineStr"/>
+      <c r="G2260" t="inlineStr"/>
     </row>
     <row r="2261" ht="15.75" customHeight="1" s="19">
       <c r="A2261" s="8" t="n">
@@ -66465,6 +66729,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2261" t="inlineStr"/>
+      <c r="G2261" t="inlineStr"/>
     </row>
     <row r="2262" ht="15.75" customHeight="1" s="19">
       <c r="A2262" s="8" t="n">
@@ -66490,6 +66756,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2262" t="inlineStr">
+        <is>
+          <t>+54 11 4418-6407</t>
+        </is>
+      </c>
+      <c r="G2262" t="inlineStr">
+        <is>
+          <t>https://wa.me/message/7TI433GAI5RCI1</t>
+        </is>
+      </c>
     </row>
     <row r="2263" ht="15.75" customHeight="1" s="19">
       <c r="A2263" s="8" t="n">
@@ -66515,6 +66791,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2263" t="inlineStr"/>
+      <c r="G2263" t="inlineStr"/>
     </row>
     <row r="2264" ht="15.75" customHeight="1" s="19">
       <c r="A2264" s="8" t="n">
@@ -66540,6 +66818,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2264" t="inlineStr"/>
+      <c r="G2264" t="inlineStr"/>
     </row>
     <row r="2265" ht="15.75" customHeight="1" s="19">
       <c r="A2265" s="8" t="n">
@@ -66565,6 +66845,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2265" t="inlineStr"/>
+      <c r="G2265" t="inlineStr"/>
     </row>
     <row r="2266" ht="15.75" customHeight="1" s="19">
       <c r="A2266" s="8" t="n">
@@ -66590,6 +66872,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2266" t="inlineStr"/>
+      <c r="G2266" t="inlineStr"/>
     </row>
     <row r="2267" ht="15.75" customHeight="1" s="19">
       <c r="A2267" s="8" t="n">
@@ -66615,6 +66899,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2267" t="inlineStr"/>
+      <c r="G2267" t="inlineStr"/>
     </row>
     <row r="2268" ht="15.75" customHeight="1" s="19">
       <c r="A2268" s="8" t="n">
@@ -66640,6 +66926,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2268" t="inlineStr"/>
+      <c r="G2268" t="inlineStr"/>
     </row>
     <row r="2269" ht="15.75" customHeight="1" s="19">
       <c r="A2269" s="8" t="n">
@@ -66665,6 +66953,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2269" t="inlineStr"/>
+      <c r="G2269" t="inlineStr"/>
     </row>
     <row r="2270" ht="15.75" customHeight="1" s="19">
       <c r="A2270" s="8" t="n">
@@ -66690,6 +66980,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2270" t="inlineStr"/>
+      <c r="G2270" t="inlineStr"/>
     </row>
     <row r="2271" ht="15.75" customHeight="1" s="19">
       <c r="A2271" s="8" t="n">
@@ -66715,6 +67007,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2271" t="inlineStr"/>
+      <c r="G2271" t="inlineStr"/>
     </row>
     <row r="2272" ht="15.75" customHeight="1" s="19">
       <c r="A2272" s="8" t="n">
@@ -66738,6 +67032,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2272" t="inlineStr"/>
+      <c r="G2272" t="inlineStr"/>
     </row>
     <row r="2273" ht="15.75" customHeight="1" s="19">
       <c r="A2273" s="8" t="n">
@@ -66763,6 +67059,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2273" t="inlineStr"/>
+      <c r="G2273" t="inlineStr"/>
     </row>
     <row r="2274" ht="15.75" customHeight="1" s="19">
       <c r="A2274" s="8" t="n">
@@ -66786,6 +67084,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2274" t="inlineStr">
+        <is>
+          <t>+54 11 5304-1372</t>
+        </is>
+      </c>
+      <c r="G2274" t="inlineStr">
+        <is>
+          <t>http://www.condolucivial.com/</t>
+        </is>
+      </c>
     </row>
     <row r="2275" ht="15.75" customHeight="1" s="19">
       <c r="A2275" s="8" t="n">
@@ -66811,6 +67119,16 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2275" t="inlineStr">
+        <is>
+          <t>+54 11 2644-3737</t>
+        </is>
+      </c>
+      <c r="G2275" t="inlineStr">
+        <is>
+          <t>http://super-interlaken.s3-website-sa-east-1.amazonaws.com/</t>
+        </is>
+      </c>
     </row>
     <row r="2276" ht="15.75" customHeight="1" s="19">
       <c r="A2276" s="8" t="n">
@@ -66834,6 +67152,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2276" t="inlineStr"/>
+      <c r="G2276" t="inlineStr"/>
     </row>
     <row r="2277" ht="15.75" customHeight="1" s="19">
       <c r="A2277" s="8" t="n">
@@ -66857,6 +67177,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2277" t="inlineStr"/>
+      <c r="G2277" t="inlineStr"/>
     </row>
     <row r="2278" ht="15.75" customHeight="1" s="19">
       <c r="A2278" s="8" t="n">
@@ -66882,6 +67204,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2278" t="inlineStr"/>
+      <c r="G2278" t="inlineStr"/>
     </row>
     <row r="2279" ht="15.75" customHeight="1" s="19">
       <c r="A2279" s="8" t="n">
@@ -66907,6 +67231,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2279" t="inlineStr"/>
+      <c r="G2279" t="inlineStr"/>
     </row>
     <row r="2280" ht="15.75" customHeight="1" s="19">
       <c r="A2280" s="8" t="n">
@@ -66932,6 +67258,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2280" t="inlineStr"/>
+      <c r="G2280" t="inlineStr"/>
     </row>
     <row r="2281" ht="15.75" customHeight="1" s="19">
       <c r="A2281" s="8" t="n">
@@ -66957,6 +67285,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2281" t="inlineStr"/>
+      <c r="G2281" t="inlineStr"/>
     </row>
     <row r="2282" ht="15.75" customHeight="1" s="19">
       <c r="A2282" s="8" t="n">
@@ -66982,6 +67312,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2282" t="inlineStr"/>
+      <c r="G2282" t="inlineStr"/>
     </row>
     <row r="2283" ht="15.75" customHeight="1" s="19">
       <c r="A2283" s="8" t="n">
@@ -67007,6 +67339,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2283" t="inlineStr"/>
+      <c r="G2283" t="inlineStr"/>
     </row>
     <row r="2284" ht="15.75" customHeight="1" s="19">
       <c r="A2284" s="8" t="n">
@@ -67032,6 +67366,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2284" t="inlineStr"/>
+      <c r="G2284" t="inlineStr"/>
     </row>
     <row r="2285" ht="15.75" customHeight="1" s="19">
       <c r="A2285" s="8" t="n">
@@ -67057,6 +67393,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2285" t="inlineStr">
+        <is>
+          <t>+54 11 3484-1690</t>
+        </is>
+      </c>
+      <c r="G2285" t="inlineStr"/>
     </row>
     <row r="2286" ht="15.75" customHeight="1" s="19">
       <c r="A2286" s="8" t="n">
@@ -67082,6 +67424,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2286" t="inlineStr">
+        <is>
+          <t>+54 11 4233-4558</t>
+        </is>
+      </c>
+      <c r="G2286" t="inlineStr"/>
     </row>
     <row r="2287" ht="15.75" customHeight="1" s="19">
       <c r="A2287" s="8" t="n">
@@ -67107,6 +67455,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2287" t="inlineStr"/>
+      <c r="G2287" t="inlineStr"/>
     </row>
     <row r="2288" ht="15.75" customHeight="1" s="19">
       <c r="A2288" s="8" t="n">
@@ -67132,6 +67482,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2288" t="inlineStr"/>
+      <c r="G2288" t="inlineStr"/>
     </row>
     <row r="2289" ht="15.75" customHeight="1" s="19">
       <c r="A2289" s="8" t="n">
@@ -67157,6 +67509,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2289" t="inlineStr"/>
+      <c r="G2289" t="inlineStr"/>
     </row>
     <row r="2290" ht="15.75" customHeight="1" s="19">
       <c r="A2290" s="8" t="n">
@@ -67182,6 +67536,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2290" t="inlineStr"/>
+      <c r="G2290" t="inlineStr"/>
     </row>
     <row r="2291" ht="15.75" customHeight="1" s="19">
       <c r="A2291" s="8" t="n">
@@ -67207,6 +67563,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2291" t="inlineStr"/>
+      <c r="G2291" t="inlineStr"/>
     </row>
     <row r="2292" ht="15.75" customHeight="1" s="19">
       <c r="A2292" s="8" t="n">
@@ -67232,6 +67590,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2292" t="inlineStr"/>
+      <c r="G2292" t="inlineStr"/>
     </row>
     <row r="2293" ht="15.75" customHeight="1" s="19">
       <c r="A2293" s="8" t="n">
@@ -67257,6 +67617,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2293" t="inlineStr"/>
+      <c r="G2293" t="inlineStr"/>
     </row>
     <row r="2294" ht="15.75" customHeight="1" s="19">
       <c r="A2294" s="8" t="n">
@@ -67282,6 +67644,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2294" t="inlineStr"/>
+      <c r="G2294" t="inlineStr"/>
     </row>
     <row r="2295" ht="15.75" customHeight="1" s="19">
       <c r="A2295" s="8" t="n">
@@ -67307,6 +67671,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2295" t="inlineStr"/>
+      <c r="G2295" t="inlineStr"/>
     </row>
     <row r="2296" ht="15.75" customHeight="1" s="19">
       <c r="A2296" s="8" t="n">
@@ -67332,6 +67698,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2296" t="inlineStr"/>
+      <c r="G2296" t="inlineStr"/>
     </row>
     <row r="2297" ht="15.75" customHeight="1" s="19">
       <c r="A2297" s="8" t="n">
@@ -67357,6 +67725,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2297" t="inlineStr"/>
+      <c r="G2297" t="inlineStr"/>
     </row>
     <row r="2298" ht="15.75" customHeight="1" s="19">
       <c r="A2298" s="8" t="n">
@@ -67382,6 +67752,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2298" t="inlineStr">
+        <is>
+          <t>+54 220 485-3061</t>
+        </is>
+      </c>
+      <c r="G2298" t="inlineStr"/>
     </row>
     <row r="2299" ht="15.75" customHeight="1" s="19">
       <c r="A2299" s="8" t="n">
@@ -67407,6 +67783,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2299" t="inlineStr"/>
+      <c r="G2299" t="inlineStr"/>
     </row>
     <row r="2300" ht="15.75" customHeight="1" s="19">
       <c r="A2300" s="8" t="n">
@@ -67432,6 +67810,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2300" t="inlineStr"/>
+      <c r="G2300" t="inlineStr"/>
     </row>
     <row r="2301" ht="15.75" customHeight="1" s="19">
       <c r="A2301" s="8" t="n">
@@ -67457,6 +67837,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F2301" t="inlineStr"/>
+      <c r="G2301" t="inlineStr"/>
     </row>
     <row r="2302" ht="15.75" customHeight="1" s="19">
       <c r="A2302" s="8" t="n">
@@ -67482,6 +67864,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2302" t="inlineStr"/>
+      <c r="G2302" t="inlineStr"/>
     </row>
     <row r="2303" ht="15.75" customHeight="1" s="19">
       <c r="A2303" s="8" t="n">

--- a/PUNTOS_DE_VENTA_completado.xlsx
+++ b/PUNTOS_DE_VENTA_completado.xlsx
@@ -67891,6 +67891,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F2303" t="inlineStr"/>
+      <c r="G2303" t="inlineStr"/>
     </row>
     <row r="2304" ht="15.75" customHeight="1" s="19">
       <c r="A2304" s="8" t="n">
@@ -67916,6 +67918,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2304" t="inlineStr"/>
+      <c r="G2304" t="inlineStr"/>
     </row>
     <row r="2305" ht="15.75" customHeight="1" s="19">
       <c r="A2305" s="8" t="n">
@@ -67941,6 +67945,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2305" t="inlineStr"/>
+      <c r="G2305" t="inlineStr"/>
     </row>
     <row r="2306" ht="15.75" customHeight="1" s="19">
       <c r="A2306" s="8" t="n">
@@ -67966,6 +67972,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2306" t="inlineStr">
+        <is>
+          <t>+54 11 5834-4390</t>
+        </is>
+      </c>
+      <c r="G2306" t="inlineStr"/>
     </row>
     <row r="2307" ht="15.75" customHeight="1" s="19">
       <c r="A2307" s="8" t="n">
@@ -67991,6 +68003,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2307" t="inlineStr"/>
+      <c r="G2307" t="inlineStr"/>
     </row>
     <row r="2308" ht="15.75" customHeight="1" s="19">
       <c r="A2308" s="8" t="n">
@@ -68016,6 +68030,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2308" t="inlineStr">
+        <is>
+          <t>+54 11 4768-0367</t>
+        </is>
+      </c>
+      <c r="G2308" t="inlineStr"/>
     </row>
     <row r="2309" ht="15.75" customHeight="1" s="19">
       <c r="A2309" s="8" t="n">
@@ -68041,6 +68061,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2309" t="inlineStr"/>
+      <c r="G2309" t="inlineStr"/>
     </row>
     <row r="2310" ht="15.75" customHeight="1" s="19">
       <c r="A2310" s="8" t="n">
@@ -68066,6 +68088,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2310" t="inlineStr"/>
+      <c r="G2310" t="inlineStr"/>
     </row>
     <row r="2311" ht="15.75" customHeight="1" s="19">
       <c r="A2311" s="8" t="n">
@@ -68091,6 +68115,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2311" t="inlineStr">
+        <is>
+          <t>+54 11 3192-6122</t>
+        </is>
+      </c>
+      <c r="G2311" t="inlineStr">
+        <is>
+          <t>https://www.petcompanyweb.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="2312" ht="15.75" customHeight="1" s="19">
       <c r="A2312" s="8" t="n">
@@ -68116,6 +68150,12 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F2312" t="inlineStr"/>
+      <c r="G2312" t="inlineStr">
+        <is>
+          <t>http://instagram.com/lasorellinapizzabar</t>
+        </is>
+      </c>
     </row>
     <row r="2313" ht="15.75" customHeight="1" s="19">
       <c r="A2313" s="8" t="n">
@@ -68141,6 +68181,16 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F2313" t="inlineStr">
+        <is>
+          <t>+54 11 4553-5821</t>
+        </is>
+      </c>
+      <c r="G2313" t="inlineStr">
+        <is>
+          <t>http://www.totalpet.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="2314" ht="15.75" customHeight="1" s="19">
       <c r="A2314" s="8" t="n">
@@ -68166,6 +68216,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F2314" t="inlineStr"/>
+      <c r="G2314" t="inlineStr"/>
     </row>
     <row r="2315" ht="15.75" customHeight="1" s="19">
       <c r="A2315" s="8" t="n">
@@ -68191,6 +68243,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F2315" t="inlineStr"/>
+      <c r="G2315" t="inlineStr"/>
     </row>
     <row r="2316" ht="15.75" customHeight="1" s="19">
       <c r="A2316" s="8" t="n">
@@ -68216,6 +68270,12 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2316" t="inlineStr">
+        <is>
+          <t>+54 11 4763-7446</t>
+        </is>
+      </c>
+      <c r="G2316" t="inlineStr"/>
     </row>
     <row r="2317" ht="15.75" customHeight="1" s="19">
       <c r="A2317" s="8" t="n">
@@ -68241,6 +68301,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2317" t="inlineStr"/>
+      <c r="G2317" t="inlineStr"/>
     </row>
     <row r="2318" ht="15.75" customHeight="1" s="19">
       <c r="A2318" s="8" t="n">
@@ -68266,6 +68328,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2318" t="inlineStr"/>
+      <c r="G2318" t="inlineStr"/>
     </row>
     <row r="2319" ht="15.75" customHeight="1" s="19">
       <c r="A2319" s="8" t="n">
@@ -68291,6 +68355,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2319" t="inlineStr"/>
+      <c r="G2319" t="inlineStr"/>
     </row>
     <row r="2320" ht="15.75" customHeight="1" s="19">
       <c r="A2320" s="8" t="n">
@@ -68316,6 +68382,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2320" t="inlineStr"/>
+      <c r="G2320" t="inlineStr"/>
     </row>
     <row r="2321" ht="15.75" customHeight="1" s="19">
       <c r="A2321" s="8" t="n">
@@ -68341,6 +68409,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F2321" t="inlineStr">
+        <is>
+          <t>+54 11 3947-6437</t>
+        </is>
+      </c>
+      <c r="G2321" t="inlineStr"/>
     </row>
     <row r="2322" ht="15.75" customHeight="1" s="19">
       <c r="A2322" s="8" t="n">
@@ -68366,6 +68440,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2322" t="inlineStr"/>
+      <c r="G2322" t="inlineStr"/>
     </row>
     <row r="2323" ht="15.75" customHeight="1" s="19">
       <c r="A2323" s="8" t="n">
@@ -68391,6 +68467,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2323" t="inlineStr">
+        <is>
+          <t>+54 11 4403-7289</t>
+        </is>
+      </c>
+      <c r="G2323" t="inlineStr">
+        <is>
+          <t>https://instagram.com/acuario.burbujas?utm_medium=copy_link</t>
+        </is>
+      </c>
     </row>
     <row r="2324" ht="15.75" customHeight="1" s="19">
       <c r="A2324" s="8" t="n">
@@ -68416,6 +68502,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2324" t="inlineStr"/>
+      <c r="G2324" t="inlineStr"/>
     </row>
     <row r="2325" ht="15.75" customHeight="1" s="19">
       <c r="A2325" s="8" t="n">
@@ -68441,6 +68529,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2325" t="inlineStr"/>
+      <c r="G2325" t="inlineStr"/>
     </row>
     <row r="2326" ht="15.75" customHeight="1" s="19">
       <c r="A2326" s="8" t="n">
@@ -68466,6 +68556,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2326" t="inlineStr"/>
+      <c r="G2326" t="inlineStr"/>
     </row>
     <row r="2327" ht="15.75" customHeight="1" s="19">
       <c r="A2327" s="8" t="n">
@@ -68491,6 +68583,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2327" t="inlineStr"/>
+      <c r="G2327" t="inlineStr"/>
     </row>
     <row r="2328" ht="15.75" customHeight="1" s="19">
       <c r="A2328" s="8" t="n">
@@ -68516,6 +68610,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2328" t="inlineStr"/>
+      <c r="G2328" t="inlineStr"/>
     </row>
     <row r="2329" ht="15.75" customHeight="1" s="19">
       <c r="A2329" s="8" t="n">
@@ -68541,6 +68637,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2329" t="inlineStr"/>
+      <c r="G2329" t="inlineStr"/>
     </row>
     <row r="2330" ht="15.75" customHeight="1" s="19">
       <c r="A2330" s="8" t="n">
@@ -68566,6 +68664,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2330" t="inlineStr"/>
+      <c r="G2330" t="inlineStr"/>
     </row>
     <row r="2331" ht="15.75" customHeight="1" s="19">
       <c r="A2331" s="8" t="n">
@@ -68591,6 +68691,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2331" t="inlineStr"/>
+      <c r="G2331" t="inlineStr"/>
     </row>
     <row r="2332" ht="15.75" customHeight="1" s="19">
       <c r="A2332" s="8" t="n">
@@ -68616,6 +68718,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2332" t="inlineStr"/>
+      <c r="G2332" t="inlineStr"/>
     </row>
     <row r="2333" ht="15.75" customHeight="1" s="19">
       <c r="A2333" s="8" t="n">
@@ -68641,6 +68745,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2333" t="inlineStr"/>
+      <c r="G2333" t="inlineStr"/>
     </row>
     <row r="2334" ht="15.75" customHeight="1" s="19">
       <c r="A2334" s="8" t="n">
@@ -68666,6 +68772,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2334" t="inlineStr"/>
+      <c r="G2334" t="inlineStr"/>
     </row>
     <row r="2335" ht="15.75" customHeight="1" s="19">
       <c r="A2335" s="8" t="n">
@@ -68691,6 +68799,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2335" t="inlineStr"/>
+      <c r="G2335" t="inlineStr"/>
     </row>
     <row r="2336" ht="15.75" customHeight="1" s="19">
       <c r="A2336" s="8" t="n">
@@ -68716,6 +68826,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2336" t="inlineStr">
+        <is>
+          <t>+54 3757 42-3103</t>
+        </is>
+      </c>
+      <c r="G2336" t="inlineStr"/>
     </row>
     <row r="2337" ht="15.75" customHeight="1" s="19">
       <c r="A2337" s="8" t="n">
@@ -68741,6 +68857,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F2337" t="inlineStr"/>
+      <c r="G2337" t="inlineStr"/>
     </row>
     <row r="2338" ht="15.75" customHeight="1" s="19">
       <c r="A2338" s="8" t="n">
@@ -68766,6 +68884,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2338" t="inlineStr">
+        <is>
+          <t>+54 9 11 3644-2092</t>
+        </is>
+      </c>
+      <c r="G2338" t="inlineStr"/>
     </row>
     <row r="2339" ht="15.75" customHeight="1" s="19">
       <c r="A2339" s="8" t="n">
@@ -68791,6 +68915,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2339" t="inlineStr"/>
+      <c r="G2339" t="inlineStr"/>
     </row>
     <row r="2340" ht="15.75" customHeight="1" s="19">
       <c r="A2340" s="8" t="n">
@@ -68816,6 +68942,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2340" t="inlineStr"/>
+      <c r="G2340" t="inlineStr"/>
     </row>
     <row r="2341" ht="15.75" customHeight="1" s="19">
       <c r="A2341" s="8" t="n">
@@ -68841,6 +68969,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2341" t="inlineStr">
+        <is>
+          <t>+54 11 3221-0729</t>
+        </is>
+      </c>
+      <c r="G2341" t="inlineStr">
+        <is>
+          <t>http://www.tyrco.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="2342" ht="15.75" customHeight="1" s="19">
       <c r="A2342" s="8" t="n">
@@ -68866,6 +69004,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2342" t="inlineStr"/>
+      <c r="G2342" t="inlineStr"/>
     </row>
     <row r="2343" ht="15.75" customHeight="1" s="19">
       <c r="A2343" s="8" t="n">
@@ -68891,6 +69031,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2343" t="inlineStr">
+        <is>
+          <t>+54 11 2353-6291</t>
+        </is>
+      </c>
+      <c r="G2343" t="inlineStr">
+        <is>
+          <t>http://www.electroyhogar.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="2344" ht="15.75" customHeight="1" s="19">
       <c r="A2344" s="8" t="n">
@@ -68916,6 +69066,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2344" t="inlineStr"/>
+      <c r="G2344" t="inlineStr"/>
     </row>
     <row r="2345" ht="15.75" customHeight="1" s="19">
       <c r="A2345" s="8" t="n">
@@ -68941,6 +69093,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2345" t="inlineStr"/>
+      <c r="G2345" t="inlineStr"/>
     </row>
     <row r="2346" ht="15.75" customHeight="1" s="19">
       <c r="A2346" s="8" t="n">
@@ -68966,6 +69120,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2346" t="inlineStr"/>
+      <c r="G2346" t="inlineStr"/>
     </row>
     <row r="2347" ht="15.75" customHeight="1" s="19">
       <c r="A2347" s="8" t="n">
@@ -68991,6 +69147,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2347" t="inlineStr"/>
+      <c r="G2347" t="inlineStr"/>
     </row>
     <row r="2348" ht="15.75" customHeight="1" s="19">
       <c r="A2348" s="8" t="n">
@@ -69016,6 +69174,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2348" t="inlineStr"/>
+      <c r="G2348" t="inlineStr"/>
     </row>
     <row r="2349" ht="15.75" customHeight="1" s="19">
       <c r="A2349" s="8" t="n">
@@ -69041,6 +69201,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2349" t="inlineStr"/>
+      <c r="G2349" t="inlineStr"/>
     </row>
     <row r="2350" ht="15.75" customHeight="1" s="19">
       <c r="A2350" s="8" t="n">
@@ -69066,6 +69228,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2350" t="inlineStr"/>
+      <c r="G2350" t="inlineStr"/>
     </row>
     <row r="2351" ht="15.75" customHeight="1" s="19">
       <c r="A2351" s="8" t="n">
@@ -69091,6 +69255,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2351" t="inlineStr"/>
+      <c r="G2351" t="inlineStr"/>
     </row>
     <row r="2352" ht="15.75" customHeight="1" s="19">
       <c r="A2352" s="8" t="n">
@@ -69116,6 +69282,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2352" t="inlineStr"/>
+      <c r="G2352" t="inlineStr"/>
     </row>
     <row r="2353" ht="15.75" customHeight="1" s="19">
       <c r="A2353" s="8" t="n">

--- a/PUNTOS_DE_VENTA_completado.xlsx
+++ b/PUNTOS_DE_VENTA_completado.xlsx
@@ -69309,6 +69309,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2353" t="inlineStr"/>
+      <c r="G2353" t="inlineStr"/>
     </row>
     <row r="2354" ht="15.75" customHeight="1" s="19">
       <c r="A2354" s="8" t="n">
@@ -69334,6 +69336,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2354" t="inlineStr"/>
+      <c r="G2354" t="inlineStr"/>
     </row>
     <row r="2355" ht="15.75" customHeight="1" s="19">
       <c r="A2355" s="8" t="n">
@@ -69359,6 +69363,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2355" t="inlineStr"/>
+      <c r="G2355" t="inlineStr"/>
     </row>
     <row r="2356" ht="15.75" customHeight="1" s="19">
       <c r="A2356" s="8" t="n">
@@ -69384,6 +69390,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2356" t="inlineStr"/>
+      <c r="G2356" t="inlineStr"/>
     </row>
     <row r="2357" ht="15.75" customHeight="1" s="19">
       <c r="A2357" s="8" t="n">
@@ -69409,6 +69417,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2357" t="inlineStr"/>
+      <c r="G2357" t="inlineStr"/>
     </row>
     <row r="2358" ht="15.75" customHeight="1" s="19">
       <c r="A2358" s="8" t="n">
@@ -69434,6 +69444,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2358" t="inlineStr"/>
+      <c r="G2358" t="inlineStr"/>
     </row>
     <row r="2359" ht="15.75" customHeight="1" s="19">
       <c r="A2359" s="8" t="n">
@@ -69459,6 +69471,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2359" t="inlineStr"/>
+      <c r="G2359" t="inlineStr"/>
     </row>
     <row r="2360" ht="15.75" customHeight="1" s="19">
       <c r="A2360" s="8" t="n">
@@ -69484,6 +69498,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2360" t="inlineStr"/>
+      <c r="G2360" t="inlineStr"/>
     </row>
     <row r="2361" ht="15.75" customHeight="1" s="19">
       <c r="A2361" s="8" t="n">
@@ -69509,6 +69525,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2361" t="inlineStr">
+        <is>
+          <t>+54 9 11 5419-4907</t>
+        </is>
+      </c>
+      <c r="G2361" t="inlineStr">
+        <is>
+          <t>https://boulan.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="2362" ht="15.75" customHeight="1" s="19">
       <c r="A2362" s="8" t="n">
@@ -69534,6 +69560,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2362" t="inlineStr"/>
+      <c r="G2362" t="inlineStr"/>
     </row>
     <row r="2363" ht="15.75" customHeight="1" s="19">
       <c r="A2363" s="8" t="n">
@@ -69559,6 +69587,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2363" t="inlineStr"/>
+      <c r="G2363" t="inlineStr">
+        <is>
+          <t>https://www.hgranelli.com/edificio-newen-ii-en-muiz-san-miguel-emprendimiento-28</t>
+        </is>
+      </c>
     </row>
     <row r="2364" ht="15.75" customHeight="1" s="19">
       <c r="A2364" s="8" t="n">
@@ -69584,6 +69618,16 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2364" t="inlineStr">
+        <is>
+          <t>+54 11 4584-6446</t>
+        </is>
+      </c>
+      <c r="G2364" t="inlineStr">
+        <is>
+          <t>http://www.dichiaramotors.com/</t>
+        </is>
+      </c>
     </row>
     <row r="2365" ht="15.75" customHeight="1" s="19">
       <c r="A2365" s="8" t="n">
@@ -69609,6 +69653,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2365" t="inlineStr"/>
+      <c r="G2365" t="inlineStr"/>
     </row>
     <row r="2366" ht="15.75" customHeight="1" s="19">
       <c r="A2366" s="8" t="n">
@@ -69634,6 +69680,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2366" t="inlineStr"/>
+      <c r="G2366" t="inlineStr"/>
     </row>
     <row r="2367" ht="15.75" customHeight="1" s="19">
       <c r="A2367" s="8" t="n">
@@ -69659,6 +69707,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2367" t="inlineStr"/>
+      <c r="G2367" t="inlineStr"/>
     </row>
     <row r="2368" ht="15.75" customHeight="1" s="19">
       <c r="A2368" s="8" t="n">
@@ -69684,6 +69734,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2368" t="inlineStr">
+        <is>
+          <t>+54 11 5960-9576</t>
+        </is>
+      </c>
+      <c r="G2368" t="inlineStr"/>
     </row>
     <row r="2369" ht="15.75" customHeight="1" s="19">
       <c r="A2369" s="8" t="n">
@@ -69709,6 +69765,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2369" t="inlineStr"/>
+      <c r="G2369" t="inlineStr"/>
     </row>
     <row r="2370" ht="15.75" customHeight="1" s="19">
       <c r="A2370" s="8" t="n">
@@ -69734,6 +69792,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2370" t="inlineStr"/>
+      <c r="G2370" t="inlineStr"/>
     </row>
     <row r="2371" ht="15.75" customHeight="1" s="19">
       <c r="A2371" s="8" t="n">
@@ -69759,6 +69819,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2371" t="inlineStr">
+        <is>
+          <t>+54 11 4661-6670</t>
+        </is>
+      </c>
+      <c r="G2371" t="inlineStr"/>
     </row>
     <row r="2372" ht="15.75" customHeight="1" s="19">
       <c r="A2372" s="8" t="n">
@@ -69784,6 +69850,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2372" t="inlineStr">
+        <is>
+          <t>+54 11 6441-9686</t>
+        </is>
+      </c>
+      <c r="G2372" t="inlineStr">
+        <is>
+          <t>https://casarossottimascot.wixsite.com/casarossotti</t>
+        </is>
+      </c>
     </row>
     <row r="2373" ht="15.75" customHeight="1" s="19">
       <c r="A2373" s="8" t="n">
@@ -69809,6 +69885,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2373" t="inlineStr"/>
+      <c r="G2373" t="inlineStr"/>
     </row>
     <row r="2374" ht="15.75" customHeight="1" s="19">
       <c r="A2374" s="8" t="n">
@@ -69834,6 +69912,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2374" t="inlineStr"/>
+      <c r="G2374" t="inlineStr"/>
     </row>
     <row r="2375" ht="15.75" customHeight="1" s="19">
       <c r="A2375" s="8" t="n">
@@ -69859,6 +69939,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2375" t="inlineStr"/>
+      <c r="G2375" t="inlineStr"/>
     </row>
     <row r="2376" ht="15.75" customHeight="1" s="19">
       <c r="A2376" s="8" t="n">
@@ -69884,6 +69966,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2376" t="inlineStr">
+        <is>
+          <t>+54 11 4296-4606</t>
+        </is>
+      </c>
+      <c r="G2376" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jacquet.mateo</t>
+        </is>
+      </c>
     </row>
     <row r="2377" ht="15.75" customHeight="1" s="19">
       <c r="A2377" s="8" t="n">
@@ -69909,6 +70001,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2377" t="inlineStr"/>
+      <c r="G2377" t="inlineStr"/>
     </row>
     <row r="2378" ht="15.75" customHeight="1" s="19">
       <c r="A2378" s="8" t="n">
@@ -69934,6 +70028,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2378" t="inlineStr"/>
+      <c r="G2378" t="inlineStr"/>
     </row>
     <row r="2379" ht="15.75" customHeight="1" s="19">
       <c r="A2379" s="8" t="n">
@@ -69959,6 +70055,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2379" t="inlineStr"/>
+      <c r="G2379" t="inlineStr"/>
     </row>
     <row r="2380" ht="15.75" customHeight="1" s="19">
       <c r="A2380" s="8" t="n">
@@ -69984,6 +70082,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2380" t="inlineStr"/>
+      <c r="G2380" t="inlineStr"/>
     </row>
     <row r="2381" ht="15.75" customHeight="1" s="19">
       <c r="A2381" s="8" t="n">
@@ -70009,6 +70109,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2381" t="inlineStr">
+        <is>
+          <t>+54 9 11 7371-3108</t>
+        </is>
+      </c>
+      <c r="G2381" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ceramica.catedral/</t>
+        </is>
+      </c>
     </row>
     <row r="2382" ht="15.75" customHeight="1" s="19">
       <c r="A2382" s="8" t="n">
@@ -70034,6 +70144,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2382" t="inlineStr"/>
+      <c r="G2382" t="inlineStr"/>
     </row>
     <row r="2383" ht="15.75" customHeight="1" s="19">
       <c r="A2383" s="8" t="n">
@@ -70059,6 +70171,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2383" t="inlineStr">
+        <is>
+          <t>+54 9 11 5842-8855</t>
+        </is>
+      </c>
+      <c r="G2383" t="inlineStr">
+        <is>
+          <t>https://veterinariabyf.com.ar/petshop/</t>
+        </is>
+      </c>
     </row>
     <row r="2384" ht="15.75" customHeight="1" s="19">
       <c r="A2384" s="8" t="n">
@@ -70084,6 +70206,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2384" t="inlineStr">
+        <is>
+          <t>+54 11 3987-4150</t>
+        </is>
+      </c>
+      <c r="G2384" t="inlineStr">
+        <is>
+          <t>https://www.aeropuertosargentina.com/ezeiza</t>
+        </is>
+      </c>
     </row>
     <row r="2385" ht="15.75" customHeight="1" s="19">
       <c r="A2385" s="8" t="n">
@@ -70109,6 +70241,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2385" t="inlineStr"/>
+      <c r="G2385" t="inlineStr"/>
     </row>
     <row r="2386" ht="15.75" customHeight="1" s="19">
       <c r="A2386" s="8" t="n">
@@ -70134,6 +70268,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2386" t="inlineStr"/>
+      <c r="G2386" t="inlineStr"/>
     </row>
     <row r="2387" ht="15.75" customHeight="1" s="19">
       <c r="A2387" s="8" t="n">
@@ -70159,6 +70295,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2387" t="inlineStr"/>
+      <c r="G2387" t="inlineStr"/>
     </row>
     <row r="2388" ht="15.75" customHeight="1" s="19">
       <c r="A2388" s="8" t="n">
@@ -70184,6 +70322,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2388" t="inlineStr"/>
+      <c r="G2388" t="inlineStr"/>
     </row>
     <row r="2389" ht="15.75" customHeight="1" s="19">
       <c r="A2389" s="8" t="n">
@@ -70209,6 +70349,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2389" t="inlineStr"/>
+      <c r="G2389" t="inlineStr"/>
     </row>
     <row r="2390" ht="15.75" customHeight="1" s="19">
       <c r="A2390" s="8" t="n">
@@ -70234,6 +70376,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2390" t="inlineStr"/>
+      <c r="G2390" t="inlineStr"/>
     </row>
     <row r="2391" ht="15.75" customHeight="1" s="19">
       <c r="A2391" s="8" t="n">
@@ -70259,6 +70403,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2391" t="inlineStr"/>
+      <c r="G2391" t="inlineStr"/>
     </row>
     <row r="2392" ht="15.75" customHeight="1" s="19">
       <c r="A2392" s="8" t="n">
@@ -70284,6 +70430,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2392" t="inlineStr"/>
+      <c r="G2392" t="inlineStr"/>
     </row>
     <row r="2393" ht="15.75" customHeight="1" s="19">
       <c r="A2393" s="8" t="n">
@@ -70309,6 +70457,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2393" t="inlineStr"/>
+      <c r="G2393" t="inlineStr"/>
     </row>
     <row r="2394" ht="15.75" customHeight="1" s="19">
       <c r="A2394" s="8" t="n">
@@ -70334,6 +70484,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2394" t="inlineStr"/>
+      <c r="G2394" t="inlineStr"/>
     </row>
     <row r="2395" ht="15.75" customHeight="1" s="19">
       <c r="A2395" s="8" t="n">
@@ -70359,6 +70511,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2395" t="inlineStr">
+        <is>
+          <t>+54 11 4233-2868</t>
+        </is>
+      </c>
+      <c r="G2395" t="inlineStr"/>
     </row>
     <row r="2396" ht="15.75" customHeight="1" s="19">
       <c r="A2396" s="8" t="n">
@@ -70384,6 +70542,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2396" t="inlineStr"/>
+      <c r="G2396" t="inlineStr"/>
     </row>
     <row r="2397" ht="15.75" customHeight="1" s="19">
       <c r="A2397" s="8" t="n">
@@ -70409,6 +70569,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2397" t="inlineStr"/>
+      <c r="G2397" t="inlineStr"/>
     </row>
     <row r="2398" ht="15.75" customHeight="1" s="19">
       <c r="A2398" s="8" t="n">
@@ -70434,6 +70596,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2398" t="inlineStr"/>
+      <c r="G2398" t="inlineStr"/>
     </row>
     <row r="2399" ht="15.75" customHeight="1" s="19">
       <c r="A2399" s="8" t="n">
@@ -70459,6 +70623,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2399" t="inlineStr"/>
+      <c r="G2399" t="inlineStr"/>
     </row>
     <row r="2400" ht="15.75" customHeight="1" s="19">
       <c r="A2400" s="8" t="n">
@@ -70484,6 +70650,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2400" t="inlineStr"/>
+      <c r="G2400" t="inlineStr"/>
     </row>
     <row r="2401" ht="15.75" customHeight="1" s="19">
       <c r="A2401" s="8" t="n">
@@ -70509,6 +70677,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2401" t="inlineStr"/>
+      <c r="G2401" t="inlineStr"/>
     </row>
     <row r="2402" ht="15.75" customHeight="1" s="19">
       <c r="A2402" s="8" t="n">
@@ -70534,6 +70704,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2402" t="inlineStr"/>
+      <c r="G2402" t="inlineStr"/>
     </row>
     <row r="2403" ht="15.75" customHeight="1" s="19">
       <c r="A2403" s="8" t="n">

--- a/PUNTOS_DE_VENTA_completado.xlsx
+++ b/PUNTOS_DE_VENTA_completado.xlsx
@@ -70731,6 +70731,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2403" t="inlineStr"/>
+      <c r="G2403" t="inlineStr"/>
     </row>
     <row r="2404" ht="15.75" customHeight="1" s="19">
       <c r="A2404" s="8" t="n">
@@ -70756,6 +70758,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2404" t="inlineStr"/>
+      <c r="G2404" t="inlineStr"/>
     </row>
     <row r="2405" ht="15.75" customHeight="1" s="19">
       <c r="A2405" s="8" t="n">
@@ -70781,6 +70785,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2405" t="inlineStr"/>
+      <c r="G2405" t="inlineStr"/>
     </row>
     <row r="2406" ht="15.75" customHeight="1" s="19">
       <c r="A2406" s="8" t="n">
@@ -70806,6 +70812,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2406" t="inlineStr">
+        <is>
+          <t>+54 11 4238-3540</t>
+        </is>
+      </c>
+      <c r="G2406" t="inlineStr"/>
     </row>
     <row r="2407" ht="15.75" customHeight="1" s="19">
       <c r="A2407" s="8" t="n">
@@ -70831,6 +70843,16 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2407" t="inlineStr">
+        <is>
+          <t>+54 11 4117-7200</t>
+        </is>
+      </c>
+      <c r="G2407" t="inlineStr">
+        <is>
+          <t>https://bitali.com/</t>
+        </is>
+      </c>
     </row>
     <row r="2408" ht="15.75" customHeight="1" s="19">
       <c r="A2408" s="8" t="n">
@@ -70856,6 +70878,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2408" t="inlineStr">
+        <is>
+          <t>+54 11 4389-0034</t>
+        </is>
+      </c>
+      <c r="G2408" t="inlineStr"/>
     </row>
     <row r="2409" ht="15.75" customHeight="1" s="19">
       <c r="A2409" s="8" t="n">
@@ -70881,6 +70909,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2409" t="inlineStr"/>
+      <c r="G2409" t="inlineStr"/>
     </row>
     <row r="2410" ht="15.75" customHeight="1" s="19">
       <c r="A2410" s="8" t="n">
@@ -70906,6 +70936,16 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2410" t="inlineStr">
+        <is>
+          <t>+54 800-122-0089</t>
+        </is>
+      </c>
+      <c r="G2410" t="inlineStr">
+        <is>
+          <t>https://www.nissan.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="2411" ht="15.75" customHeight="1" s="19">
       <c r="A2411" s="8" t="n">
@@ -70931,6 +70971,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2411" t="inlineStr"/>
+      <c r="G2411" t="inlineStr"/>
     </row>
     <row r="2412" ht="15.75" customHeight="1" s="19">
       <c r="A2412" s="8" t="n">
@@ -70956,6 +70998,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2412" t="inlineStr"/>
+      <c r="G2412" t="inlineStr"/>
     </row>
     <row r="2413" ht="15.75" customHeight="1" s="19">
       <c r="A2413" s="8" t="n">
@@ -70981,6 +71025,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F2413" t="inlineStr"/>
+      <c r="G2413" t="inlineStr"/>
     </row>
     <row r="2414" ht="15.75" customHeight="1" s="19">
       <c r="A2414" s="8" t="n">
@@ -71006,6 +71052,8 @@
           <t>Autoservicio</t>
         </is>
       </c>
+      <c r="F2414" t="inlineStr"/>
+      <c r="G2414" t="inlineStr"/>
     </row>
     <row r="2415" ht="15.75" customHeight="1" s="19">
       <c r="A2415" s="8" t="n">
@@ -71031,6 +71079,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2415" t="inlineStr">
+        <is>
+          <t>+54 11 5083-0449</t>
+        </is>
+      </c>
+      <c r="G2415" t="inlineStr"/>
     </row>
     <row r="2416" ht="15.75" customHeight="1" s="19">
       <c r="A2416" s="8" t="n">
@@ -71056,6 +71110,8 @@
           <t>Pet shop</t>
         </is>
       </c>
+      <c r="F2416" t="inlineStr"/>
+      <c r="G2416" t="inlineStr"/>
     </row>
     <row r="2417" ht="15.75" customHeight="1" s="19">
       <c r="A2417" s="8" t="n">
@@ -71081,6 +71137,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2417" t="inlineStr"/>
+      <c r="G2417" t="inlineStr"/>
     </row>
     <row r="2418" ht="15.75" customHeight="1" s="19">
       <c r="A2418" s="8" t="n">
@@ -71106,6 +71164,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2418" t="inlineStr"/>
+      <c r="G2418" t="inlineStr"/>
     </row>
     <row r="2419" ht="15.75" customHeight="1" s="19">
       <c r="A2419" s="8" t="n">
@@ -71131,6 +71191,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2419" t="inlineStr"/>
+      <c r="G2419" t="inlineStr"/>
     </row>
     <row r="2420" ht="15.75" customHeight="1" s="19">
       <c r="A2420" s="8" t="n">
@@ -71156,6 +71218,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F2420" t="inlineStr"/>
+      <c r="G2420" t="inlineStr"/>
     </row>
     <row r="2421" ht="15.75" customHeight="1" s="19">
       <c r="A2421" s="8" t="n">
@@ -71181,6 +71245,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2421" t="inlineStr">
+        <is>
+          <t>+54 11 5524-6217</t>
+        </is>
+      </c>
+      <c r="G2421" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cmo_ezeiza?igsh=MW9jZWoyNW8wdWQ2OA==</t>
+        </is>
+      </c>
     </row>
     <row r="2422" ht="15.75" customHeight="1" s="19">
       <c r="A2422" s="8" t="n">
@@ -71206,6 +71280,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2422" t="inlineStr"/>
+      <c r="G2422" t="inlineStr"/>
     </row>
     <row r="2423" ht="15.75" customHeight="1" s="19">
       <c r="A2423" s="8" t="n">
@@ -71231,6 +71307,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2423" t="inlineStr"/>
+      <c r="G2423" t="inlineStr"/>
     </row>
     <row r="2424" ht="15.75" customHeight="1" s="19">
       <c r="A2424" s="8" t="n">
@@ -71256,6 +71334,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2424" t="inlineStr"/>
+      <c r="G2424" t="inlineStr"/>
     </row>
     <row r="2425" ht="15.75" customHeight="1" s="19">
       <c r="A2425" s="8" t="n">
@@ -71281,6 +71361,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2425" t="inlineStr"/>
+      <c r="G2425" t="inlineStr"/>
     </row>
     <row r="2426" ht="15.75" customHeight="1" s="19">
       <c r="A2426" s="8" t="n">
@@ -71306,6 +71388,12 @@
           <t>Veterinaria</t>
         </is>
       </c>
+      <c r="F2426" t="inlineStr">
+        <is>
+          <t>+54 11 4501-2925</t>
+        </is>
+      </c>
+      <c r="G2426" t="inlineStr"/>
     </row>
     <row r="2427" ht="15.75" customHeight="1" s="19">
       <c r="A2427" s="8" t="n">
@@ -71331,6 +71419,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2427" t="inlineStr"/>
+      <c r="G2427" t="inlineStr"/>
     </row>
     <row r="2428" ht="15.75" customHeight="1" s="19">
       <c r="A2428" s="8" t="n">
@@ -71356,6 +71446,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2428" t="inlineStr"/>
+      <c r="G2428" t="inlineStr"/>
     </row>
     <row r="2429" ht="15.75" customHeight="1" s="19">
       <c r="A2429" s="8" t="n">
@@ -71381,6 +71473,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F2429" t="inlineStr"/>
+      <c r="G2429" t="inlineStr"/>
     </row>
     <row r="2430" ht="15.75" customHeight="1" s="19">
       <c r="A2430" s="8" t="n">
@@ -71406,6 +71500,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2430" t="inlineStr"/>
+      <c r="G2430" t="inlineStr"/>
     </row>
     <row r="2431" ht="15.75" customHeight="1" s="19">
       <c r="A2431" s="8" t="n">
@@ -71431,6 +71527,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2431" t="inlineStr">
+        <is>
+          <t>+54 11 4367-6700</t>
+        </is>
+      </c>
+      <c r="G2431" t="inlineStr">
+        <is>
+          <t>https://www.clinicamg.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="2432" ht="15.75" customHeight="1" s="19">
       <c r="A2432" s="8" t="n">
@@ -71456,6 +71562,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2432" t="inlineStr"/>
+      <c r="G2432" t="inlineStr"/>
     </row>
     <row r="2433" ht="15.75" customHeight="1" s="19">
       <c r="A2433" s="8" t="n">
@@ -71481,6 +71589,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2433" t="inlineStr"/>
+      <c r="G2433" t="inlineStr"/>
     </row>
     <row r="2434" ht="15.75" customHeight="1" s="19">
       <c r="A2434" s="8" t="n">
@@ -71506,6 +71616,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2434" t="inlineStr"/>
+      <c r="G2434" t="inlineStr"/>
     </row>
     <row r="2435" ht="15.75" customHeight="1" s="19">
       <c r="A2435" s="8" t="n">
@@ -71531,6 +71643,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2435" t="inlineStr"/>
+      <c r="G2435" t="inlineStr"/>
     </row>
     <row r="2436" ht="15.75" customHeight="1" s="19">
       <c r="A2436" s="8" t="n">
@@ -71556,6 +71670,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2436" t="inlineStr"/>
+      <c r="G2436" t="inlineStr"/>
     </row>
     <row r="2437" ht="15.75" customHeight="1" s="19">
       <c r="A2437" s="8" t="n">
@@ -71581,6 +71697,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2437" t="inlineStr"/>
+      <c r="G2437" t="inlineStr"/>
     </row>
     <row r="2438" ht="15.75" customHeight="1" s="19">
       <c r="A2438" s="8" t="n">
@@ -71606,6 +71724,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2438" t="inlineStr"/>
+      <c r="G2438" t="inlineStr"/>
     </row>
     <row r="2439" ht="15.75" customHeight="1" s="19">
       <c r="A2439" s="8" t="n">
@@ -71631,6 +71751,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2439" t="inlineStr"/>
+      <c r="G2439" t="inlineStr"/>
     </row>
     <row r="2440" ht="15.75" customHeight="1" s="19">
       <c r="A2440" s="8" t="n">
@@ -71656,6 +71778,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2440" t="inlineStr"/>
+      <c r="G2440" t="inlineStr"/>
     </row>
     <row r="2441" ht="15.75" customHeight="1" s="19">
       <c r="A2441" s="8" t="n">
@@ -71681,6 +71805,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2441" t="inlineStr"/>
+      <c r="G2441" t="inlineStr"/>
     </row>
     <row r="2442" ht="15.75" customHeight="1" s="19">
       <c r="A2442" s="8" t="n">
@@ -71706,6 +71832,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2442" t="inlineStr"/>
+      <c r="G2442" t="inlineStr"/>
     </row>
     <row r="2443" ht="15.75" customHeight="1" s="19">
       <c r="A2443" s="8" t="n">
@@ -71731,6 +71859,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2443" t="inlineStr"/>
+      <c r="G2443" t="inlineStr"/>
     </row>
     <row r="2444" ht="15.75" customHeight="1" s="19">
       <c r="A2444" s="8" t="n">
@@ -71756,6 +71886,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2444" t="inlineStr"/>
+      <c r="G2444" t="inlineStr"/>
     </row>
     <row r="2445" ht="15.75" customHeight="1" s="19">
       <c r="A2445" s="8" t="n">
@@ -71781,6 +71913,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2445" t="inlineStr"/>
+      <c r="G2445" t="inlineStr"/>
     </row>
     <row r="2446" ht="15.75" customHeight="1" s="19">
       <c r="A2446" s="8" t="n">
@@ -71806,6 +71940,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2446" t="inlineStr">
+        <is>
+          <t>+54 11 6080-8738</t>
+        </is>
+      </c>
+      <c r="G2446" t="inlineStr">
+        <is>
+          <t>https://www.kiwano.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="2447" ht="15.75" customHeight="1" s="19">
       <c r="A2447" s="8" t="n">
@@ -71831,6 +71975,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2447" t="inlineStr"/>
+      <c r="G2447" t="inlineStr"/>
     </row>
     <row r="2448" ht="15.75" customHeight="1" s="19">
       <c r="A2448" s="8" t="n">
@@ -71856,6 +72002,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F2448" t="inlineStr"/>
+      <c r="G2448" t="inlineStr"/>
     </row>
     <row r="2449" ht="15.75" customHeight="1" s="19">
       <c r="A2449" s="8" t="n">
@@ -71881,6 +72029,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2449" t="inlineStr"/>
+      <c r="G2449" t="inlineStr"/>
     </row>
     <row r="2450" ht="15.75" customHeight="1" s="19">
       <c r="A2450" s="8" t="n">
@@ -71906,6 +72056,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2450" t="inlineStr"/>
+      <c r="G2450" t="inlineStr"/>
     </row>
     <row r="2451" ht="15.75" customHeight="1" s="19">
       <c r="A2451" s="8" t="n">
@@ -71931,6 +72083,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2451" t="inlineStr">
+        <is>
+          <t>+54 11 4451-0940</t>
+        </is>
+      </c>
+      <c r="G2451" t="inlineStr">
+        <is>
+          <t>http://fb.me/encendidogrosselli</t>
+        </is>
+      </c>
     </row>
     <row r="2452" ht="15.75" customHeight="1" s="19">
       <c r="A2452" s="8" t="n">
@@ -71956,6 +72118,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2452" t="inlineStr"/>
+      <c r="G2452" t="inlineStr"/>
     </row>
     <row r="2453" ht="15.75" customHeight="1" s="19">
       <c r="A2453" s="8" t="n">
@@ -71981,6 +72145,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2453" t="inlineStr">
+        <is>
+          <t>+54 11 7359-0854</t>
+        </is>
+      </c>
+      <c r="G2453" t="inlineStr"/>
     </row>
     <row r="2454" ht="15.75" customHeight="1" s="19">
       <c r="A2454" s="8" t="n">
@@ -72006,6 +72176,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2454" t="inlineStr">
+        <is>
+          <t>+54 11 4749-8535</t>
+        </is>
+      </c>
+      <c r="G2454" t="inlineStr">
+        <is>
+          <t>http://www.aguadulce.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="2455" ht="15.75" customHeight="1" s="19">
       <c r="A2455" s="8" t="n">
@@ -72031,6 +72211,12 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2455" t="inlineStr">
+        <is>
+          <t>+54 11 2882-5223</t>
+        </is>
+      </c>
+      <c r="G2455" t="inlineStr"/>
     </row>
     <row r="2456" ht="15.75" customHeight="1" s="19">
       <c r="A2456" s="8" t="n">
@@ -72056,6 +72242,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2456" t="inlineStr"/>
+      <c r="G2456" t="inlineStr"/>
     </row>
     <row r="2457" ht="15.75" customHeight="1" s="19">
       <c r="A2457" s="8" t="n">
@@ -72081,6 +72269,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2457" t="inlineStr"/>
+      <c r="G2457" t="inlineStr"/>
     </row>
     <row r="2458" ht="15.75" customHeight="1" s="19">
       <c r="A2458" s="8" t="n">
@@ -72106,6 +72296,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2458" t="inlineStr"/>
+      <c r="G2458" t="inlineStr"/>
     </row>
     <row r="2459" ht="15.75" customHeight="1" s="19">
       <c r="A2459" s="8" t="n">
@@ -72131,6 +72323,8 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2459" t="inlineStr"/>
+      <c r="G2459" t="inlineStr"/>
     </row>
     <row r="2460" ht="15.75" customHeight="1" s="19">
       <c r="A2460" s="8" t="n">
@@ -72156,6 +72350,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F2460" t="inlineStr"/>
+      <c r="G2460" t="inlineStr"/>
     </row>
     <row r="2461" ht="15.75" customHeight="1" s="19">
       <c r="A2461" s="8" t="n">
@@ -72177,6 +72373,16 @@
           <t>Forrajeria</t>
         </is>
       </c>
+      <c r="F2461" t="inlineStr">
+        <is>
+          <t>+54 11 4757-2130</t>
+        </is>
+      </c>
+      <c r="G2461" t="inlineStr">
+        <is>
+          <t>http://www.santuariodelourdes.org.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="2462" ht="15.75" customHeight="1" s="19">
       <c r="A2462" s="8" t="n">
@@ -72202,6 +72408,16 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2462" t="inlineStr">
+        <is>
+          <t>+54 11 3616-0117</t>
+        </is>
+      </c>
+      <c r="G2462" t="inlineStr">
+        <is>
+          <t>https://nidodebarro.empretienda.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="2463" ht="15.75" customHeight="1" s="19">
       <c r="A2463" s="8" t="n">
@@ -72227,6 +72443,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2463" t="inlineStr"/>
+      <c r="G2463" t="inlineStr"/>
     </row>
     <row r="2464" ht="15.75" customHeight="1" s="19">
       <c r="A2464" s="8" t="n">
@@ -72252,6 +72470,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2464" t="inlineStr"/>
+      <c r="G2464" t="inlineStr"/>
     </row>
     <row r="2465" ht="15.75" customHeight="1" s="19">
       <c r="A2465" s="8" t="n">
@@ -72277,6 +72497,12 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2465" t="inlineStr">
+        <is>
+          <t>+54 11 6151-2365</t>
+        </is>
+      </c>
+      <c r="G2465" t="inlineStr"/>
     </row>
     <row r="2466" ht="15.75" customHeight="1" s="19">
       <c r="A2466" s="8" t="n">
@@ -72302,6 +72528,12 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2466" t="inlineStr">
+        <is>
+          <t>+54 2323 47-8161</t>
+        </is>
+      </c>
+      <c r="G2466" t="inlineStr"/>
     </row>
     <row r="2467" ht="15.75" customHeight="1" s="19">
       <c r="A2467" s="8" t="n">
@@ -72327,6 +72559,16 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2467" t="inlineStr">
+        <is>
+          <t>+54 2323 47-8403</t>
+        </is>
+      </c>
+      <c r="G2467" t="inlineStr">
+        <is>
+          <t>http://www.ferredel.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="2468" ht="15.75" customHeight="1" s="19">
       <c r="A2468" s="8" t="n">
@@ -72352,6 +72594,16 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2468" t="inlineStr">
+        <is>
+          <t>+54 9 11 3342-8726</t>
+        </is>
+      </c>
+      <c r="G2468" t="inlineStr">
+        <is>
+          <t>http://www.elrusotiendademascotas.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="2469" ht="15.75" customHeight="1" s="19">
       <c r="A2469" s="8" t="n">
@@ -72377,6 +72629,12 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2469" t="inlineStr">
+        <is>
+          <t>+54 2323 47-8161</t>
+        </is>
+      </c>
+      <c r="G2469" t="inlineStr"/>
     </row>
     <row r="2470" ht="15.75" customHeight="1" s="19">
       <c r="A2470" s="8" t="n">
@@ -72402,6 +72660,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2470" t="inlineStr"/>
+      <c r="G2470" t="inlineStr"/>
     </row>
     <row r="2471" ht="15.75" customHeight="1" s="19">
       <c r="A2471" s="8" t="n">
@@ -72427,6 +72687,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2471" t="inlineStr"/>
+      <c r="G2471" t="inlineStr"/>
     </row>
     <row r="2472" ht="15.75" customHeight="1" s="19">
       <c r="A2472" s="8" t="n">
@@ -72452,6 +72714,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2472" t="inlineStr"/>
+      <c r="G2472" t="inlineStr"/>
     </row>
     <row r="2473" ht="15.75" customHeight="1" s="19">
       <c r="A2473" s="8" t="n">
@@ -72477,6 +72741,16 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2473" t="inlineStr">
+        <is>
+          <t>+54 11 4961-3022</t>
+        </is>
+      </c>
+      <c r="G2473" t="inlineStr">
+        <is>
+          <t>http://www.eduardodeluca.com.ar</t>
+        </is>
+      </c>
     </row>
     <row r="2474" ht="15.75" customHeight="1" s="19">
       <c r="A2474" s="8" t="n">
@@ -72502,6 +72776,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2474" t="inlineStr"/>
+      <c r="G2474" t="inlineStr"/>
     </row>
     <row r="2475" ht="15.75" customHeight="1" s="19">
       <c r="A2475" s="8" t="n">
@@ -72527,6 +72803,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2475" t="inlineStr"/>
+      <c r="G2475" t="inlineStr"/>
     </row>
     <row r="2476" ht="15.75" customHeight="1" s="19">
       <c r="A2476" s="8" t="n">
@@ -72552,6 +72830,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2476" t="inlineStr"/>
+      <c r="G2476" t="inlineStr"/>
     </row>
     <row r="2477" ht="15.75" customHeight="1" s="19">
       <c r="A2477" s="8" t="n">
@@ -72577,6 +72857,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2477" t="inlineStr"/>
+      <c r="G2477" t="inlineStr"/>
     </row>
     <row r="2478" ht="15.75" customHeight="1" s="19">
       <c r="A2478" s="8" t="n">
@@ -72602,6 +72884,16 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2478" t="inlineStr">
+        <is>
+          <t>+54 11 3637-4289</t>
+        </is>
+      </c>
+      <c r="G2478" t="inlineStr">
+        <is>
+          <t>https://www.animaladasya.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="2479" ht="15.75" customHeight="1" s="19">
       <c r="A2479" s="8" t="n">
@@ -72627,6 +72919,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2479" t="inlineStr"/>
+      <c r="G2479" t="inlineStr"/>
     </row>
     <row r="2480" ht="15.75" customHeight="1" s="19">
       <c r="A2480" s="8" t="n">
@@ -72652,6 +72946,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2480" t="inlineStr"/>
+      <c r="G2480" t="inlineStr"/>
     </row>
     <row r="2481" ht="15.75" customHeight="1" s="19">
       <c r="A2481" s="8" t="n">
@@ -72677,6 +72973,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2481" t="inlineStr"/>
+      <c r="G2481" t="inlineStr"/>
     </row>
     <row r="2482" ht="15.75" customHeight="1" s="19">
       <c r="A2482" s="8" t="n">
@@ -72702,6 +73000,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2482" t="inlineStr"/>
+      <c r="G2482" t="inlineStr"/>
     </row>
     <row r="2483" ht="15.75" customHeight="1" s="19">
       <c r="A2483" s="8" t="n">
@@ -72727,6 +73027,12 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2483" t="inlineStr"/>
+      <c r="G2483" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/v_once_escalada/</t>
+        </is>
+      </c>
     </row>
     <row r="2484" ht="15.75" customHeight="1" s="19">
       <c r="A2484" s="8" t="n">
@@ -72752,6 +73058,12 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2484" t="inlineStr">
+        <is>
+          <t>+54 11 5697-8284</t>
+        </is>
+      </c>
+      <c r="G2484" t="inlineStr"/>
     </row>
     <row r="2485" ht="15.75" customHeight="1" s="19">
       <c r="A2485" s="8" t="n">
@@ -72777,6 +73089,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2485" t="inlineStr"/>
+      <c r="G2485" t="inlineStr"/>
     </row>
     <row r="2486" ht="15.75" customHeight="1" s="19">
       <c r="A2486" s="8" t="n">
@@ -72802,6 +73116,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2486" t="inlineStr"/>
+      <c r="G2486" t="inlineStr"/>
     </row>
     <row r="2487" ht="15.75" customHeight="1" s="19">
       <c r="A2487" s="8" t="n">
@@ -72827,6 +73143,16 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2487" t="inlineStr">
+        <is>
+          <t>+54 11 2197-2245</t>
+        </is>
+      </c>
+      <c r="G2487" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/distribuidora.carajaville</t>
+        </is>
+      </c>
     </row>
     <row r="2488" ht="15.75" customHeight="1" s="19">
       <c r="A2488" s="8" t="n">
@@ -72852,6 +73178,16 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2488" t="inlineStr">
+        <is>
+          <t>+54 11 4755-6097</t>
+        </is>
+      </c>
+      <c r="G2488" t="inlineStr">
+        <is>
+          <t>http://www.distriballester.com/</t>
+        </is>
+      </c>
     </row>
     <row r="2489" ht="15.75" customHeight="1" s="19">
       <c r="A2489" s="8" t="n">
@@ -72877,6 +73213,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2489" t="inlineStr"/>
+      <c r="G2489" t="inlineStr"/>
     </row>
     <row r="2490" ht="15.75" customHeight="1" s="19">
       <c r="A2490" s="8" t="n">
@@ -72902,6 +73240,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2490" t="inlineStr"/>
+      <c r="G2490" t="inlineStr"/>
     </row>
     <row r="2491" ht="15.75" customHeight="1" s="19">
       <c r="A2491" s="8" t="n">
@@ -72927,6 +73267,16 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2491" t="inlineStr">
+        <is>
+          <t>+54 11 4541-5108</t>
+        </is>
+      </c>
+      <c r="G2491" t="inlineStr">
+        <is>
+          <t>http://www.gregoruttisa.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="2492" ht="15.75" customHeight="1" s="19">
       <c r="A2492" s="8" t="n">
@@ -72952,6 +73302,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2492" t="inlineStr"/>
+      <c r="G2492" t="inlineStr"/>
     </row>
     <row r="2493" ht="15.75" customHeight="1" s="19">
       <c r="A2493" s="8" t="n">
@@ -72977,6 +73329,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2493" t="inlineStr"/>
+      <c r="G2493" t="inlineStr"/>
     </row>
     <row r="2494" ht="15.75" customHeight="1" s="19">
       <c r="A2494" s="8" t="n">
@@ -73002,6 +73356,16 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2494" t="inlineStr">
+        <is>
+          <t>+54 11 3287-7356</t>
+        </is>
+      </c>
+      <c r="G2494" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/1836mascotas/</t>
+        </is>
+      </c>
     </row>
     <row r="2495" ht="15.75" customHeight="1" s="19">
       <c r="A2495" s="8" t="n">
@@ -73027,6 +73391,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2495" t="inlineStr"/>
+      <c r="G2495" t="inlineStr"/>
     </row>
     <row r="2496" ht="15.75" customHeight="1" s="19">
       <c r="A2496" s="8" t="n">
@@ -73048,6 +73414,16 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2496" t="inlineStr">
+        <is>
+          <t>+54 11 5900-9917</t>
+        </is>
+      </c>
+      <c r="G2496" t="inlineStr">
+        <is>
+          <t>https://www.miautopartes.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="2497" ht="15.75" customHeight="1" s="19">
       <c r="A2497" s="8" t="n">
@@ -73073,6 +73449,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2497" t="inlineStr"/>
+      <c r="G2497" t="inlineStr"/>
     </row>
     <row r="2498" ht="15.75" customHeight="1" s="19">
       <c r="A2498" s="8" t="n">
@@ -73098,6 +73476,16 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2498" t="inlineStr">
+        <is>
+          <t>+54 230 442-9482</t>
+        </is>
+      </c>
+      <c r="G2498" t="inlineStr">
+        <is>
+          <t>https://forrajeriadelpilar.com.ar/</t>
+        </is>
+      </c>
     </row>
     <row r="2499" ht="15.75" customHeight="1" s="19">
       <c r="A2499" s="8" t="n">
@@ -73123,6 +73511,8 @@
           <t>Mayoristas</t>
         </is>
       </c>
+      <c r="F2499" t="inlineStr"/>
+      <c r="G2499" t="inlineStr"/>
     </row>
     <row r="2500" ht="15.75" customHeight="1" s="19">
       <c r="A2500" s="8" t="n">
@@ -73148,6 +73538,8 @@
           <t>Pet Shop</t>
         </is>
       </c>
+      <c r="F2500" t="inlineStr"/>
+      <c r="G2500" t="inlineStr"/>
     </row>
     <row r="2501" ht="15.75" customHeight="1" s="19">
       <c r="A2501" s="8" t="n">
@@ -73173,6 +73565,8 @@
           <t>Pet Shop con camilla veterinaria</t>
         </is>
       </c>
+      <c r="F2501" t="inlineStr"/>
+      <c r="G2501" t="inlineStr"/>
     </row>
     <row r="2502" ht="15.75" customHeight="1" s="19">
       <c r="A2502" s="8" t="n">
@@ -73196,6 +73590,16 @@
       <c r="E2502" s="9" t="inlineStr">
         <is>
           <t>Pet Shop con camilla veterinaria</t>
+        </is>
+      </c>
+      <c r="F2502" t="inlineStr">
+        <is>
+          <t>+54 11 4543-7741</t>
+        </is>
+      </c>
+      <c r="G2502" t="inlineStr">
+        <is>
+          <t>https://www.veterinarias.com.ar/animal-vet-clinica-veterinaria.html</t>
         </is>
       </c>
     </row>
